--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>33155861</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>4.69649982452393</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>4.49499988555908</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>4.60150003433228</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>24593115</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>4.58850002288818</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>4.45900011062622</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>4.54099988937378</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>4.48699998855591</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>58756337</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>4.44799995422363</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>4.31150007247925</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>4.42799997329712</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>4.33750009536743</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>43003506</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>4.49700021743774</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>4.35300016403198</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>4.36749982833862</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>4.4355001449585</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>30002695</v>
+        <v>22913780</v>
       </c>
       <c r="C2715" t="n">
-        <v>4.82950019836426</v>
+        <v>4.87200021743774</v>
       </c>
       <c r="D2715" t="n">
-        <v>4.64650011062622</v>
+        <v>4.77250003814697</v>
       </c>
       <c r="E2715" t="n">
-        <v>4.76999998092651</v>
+        <v>4.77400016784668</v>
       </c>
       <c r="F2715" t="n">
-        <v>4.67150020599365</v>
+        <v>4.80600023269653</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>28451543</v>
+        <v>30002695</v>
       </c>
       <c r="C2716" t="n">
-        <v>4.72599983215332</v>
+        <v>4.82950019836426</v>
       </c>
       <c r="D2716" t="n">
-        <v>4.55100011825562</v>
+        <v>4.64650011062622</v>
       </c>
       <c r="E2716" t="n">
-        <v>4.66499996185303</v>
+        <v>4.76999998092651</v>
       </c>
       <c r="F2716" t="n">
-        <v>4.56750011444092</v>
+        <v>4.67150020599365</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>30687453</v>
+        <v>28451543</v>
       </c>
       <c r="C2717" t="n">
-        <v>4.62400007247925</v>
+        <v>4.72599983215332</v>
       </c>
       <c r="D2717" t="n">
-        <v>4.49499988555908</v>
+        <v>4.55100011825562</v>
       </c>
       <c r="E2717" t="n">
-        <v>4.57250022888184</v>
+        <v>4.66499996185303</v>
       </c>
       <c r="F2717" t="n">
-        <v>4.54650020599365</v>
+        <v>4.56750011444092</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>29909478</v>
+        <v>30687453</v>
       </c>
       <c r="C2718" t="n">
-        <v>4.69600009918213</v>
+        <v>4.62400007247925</v>
       </c>
       <c r="D2718" t="n">
-        <v>4.52099990844727</v>
+        <v>4.49499988555908</v>
       </c>
       <c r="E2718" t="n">
-        <v>4.57000017166138</v>
+        <v>4.57250022888184</v>
       </c>
       <c r="F2718" t="n">
-        <v>4.67000007629395</v>
+        <v>4.54650020599365</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>33155861</v>
+        <v>29909478</v>
       </c>
       <c r="C2719" t="n">
-        <v>4.69649982452393</v>
+        <v>4.69600009918213</v>
       </c>
       <c r="D2719" t="n">
-        <v>4.49499988555908</v>
+        <v>4.52099990844727</v>
       </c>
       <c r="E2719" t="n">
-        <v>4.60150003433228</v>
+        <v>4.57000017166138</v>
       </c>
       <c r="F2719" t="n">
-        <v>4.53999996185303</v>
+        <v>4.67000007629395</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>24593115</v>
+        <v>33155861</v>
       </c>
       <c r="C2720" t="n">
-        <v>4.58850002288818</v>
+        <v>4.69649982452393</v>
       </c>
       <c r="D2720" t="n">
-        <v>4.45900011062622</v>
+        <v>4.49499988555908</v>
       </c>
       <c r="E2720" t="n">
-        <v>4.54099988937378</v>
+        <v>4.60150003433228</v>
       </c>
       <c r="F2720" t="n">
-        <v>4.48699998855591</v>
+        <v>4.53999996185303</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>58756337</v>
+        <v>24593115</v>
       </c>
       <c r="C2721" t="n">
-        <v>4.44799995422363</v>
+        <v>4.58850002288818</v>
       </c>
       <c r="D2721" t="n">
-        <v>4.31150007247925</v>
+        <v>4.45900011062622</v>
       </c>
       <c r="E2721" t="n">
-        <v>4.42799997329712</v>
+        <v>4.54099988937378</v>
       </c>
       <c r="F2721" t="n">
-        <v>4.33750009536743</v>
+        <v>4.48699998855591</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>43003506</v>
+        <v>58756337</v>
       </c>
       <c r="C2722" t="n">
-        <v>4.49700021743774</v>
+        <v>4.44799995422363</v>
       </c>
       <c r="D2722" t="n">
-        <v>4.35300016403198</v>
+        <v>4.31150007247925</v>
       </c>
       <c r="E2722" t="n">
-        <v>4.36749982833862</v>
+        <v>4.42799997329712</v>
       </c>
       <c r="F2722" t="n">
-        <v>4.4355001449585</v>
+        <v>4.33750009536743</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>91701393</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>4.44449996948242</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>4.15350008010864</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>4.43499994277954</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>4.20349979400635</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>3.89750003814697</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>3.98449993133545</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>56006333</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>4.17150020599365</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>4.01000022888184</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>4.01800012588501</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>4.01800012588501</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>4.06899976730347</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>61217545</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>4.06750011444092</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>4.06799983978271</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>4.06799983978271</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>4.12449979782104</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>46155128</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>3.93400001525879</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>4.09899997711182</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>4.09899997711182</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>4.00150012969971</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>33989216</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>4.11700010299683</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>4.00299978256226</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>4.03749990463257</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>40189190</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>4.12599992752075</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>3.94199991226196</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>4.05000019073486</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>3.96950006484985</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -473,7 +473,7 @@
         <v>7.49471807479858</v>
       </c>
       <c r="G4" t="n">
-        <v>3.91636347770691</v>
+        <v>3.91636300086975</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>7.24898910522461</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7879581451416</v>
+        <v>3.78795790672302</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>6.95128011703491</v>
       </c>
       <c r="G6" t="n">
-        <v>3.63238930702209</v>
+        <v>3.63238954544067</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>6.92292594909668</v>
       </c>
       <c r="G7" t="n">
-        <v>3.61757326126099</v>
+        <v>3.61757373809814</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>7.11667394638062</v>
       </c>
       <c r="G8" t="n">
-        <v>3.71881675720215</v>
+        <v>3.71881628036499</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>7.02216291427612</v>
       </c>
       <c r="G9" t="n">
-        <v>3.66942977905273</v>
+        <v>3.66942954063416</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>6.46454811096191</v>
       </c>
       <c r="G10" t="n">
-        <v>3.37804818153381</v>
+        <v>3.37804841995239</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>6.28497791290283</v>
       </c>
       <c r="G11" t="n">
-        <v>3.28421425819397</v>
+        <v>3.28421378135681</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>6.10068082809448</v>
       </c>
       <c r="G12" t="n">
-        <v>3.18790912628174</v>
+        <v>3.18790936470032</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>6.25662422180176</v>
       </c>
       <c r="G13" t="n">
-        <v>3.26939725875854</v>
+        <v>3.26939797401428</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>6.23299694061279</v>
       </c>
       <c r="G15" t="n">
-        <v>3.25705122947693</v>
+        <v>3.25705099105835</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>6.24244785308838</v>
       </c>
       <c r="G17" t="n">
-        <v>3.26198935508728</v>
+        <v>3.26198959350586</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>6.56851005554199</v>
       </c>
       <c r="G19" t="n">
-        <v>3.43237328529358</v>
+        <v>3.43237376213074</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>6.09595584869385</v>
       </c>
       <c r="G20" t="n">
-        <v>3.18544006347656</v>
+        <v>3.18544054031372</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>6.04869985580444</v>
       </c>
       <c r="G22" t="n">
-        <v>3.16074705123901</v>
+        <v>3.16074681282043</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.88803195953369</v>
       </c>
       <c r="G23" t="n">
-        <v>3.07679009437561</v>
+        <v>3.07678961753845</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.6517539024353</v>
       </c>
       <c r="G24" t="n">
-        <v>2.95332312583923</v>
+        <v>2.9533224105835</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>5.58087110519409</v>
       </c>
       <c r="G25" t="n">
-        <v>2.91628289222717</v>
+        <v>2.91628313064575</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>5.08468914031982</v>
       </c>
       <c r="G27" t="n">
-        <v>2.65700316429138</v>
+        <v>2.6570029258728</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.94292211532593</v>
       </c>
       <c r="G28" t="n">
-        <v>2.58292269706726</v>
+        <v>2.58292293548584</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.23118114471436</v>
       </c>
       <c r="G29" t="n">
-        <v>2.7335524559021</v>
+        <v>2.73355293273926</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.9618239402771</v>
       </c>
       <c r="G30" t="n">
-        <v>2.59279990196228</v>
+        <v>2.59280014038086</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.36349582672119</v>
       </c>
       <c r="G32" t="n">
-        <v>2.80269360542297</v>
+        <v>2.80269384384155</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>5.54779195785522</v>
       </c>
       <c r="G34" t="n">
-        <v>2.89899754524231</v>
+        <v>2.89899730682373</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5.50998783111572</v>
       </c>
       <c r="G35" t="n">
-        <v>2.87924265861511</v>
+        <v>2.87924242019653</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>5.37767219543457</v>
       </c>
       <c r="G36" t="n">
-        <v>2.81010174751282</v>
+        <v>2.81010103225708</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>5.43437910079956</v>
       </c>
       <c r="G38" t="n">
-        <v>2.83973360061646</v>
+        <v>2.83973336219788</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>5.21700382232666</v>
       </c>
       <c r="G39" t="n">
-        <v>2.72614455223083</v>
+        <v>2.72614431381226</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>5.43437910079956</v>
       </c>
       <c r="G40" t="n">
-        <v>2.83973360061646</v>
+        <v>2.83973336219788</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>5.75099086761475</v>
       </c>
       <c r="G41" t="n">
-        <v>3.00517892837524</v>
+        <v>3.00517845153809</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>5.9967188835144</v>
       </c>
       <c r="G42" t="n">
-        <v>3.13358378410339</v>
+        <v>3.13358402252197</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>6.46454811096191</v>
       </c>
       <c r="G44" t="n">
-        <v>3.37804818153381</v>
+        <v>3.37804841995239</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>6.62994289398193</v>
       </c>
       <c r="G46" t="n">
-        <v>3.46447539329529</v>
+        <v>3.46447563171387</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>6.58741283416748</v>
       </c>
       <c r="G47" t="n">
-        <v>3.44225144386292</v>
+        <v>3.44225120544434</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>6.14321088790894</v>
       </c>
       <c r="G50" t="n">
-        <v>3.21013355255127</v>
+        <v>3.21013331413269</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>6.43146991729736</v>
       </c>
       <c r="G53" t="n">
-        <v>3.36076331138611</v>
+        <v>3.36076307296753</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>6.59213781356812</v>
       </c>
       <c r="G54" t="n">
-        <v>3.44472026824951</v>
+        <v>3.44471979141235</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>6.72445297241211</v>
       </c>
       <c r="G58" t="n">
-        <v>3.51386141777039</v>
+        <v>3.51386117935181</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>6.6535701751709</v>
       </c>
       <c r="G59" t="n">
-        <v>3.47682166099548</v>
+        <v>3.47682189941406</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>6.37948894500732</v>
       </c>
       <c r="G60" t="n">
-        <v>3.33360052108765</v>
+        <v>3.33360075950623</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>6.46454811096191</v>
       </c>
       <c r="G61" t="n">
-        <v>3.37804818153381</v>
+        <v>3.37804841995239</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>6.84259176254272</v>
       </c>
       <c r="G62" t="n">
-        <v>3.57559490203857</v>
+        <v>3.57559418678284</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>6.38421392440796</v>
       </c>
       <c r="G64" t="n">
-        <v>3.33607006072998</v>
+        <v>3.3360698223114</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>6.40784215927124</v>
       </c>
       <c r="G65" t="n">
-        <v>3.34841632843018</v>
+        <v>3.34841656684875</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>6.08650493621826</v>
       </c>
       <c r="G66" t="n">
-        <v>3.18050169944763</v>
+        <v>3.18050241470337</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.76989316940308</v>
       </c>
       <c r="G68" t="n">
-        <v>3.01505637168884</v>
+        <v>3.01505661010742</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>6.00144481658936</v>
       </c>
       <c r="G69" t="n">
-        <v>3.13605380058289</v>
+        <v>3.13605356216431</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>6.06287717819214</v>
       </c>
       <c r="G71" t="n">
-        <v>3.16815543174744</v>
+        <v>3.16815519332886</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>6.35113477706909</v>
       </c>
       <c r="G72" t="n">
-        <v>3.3187837600708</v>
+        <v>3.31878399848938</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>6.41729307174683</v>
       </c>
       <c r="G73" t="n">
-        <v>3.35335540771484</v>
+        <v>3.35335493087769</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>6.82368993759155</v>
       </c>
       <c r="G77" t="n">
-        <v>3.56571769714355</v>
+        <v>3.56571793556213</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>6.95128011703491</v>
       </c>
       <c r="G78" t="n">
-        <v>3.63238930702209</v>
+        <v>3.63238954544067</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>6.78588581085205</v>
       </c>
       <c r="G79" t="n">
-        <v>3.54596352577209</v>
+        <v>3.54596304893494</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>6.64884519577026</v>
       </c>
       <c r="G81" t="n">
-        <v>3.47435235977173</v>
+        <v>3.47435307502747</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>6.76225805282593</v>
       </c>
       <c r="G82" t="n">
-        <v>3.53361630439758</v>
+        <v>3.53361678123474</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>6.92292594909668</v>
       </c>
       <c r="G83" t="n">
-        <v>3.61757326126099</v>
+        <v>3.61757373809814</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>6.4739990234375</v>
       </c>
       <c r="G87" t="n">
-        <v>3.3829870223999</v>
+        <v>3.38298678398132</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>6.3086051940918</v>
       </c>
       <c r="G88" t="n">
-        <v>3.29656052589417</v>
+        <v>3.29656028747559</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>6.35113477706909</v>
       </c>
       <c r="G89" t="n">
-        <v>3.3187837600708</v>
+        <v>3.31878399848938</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>6.25189876556396</v>
       </c>
       <c r="G90" t="n">
-        <v>3.26692795753479</v>
+        <v>3.26692867279053</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>6.34640979766846</v>
       </c>
       <c r="G92" t="n">
-        <v>3.31631517410278</v>
+        <v>3.3163149356842</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>6.46927404403687</v>
       </c>
       <c r="G94" t="n">
-        <v>3.38051748275757</v>
+        <v>3.38051795959473</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>6.37476301193237</v>
       </c>
       <c r="G95" t="n">
-        <v>3.33113098144531</v>
+        <v>3.33113121986389</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>5.94946384429932</v>
       </c>
       <c r="G96" t="n">
-        <v>3.10889101028442</v>
+        <v>3.108891248703</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.95891523361206</v>
       </c>
       <c r="G97" t="n">
-        <v>3.11382985115051</v>
+        <v>3.11382961273193</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5.93528699874878</v>
       </c>
       <c r="G98" t="n">
-        <v>3.10148310661316</v>
+        <v>3.10148334503174</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>5.69900989532471</v>
       </c>
       <c r="G100" t="n">
-        <v>2.97801637649536</v>
+        <v>2.97801661491394</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.87385511398315</v>
       </c>
       <c r="G101" t="n">
-        <v>3.06938195228577</v>
+        <v>3.06938147544861</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>6.04869985580444</v>
       </c>
       <c r="G102" t="n">
-        <v>3.16074705123901</v>
+        <v>3.16074681282043</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.97781705856323</v>
       </c>
       <c r="G103" t="n">
-        <v>3.12370705604553</v>
+        <v>3.12370729446411</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.87858104705811</v>
       </c>
       <c r="G104" t="n">
-        <v>3.0718514919281</v>
+        <v>3.07185125350952</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>6.04397487640381</v>
       </c>
       <c r="G105" t="n">
-        <v>3.15827822685242</v>
+        <v>3.15827798843384</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>6.06287717819214</v>
       </c>
       <c r="G106" t="n">
-        <v>3.16815543174744</v>
+        <v>3.16815519332886</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.88330602645874</v>
       </c>
       <c r="G107" t="n">
-        <v>3.07431983947754</v>
+        <v>3.07432007789612</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>6.00144481658936</v>
       </c>
       <c r="G108" t="n">
-        <v>3.13605380058289</v>
+        <v>3.13605356216431</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>5.82187414169312</v>
       </c>
       <c r="G109" t="n">
-        <v>3.04221940040588</v>
+        <v>3.0422191619873</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.81714820861816</v>
       </c>
       <c r="G110" t="n">
-        <v>3.03974938392639</v>
+        <v>3.03974986076355</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>6.06287717819214</v>
       </c>
       <c r="G111" t="n">
-        <v>3.16815543174744</v>
+        <v>3.16815519332886</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>6.02507209777832</v>
       </c>
       <c r="G112" t="n">
-        <v>3.14840006828308</v>
+        <v>3.1483998298645</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.97309112548828</v>
       </c>
       <c r="G113" t="n">
-        <v>3.1212375164032</v>
+        <v>3.12123775482178</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.76989316940308</v>
       </c>
       <c r="G114" t="n">
-        <v>3.01505637168884</v>
+        <v>3.01505661010742</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.60922384262085</v>
       </c>
       <c r="G115" t="n">
-        <v>2.93109893798828</v>
+        <v>2.93109846115112</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.47690916061401</v>
       </c>
       <c r="G118" t="n">
-        <v>2.86195755004883</v>
+        <v>2.86195731163025</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.6139497756958</v>
       </c>
       <c r="G119" t="n">
-        <v>2.93356823921204</v>
+        <v>2.93356776237488</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.90693378448486</v>
       </c>
       <c r="G121" t="n">
-        <v>3.08666658401489</v>
+        <v>3.08666706085205</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.83605098724365</v>
       </c>
       <c r="G122" t="n">
-        <v>3.04962754249573</v>
+        <v>3.04962730407715</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.06106090545654</v>
       </c>
       <c r="G125" t="n">
-        <v>2.64465618133545</v>
+        <v>2.64465641975403</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.09414005279541</v>
       </c>
       <c r="G127" t="n">
-        <v>2.66194200515747</v>
+        <v>2.66194224357605</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.19337606430054</v>
       </c>
       <c r="G128" t="n">
-        <v>2.71379733085632</v>
+        <v>2.71379780769348</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.06106090545654</v>
       </c>
       <c r="G130" t="n">
-        <v>2.64465618133545</v>
+        <v>2.64465641975403</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.84841108322144</v>
       </c>
       <c r="G131" t="n">
-        <v>2.53353643417358</v>
+        <v>2.533536195755</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.82950878143311</v>
       </c>
       <c r="G132" t="n">
-        <v>2.52365899085999</v>
+        <v>2.52365875244141</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.87676382064819</v>
       </c>
       <c r="G133" t="n">
-        <v>2.54835200309753</v>
+        <v>2.54835176467896</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.23118114471436</v>
       </c>
       <c r="G134" t="n">
-        <v>2.7335524559021</v>
+        <v>2.73355293273926</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>5.4485559463501</v>
       </c>
       <c r="G135" t="n">
-        <v>2.84714221954346</v>
+        <v>2.84714198112488</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.67065620422363</v>
       </c>
       <c r="G136" t="n">
-        <v>2.96320009231567</v>
+        <v>2.96320033073425</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>5.57142019271851</v>
       </c>
       <c r="G137" t="n">
-        <v>2.91134428977966</v>
+        <v>2.91134452819824</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5.74626493453979</v>
       </c>
       <c r="G139" t="n">
-        <v>3.00270986557007</v>
+        <v>3.00270962715149</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.66120481491089</v>
       </c>
       <c r="G141" t="n">
-        <v>2.95826125144958</v>
+        <v>2.95826148986816</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.88803195953369</v>
       </c>
       <c r="G142" t="n">
-        <v>3.07679009437561</v>
+        <v>3.07678961753845</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.94946384429932</v>
       </c>
       <c r="G143" t="n">
-        <v>3.10889101028442</v>
+        <v>3.108891248703</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.9116587638855</v>
       </c>
       <c r="G144" t="n">
-        <v>3.08913612365723</v>
+        <v>3.08913588523865</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.93056201934814</v>
       </c>
       <c r="G145" t="n">
-        <v>3.0990138053894</v>
+        <v>3.09901356697083</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.98254299163818</v>
       </c>
       <c r="G146" t="n">
-        <v>3.12617611885071</v>
+        <v>3.12617659568787</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.8691291809082</v>
       </c>
       <c r="G147" t="n">
-        <v>3.06691217422485</v>
+        <v>3.06691265106201</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>5.44383001327515</v>
       </c>
       <c r="G149" t="n">
-        <v>2.84467220306396</v>
+        <v>2.84467244148254</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>5.15084600448608</v>
       </c>
       <c r="G151" t="n">
-        <v>2.69157338142395</v>
+        <v>2.69157361984253</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.5241641998291</v>
       </c>
       <c r="G153" t="n">
-        <v>2.88665103912354</v>
+        <v>2.88665056228638</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.75099086761475</v>
       </c>
       <c r="G154" t="n">
-        <v>3.00517892837524</v>
+        <v>3.00517845153809</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.75099086761475</v>
       </c>
       <c r="G155" t="n">
-        <v>3.00517892837524</v>
+        <v>3.00517845153809</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.85022687911987</v>
       </c>
       <c r="G156" t="n">
-        <v>3.05703473091125</v>
+        <v>3.05703520774841</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>5.82187414169312</v>
       </c>
       <c r="G158" t="n">
-        <v>3.04221940040588</v>
+        <v>3.0422191619873</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.81714820861816</v>
       </c>
       <c r="G159" t="n">
-        <v>3.03974938392639</v>
+        <v>3.03974986076355</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>5.68955898284912</v>
       </c>
       <c r="G162" t="n">
-        <v>2.97307825088501</v>
+        <v>2.97307777404785</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>5.51943922042847</v>
       </c>
       <c r="G163" t="n">
-        <v>2.88418173789978</v>
+        <v>2.88418197631836</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>5.58559703826904</v>
       </c>
       <c r="G164" t="n">
-        <v>2.91875243186951</v>
+        <v>2.91875267028809</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>5.69900989532471</v>
       </c>
       <c r="G165" t="n">
-        <v>2.97801637649536</v>
+        <v>2.97801661491394</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.80769681930542</v>
       </c>
       <c r="G166" t="n">
-        <v>3.0348105430603</v>
+        <v>3.03481078147888</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>5.72736310958862</v>
       </c>
       <c r="G169" t="n">
-        <v>2.99283218383789</v>
+        <v>2.99283266067505</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>5.8691291809082</v>
       </c>
       <c r="G170" t="n">
-        <v>3.06691217422485</v>
+        <v>3.06691265106201</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>5.6517539024353</v>
       </c>
       <c r="G173" t="n">
-        <v>2.95332312583923</v>
+        <v>2.9533224105835</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>5.64702892303467</v>
       </c>
       <c r="G174" t="n">
-        <v>2.95085382461548</v>
+        <v>2.9508535861969</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.68010807037354</v>
       </c>
       <c r="G175" t="n">
-        <v>2.96813917160034</v>
+        <v>2.96813893318176</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>5.81714820861816</v>
       </c>
       <c r="G176" t="n">
-        <v>3.03974938392639</v>
+        <v>3.03974986076355</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>5.74626493453979</v>
       </c>
       <c r="G177" t="n">
-        <v>3.00270986557007</v>
+        <v>3.00270962715149</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.55724287033081</v>
       </c>
       <c r="G179" t="n">
-        <v>2.90393567085266</v>
+        <v>2.90393590927124</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.48163509368896</v>
       </c>
       <c r="G180" t="n">
-        <v>2.86442732810974</v>
+        <v>2.86442708969116</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>5.55251789093018</v>
       </c>
       <c r="G184" t="n">
-        <v>2.90146732330322</v>
+        <v>2.90146708488464</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>5.42020177841187</v>
       </c>
       <c r="G185" t="n">
-        <v>2.83232498168945</v>
+        <v>2.83232522010803</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>5.37767219543457</v>
       </c>
       <c r="G186" t="n">
-        <v>2.81010174751282</v>
+        <v>2.81010103225708</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>5.44383001327515</v>
       </c>
       <c r="G188" t="n">
-        <v>2.84467220306396</v>
+        <v>2.84467244148254</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>5.18392515182495</v>
       </c>
       <c r="G191" t="n">
-        <v>2.70885920524597</v>
+        <v>2.70885896682739</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>5.33986806869507</v>
       </c>
       <c r="G193" t="n">
-        <v>2.79034686088562</v>
+        <v>2.7903470993042</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>5.43910503387451</v>
       </c>
       <c r="G195" t="n">
-        <v>2.84220337867737</v>
+        <v>2.84220361709595</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>5.533616065979</v>
       </c>
       <c r="G196" t="n">
-        <v>2.89158987998962</v>
+        <v>2.8915901184082</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>5.49581098556519</v>
       </c>
       <c r="G197" t="n">
-        <v>2.87183475494385</v>
+        <v>2.87183499336243</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>5.58559703826904</v>
       </c>
       <c r="G199" t="n">
-        <v>2.91875243186951</v>
+        <v>2.91875267028809</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>5.5666937828064</v>
       </c>
       <c r="G200" t="n">
-        <v>2.90887475013733</v>
+        <v>2.90887451171875</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>5.42020177841187</v>
       </c>
       <c r="G203" t="n">
-        <v>2.83232498168945</v>
+        <v>2.83232522010803</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>5.43437910079956</v>
       </c>
       <c r="G204" t="n">
-        <v>2.83973360061646</v>
+        <v>2.83973336219788</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>5.40129995346069</v>
       </c>
       <c r="G205" t="n">
-        <v>2.82244801521301</v>
+        <v>2.82244825363159</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>5.43910503387451</v>
       </c>
       <c r="G206" t="n">
-        <v>2.84220337867737</v>
+        <v>2.84220361709595</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>5.47218322753906</v>
       </c>
       <c r="G207" t="n">
-        <v>2.85948801040649</v>
+        <v>2.85948777198792</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>5.47690916061401</v>
       </c>
       <c r="G208" t="n">
-        <v>2.86195755004883</v>
+        <v>2.86195731163025</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>5.57142019271851</v>
       </c>
       <c r="G209" t="n">
-        <v>2.91134428977966</v>
+        <v>2.91134452819824</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>5.8691291809082</v>
       </c>
       <c r="G211" t="n">
-        <v>3.06691217422485</v>
+        <v>3.06691265106201</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>6.22354507446289</v>
       </c>
       <c r="G212" t="n">
-        <v>3.25211215019226</v>
+        <v>3.25211238861084</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>6.23299694061279</v>
       </c>
       <c r="G213" t="n">
-        <v>3.25705122947693</v>
+        <v>3.25705099105835</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>6.30388021469116</v>
       </c>
       <c r="G214" t="n">
-        <v>3.29409170150757</v>
+        <v>3.29409098625183</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>5.85022687911987</v>
       </c>
       <c r="G216" t="n">
-        <v>3.05703473091125</v>
+        <v>3.05703520774841</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>5.80297183990479</v>
       </c>
       <c r="G217" t="n">
-        <v>3.03234195709229</v>
+        <v>3.03234171867371</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>6.09595584869385</v>
       </c>
       <c r="G219" t="n">
-        <v>3.18544006347656</v>
+        <v>3.18544054031372</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>6.05815076828003</v>
       </c>
       <c r="G220" t="n">
-        <v>3.16568517684937</v>
+        <v>3.16568541526794</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>6.38421392440796</v>
       </c>
       <c r="G222" t="n">
-        <v>3.33607006072998</v>
+        <v>3.3360698223114</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>6.74335622787476</v>
       </c>
       <c r="G223" t="n">
-        <v>3.52373957633972</v>
+        <v>3.52373933792114</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>6.50235319137573</v>
       </c>
       <c r="G225" t="n">
-        <v>3.39780282974243</v>
+        <v>3.39780306816101</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>6.62049102783203</v>
       </c>
       <c r="G227" t="n">
-        <v>3.45953607559204</v>
+        <v>3.45953631401062</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>6.65829610824585</v>
       </c>
       <c r="G228" t="n">
-        <v>3.4792914390564</v>
+        <v>3.47929167747498</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>6.68664884567261</v>
       </c>
       <c r="G229" t="n">
-        <v>3.49410724639893</v>
+        <v>3.49410676956177</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>6.80478811264038</v>
       </c>
       <c r="G231" t="n">
-        <v>3.55584001541138</v>
+        <v>3.55584049224854</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>6.92292594909668</v>
       </c>
       <c r="G232" t="n">
-        <v>3.61757326126099</v>
+        <v>3.61757373809814</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>6.86149406433105</v>
       </c>
       <c r="G233" t="n">
-        <v>3.58547210693359</v>
+        <v>3.58547258377075</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>6.83314085006714</v>
       </c>
       <c r="G234" t="n">
-        <v>3.57065606117249</v>
+        <v>3.57065629959106</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>6.81423902511597</v>
       </c>
       <c r="G235" t="n">
-        <v>3.56077909469604</v>
+        <v>3.56077861785889</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>6.88984823226929</v>
       </c>
       <c r="G236" t="n">
-        <v>3.60028910636902</v>
+        <v>3.60028886795044</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>6.93237781524658</v>
       </c>
       <c r="G237" t="n">
-        <v>3.62251281738281</v>
+        <v>3.62251305580139</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>6.80951309204102</v>
       </c>
       <c r="G238" t="n">
-        <v>3.55830979347229</v>
+        <v>3.55830955505371</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>7.12139892578125</v>
       </c>
       <c r="G239" t="n">
-        <v>3.72128534317017</v>
+        <v>3.72128486633301</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7.38130521774292</v>
       </c>
       <c r="G241" t="n">
-        <v>3.85709929466248</v>
+        <v>3.85709953308105</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>7.52307081222534</v>
       </c>
       <c r="G243" t="n">
-        <v>3.93117904663086</v>
+        <v>3.9311785697937</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>7.9483699798584</v>
       </c>
       <c r="G247" t="n">
-        <v>4.15341901779175</v>
+        <v>4.15341949462891</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>8.02870464324951</v>
       </c>
       <c r="G248" t="n">
-        <v>4.19539833068848</v>
+        <v>4.19539737701416</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.07123470306396</v>
       </c>
       <c r="G249" t="n">
-        <v>4.21762228012085</v>
+        <v>4.21762132644653</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>8.22245216369629</v>
       </c>
       <c r="G250" t="n">
-        <v>4.29664087295532</v>
+        <v>4.29664039611816</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>8.24135398864746</v>
       </c>
       <c r="G251" t="n">
-        <v>4.30651760101318</v>
+        <v>4.30651807785034</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>7.99090003967285</v>
       </c>
       <c r="G252" t="n">
-        <v>4.17564296722412</v>
+        <v>4.17564344406128</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>8.16102027893066</v>
       </c>
       <c r="G253" t="n">
-        <v>4.26453924179077</v>
+        <v>4.26453971862793</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>8.24608039855957</v>
       </c>
       <c r="G255" t="n">
-        <v>4.30898714065552</v>
+        <v>4.30898761749268</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>8.16102027893066</v>
       </c>
       <c r="G256" t="n">
-        <v>4.26453924179077</v>
+        <v>4.26453971862793</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>8.46345520019531</v>
       </c>
       <c r="G258" t="n">
-        <v>4.42257595062256</v>
+        <v>4.42257690429688</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>8.62412357330322</v>
       </c>
       <c r="G259" t="n">
-        <v>4.5065336227417</v>
+        <v>4.50653409957886</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>8.74698829650879</v>
       </c>
       <c r="G261" t="n">
-        <v>4.57073783874512</v>
+        <v>4.5707368850708</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>9.35658264160156</v>
       </c>
       <c r="G262" t="n">
-        <v>4.88927984237671</v>
+        <v>4.88928031921387</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>9.48889923095703</v>
       </c>
       <c r="G263" t="n">
-        <v>4.95842313766479</v>
+        <v>4.95842266082764</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>9.59286117553711</v>
       </c>
       <c r="G264" t="n">
-        <v>5.01274681091309</v>
+        <v>5.0127477645874</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>9.89529609680176</v>
       </c>
       <c r="G265" t="n">
-        <v>5.17078495025635</v>
+        <v>5.17078447341919</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>8.29806137084961</v>
       </c>
       <c r="G266" t="n">
-        <v>4.33615064620972</v>
+        <v>4.33615016937256</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>8.31696319580078</v>
       </c>
       <c r="G268" t="n">
-        <v>4.34602737426758</v>
+        <v>4.34602689743042</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>8.88402938842773</v>
       </c>
       <c r="G272" t="n">
-        <v>4.64234733581543</v>
+        <v>4.64234781265259</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>9.03052139282227</v>
       </c>
       <c r="G273" t="n">
-        <v>4.71889686584473</v>
+        <v>4.71889638900757</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.56450843811035</v>
       </c>
       <c r="G274" t="n">
-        <v>4.99793148040771</v>
+        <v>4.99793195724487</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.81023597717285</v>
       </c>
       <c r="G277" t="n">
-        <v>5.12633657455444</v>
+        <v>5.12633609771729</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.54560470581055</v>
       </c>
       <c r="G279" t="n">
-        <v>4.9880542755127</v>
+        <v>4.98805379867554</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.55505561828613</v>
       </c>
       <c r="G280" t="n">
-        <v>4.99299192428589</v>
+        <v>4.99299240112305</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>9.57395935058594</v>
       </c>
       <c r="G281" t="n">
-        <v>5.00287103652954</v>
+        <v>5.00287008285522</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.65901756286621</v>
       </c>
       <c r="G282" t="n">
-        <v>5.04731798171997</v>
+        <v>5.04731750488281</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>9.4227409362793</v>
       </c>
       <c r="G283" t="n">
-        <v>4.92385149002075</v>
+        <v>4.92385101318359</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>9.37548637390137</v>
       </c>
       <c r="G285" t="n">
-        <v>4.8991584777832</v>
+        <v>4.89915800094604</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>9.59286117553711</v>
       </c>
       <c r="G287" t="n">
-        <v>5.01274681091309</v>
+        <v>5.0127477645874</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>9.81023597717285</v>
       </c>
       <c r="G288" t="n">
-        <v>5.12633657455444</v>
+        <v>5.12633609771729</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>10.2166328430176</v>
       </c>
       <c r="G289" t="n">
-        <v>5.33869934082031</v>
+        <v>5.33869886398315</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>10.1882801055908</v>
       </c>
       <c r="G291" t="n">
-        <v>5.32388401031494</v>
+        <v>5.3238844871521</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>10.1977310180664</v>
       </c>
       <c r="G293" t="n">
-        <v>5.32882261276245</v>
+        <v>5.32882213592529</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>10.2166328430176</v>
       </c>
       <c r="G294" t="n">
-        <v>5.33869934082031</v>
+        <v>5.33869886398315</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>10.1882801055908</v>
       </c>
       <c r="G295" t="n">
-        <v>5.32388401031494</v>
+        <v>5.3238844871521</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>9.59286117553711</v>
       </c>
       <c r="G297" t="n">
-        <v>5.01274681091309</v>
+        <v>5.0127477645874</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>9.91419792175293</v>
       </c>
       <c r="G302" t="n">
-        <v>5.18066167831421</v>
+        <v>5.18066215515137</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>9.81968688964844</v>
       </c>
       <c r="G303" t="n">
-        <v>5.13127517700195</v>
+        <v>5.13127470016479</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.82913780212402</v>
       </c>
       <c r="G304" t="n">
-        <v>5.13621377944946</v>
+        <v>5.13621425628662</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>9.81023597717285</v>
       </c>
       <c r="G309" t="n">
-        <v>5.12633657455444</v>
+        <v>5.12633609771729</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.99925804138184</v>
       </c>
       <c r="G310" t="n">
-        <v>5.22510957717896</v>
+        <v>5.22511053085327</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.1882801055908</v>
       </c>
       <c r="G311" t="n">
-        <v>5.32388401031494</v>
+        <v>5.3238844871521</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>10.1504745483398</v>
       </c>
       <c r="G312" t="n">
-        <v>5.30412769317627</v>
+        <v>5.30412817001343</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>9.97090530395508</v>
       </c>
       <c r="G313" t="n">
-        <v>5.21029472351074</v>
+        <v>5.21029424667358</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>9.59286117553711</v>
       </c>
       <c r="G314" t="n">
-        <v>5.01274681091309</v>
+        <v>5.0127477645874</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>9.49835014343262</v>
       </c>
       <c r="G317" t="n">
-        <v>4.96336126327515</v>
+        <v>4.96336078643799</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.44164276123047</v>
       </c>
       <c r="G318" t="n">
-        <v>4.93372821807861</v>
+        <v>4.93372774124146</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>9.71572494506836</v>
       </c>
       <c r="G319" t="n">
-        <v>5.07695007324219</v>
+        <v>5.07694959640503</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>9.20536613464355</v>
       </c>
       <c r="G323" t="n">
-        <v>4.81026220321655</v>
+        <v>4.81026268005371</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>9.24789619445801</v>
       </c>
       <c r="G324" t="n">
-        <v>4.83248615264893</v>
+        <v>4.83248662948608</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>9.0777759552002</v>
       </c>
       <c r="G325" t="n">
-        <v>4.74358987808228</v>
+        <v>4.74359035491943</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>9.15810966491699</v>
       </c>
       <c r="G326" t="n">
-        <v>4.78556871414185</v>
+        <v>4.78556823730469</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>9.05887413024902</v>
       </c>
       <c r="G327" t="n">
-        <v>4.73371315002441</v>
+        <v>4.7337121963501</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.52016162872314</v>
       </c>
       <c r="G332" t="n">
-        <v>4.45220899581909</v>
+        <v>4.45220851898193</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>9.00216674804688</v>
       </c>
       <c r="G334" t="n">
-        <v>4.7040810585022</v>
+        <v>4.70408010482788</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>8.86040115356445</v>
       </c>
       <c r="G335" t="n">
-        <v>4.63000106811523</v>
+        <v>4.62999963760376</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>9.17228698730469</v>
       </c>
       <c r="G336" t="n">
-        <v>4.79297637939453</v>
+        <v>4.79297685623169</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>9.1628360748291</v>
       </c>
       <c r="G337" t="n">
-        <v>4.78803730010986</v>
+        <v>4.78803777694702</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>10.018159866333</v>
       </c>
       <c r="G338" t="n">
-        <v>5.23498678207397</v>
+        <v>5.23498773574829</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>9.81968688964844</v>
       </c>
       <c r="G340" t="n">
-        <v>5.13127517700195</v>
+        <v>5.13127470016479</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>9.4085636138916</v>
       </c>
       <c r="G341" t="n">
-        <v>4.91644334793091</v>
+        <v>4.91644239425659</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>9.71572494506836</v>
       </c>
       <c r="G344" t="n">
-        <v>5.07695007324219</v>
+        <v>5.07694959640503</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>9.41329002380371</v>
       </c>
       <c r="G348" t="n">
-        <v>4.91891193389893</v>
+        <v>4.91891288757324</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>9.61176300048828</v>
       </c>
       <c r="G350" t="n">
-        <v>5.02262496948242</v>
+        <v>5.02262401580811</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>9.56450843811035</v>
       </c>
       <c r="G351" t="n">
-        <v>4.99793148040771</v>
+        <v>4.99793195724487</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>9.12503242492676</v>
       </c>
       <c r="G352" t="n">
-        <v>4.76828384399414</v>
+        <v>4.76828336715698</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.18646430969238</v>
       </c>
       <c r="G354" t="n">
-        <v>4.80038547515869</v>
+        <v>4.80038499832153</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>8.97381401062012</v>
       </c>
       <c r="G356" t="n">
-        <v>4.68926429748535</v>
+        <v>4.68926382064819</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>8.92183303833008</v>
       </c>
       <c r="G357" t="n">
-        <v>4.66210174560547</v>
+        <v>4.66210222244263</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.88402938842773</v>
       </c>
       <c r="G358" t="n">
-        <v>4.64234733581543</v>
+        <v>4.64234781265259</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>8.94073486328125</v>
       </c>
       <c r="G359" t="n">
-        <v>4.67197895050049</v>
+        <v>4.6719799041748</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>8.78479194641113</v>
       </c>
       <c r="G360" t="n">
-        <v>4.59049081802368</v>
+        <v>4.59049129486084</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>8.8320484161377</v>
       </c>
       <c r="G362" t="n">
-        <v>4.61518526077271</v>
+        <v>4.61518478393555</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>9.1628360748291</v>
       </c>
       <c r="G365" t="n">
-        <v>4.78803730010986</v>
+        <v>4.78803777694702</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.21954345703125</v>
       </c>
       <c r="G370" t="n">
-        <v>4.81767082214355</v>
+        <v>4.8176703453064</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.44164276123047</v>
       </c>
       <c r="G371" t="n">
-        <v>4.93372821807861</v>
+        <v>4.93372774124146</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>9.03524589538574</v>
       </c>
       <c r="G373" t="n">
-        <v>4.7213659286499</v>
+        <v>4.72136640548706</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>8.97381401062012</v>
       </c>
       <c r="G375" t="n">
-        <v>4.68926429748535</v>
+        <v>4.68926382064819</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>9.05887413024902</v>
       </c>
       <c r="G377" t="n">
-        <v>4.73371315002441</v>
+        <v>4.7337121963501</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>9.17228698730469</v>
       </c>
       <c r="G379" t="n">
-        <v>4.79297637939453</v>
+        <v>4.79297685623169</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>9.14393424987793</v>
       </c>
       <c r="G380" t="n">
-        <v>4.77816104888916</v>
+        <v>4.778160572052</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>9.03524589538574</v>
       </c>
       <c r="G381" t="n">
-        <v>4.7213659286499</v>
+        <v>4.72136640548706</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>9.11085510253906</v>
       </c>
       <c r="G382" t="n">
-        <v>4.76087522506714</v>
+        <v>4.76087617874146</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>8.8320484161377</v>
       </c>
       <c r="G383" t="n">
-        <v>4.61518526077271</v>
+        <v>4.61518478393555</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>8.72336006164551</v>
       </c>
       <c r="G384" t="n">
-        <v>4.55839061737061</v>
+        <v>4.55838966369629</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>9.15826511383057</v>
       </c>
       <c r="G387" t="n">
-        <v>4.78564977645874</v>
+        <v>4.78564929962158</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>9.93647956848145</v>
       </c>
       <c r="G393" t="n">
-        <v>5.19230508804321</v>
+        <v>5.19230556488037</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>9.89851760864258</v>
       </c>
       <c r="G395" t="n">
-        <v>5.17246866226196</v>
+        <v>5.17246770858765</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>9.90800857543945</v>
       </c>
       <c r="G397" t="n">
-        <v>5.17742776870728</v>
+        <v>5.17742824554443</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>9.52839183807373</v>
       </c>
       <c r="G400" t="n">
-        <v>4.97905969619751</v>
+        <v>4.97905874252319</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.54737186431885</v>
       </c>
       <c r="G401" t="n">
-        <v>4.9889760017395</v>
+        <v>4.98897695541382</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>9.64227676391602</v>
       </c>
       <c r="G402" t="n">
-        <v>5.03856945037842</v>
+        <v>5.03856897354126</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>9.63278579711914</v>
       </c>
       <c r="G403" t="n">
-        <v>5.03361082077026</v>
+        <v>5.03360986709595</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>9.64227676391602</v>
       </c>
       <c r="G404" t="n">
-        <v>5.03856945037842</v>
+        <v>5.03856897354126</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>9.68023777008057</v>
       </c>
       <c r="G405" t="n">
-        <v>5.05840635299683</v>
+        <v>5.05840682983398</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>9.54737186431885</v>
       </c>
       <c r="G407" t="n">
-        <v>4.9889760017395</v>
+        <v>4.98897695541382</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>9.62329578399658</v>
       </c>
       <c r="G408" t="n">
-        <v>5.02865076065063</v>
+        <v>5.02865123748779</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.71819972991943</v>
       </c>
       <c r="G409" t="n">
-        <v>5.07824325561523</v>
+        <v>5.07824277877808</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.68023777008057</v>
       </c>
       <c r="G411" t="n">
-        <v>5.05840635299683</v>
+        <v>5.05840682983398</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>10.0788373947144</v>
       </c>
       <c r="G415" t="n">
-        <v>5.26669406890869</v>
+        <v>5.26669454574585</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>10.3445692062378</v>
       </c>
       <c r="G416" t="n">
-        <v>5.40555238723755</v>
+        <v>5.40555191040039</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>10.1547603607178</v>
       </c>
       <c r="G418" t="n">
-        <v>5.30636692047119</v>
+        <v>5.30636739730835</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>10.8855228424072</v>
       </c>
       <c r="G420" t="n">
-        <v>5.68822813034058</v>
+        <v>5.68822765350342</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>11.8535470962524</v>
       </c>
       <c r="G422" t="n">
-        <v>6.19406890869141</v>
+        <v>6.19406938552856</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>11.7681331634521</v>
       </c>
       <c r="G423" t="n">
-        <v>6.14943599700928</v>
+        <v>6.1494345664978</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>11.616286277771</v>
       </c>
       <c r="G425" t="n">
-        <v>6.07008790969849</v>
+        <v>6.07008743286133</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>11.7491521835327</v>
       </c>
       <c r="G426" t="n">
-        <v>6.13951683044434</v>
+        <v>6.13951730728149</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>12.0053939819336</v>
       </c>
       <c r="G427" t="n">
-        <v>6.27341604232788</v>
+        <v>6.27341556549072</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>12.6602344512939</v>
       </c>
       <c r="G428" t="n">
-        <v>6.61560297012329</v>
+        <v>6.61560249328613</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>12.4988956451416</v>
       </c>
       <c r="G429" t="n">
-        <v>6.53129434585571</v>
+        <v>6.53129529953003</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>12.4514436721802</v>
       </c>
       <c r="G430" t="n">
-        <v>6.50649976730347</v>
+        <v>6.50649929046631</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>12.9829082489014</v>
       </c>
       <c r="G431" t="n">
-        <v>6.78421497344971</v>
+        <v>6.78421545028687</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>12.8405523300171</v>
       </c>
       <c r="G432" t="n">
-        <v>6.70982789993286</v>
+        <v>6.7098274230957</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>12.8690233230591</v>
       </c>
       <c r="G433" t="n">
-        <v>6.72470664978027</v>
+        <v>6.72470569610596</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>12.9544372558594</v>
       </c>
       <c r="G434" t="n">
-        <v>6.76933765411377</v>
+        <v>6.76933860778809</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>12.9829082489014</v>
       </c>
       <c r="G435" t="n">
-        <v>6.78421497344971</v>
+        <v>6.78421545028687</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>13.0208702087402</v>
       </c>
       <c r="G436" t="n">
-        <v>6.80405330657959</v>
+        <v>6.80405378341675</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>13.3340539932251</v>
       </c>
       <c r="G437" t="n">
-        <v>6.96770715713501</v>
+        <v>6.96770620346069</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>13.1727170944214</v>
       </c>
       <c r="G438" t="n">
-        <v>6.88340044021606</v>
+        <v>6.88339996337891</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>13.3815059661865</v>
       </c>
       <c r="G439" t="n">
-        <v>6.99250268936157</v>
+        <v>6.99250364303589</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>13.5428438186646</v>
       </c>
       <c r="G440" t="n">
-        <v>7.07681035995483</v>
+        <v>7.07680988311768</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>13.6757097244263</v>
       </c>
       <c r="G441" t="n">
-        <v>7.14623928070068</v>
+        <v>7.14623975753784</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>13.7421426773071</v>
       </c>
       <c r="G442" t="n">
-        <v>7.18095302581787</v>
+        <v>7.18095350265503</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>13.998384475708</v>
       </c>
       <c r="G444" t="n">
-        <v>7.31485271453857</v>
+        <v>7.31485176086426</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>14.0363464355469</v>
       </c>
       <c r="G445" t="n">
-        <v>7.33469009399414</v>
+        <v>7.33468914031982</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>14.1312503814697</v>
       </c>
       <c r="G446" t="n">
-        <v>7.38428115844727</v>
+        <v>7.38428258895874</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>14.0932893753052</v>
       </c>
       <c r="G447" t="n">
-        <v>7.36444473266602</v>
+        <v>7.36444568634033</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>14.3874921798706</v>
       </c>
       <c r="G448" t="n">
-        <v>7.51818037033081</v>
+        <v>7.51818132400513</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>14.5108671188354</v>
       </c>
       <c r="G449" t="n">
-        <v>7.58265066146851</v>
+        <v>7.58264970779419</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>14.4254541397095</v>
       </c>
       <c r="G451" t="n">
-        <v>7.53801774978638</v>
+        <v>7.53801870346069</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>14.3400402069092</v>
       </c>
       <c r="G452" t="n">
-        <v>7.49338531494141</v>
+        <v>7.49338483810425</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>14.1787023544312</v>
       </c>
       <c r="G453" t="n">
-        <v>7.40907859802246</v>
+        <v>7.40907764434814</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>14.3969821929932</v>
       </c>
       <c r="G454" t="n">
-        <v>7.52313995361328</v>
+        <v>7.52313947677612</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>14.188193321228</v>
       </c>
       <c r="G455" t="n">
-        <v>7.41403770446777</v>
+        <v>7.41403818130493</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>14.3590211868286</v>
       </c>
       <c r="G456" t="n">
-        <v>7.50330448150635</v>
+        <v>7.50330400466919</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>14.2071743011475</v>
       </c>
       <c r="G457" t="n">
-        <v>7.4239559173584</v>
+        <v>7.42395544052124</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>14.2736072540283</v>
       </c>
       <c r="G458" t="n">
-        <v>7.45866966247559</v>
+        <v>7.45867013931274</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>13.9888944625854</v>
       </c>
       <c r="G460" t="n">
-        <v>7.30989360809326</v>
+        <v>7.3098931312561</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>13.2771120071411</v>
       </c>
       <c r="G462" t="n">
-        <v>6.93795108795166</v>
+        <v>6.93795204162598</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>13.5048818588257</v>
       </c>
       <c r="G463" t="n">
-        <v>7.05697345733643</v>
+        <v>7.05697298049927</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>13.4384489059448</v>
       </c>
       <c r="G464" t="n">
-        <v>7.02225971221924</v>
+        <v>7.02225828170776</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>13.6662187576294</v>
       </c>
       <c r="G466" t="n">
-        <v>7.14127969741821</v>
+        <v>7.14127922058105</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>14.0648174285889</v>
       </c>
       <c r="G467" t="n">
-        <v>7.34956741333008</v>
+        <v>7.34956693649292</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>13.9888944625854</v>
       </c>
       <c r="G468" t="n">
-        <v>7.30989360809326</v>
+        <v>7.3098931312561</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>14.0837984085083</v>
       </c>
       <c r="G469" t="n">
-        <v>7.35948657989502</v>
+        <v>7.3594856262207</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>14.0837984085083</v>
       </c>
       <c r="G470" t="n">
-        <v>7.35948657989502</v>
+        <v>7.3594856262207</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>14.5108671188354</v>
       </c>
       <c r="G472" t="n">
-        <v>7.58265066146851</v>
+        <v>7.58264970779419</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>14.7955799102783</v>
       </c>
       <c r="G474" t="n">
-        <v>7.73142671585083</v>
+        <v>7.73142719268799</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>14.2641162872314</v>
       </c>
       <c r="G476" t="n">
-        <v>7.45371055603027</v>
+        <v>7.45371150970459</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>13.9319505691528</v>
       </c>
       <c r="G477" t="n">
-        <v>7.28013753890991</v>
+        <v>7.28013849258423</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>14.0458364486694</v>
       </c>
       <c r="G478" t="n">
-        <v>7.33964967727661</v>
+        <v>7.33964920043945</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>14.0363464355469</v>
       </c>
       <c r="G479" t="n">
-        <v>7.33469009399414</v>
+        <v>7.33468914031982</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>14.1122694015503</v>
       </c>
       <c r="G480" t="n">
-        <v>7.37436199188232</v>
+        <v>7.37436246871948</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>13.8750085830688</v>
       </c>
       <c r="G481" t="n">
-        <v>7.25038242340088</v>
+        <v>7.25038194656372</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>13.9888944625854</v>
       </c>
       <c r="G483" t="n">
-        <v>7.30989360809326</v>
+        <v>7.3098931312561</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>14.2261552810669</v>
       </c>
       <c r="G484" t="n">
-        <v>7.43387508392334</v>
+        <v>7.43387413024902</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>14.188193321228</v>
       </c>
       <c r="G486" t="n">
-        <v>7.41403770446777</v>
+        <v>7.41403818130493</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>14.0932893753052</v>
       </c>
       <c r="G487" t="n">
-        <v>7.36444473266602</v>
+        <v>7.36444568634033</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>13.9888944625854</v>
       </c>
       <c r="G488" t="n">
-        <v>7.30989360809326</v>
+        <v>7.3098931312561</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>13.7231616973877</v>
       </c>
       <c r="G491" t="n">
-        <v>7.17103576660156</v>
+        <v>7.1710352897644</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>13.6851997375488</v>
       </c>
       <c r="G492" t="n">
-        <v>7.15119886398315</v>
+        <v>7.15119791030884</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>13.8465366363525</v>
       </c>
       <c r="G494" t="n">
-        <v>7.23550510406494</v>
+        <v>7.23550462722778</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>13.8750085830688</v>
       </c>
       <c r="G495" t="n">
-        <v>7.25038242340088</v>
+        <v>7.25038194656372</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>13.6757097244263</v>
       </c>
       <c r="G496" t="n">
-        <v>7.14623928070068</v>
+        <v>7.14623975753784</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>13.7611227035522</v>
       </c>
       <c r="G497" t="n">
-        <v>7.19087171554565</v>
+        <v>7.19087219238281</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>14.1312503814697</v>
       </c>
       <c r="G498" t="n">
-        <v>7.38428115844727</v>
+        <v>7.38428258895874</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>14.4159631729126</v>
       </c>
       <c r="G499" t="n">
-        <v>7.53305864334106</v>
+        <v>7.53305912017822</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>14.3685111999512</v>
       </c>
       <c r="G501" t="n">
-        <v>7.50826358795166</v>
+        <v>7.50826263427734</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>14.2356452941895</v>
       </c>
       <c r="G502" t="n">
-        <v>7.43883323669434</v>
+        <v>7.43883275985718</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>14.2546262741089</v>
       </c>
       <c r="G503" t="n">
-        <v>7.44875144958496</v>
+        <v>7.44875288009644</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>14.6152620315552</v>
       </c>
       <c r="G504" t="n">
-        <v>7.63720178604126</v>
+        <v>7.63720273971558</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>14.6437330245972</v>
       </c>
       <c r="G505" t="n">
-        <v>7.65208053588867</v>
+        <v>7.65207958221436</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>14.6247529983521</v>
       </c>
       <c r="G506" t="n">
-        <v>7.64216184616089</v>
+        <v>7.64216136932373</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>14.434944152832</v>
       </c>
       <c r="G510" t="n">
-        <v>7.54297733306885</v>
+        <v>7.54297637939453</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>14.1502313613892</v>
       </c>
       <c r="G511" t="n">
-        <v>7.39420127868652</v>
+        <v>7.39420032501221</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>14.3874921798706</v>
       </c>
       <c r="G512" t="n">
-        <v>7.51818037033081</v>
+        <v>7.51818132400513</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>17.5288238525391</v>
       </c>
       <c r="G517" t="n">
-        <v>9.15968322753906</v>
+        <v>9.15968132019043</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>18.1551933288574</v>
       </c>
       <c r="G520" t="n">
-        <v>9.48699188232422</v>
+        <v>9.48699378967285</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>17.8514995574951</v>
       </c>
       <c r="G523" t="n">
-        <v>9.32829761505127</v>
+        <v>9.32829666137695</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>18.1836643218994</v>
       </c>
       <c r="G524" t="n">
-        <v>9.50187015533447</v>
+        <v>9.50186920166016</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>18.6866569519043</v>
       </c>
       <c r="G526" t="n">
-        <v>9.76470851898193</v>
+        <v>9.76470756530762</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>18.5727710723877</v>
       </c>
       <c r="G527" t="n">
-        <v>9.70519733428955</v>
+        <v>9.70519828796387</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>18.4493961334229</v>
       </c>
       <c r="G528" t="n">
-        <v>9.64072895050049</v>
+        <v>9.64072799682617</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>18.4304141998291</v>
       </c>
       <c r="G529" t="n">
-        <v>9.63080883026123</v>
+        <v>9.63080787658691</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>18.791051864624</v>
       </c>
       <c r="G530" t="n">
-        <v>9.819260597229</v>
+        <v>9.81925964355469</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>18.5310134887695</v>
       </c>
       <c r="G532" t="n">
-        <v>9.68337631225586</v>
+        <v>9.68337726593018</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>17.8951549530029</v>
       </c>
       <c r="G538" t="n">
-        <v>9.35110855102539</v>
+        <v>9.35111045837402</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>16.410852432251</v>
       </c>
       <c r="G542" t="n">
-        <v>8.5754861831665</v>
+        <v>8.57548713684082</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>16.7980613708496</v>
       </c>
       <c r="G543" t="n">
-        <v>8.77782249450684</v>
+        <v>8.77782440185547</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>17.120735168457</v>
       </c>
       <c r="G547" t="n">
-        <v>8.94643592834473</v>
+        <v>8.94643688201904</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>17.2023544311523</v>
       </c>
       <c r="G548" t="n">
-        <v>8.98908805847168</v>
+        <v>8.98908615112305</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>16.8588008880615</v>
       </c>
       <c r="G549" t="n">
-        <v>8.80956363677979</v>
+        <v>8.80956268310547</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>16.6765842437744</v>
       </c>
       <c r="G553" t="n">
-        <v>8.71434593200684</v>
+        <v>8.71434688568115</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>16.2172470092773</v>
       </c>
       <c r="G554" t="n">
-        <v>8.47431945800781</v>
+        <v>8.4743185043335</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>15.3365354537964</v>
       </c>
       <c r="G556" t="n">
-        <v>8.01410293579102</v>
+        <v>8.01410388946533</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>16.3861751556396</v>
       </c>
       <c r="G559" t="n">
-        <v>8.56259250640869</v>
+        <v>8.56259155273438</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>16.3254375457764</v>
       </c>
       <c r="G562" t="n">
-        <v>8.53085422515869</v>
+        <v>8.53085327148438</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>16.6822776794434</v>
       </c>
       <c r="G568" t="n">
-        <v>8.71732139587402</v>
+        <v>8.71732044219971</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>15.7901773452759</v>
       </c>
       <c r="G570" t="n">
-        <v>8.25115394592285</v>
+        <v>8.25115299224854</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>15.6611080169678</v>
       </c>
       <c r="G574" t="n">
-        <v>8.18370914459229</v>
+        <v>8.1837100982666</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>16.8075523376465</v>
       </c>
       <c r="G575" t="n">
-        <v>8.7827844619751</v>
+        <v>8.78278350830078</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>17.5269260406494</v>
       </c>
       <c r="G577" t="n">
-        <v>9.15869045257568</v>
+        <v>9.15869235992432</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>17.8230285644531</v>
       </c>
       <c r="G580" t="n">
-        <v>9.3134183883667</v>
+        <v>9.31341934204102</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>18.0583896636963</v>
       </c>
       <c r="G583" t="n">
-        <v>9.43640899658203</v>
+        <v>9.43640804290771</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>17.917932510376</v>
       </c>
       <c r="G584" t="n">
-        <v>9.36301136016846</v>
+        <v>9.36301231384277</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>18.5803642272949</v>
       </c>
       <c r="G585" t="n">
-        <v>9.7091646194458</v>
+        <v>9.70916557312012</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>18.6923503875732</v>
       </c>
       <c r="G586" t="n">
-        <v>9.7676830291748</v>
+        <v>9.76768398284912</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>18.7379055023193</v>
       </c>
       <c r="G590" t="n">
-        <v>9.79148864746094</v>
+        <v>9.79148960113525</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>18.1684799194336</v>
       </c>
       <c r="G591" t="n">
-        <v>9.49393653869629</v>
+        <v>9.49393558502197</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>18.0166320800781</v>
       </c>
       <c r="G593" t="n">
-        <v>9.41458702087402</v>
+        <v>9.41458892822266</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>17.640811920166</v>
       </c>
       <c r="G596" t="n">
-        <v>9.21820259094238</v>
+        <v>9.2182035446167</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>18.2121353149414</v>
       </c>
       <c r="G597" t="n">
-        <v>9.51674747467041</v>
+        <v>9.51674556732178</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>18.2481994628906</v>
       </c>
       <c r="G598" t="n">
-        <v>9.53559303283691</v>
+        <v>9.5355920791626</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>18.1419067382812</v>
       </c>
       <c r="G599" t="n">
-        <v>9.4800500869751</v>
+        <v>9.48005104064941</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>17.7888622283936</v>
       </c>
       <c r="G600" t="n">
-        <v>9.29556655883789</v>
+        <v>9.29556560516357</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>18.0223274230957</v>
       </c>
       <c r="G603" t="n">
-        <v>9.41756439208984</v>
+        <v>9.41756343841553</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>17.8116397857666</v>
       </c>
       <c r="G605" t="n">
-        <v>9.30746936798096</v>
+        <v>9.30746841430664</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>17.9274215698242</v>
       </c>
       <c r="G606" t="n">
-        <v>9.36797046661377</v>
+        <v>9.36797142028809</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>18.0640850067139</v>
       </c>
       <c r="G608" t="n">
-        <v>9.4393835067749</v>
+        <v>9.43938446044922</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>18.3639812469482</v>
       </c>
       <c r="G609" t="n">
-        <v>9.59609508514404</v>
+        <v>9.59609603881836</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>17.8078422546387</v>
       </c>
       <c r="G612" t="n">
-        <v>9.30548572540283</v>
+        <v>9.30548477172852</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>17.346607208252</v>
       </c>
       <c r="G614" t="n">
-        <v>9.06446552276611</v>
+        <v>9.0644645690918</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>18.0413074493408</v>
       </c>
       <c r="G615" t="n">
-        <v>9.42748069763184</v>
+        <v>9.42748165130615</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>18.411434173584</v>
       </c>
       <c r="G616" t="n">
-        <v>9.62089061737061</v>
+        <v>9.62089157104492</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>16.9859714508057</v>
       </c>
       <c r="G619" t="n">
-        <v>8.87601566314697</v>
+        <v>8.87601661682129</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>16.9593982696533</v>
       </c>
       <c r="G620" t="n">
-        <v>8.86212921142578</v>
+        <v>8.86213111877441</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>17.4908638000488</v>
       </c>
       <c r="G621" t="n">
-        <v>9.13984870910645</v>
+        <v>9.13984680175781</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>17.0448112487793</v>
       </c>
       <c r="G622" t="n">
-        <v>8.90676307678223</v>
+        <v>8.90676403045654</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>17.1909656524658</v>
       </c>
       <c r="G623" t="n">
-        <v>8.98313522338867</v>
+        <v>8.98313426971436</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>16.9366207122803</v>
       </c>
       <c r="G625" t="n">
-        <v>8.85022735595703</v>
+        <v>8.85022640228271</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>16.9821758270264</v>
       </c>
       <c r="G627" t="n">
-        <v>8.87403106689453</v>
+        <v>8.87403297424316</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>17.0789775848389</v>
       </c>
       <c r="G628" t="n">
-        <v>8.92461776733398</v>
+        <v>8.92461681365967</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>15.1751976013184</v>
       </c>
       <c r="G633" t="n">
-        <v>7.92979669570923</v>
+        <v>7.92979621887207</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>15.7711973190308</v>
       </c>
       <c r="G635" t="n">
-        <v>8.24123573303223</v>
+        <v>8.24123477935791</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>15.2245483398438</v>
       </c>
       <c r="G636" t="n">
-        <v>7.95558500289917</v>
+        <v>7.95558404922485</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>15.505464553833</v>
       </c>
       <c r="G638" t="n">
-        <v>8.10237693786621</v>
+        <v>8.10237789154053</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>15.3839874267578</v>
       </c>
       <c r="G640" t="n">
-        <v>8.03890037536621</v>
+        <v>8.03889942169189</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>16.2760887145996</v>
       </c>
       <c r="G641" t="n">
-        <v>8.50506591796875</v>
+        <v>8.50506687164307</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>15.7180500030518</v>
       </c>
       <c r="G646" t="n">
-        <v>8.21346473693848</v>
+        <v>8.21346378326416</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>15.7920761108398</v>
       </c>
       <c r="G647" t="n">
-        <v>8.25214576721191</v>
+        <v>8.25214672088623</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>15.3460254669189</v>
       </c>
       <c r="G653" t="n">
-        <v>8.01906204223633</v>
+        <v>8.01906299591064</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>13.2771120071411</v>
       </c>
       <c r="G655" t="n">
-        <v>6.93795108795166</v>
+        <v>6.93795204162598</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>13.7421426773071</v>
       </c>
       <c r="G656" t="n">
-        <v>7.18095302581787</v>
+        <v>7.18095350265503</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>13.7041807174683</v>
       </c>
       <c r="G657" t="n">
-        <v>7.16111660003662</v>
+        <v>7.16111707687378</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>13.9015817642212</v>
       </c>
       <c r="G658" t="n">
-        <v>7.26426792144775</v>
+        <v>7.26426887512207</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>13.8541297912598</v>
       </c>
       <c r="G659" t="n">
-        <v>7.23947334289551</v>
+        <v>7.23947286605835</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>13.4877986907959</v>
       </c>
       <c r="G660" t="n">
-        <v>7.04804611206055</v>
+        <v>7.04804658889771</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>13.4764108657837</v>
       </c>
       <c r="G661" t="n">
-        <v>7.04209566116333</v>
+        <v>7.04209661483765</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>13.8427410125732</v>
       </c>
       <c r="G663" t="n">
-        <v>7.23352193832397</v>
+        <v>7.23352098464966</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>13.7839012145996</v>
       </c>
       <c r="G664" t="n">
-        <v>7.20277452468872</v>
+        <v>7.20277404785156</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>13.4802074432373</v>
       </c>
       <c r="G667" t="n">
-        <v>7.0440788269043</v>
+        <v>7.04407930374146</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>13.3511371612549</v>
       </c>
       <c r="G668" t="n">
-        <v>6.97663354873657</v>
+        <v>6.97663450241089</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>13.3340539932251</v>
       </c>
       <c r="G669" t="n">
-        <v>6.96770715713501</v>
+        <v>6.96770620346069</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>13.0284624099731</v>
       </c>
       <c r="G670" t="n">
-        <v>6.808021068573</v>
+        <v>6.80801963806152</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>13.0113792419434</v>
       </c>
       <c r="G671" t="n">
-        <v>6.79909420013428</v>
+        <v>6.79909372329712</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>13.4289579391479</v>
       </c>
       <c r="G672" t="n">
-        <v>7.01729869842529</v>
+        <v>7.01729822158813</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>13.6301555633545</v>
       </c>
       <c r="G673" t="n">
-        <v>7.12243461608887</v>
+        <v>7.12243509292603</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>13.318868637085</v>
       </c>
       <c r="G675" t="n">
-        <v>6.95977163314819</v>
+        <v>6.95977210998535</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>13.7516326904297</v>
       </c>
       <c r="G676" t="n">
-        <v>7.18591260910034</v>
+        <v>7.18591213226318</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>14.2280530929565</v>
       </c>
       <c r="G677" t="n">
-        <v>7.4348669052124</v>
+        <v>7.43486595153809</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>14.2128677368164</v>
       </c>
       <c r="G678" t="n">
-        <v>7.42693185806274</v>
+        <v>7.42693090438843</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>14.0875940322876</v>
       </c>
       <c r="G680" t="n">
-        <v>7.36146879196167</v>
+        <v>7.36146926879883</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>13.8180656433105</v>
       </c>
       <c r="G681" t="n">
-        <v>7.22062587738037</v>
+        <v>7.220627784729</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>14.1483325958252</v>
       </c>
       <c r="G683" t="n">
-        <v>7.39320802688599</v>
+        <v>7.39320755004883</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>13.8294553756714</v>
       </c>
       <c r="G684" t="n">
-        <v>7.22657918930054</v>
+        <v>7.22657871246338</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>13.6662187576294</v>
       </c>
       <c r="G685" t="n">
-        <v>7.14127969741821</v>
+        <v>7.14127922058105</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>13.6757097244263</v>
       </c>
       <c r="G686" t="n">
-        <v>7.14623928070068</v>
+        <v>7.14623975753784</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>13.808575630188</v>
       </c>
       <c r="G687" t="n">
-        <v>7.21566772460938</v>
+        <v>7.21566867828369</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>14.3191614151001</v>
       </c>
       <c r="G689" t="n">
-        <v>7.48247480392456</v>
+        <v>7.48247575759888</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>14.2147655487061</v>
       </c>
       <c r="G691" t="n">
-        <v>7.42792272567749</v>
+        <v>7.42792367935181</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>14.2717094421387</v>
       </c>
       <c r="G692" t="n">
-        <v>7.45767784118652</v>
+        <v>7.457679271698</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>14.3210592269897</v>
       </c>
       <c r="G693" t="n">
-        <v>7.48346662521362</v>
+        <v>7.48346567153931</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>14.5810966491699</v>
       </c>
       <c r="G694" t="n">
-        <v>7.61934995651245</v>
+        <v>7.61934852600098</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>14.7993774414062</v>
       </c>
       <c r="G695" t="n">
-        <v>7.73341083526611</v>
+        <v>7.73341178894043</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>14.6247529983521</v>
       </c>
       <c r="G697" t="n">
-        <v>7.64216184616089</v>
+        <v>7.64216136932373</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>14.6741027832031</v>
       </c>
       <c r="G700" t="n">
-        <v>7.66794967651367</v>
+        <v>7.66794919967651</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>14.3723068237305</v>
       </c>
       <c r="G701" t="n">
-        <v>7.51024675369263</v>
+        <v>7.51024532318115</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>14.7025737762451</v>
       </c>
       <c r="G702" t="n">
-        <v>7.68282699584961</v>
+        <v>7.68282651901245</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>14.7234525680542</v>
       </c>
       <c r="G703" t="n">
-        <v>7.6937370300293</v>
+        <v>7.69373750686646</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>14.6209564208984</v>
       </c>
       <c r="G704" t="n">
-        <v>7.64017868041992</v>
+        <v>7.64017772674561</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>14.5013771057129</v>
       </c>
       <c r="G705" t="n">
-        <v>7.57769203186035</v>
+        <v>7.57769155502319</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>14.0553274154663</v>
       </c>
       <c r="G707" t="n">
-        <v>7.34460830688477</v>
+        <v>7.34460878372192</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>14.2033777236938</v>
       </c>
       <c r="G708" t="n">
-        <v>7.42197275161743</v>
+        <v>7.42197179794312</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>13.4156723022461</v>
       </c>
       <c r="G709" t="n">
-        <v>7.01035737991333</v>
+        <v>7.01035642623901</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>13.3245639801025</v>
       </c>
       <c r="G710" t="n">
-        <v>6.9627480506897</v>
+        <v>6.96274757385254</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>13.2581310272217</v>
       </c>
       <c r="G711" t="n">
-        <v>6.92803382873535</v>
+        <v>6.92803478240967</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>13.2922964096069</v>
       </c>
       <c r="G712" t="n">
-        <v>6.94588613510132</v>
+        <v>6.94588708877563</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>13.7364482879639</v>
       </c>
       <c r="G713" t="n">
-        <v>7.17797803878784</v>
+        <v>7.177978515625</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>13.1613283157349</v>
       </c>
       <c r="G714" t="n">
-        <v>6.87744903564453</v>
+        <v>6.87744951248169</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>13.0626277923584</v>
       </c>
       <c r="G715" t="n">
-        <v>6.82587337493896</v>
+        <v>6.82587385177612</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>12.7570362091064</v>
       </c>
       <c r="G716" t="n">
-        <v>6.66618633270264</v>
+        <v>6.66618680953979</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>13.4156723022461</v>
       </c>
       <c r="G720" t="n">
-        <v>7.01035737991333</v>
+        <v>7.01035642623901</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>13.2581310272217</v>
       </c>
       <c r="G721" t="n">
-        <v>6.92803382873535</v>
+        <v>6.92803478240967</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>13.4859008789062</v>
       </c>
       <c r="G722" t="n">
-        <v>7.04705381393433</v>
+        <v>7.0470552444458</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>12.7646284103394</v>
       </c>
       <c r="G724" t="n">
-        <v>6.67015409469604</v>
+        <v>6.6701545715332</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>13.4517345428467</v>
       </c>
       <c r="G726" t="n">
-        <v>7.02920198440552</v>
+        <v>7.02920150756836</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>13.8958883285522</v>
       </c>
       <c r="G729" t="n">
-        <v>7.26129388809204</v>
+        <v>7.26129341125488</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>13.9452381134033</v>
       </c>
       <c r="G730" t="n">
-        <v>7.28708124160767</v>
+        <v>7.28708076477051</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>13.5618238449097</v>
       </c>
       <c r="G731" t="n">
-        <v>7.08672761917114</v>
+        <v>7.08672714233398</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>13.4289579391479</v>
       </c>
       <c r="G732" t="n">
-        <v>7.01729869842529</v>
+        <v>7.01729822158813</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>13.83704662323</v>
       </c>
       <c r="G734" t="n">
-        <v>7.23054599761963</v>
+        <v>7.23054647445679</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>13.6301555633545</v>
       </c>
       <c r="G736" t="n">
-        <v>7.12243461608887</v>
+        <v>7.12243509292603</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>13.641544342041</v>
       </c>
       <c r="G737" t="n">
-        <v>7.12838649749756</v>
+        <v>7.12838554382324</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>13.2866020202637</v>
       </c>
       <c r="G738" t="n">
-        <v>6.94291019439697</v>
+        <v>6.94291114807129</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>13.4194679260254</v>
       </c>
       <c r="G739" t="n">
-        <v>7.01233959197998</v>
+        <v>7.01234006881714</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>13.261926651001</v>
       </c>
       <c r="G740" t="n">
-        <v>6.93001747131348</v>
+        <v>6.93001699447632</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>13.3777103424072</v>
       </c>
       <c r="G741" t="n">
-        <v>6.99052047729492</v>
+        <v>6.99051952362061</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>14.0439376831055</v>
       </c>
       <c r="G742" t="n">
-        <v>7.33865690231323</v>
+        <v>7.33865547180176</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>13.8541297912598</v>
       </c>
       <c r="G744" t="n">
-        <v>7.23947334289551</v>
+        <v>7.23947286605835</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>13.8294553756714</v>
       </c>
       <c r="G746" t="n">
-        <v>7.22657918930054</v>
+        <v>7.22657871246338</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>14.0629186630249</v>
       </c>
       <c r="G748" t="n">
-        <v>7.3485746383667</v>
+        <v>7.34857606887817</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>13.8446388244629</v>
       </c>
       <c r="G749" t="n">
-        <v>7.2345142364502</v>
+        <v>7.23451280593872</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>13.0607299804688</v>
       </c>
       <c r="G751" t="n">
-        <v>6.8248815536499</v>
+        <v>6.82488203048706</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>12.6507425308228</v>
       </c>
       <c r="G752" t="n">
-        <v>6.61064291000366</v>
+        <v>6.61064195632935</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>12.9810104370117</v>
       </c>
       <c r="G753" t="n">
-        <v>6.7832236289978</v>
+        <v>6.78322458267212</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>13.2353544235229</v>
       </c>
       <c r="G754" t="n">
-        <v>6.9161319732666</v>
+        <v>6.91613149642944</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>13.2467422485352</v>
       </c>
       <c r="G755" t="n">
-        <v>6.92208290100098</v>
+        <v>6.92208194732666</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>13.1442451477051</v>
       </c>
       <c r="G756" t="n">
-        <v>6.86852264404297</v>
+        <v>6.86852216720581</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>13.0683221817017</v>
       </c>
       <c r="G757" t="n">
-        <v>6.82884883880615</v>
+        <v>6.82884836196899</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>13.0569343566895</v>
       </c>
       <c r="G758" t="n">
-        <v>6.82289791107178</v>
+        <v>6.82289886474609</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>13.261926651001</v>
       </c>
       <c r="G759" t="n">
-        <v>6.93001747131348</v>
+        <v>6.93001699447632</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>12.8652267456055</v>
       </c>
       <c r="G760" t="n">
-        <v>6.72272253036499</v>
+        <v>6.72272157669067</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>12.4552402496338</v>
       </c>
       <c r="G761" t="n">
-        <v>6.50848293304443</v>
+        <v>6.50848340988159</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>12.0357627868652</v>
       </c>
       <c r="G763" t="n">
-        <v>6.28928518295288</v>
+        <v>6.28928565979004</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>11.9256744384766</v>
       </c>
       <c r="G764" t="n">
-        <v>6.2317590713501</v>
+        <v>6.23175811767578</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>11.783317565918</v>
       </c>
       <c r="G765" t="n">
-        <v>6.15736961364746</v>
+        <v>6.1573691368103</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>12.5368576049805</v>
       </c>
       <c r="G767" t="n">
-        <v>6.55113220214844</v>
+        <v>6.55113172531128</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>12.6849088668823</v>
       </c>
       <c r="G768" t="n">
-        <v>6.6284966468811</v>
+        <v>6.62849617004395</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>13.0569343566895</v>
       </c>
       <c r="G769" t="n">
-        <v>6.82289791107178</v>
+        <v>6.82289886474609</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>13.4877986907959</v>
       </c>
       <c r="G771" t="n">
-        <v>7.04804611206055</v>
+        <v>7.04804658889771</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>13.4175701141357</v>
       </c>
       <c r="G772" t="n">
-        <v>7.01134824752808</v>
+        <v>7.01134872436523</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>13.7022829055786</v>
       </c>
       <c r="G773" t="n">
-        <v>7.16012477874756</v>
+        <v>7.16012525558472</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>13.998384475708</v>
       </c>
       <c r="G776" t="n">
-        <v>7.31485271453857</v>
+        <v>7.31485176086426</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>14.0097732543945</v>
       </c>
       <c r="G777" t="n">
-        <v>7.32080411911011</v>
+        <v>7.32080459594727</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>13.808575630188</v>
       </c>
       <c r="G780" t="n">
-        <v>7.21566772460938</v>
+        <v>7.21566867828369</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>13.7535314559937</v>
       </c>
       <c r="G782" t="n">
-        <v>7.1869044303894</v>
+        <v>7.18690538406372</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>13.7592248916626</v>
       </c>
       <c r="G783" t="n">
-        <v>7.18987941741943</v>
+        <v>7.18988084793091</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>13.9414415359497</v>
       </c>
       <c r="G784" t="n">
-        <v>7.28509759902954</v>
+        <v>7.2850980758667</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>14.1578226089478</v>
       </c>
       <c r="G785" t="n">
-        <v>7.39816761016846</v>
+        <v>7.39816665649414</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>14.3020782470703</v>
       </c>
       <c r="G786" t="n">
-        <v>7.47354793548584</v>
+        <v>7.47354698181152</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>14.0648174285889</v>
       </c>
       <c r="G787" t="n">
-        <v>7.34956741333008</v>
+        <v>7.34956693649292</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>14.4045753479004</v>
       </c>
       <c r="G788" t="n">
-        <v>7.52710771560669</v>
+        <v>7.52710723876953</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>12.6981954574585</v>
       </c>
       <c r="G790" t="n">
-        <v>6.63543844223022</v>
+        <v>6.63543891906738</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>12.2616348266602</v>
       </c>
       <c r="G795" t="n">
-        <v>6.40731525421143</v>
+        <v>6.40731382369995</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>12.3622341156006</v>
       </c>
       <c r="G796" t="n">
-        <v>6.45988368988037</v>
+        <v>6.45988273620605</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>12.3413553237915</v>
       </c>
       <c r="G797" t="n">
-        <v>6.44897127151489</v>
+        <v>6.44897222518921</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>12.3470487594604</v>
       </c>
       <c r="G798" t="n">
-        <v>6.45194721221924</v>
+        <v>6.4519476890564</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>12.5862083435059</v>
       </c>
       <c r="G799" t="n">
-        <v>6.57692050933838</v>
+        <v>6.57692003250122</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>12.4609346389771</v>
       </c>
       <c r="G801" t="n">
-        <v>6.51145887374878</v>
+        <v>6.51145839691162</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>12.5273675918579</v>
       </c>
       <c r="G802" t="n">
-        <v>6.54617309570312</v>
+        <v>6.54617357254028</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>12.3546419143677</v>
       </c>
       <c r="G804" t="n">
-        <v>6.45591497421265</v>
+        <v>6.4559154510498</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>12.3204755783081</v>
       </c>
       <c r="G805" t="n">
-        <v>6.43806171417236</v>
+        <v>6.43806219100952</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>12.271125793457</v>
       </c>
       <c r="G806" t="n">
-        <v>6.4122748374939</v>
+        <v>6.41227388381958</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>12.1762218475342</v>
       </c>
       <c r="G807" t="n">
-        <v>6.3626823425293</v>
+        <v>6.36268186569214</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>12.2768201828003</v>
       </c>
       <c r="G808" t="n">
-        <v>6.41524982452393</v>
+        <v>6.41525030136108</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>12.7247676849365</v>
       </c>
       <c r="G809" t="n">
-        <v>6.64932489395142</v>
+        <v>6.64932441711426</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>12.1078910827637</v>
       </c>
       <c r="G811" t="n">
-        <v>6.32697534561157</v>
+        <v>6.32697629928589</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>12.1838140487671</v>
       </c>
       <c r="G812" t="n">
-        <v>6.36664867401123</v>
+        <v>6.36664962768555</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>12.168628692627</v>
       </c>
       <c r="G813" t="n">
-        <v>6.35871315002441</v>
+        <v>6.35871362686157</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>12.0642347335815</v>
       </c>
       <c r="G814" t="n">
-        <v>6.30416393280029</v>
+        <v>6.30416345596313</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.7000932693481</v>
       </c>
       <c r="G818" t="n">
-        <v>6.63643074035645</v>
+        <v>6.63643169403076</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>12.38121509552</v>
       </c>
       <c r="G819" t="n">
-        <v>6.46980142593384</v>
+        <v>6.46980237960815</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>12.4324626922607</v>
       </c>
       <c r="G820" t="n">
-        <v>6.49658107757568</v>
+        <v>6.49658012390137</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>12.3698263168335</v>
       </c>
       <c r="G822" t="n">
-        <v>6.46384954452515</v>
+        <v>6.46385049819946</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>12.4229726791382</v>
       </c>
       <c r="G823" t="n">
-        <v>6.49162197113037</v>
+        <v>6.49162149429321</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>12.7475461959839</v>
       </c>
       <c r="G824" t="n">
-        <v>6.66122722625732</v>
+        <v>6.66122770309448</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>12.8974943161011</v>
       </c>
       <c r="G827" t="n">
-        <v>6.73958301544189</v>
+        <v>6.73958349227905</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>13.0246658325195</v>
       </c>
       <c r="G828" t="n">
-        <v>6.80603647232056</v>
+        <v>6.80603551864624</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>13.0303602218628</v>
       </c>
       <c r="G830" t="n">
-        <v>6.8090124130249</v>
+        <v>6.80901288986206</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>13.0322580337524</v>
       </c>
       <c r="G831" t="n">
-        <v>6.81000471115112</v>
+        <v>6.81000423431396</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>13.2790098190308</v>
       </c>
       <c r="G832" t="n">
-        <v>6.93894386291504</v>
+        <v>6.93894338607788</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>13.1879005432129</v>
       </c>
       <c r="G834" t="n">
-        <v>6.89133548736572</v>
+        <v>6.89133405685425</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>13.1898002624512</v>
       </c>
       <c r="G835" t="n">
-        <v>6.89232683181763</v>
+        <v>6.89232778549194</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>13.5751113891602</v>
       </c>
       <c r="G837" t="n">
-        <v>7.09367179870605</v>
+        <v>7.09367084503174</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>13.7136707305908</v>
       </c>
       <c r="G838" t="n">
-        <v>7.16607522964478</v>
+        <v>7.16607666015625</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>13.9566259384155</v>
       </c>
       <c r="G839" t="n">
-        <v>7.29303216934204</v>
+        <v>7.29303121566772</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>13.2884998321533</v>
       </c>
       <c r="G841" t="n">
-        <v>7.28431081771851</v>
+        <v>7.28431129455566</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>13.0322580337524</v>
       </c>
       <c r="G843" t="n">
-        <v>7.14384841918945</v>
+        <v>7.14384889602661</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>13.1195697784424</v>
       </c>
       <c r="G845" t="n">
-        <v>7.19171047210693</v>
+        <v>7.19170999526978</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>12.8595333099365</v>
       </c>
       <c r="G847" t="n">
-        <v>7.04916620254517</v>
+        <v>7.04916667938232</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>12.9012899398804</v>
       </c>
       <c r="G851" t="n">
-        <v>7.07205629348755</v>
+        <v>7.07205581665039</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>12.2920045852661</v>
       </c>
       <c r="G853" t="n">
-        <v>6.73806667327881</v>
+        <v>6.73806619644165</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>12.0604381561279</v>
       </c>
       <c r="G854" t="n">
-        <v>6.61112928390503</v>
+        <v>6.61112976074219</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>12.4305648803711</v>
       </c>
       <c r="G856" t="n">
-        <v>6.81402063369751</v>
+        <v>6.81402015686035</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>12.5691251754761</v>
       </c>
       <c r="G857" t="n">
-        <v>6.88997459411621</v>
+        <v>6.88997411727905</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>12.686806678772</v>
       </c>
       <c r="G858" t="n">
-        <v>6.95448350906372</v>
+        <v>6.95448398590088</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>11.2708349227905</v>
       </c>
       <c r="G860" t="n">
-        <v>6.88365364074707</v>
+        <v>6.88365459442139</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>11.177827835083</v>
       </c>
       <c r="G861" t="n">
-        <v>6.82684993743896</v>
+        <v>6.82685041427612</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>11.7396621704102</v>
       </c>
       <c r="G864" t="n">
-        <v>7.16999053955078</v>
+        <v>7.16998958587646</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>11.6352672576904</v>
       </c>
       <c r="G865" t="n">
-        <v>7.10623073577881</v>
+        <v>7.10623025894165</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>11.398006439209</v>
       </c>
       <c r="G867" t="n">
-        <v>6.96132326126099</v>
+        <v>6.96132278442383</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>10.794415473938</v>
       </c>
       <c r="G869" t="n">
-        <v>6.59268188476562</v>
+        <v>6.59268093109131</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>11.2119941711426</v>
       </c>
       <c r="G870" t="n">
-        <v>6.84771680831909</v>
+        <v>6.84771728515625</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>11.1038026809692</v>
       </c>
       <c r="G871" t="n">
-        <v>6.78163909912109</v>
+        <v>6.78163862228394</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>11.0753316879272</v>
       </c>
       <c r="G873" t="n">
-        <v>6.7642502784729</v>
+        <v>6.76425123214722</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>11.2670383453369</v>
       </c>
       <c r="G874" t="n">
-        <v>6.88133573532104</v>
+        <v>6.88133478164673</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>11.3733310699463</v>
       </c>
       <c r="G875" t="n">
-        <v>6.94625425338745</v>
+        <v>6.94625329971313</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>11.2898149490356</v>
       </c>
       <c r="G877" t="n">
-        <v>6.89524507522583</v>
+        <v>6.89524555206299</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>11.3372678756714</v>
       </c>
       <c r="G879" t="n">
-        <v>6.92422771453857</v>
+        <v>6.92422819137573</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>11.4378662109375</v>
       </c>
       <c r="G880" t="n">
-        <v>6.98566770553589</v>
+        <v>6.98566818237305</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>11.5669355392456</v>
       </c>
       <c r="G881" t="n">
-        <v>7.06449747085571</v>
+        <v>7.0644965171814</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>11.7073936462402</v>
       </c>
       <c r="G882" t="n">
-        <v>7.15028190612793</v>
+        <v>7.15028095245361</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>11.7187833786011</v>
       </c>
       <c r="G889" t="n">
-        <v>7.15723848342896</v>
+        <v>7.15723752975464</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>12.0395593643188</v>
       </c>
       <c r="G892" t="n">
-        <v>7.35315275192261</v>
+        <v>7.35315179824829</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>11.9940052032471</v>
       </c>
       <c r="G893" t="n">
-        <v>7.32532930374146</v>
+        <v>7.32532978057861</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>11.9351654052734</v>
       </c>
       <c r="G894" t="n">
-        <v>7.28939247131348</v>
+        <v>7.28939390182495</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>11.8041973114014</v>
       </c>
       <c r="G895" t="n">
-        <v>7.20940399169922</v>
+        <v>7.20940494537354</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>11.7966041564941</v>
       </c>
       <c r="G896" t="n">
-        <v>7.20476627349854</v>
+        <v>7.20476722717285</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>11.7073936462402</v>
       </c>
       <c r="G897" t="n">
-        <v>7.15028190612793</v>
+        <v>7.15028095245361</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>11.9313688278198</v>
       </c>
       <c r="G898" t="n">
-        <v>7.28707408905029</v>
+        <v>7.28707456588745</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>11.5669355392456</v>
       </c>
       <c r="G901" t="n">
-        <v>7.06449747085571</v>
+        <v>7.0644965171814</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>11.5840187072754</v>
       </c>
       <c r="G902" t="n">
-        <v>7.07493019104004</v>
+        <v>7.0749306678772</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>11.3942098617554</v>
       </c>
       <c r="G903" t="n">
-        <v>6.95900678634644</v>
+        <v>6.95900535583496</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>11.398006439209</v>
       </c>
       <c r="G904" t="n">
-        <v>6.96132326126099</v>
+        <v>6.96132278442383</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>11.971227645874</v>
       </c>
       <c r="G906" t="n">
-        <v>7.3114185333252</v>
+        <v>7.31141805648804</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>11.7187833786011</v>
       </c>
       <c r="G908" t="n">
-        <v>7.15723848342896</v>
+        <v>7.15723752975464</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>11.6048984527588</v>
       </c>
       <c r="G909" t="n">
-        <v>7.08768320083618</v>
+        <v>7.08768272399902</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>11.1038026809692</v>
       </c>
       <c r="G910" t="n">
-        <v>6.78163909912109</v>
+        <v>6.78163862228394</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.4226808547974</v>
       </c>
       <c r="G911" t="n">
-        <v>6.97639322280884</v>
+        <v>6.976393699646</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>11.4587450027466</v>
       </c>
       <c r="G912" t="n">
-        <v>6.99841976165771</v>
+        <v>6.99841928482056</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>11.0772304534912</v>
       </c>
       <c r="G914" t="n">
-        <v>6.76541042327881</v>
+        <v>6.76540994644165</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>11.1038026809692</v>
       </c>
       <c r="G916" t="n">
-        <v>6.78163909912109</v>
+        <v>6.78163862228394</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>11.2461585998535</v>
       </c>
       <c r="G917" t="n">
-        <v>6.8685827255249</v>
+        <v>6.86858320236206</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>11.0145931243896</v>
       </c>
       <c r="G918" t="n">
-        <v>6.72715377807617</v>
+        <v>6.72715425491333</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>11.0088987350464</v>
       </c>
       <c r="G919" t="n">
-        <v>6.7236762046814</v>
+        <v>6.72367668151855</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>11.1759300231934</v>
       </c>
       <c r="G920" t="n">
-        <v>6.82569122314453</v>
+        <v>6.82569026947021</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>10.7830257415771</v>
       </c>
       <c r="G921" t="n">
-        <v>6.58572435379028</v>
+        <v>6.5857253074646</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>10.4907207489014</v>
       </c>
       <c r="G922" t="n">
-        <v>6.40719985961914</v>
+        <v>6.40719938278198</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>10.6862239837646</v>
       </c>
       <c r="G923" t="n">
-        <v>6.52660274505615</v>
+        <v>6.52660322189331</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>10.5875244140625</v>
       </c>
       <c r="G924" t="n">
-        <v>6.46632289886475</v>
+        <v>6.46632194519043</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>10.9405679702759</v>
       </c>
       <c r="G925" t="n">
-        <v>6.68194341659546</v>
+        <v>6.68194389343262</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>10.9538536071777</v>
       </c>
       <c r="G926" t="n">
-        <v>6.69005823135376</v>
+        <v>6.6900577545166</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>10.7165927886963</v>
       </c>
       <c r="G927" t="n">
-        <v>6.54515075683594</v>
+        <v>6.5451512336731</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>11.0088987350464</v>
       </c>
       <c r="G929" t="n">
-        <v>6.7236762046814</v>
+        <v>6.72367668151855</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>11.0430641174316</v>
       </c>
       <c r="G930" t="n">
-        <v>6.74454355239868</v>
+        <v>6.74454307556152</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>11.1417646408081</v>
       </c>
       <c r="G931" t="n">
-        <v>6.80482482910156</v>
+        <v>6.80482387542725</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>11.3372678756714</v>
       </c>
       <c r="G934" t="n">
-        <v>6.92422771453857</v>
+        <v>6.92422819137573</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>11.5973052978516</v>
       </c>
       <c r="G935" t="n">
-        <v>7.08304595947266</v>
+        <v>7.0830454826355</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>11.9370632171631</v>
       </c>
       <c r="G936" t="n">
-        <v>7.29055213928223</v>
+        <v>7.29055309295654</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>11.9617376327515</v>
       </c>
       <c r="G937" t="n">
-        <v>7.30562210083008</v>
+        <v>7.30562353134155</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>12.0718269348145</v>
       </c>
       <c r="G938" t="n">
-        <v>7.37285804748535</v>
+        <v>7.37285900115967</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>11.9237756729126</v>
       </c>
       <c r="G939" t="n">
-        <v>7.28243637084961</v>
+        <v>7.28243732452393</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>11.9313688278198</v>
       </c>
       <c r="G941" t="n">
-        <v>7.28707408905029</v>
+        <v>7.28707456588745</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>11.7681331634521</v>
       </c>
       <c r="G946" t="n">
-        <v>7.18737936019897</v>
+        <v>7.18737840652466</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>11.7073936462402</v>
       </c>
       <c r="G947" t="n">
-        <v>7.15028190612793</v>
+        <v>7.15028095245361</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>11.5764255523682</v>
       </c>
       <c r="G948" t="n">
-        <v>7.07029342651367</v>
+        <v>7.07029294967651</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>11.341064453125</v>
       </c>
       <c r="G949" t="n">
-        <v>6.92654657363892</v>
+        <v>6.92654705047607</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>11.208197593689</v>
       </c>
       <c r="G951" t="n">
-        <v>6.84539842605591</v>
+        <v>6.84539890289307</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>11.2613439559937</v>
       </c>
       <c r="G952" t="n">
-        <v>6.87785625457764</v>
+        <v>6.87785673141479</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>11.2670383453369</v>
       </c>
       <c r="G953" t="n">
-        <v>6.88133573532104</v>
+        <v>6.88133478164673</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>10.6577529907227</v>
       </c>
       <c r="G959" t="n">
-        <v>6.50921535491943</v>
+        <v>6.50921440124512</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>10.7222881317139</v>
       </c>
       <c r="G960" t="n">
-        <v>6.54862976074219</v>
+        <v>6.54862880706787</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>11.2575483322144</v>
       </c>
       <c r="G962" t="n">
-        <v>6.87553930282593</v>
+        <v>6.87553977966309</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>11.3277769088745</v>
       </c>
       <c r="G963" t="n">
-        <v>6.91843175888062</v>
+        <v>6.91843128204346</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>11.4587450027466</v>
       </c>
       <c r="G964" t="n">
-        <v>6.99841976165771</v>
+        <v>6.99841928482056</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>11.2518539428711</v>
       </c>
       <c r="G967" t="n">
-        <v>6.87206125259399</v>
+        <v>6.87206077575684</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>11.2537517547607</v>
       </c>
       <c r="G971" t="n">
-        <v>6.87321996688843</v>
+        <v>6.87321949005127</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>11.2442607879639</v>
       </c>
       <c r="G972" t="n">
-        <v>6.86742448806763</v>
+        <v>6.86742401123047</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>11.3031015396118</v>
       </c>
       <c r="G973" t="n">
-        <v>6.90336132049561</v>
+        <v>6.90336084365845</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>12.2141828536987</v>
       </c>
       <c r="G975" t="n">
-        <v>7.45980215072632</v>
+        <v>7.45980310440063</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>13.2182712554932</v>
       </c>
       <c r="G976" t="n">
-        <v>8.0730504989624</v>
+        <v>8.07304954528809</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>13.7136707305908</v>
       </c>
       <c r="G979" t="n">
-        <v>8.37561511993408</v>
+        <v>8.37561416625977</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>13.721263885498</v>
       </c>
       <c r="G980" t="n">
-        <v>8.38025188446045</v>
+        <v>8.38025093078613</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>13.7649202346802</v>
       </c>
       <c r="G981" t="n">
-        <v>8.40691471099854</v>
+        <v>8.40691375732422</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>13.7706136703491</v>
       </c>
       <c r="G983" t="n">
-        <v>8.41039085388184</v>
+        <v>8.41039180755615</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>13.7763080596924</v>
       </c>
       <c r="G985" t="n">
-        <v>8.41386890411377</v>
+        <v>8.41386985778809</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>13.7895946502686</v>
       </c>
       <c r="G987" t="n">
-        <v>8.4219856262207</v>
+        <v>8.42198467254639</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>13.256233215332</v>
       </c>
       <c r="G990" t="n">
-        <v>8.09623336791992</v>
+        <v>8.09623432159424</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>12.7551383972168</v>
       </c>
       <c r="G991" t="n">
-        <v>7.79019165039062</v>
+        <v>7.79019069671631</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>12.8974943161011</v>
       </c>
       <c r="G994" t="n">
-        <v>7.87713575363159</v>
+        <v>7.87713479995728</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>12.9202709197998</v>
       </c>
       <c r="G995" t="n">
-        <v>7.89104652404785</v>
+        <v>7.89104461669922</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>12.8044881820679</v>
       </c>
       <c r="G996" t="n">
-        <v>7.82033157348633</v>
+        <v>7.82033252716064</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>12.7361574172974</v>
       </c>
       <c r="G997" t="n">
-        <v>7.77859878540039</v>
+        <v>7.77859783172607</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>12.6146793365479</v>
       </c>
       <c r="G998" t="n">
-        <v>7.70440626144409</v>
+        <v>7.70440578460693</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>12.5292663574219</v>
       </c>
       <c r="G999" t="n">
-        <v>7.65223932266235</v>
+        <v>7.65224027633667</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>12.686806678772</v>
       </c>
       <c r="G1000" t="n">
-        <v>7.74845743179321</v>
+        <v>7.74845838546753</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>12.5786161422729</v>
       </c>
       <c r="G1001" t="n">
-        <v>7.68238067626953</v>
+        <v>7.68237924575806</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>12.4780168533325</v>
       </c>
       <c r="G1003" t="n">
-        <v>7.62093877792358</v>
+        <v>7.62093925476074</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>12.409686088562</v>
       </c>
       <c r="G1004" t="n">
-        <v>7.5792064666748</v>
+        <v>7.57920694351196</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>12.2198781967163</v>
       </c>
       <c r="G1005" t="n">
-        <v>7.46328115463257</v>
+        <v>7.46328163146973</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>12.7836093902588</v>
       </c>
       <c r="G1008" t="n">
-        <v>7.8075795173645</v>
+        <v>7.80757999420166</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>12.9107809066772</v>
       </c>
       <c r="G1010" t="n">
-        <v>7.8852481842041</v>
+        <v>7.88525009155273</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>12.817774772644</v>
       </c>
       <c r="G1013" t="n">
-        <v>7.82844638824463</v>
+        <v>7.82844686508179</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>12.7456474304199</v>
       </c>
       <c r="G1014" t="n">
-        <v>7.78439474105835</v>
+        <v>7.78439426422119</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>12.6754179000854</v>
       </c>
       <c r="G1016" t="n">
-        <v>7.74150276184082</v>
+        <v>7.74150228500366</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>12.4115839004517</v>
       </c>
       <c r="G1017" t="n">
-        <v>7.58036518096924</v>
+        <v>7.5803656578064</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>12.242654800415</v>
       </c>
       <c r="G1018" t="n">
-        <v>7.47719287872314</v>
+        <v>7.47719144821167</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>12.299596786499</v>
       </c>
       <c r="G1019" t="n">
-        <v>7.51197004318237</v>
+        <v>7.51196908950806</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>12.1781196594238</v>
       </c>
       <c r="G1021" t="n">
-        <v>7.43777656555176</v>
+        <v>7.43777751922607</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>12.1762218475342</v>
       </c>
       <c r="G1022" t="n">
-        <v>7.4366192817688</v>
+        <v>7.43661880493164</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>12.1002979278564</v>
       </c>
       <c r="G1023" t="n">
-        <v>7.39024829864502</v>
+        <v>7.39024877548218</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>12.0642347335815</v>
       </c>
       <c r="G1024" t="n">
-        <v>7.3682222366333</v>
+        <v>7.36822128295898</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>11.8364639282227</v>
       </c>
       <c r="G1025" t="n">
-        <v>7.2291111946106</v>
+        <v>7.22911167144775</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>11.7985019683838</v>
       </c>
       <c r="G1027" t="n">
-        <v>7.20592594146729</v>
+        <v>7.20592641830444</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>11.8231782913208</v>
       </c>
       <c r="G1028" t="n">
-        <v>7.22099733352661</v>
+        <v>7.22099637985229</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>11.7017002105713</v>
       </c>
       <c r="G1029" t="n">
-        <v>7.14680480957031</v>
+        <v>7.14680433273315</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>11.5973052978516</v>
       </c>
       <c r="G1030" t="n">
-        <v>7.08304595947266</v>
+        <v>7.0830454826355</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>11.4321718215942</v>
       </c>
       <c r="G1031" t="n">
-        <v>6.98218965530396</v>
+        <v>6.98219013214111</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>11.5232801437378</v>
       </c>
       <c r="G1032" t="n">
-        <v>7.03783369064331</v>
+        <v>7.03783464431763</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>11.2518539428711</v>
       </c>
       <c r="G1033" t="n">
-        <v>6.87206125259399</v>
+        <v>6.87206077575684</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>11.4018020629883</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.96364116668701</v>
+        <v>6.96364164352417</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>11.318286895752</v>
       </c>
       <c r="G1036" t="n">
-        <v>6.9126353263855</v>
+        <v>6.91263484954834</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>11.1341724395752</v>
       </c>
       <c r="G1037" t="n">
-        <v>6.80018758773804</v>
+        <v>6.80018711090088</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>11.398006439209</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.96132326126099</v>
+        <v>6.96132278442383</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>11.777624130249</v>
       </c>
       <c r="G1041" t="n">
-        <v>7.19317483901978</v>
+        <v>7.19317579269409</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>11.3733310699463</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.94625425338745</v>
+        <v>6.94625329971313</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>11.5137901306152</v>
       </c>
       <c r="G1044" t="n">
-        <v>7.03203821182251</v>
+        <v>7.03203868865967</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>11.942756652832</v>
       </c>
       <c r="G1045" t="n">
-        <v>7.29403066635132</v>
+        <v>7.29403018951416</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>11.7985019683838</v>
       </c>
       <c r="G1046" t="n">
-        <v>7.20592594146729</v>
+        <v>7.20592641830444</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>11.6922101974487</v>
       </c>
       <c r="G1048" t="n">
-        <v>7.14100885391235</v>
+        <v>7.1410083770752</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>11.5840187072754</v>
       </c>
       <c r="G1049" t="n">
-        <v>7.07493019104004</v>
+        <v>7.0749306678772</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>11.6504516601562</v>
       </c>
       <c r="G1051" t="n">
-        <v>7.1155047416687</v>
+        <v>7.11550426483154</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>11.4644393920898</v>
       </c>
       <c r="G1052" t="n">
-        <v>7.00189828872681</v>
+        <v>7.00189781188965</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>10.7621469497681</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.57297277450562</v>
+        <v>6.57297372817993</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>10.684326171875</v>
       </c>
       <c r="G1054" t="n">
-        <v>6.52544355392456</v>
+        <v>6.52544450759888</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>11.1759300231934</v>
       </c>
       <c r="G1055" t="n">
-        <v>6.82569122314453</v>
+        <v>6.82569026947021</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>10.6691408157349</v>
       </c>
       <c r="G1057" t="n">
-        <v>6.51617002487183</v>
+        <v>6.51616954803467</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>10.2762365341187</v>
       </c>
       <c r="G1058" t="n">
-        <v>6.27620363235474</v>
+        <v>6.27620315551758</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>10.4318809509277</v>
       </c>
       <c r="G1060" t="n">
-        <v>6.37126302719116</v>
+        <v>6.37126350402832</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>10.2895240783691</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.2843189239502</v>
+        <v>6.28431940078735</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>9.98203372955322</v>
       </c>
       <c r="G1062" t="n">
-        <v>6.09651947021484</v>
+        <v>6.09651851654053</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>8.8526725769043</v>
       </c>
       <c r="G1064" t="n">
-        <v>5.40676307678223</v>
+        <v>5.40676259994507</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>7.4224648475647</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.53326463699341</v>
+        <v>4.53326511383057</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>7.95392894744873</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.85785579681396</v>
+        <v>4.85785627365112</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>5.8081431388855</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.54731917381287</v>
+        <v>3.54731893539429</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>5.83092021942139</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.56122994422913</v>
+        <v>3.56123042106628</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>5.5832200050354</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.40994715690613</v>
+        <v>3.40994739532471</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>6.48576021194458</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.96117305755615</v>
+        <v>3.96117353439331</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>6.53985500335693</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.99421119689941</v>
+        <v>3.99421072006226</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>6.23711013793945</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.8093101978302</v>
+        <v>3.80930995941162</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>6.00079917907715</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.66498374938965</v>
+        <v>3.66498398780823</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>5.88406610488892</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.59368968009949</v>
+        <v>3.59368872642517</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6.27886819839478</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.83481359481812</v>
+        <v>3.83481383323669</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>6.68505907058716</v>
       </c>
       <c r="G1084" t="n">
-        <v>4.08289480209351</v>
+        <v>4.08289432525635</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>7.07986116409302</v>
       </c>
       <c r="G1087" t="n">
-        <v>4.32401990890503</v>
+        <v>4.32402038574219</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>6.72017288208008</v>
       </c>
       <c r="G1088" t="n">
-        <v>4.10434055328369</v>
+        <v>4.10434103012085</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>6.74674606323242</v>
       </c>
       <c r="G1089" t="n">
-        <v>4.12057018280029</v>
+        <v>4.12056970596313</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>7.05138921737671</v>
       </c>
       <c r="G1091" t="n">
-        <v>4.30663013458252</v>
+        <v>4.30663108825684</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>6.73630714416504</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.11419486999512</v>
+        <v>4.1141939163208</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>6.88056087493896</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.20229721069336</v>
+        <v>4.20229768753052</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>6.97546577453613</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.26026010513306</v>
+        <v>4.26026105880737</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>7.60752820968628</v>
       </c>
       <c r="G1099" t="n">
-        <v>4.64629220962524</v>
+        <v>4.64629173278809</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>7.17856121063232</v>
       </c>
       <c r="G1100" t="n">
-        <v>4.38430023193359</v>
+        <v>4.38430070877075</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>7.23929977416992</v>
       </c>
       <c r="G1102" t="n">
-        <v>4.42139673233032</v>
+        <v>4.42139720916748</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>7.37406396865845</v>
       </c>
       <c r="G1104" t="n">
-        <v>4.50370311737061</v>
+        <v>4.50370407104492</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>7.20513391494751</v>
       </c>
       <c r="G1106" t="n">
-        <v>4.40053033828735</v>
+        <v>4.4005298614502</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>6.96502590179443</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.25388431549072</v>
+        <v>4.25388479232788</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>7.53065586090088</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.59934282302856</v>
+        <v>4.59934234619141</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>7.53729915618896</v>
       </c>
       <c r="G1119" t="n">
-        <v>4.6033992767334</v>
+        <v>4.60339975357056</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>7.80208206176758</v>
       </c>
       <c r="G1120" t="n">
-        <v>4.76511573791504</v>
+        <v>4.7651162147522</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>8.32120895385742</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.08217239379883</v>
+        <v>5.08217191696167</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>8.25952053070068</v>
       </c>
       <c r="G1123" t="n">
-        <v>5.04449558258057</v>
+        <v>5.04449605941772</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>8.83748817443848</v>
       </c>
       <c r="G1124" t="n">
-        <v>5.39748907089233</v>
+        <v>5.39748859405518</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>8.53569316864014</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.21316766738892</v>
+        <v>5.21316814422607</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>7.77835607528687</v>
       </c>
       <c r="G1130" t="n">
-        <v>4.75062465667725</v>
+        <v>4.75062417984009</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>7.97006320953369</v>
       </c>
       <c r="G1132" t="n">
-        <v>4.86771059036255</v>
+        <v>4.86771011352539</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>7.945387840271</v>
       </c>
       <c r="G1133" t="n">
-        <v>4.85264015197754</v>
+        <v>4.85263967514038</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>8.02225971221924</v>
       </c>
       <c r="G1134" t="n">
-        <v>4.89958906173706</v>
+        <v>4.8995885848999</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>8.1314001083374</v>
       </c>
       <c r="G1135" t="n">
-        <v>4.96624660491943</v>
+        <v>4.96624708175659</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>8.602126121521</v>
       </c>
       <c r="G1136" t="n">
-        <v>5.25374221801758</v>
+        <v>5.25374174118042</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>8.22345733642578</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.02246952056885</v>
+        <v>5.02247047424316</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>8.19498634338379</v>
       </c>
       <c r="G1139" t="n">
-        <v>5.00508117675781</v>
+        <v>5.00508165359497</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>8.37815093994141</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.11694955825806</v>
+        <v>5.11695003509521</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>8.48824024200439</v>
       </c>
       <c r="G1141" t="n">
-        <v>5.1841869354248</v>
+        <v>5.18418598175049</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>8.52525329589844</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.20679235458374</v>
+        <v>5.20679187774658</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>8.19118976593018</v>
       </c>
       <c r="G1148" t="n">
-        <v>5.00276327133179</v>
+        <v>5.00276279449463</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>8.70557117462158</v>
       </c>
       <c r="G1153" t="n">
-        <v>5.3169207572937</v>
+        <v>5.31692123413086</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>8.74637985229492</v>
       </c>
       <c r="G1155" t="n">
-        <v>5.34184503555298</v>
+        <v>5.34184455871582</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>8.76630973815918</v>
       </c>
       <c r="G1156" t="n">
-        <v>5.35401678085327</v>
+        <v>5.35401630401611</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>8.61066722869873</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.258957862854</v>
+        <v>5.25895833969116</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>8.80047607421875</v>
       </c>
       <c r="G1161" t="n">
-        <v>5.37488412857056</v>
+        <v>5.37488460540771</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>8.69038677215576</v>
       </c>
       <c r="G1162" t="n">
-        <v>5.30764722824097</v>
+        <v>5.30764675140381</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>8.57460308074951</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.2369327545166</v>
+        <v>5.23693227767944</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>8.8242015838623</v>
       </c>
       <c r="G1168" t="n">
-        <v>5.38937425613403</v>
+        <v>5.38937377929688</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>8.81186389923096</v>
       </c>
       <c r="G1169" t="n">
-        <v>5.38183975219727</v>
+        <v>5.38184022903442</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>8.96371078491211</v>
       </c>
       <c r="G1170" t="n">
-        <v>5.47457933425903</v>
+        <v>5.47457981109619</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>9.43633365631104</v>
       </c>
       <c r="G1171" t="n">
-        <v>5.76323366165161</v>
+        <v>5.76323318481445</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>9.40122032165527</v>
       </c>
       <c r="G1172" t="n">
-        <v>5.74178791046143</v>
+        <v>5.74178838729858</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>9.26265907287598</v>
       </c>
       <c r="G1173" t="n">
-        <v>5.65716218948364</v>
+        <v>5.65716171264648</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>9.19622611999512</v>
       </c>
       <c r="G1174" t="n">
-        <v>5.61658763885498</v>
+        <v>5.61658811569214</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>9.13643741607666</v>
       </c>
       <c r="G1180" t="n">
-        <v>5.58007287979126</v>
+        <v>5.5800724029541</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>9.08234119415283</v>
       </c>
       <c r="G1182" t="n">
-        <v>5.54703330993652</v>
+        <v>5.54703235626221</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>8.80617046356201</v>
       </c>
       <c r="G1188" t="n">
-        <v>5.37836217880249</v>
+        <v>5.37836170196533</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>8.95042419433594</v>
       </c>
       <c r="G1189" t="n">
-        <v>5.46646499633789</v>
+        <v>5.46646547317505</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>9.14402866363525</v>
       </c>
       <c r="G1190" t="n">
-        <v>5.58470869064331</v>
+        <v>5.58470821380615</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>9.38223934173584</v>
       </c>
       <c r="G1193" t="n">
-        <v>5.73019599914551</v>
+        <v>5.73019552230835</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>9.4742956161499</v>
       </c>
       <c r="G1195" t="n">
-        <v>5.78641891479492</v>
+        <v>5.78641939163208</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>10.2610530853271</v>
       </c>
       <c r="G1197" t="n">
-        <v>6.26693058013916</v>
+        <v>6.266930103302</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>10.2154989242554</v>
       </c>
       <c r="G1198" t="n">
-        <v>6.23910856246948</v>
+        <v>6.23910808563232</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>9.8491678237915</v>
       </c>
       <c r="G1199" t="n">
-        <v>6.01537227630615</v>
+        <v>6.01537179946899</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>9.69732093811035</v>
       </c>
       <c r="G1201" t="n">
-        <v>5.92263174057007</v>
+        <v>5.92263126373291</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>9.84347438812256</v>
       </c>
       <c r="G1203" t="n">
-        <v>6.01189470291138</v>
+        <v>6.01189422607422</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>9.70870971679688</v>
       </c>
       <c r="G1204" t="n">
-        <v>5.92958736419678</v>
+        <v>5.92958784103394</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>9.9345817565918</v>
       </c>
       <c r="G1207" t="n">
-        <v>6.06753921508789</v>
+        <v>6.06753873825073</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>9.8491678237915</v>
       </c>
       <c r="G1208" t="n">
-        <v>6.01537227630615</v>
+        <v>6.01537179946899</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>9.82259464263916</v>
       </c>
       <c r="G1209" t="n">
-        <v>5.99914264678955</v>
+        <v>5.99914169311523</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>10.1281871795654</v>
       </c>
       <c r="G1211" t="n">
-        <v>6.18578243255615</v>
+        <v>6.18578195571899</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>10.1357793807983</v>
       </c>
       <c r="G1213" t="n">
-        <v>6.19041967391968</v>
+        <v>6.19041872024536</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>9.99532127380371</v>
       </c>
       <c r="G1214" t="n">
-        <v>6.10463523864746</v>
+        <v>6.1046347618103</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>10.0921230316162</v>
       </c>
       <c r="G1215" t="n">
-        <v>6.16375637054443</v>
+        <v>6.16375684738159</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>9.92319297790527</v>
       </c>
       <c r="G1216" t="n">
-        <v>6.06058168411255</v>
+        <v>6.06058216094971</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>9.81690120697021</v>
       </c>
       <c r="G1218" t="n">
-        <v>5.99566459655762</v>
+        <v>5.99566507339478</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>10.2325811386108</v>
       </c>
       <c r="G1219" t="n">
-        <v>6.24954080581665</v>
+        <v>6.24954128265381</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>10.1984157562256</v>
       </c>
       <c r="G1220" t="n">
-        <v>6.22867393493652</v>
+        <v>6.22867441177368</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>10.2287845611572</v>
       </c>
       <c r="G1221" t="n">
-        <v>6.24722242355347</v>
+        <v>6.24722290039062</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>10.1604537963867</v>
       </c>
       <c r="G1222" t="n">
-        <v>6.20548963546753</v>
+        <v>6.20548915863037</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>10.5343770980835</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.43386316299438</v>
+        <v>6.43386220932007</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>10.6103010177612</v>
       </c>
       <c r="G1225" t="n">
-        <v>6.48023462295532</v>
+        <v>6.48023271560669</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>10.4337787628174</v>
       </c>
       <c r="G1226" t="n">
-        <v>6.37242221832275</v>
+        <v>6.37242364883423</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>10.0048112869263</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.11043167114258</v>
+        <v>6.11043119430542</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>10.2686452865601</v>
       </c>
       <c r="G1230" t="n">
-        <v>6.27156686782837</v>
+        <v>6.27156734466553</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>10.4451665878296</v>
       </c>
       <c r="G1231" t="n">
-        <v>6.3793773651123</v>
+        <v>6.37937688827515</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>10.6634473800659</v>
       </c>
       <c r="G1234" t="n">
-        <v>6.51269149780273</v>
+        <v>6.51269292831421</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>11.3144912719727</v>
       </c>
       <c r="G1235" t="n">
-        <v>6.91031694412231</v>
+        <v>6.91031646728516</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>11.5973052978516</v>
       </c>
       <c r="G1236" t="n">
-        <v>7.08304595947266</v>
+        <v>7.0830454826355</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>11.4473571777344</v>
       </c>
       <c r="G1238" t="n">
-        <v>6.99146461486816</v>
+        <v>6.99146509170532</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>11.9484510421753</v>
       </c>
       <c r="G1240" t="n">
-        <v>7.29750728607178</v>
+        <v>7.29750776290894</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>12.2236738204956</v>
       </c>
       <c r="G1244" t="n">
-        <v>7.46559953689575</v>
+        <v>7.46559858322144</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>12.1933040618896</v>
       </c>
       <c r="G1245" t="n">
-        <v>7.44705104827881</v>
+        <v>7.44705200195312</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>12.4267692565918</v>
       </c>
       <c r="G1246" t="n">
-        <v>7.58964014053345</v>
+        <v>7.58963966369629</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>12.4210748672485</v>
       </c>
       <c r="G1248" t="n">
-        <v>7.58616256713867</v>
+        <v>7.58616209030151</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>12.5520429611206</v>
       </c>
       <c r="G1249" t="n">
-        <v>7.66615152359009</v>
+        <v>7.66615104675293</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>12.4001960754395</v>
       </c>
       <c r="G1250" t="n">
-        <v>7.573410987854</v>
+        <v>7.57341051101685</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>12.5083866119385</v>
       </c>
       <c r="G1252" t="n">
-        <v>7.63948726654053</v>
+        <v>7.63948774337769</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>12.5558385848999</v>
       </c>
       <c r="G1253" t="n">
-        <v>7.6684684753418</v>
+        <v>7.66846895217896</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>12.7760171890259</v>
       </c>
       <c r="G1255" t="n">
-        <v>7.80294370651245</v>
+        <v>7.80294275283813</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>13.12526512146</v>
       </c>
       <c r="G1258" t="n">
-        <v>8.01624488830566</v>
+        <v>8.01624584197998</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>13.1157741546631</v>
       </c>
       <c r="G1260" t="n">
-        <v>8.01044940948486</v>
+        <v>8.01045036315918</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>14.0325498580933</v>
       </c>
       <c r="G1268" t="n">
-        <v>8.57036781311035</v>
+        <v>8.57036972045898</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>14.0837984085083</v>
       </c>
       <c r="G1272" t="n">
-        <v>8.60166931152344</v>
+        <v>8.60166835784912</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>14.0344476699829</v>
       </c>
       <c r="G1274" t="n">
-        <v>8.57152843475342</v>
+        <v>8.57152938842773</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>13.64723777771</v>
       </c>
       <c r="G1276" t="n">
-        <v>8.33504009246826</v>
+        <v>8.33503913879395</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>12.4723234176636</v>
       </c>
       <c r="G1279" t="n">
-        <v>8.78281116485596</v>
+        <v>8.78280925750732</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>11.9294700622559</v>
       </c>
       <c r="G1280" t="n">
-        <v>8.40054130554199</v>
+        <v>8.40054035186768</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>11.9294700622559</v>
       </c>
       <c r="G1281" t="n">
-        <v>8.40054130554199</v>
+        <v>8.40054035186768</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>13.1670227050781</v>
       </c>
       <c r="G1282" t="n">
-        <v>9.27200603485107</v>
+        <v>9.27200698852539</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>12.9506406784058</v>
       </c>
       <c r="G1284" t="n">
-        <v>9.11963272094727</v>
+        <v>9.11963367462158</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>12.5653285980225</v>
       </c>
       <c r="G1285" t="n">
-        <v>8.84830284118652</v>
+        <v>8.84830188751221</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>11.9807186126709</v>
       </c>
       <c r="G1286" t="n">
-        <v>8.43662929534912</v>
+        <v>8.43663024902344</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>11.7947063446045</v>
       </c>
       <c r="G1288" t="n">
-        <v>8.30564308166504</v>
+        <v>8.30564403533936</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>11.9636363983154</v>
       </c>
       <c r="G1291" t="n">
-        <v>8.42460060119629</v>
+        <v>8.42460155487061</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>12.4419536590576</v>
       </c>
       <c r="G1294" t="n">
-        <v>8.76142501831055</v>
+        <v>8.76142406463623</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>12.6830110549927</v>
       </c>
       <c r="G1295" t="n">
-        <v>8.93117332458496</v>
+        <v>8.93117237091064</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>12.9069852828979</v>
       </c>
       <c r="G1296" t="n">
-        <v>9.08889293670654</v>
+        <v>9.08889198303223</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>12.5577373504639</v>
       </c>
       <c r="G1298" t="n">
-        <v>8.84295654296875</v>
+        <v>8.84295749664307</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>12.489405632019</v>
       </c>
       <c r="G1299" t="n">
-        <v>8.79483890533447</v>
+        <v>8.79483985900879</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>12.7209720611572</v>
       </c>
       <c r="G1301" t="n">
-        <v>8.95790386199951</v>
+        <v>8.95790481567383</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>12.8120803833008</v>
       </c>
       <c r="G1302" t="n">
-        <v>9.02206039428711</v>
+        <v>9.02206230163574</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>12.6070871353149</v>
       </c>
       <c r="G1304" t="n">
-        <v>8.87770843505859</v>
+        <v>8.87770938873291</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>12.6981954574585</v>
       </c>
       <c r="G1305" t="n">
-        <v>8.94186592102051</v>
+        <v>8.94186496734619</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>12.5311641693115</v>
       </c>
       <c r="G1306" t="n">
-        <v>8.82424449920654</v>
+        <v>8.82424640655518</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>12.5956993103027</v>
       </c>
       <c r="G1307" t="n">
-        <v>8.86968994140625</v>
+        <v>8.86969089508057</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>12.8671245574951</v>
       </c>
       <c r="G1309" t="n">
-        <v>9.06082439422607</v>
+        <v>9.06082344055176</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>13.2144746780396</v>
       </c>
       <c r="G1311" t="n">
-        <v>9.30542087554932</v>
+        <v>9.30542182922363</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>13.1613283157349</v>
       </c>
       <c r="G1313" t="n">
-        <v>9.26799583435059</v>
+        <v>9.2679967880249</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>13.7459392547607</v>
       </c>
       <c r="G1316" t="n">
-        <v>9.67967128753662</v>
+        <v>9.6796703338623</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>14.4501285552979</v>
       </c>
       <c r="G1319" t="n">
-        <v>10.1755485534668</v>
+        <v>10.1755495071411</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>14.6494283676147</v>
       </c>
       <c r="G1320" t="n">
-        <v>10.3158931732178</v>
+        <v>10.3158922195435</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>14.8579998016357</v>
       </c>
       <c r="G1321" t="n">
-        <v>10.602707862854</v>
+        <v>10.6027088165283</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G1322" t="n">
-        <v>10.5399122238159</v>
+        <v>10.5399112701416</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>14.9460000991821</v>
       </c>
       <c r="G1323" t="n">
-        <v>10.6655044555664</v>
+        <v>10.6655054092407</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1325" t="n">
-        <v>10.5970001220703</v>
+        <v>10.596999168396</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>14.1940002441406</v>
       </c>
       <c r="G1327" t="n">
-        <v>10.1288766860962</v>
+        <v>10.1288757324219</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>14.6379995346069</v>
       </c>
       <c r="G1330" t="n">
-        <v>10.4457149505615</v>
+        <v>10.4457159042358</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1332" t="n">
-        <v>10.7754011154175</v>
+        <v>10.7754001617432</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>15.0839996337891</v>
       </c>
       <c r="G1333" t="n">
-        <v>10.7639827728271</v>
+        <v>10.7639818191528</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G1336" t="n">
-        <v>10.9109840393066</v>
+        <v>10.910984992981</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>14.9379997253418</v>
       </c>
       <c r="G1339" t="n">
-        <v>10.6597957611084</v>
+        <v>10.6597967147827</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>15.1459999084473</v>
       </c>
       <c r="G1340" t="n">
-        <v>10.8082256317139</v>
+        <v>10.8082246780396</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>15.0419998168945</v>
       </c>
       <c r="G1342" t="n">
-        <v>10.7340116500854</v>
+        <v>10.7340097427368</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>15.2620000839233</v>
       </c>
       <c r="G1343" t="n">
-        <v>10.8910036087036</v>
+        <v>10.8910026550293</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>14.1940002441406</v>
       </c>
       <c r="G1345" t="n">
-        <v>10.3457984924316</v>
+        <v>10.3457975387573</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1347" t="n">
-        <v>10.481369972229</v>
+        <v>10.4813709259033</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1349" t="n">
-        <v>10.4667921066284</v>
+        <v>10.4667930603027</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>14.3920001983643</v>
       </c>
       <c r="G1351" t="n">
-        <v>10.4901161193848</v>
+        <v>10.4901170730591</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>13.8240003585815</v>
       </c>
       <c r="G1353" t="n">
-        <v>10.0761089324951</v>
+        <v>10.0761108398438</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>13.8879995346069</v>
       </c>
       <c r="G1355" t="n">
-        <v>10.1227579116821</v>
+        <v>10.1227588653564</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1356" t="n">
-        <v>10.8312339782715</v>
+        <v>10.8312349319458</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>14.9139995574951</v>
       </c>
       <c r="G1357" t="n">
-        <v>10.8705949783325</v>
+        <v>10.8705940246582</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1359" t="n">
-        <v>11.0061683654785</v>
+        <v>11.0061674118042</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1362" t="n">
-        <v>10.678168296814</v>
+        <v>10.6781692504883</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>15.0979995727539</v>
       </c>
       <c r="G1364" t="n">
-        <v>11.0047092437744</v>
+        <v>11.0047082901001</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G1366" t="n">
-        <v>10.7364797592163</v>
+        <v>10.736478805542</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>15.3159999847412</v>
       </c>
       <c r="G1368" t="n">
-        <v>11.1636056900024</v>
+        <v>11.1636066436768</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>15.4739999771118</v>
       </c>
       <c r="G1370" t="n">
-        <v>11.2787704467773</v>
+        <v>11.2787714004517</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>15.4460000991821</v>
       </c>
       <c r="G1371" t="n">
-        <v>11.2583608627319</v>
+        <v>11.2583618164062</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>16.1060009002686</v>
       </c>
       <c r="G1373" t="n">
-        <v>11.7394275665283</v>
+        <v>11.739426612854</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>16.3460006713867</v>
       </c>
       <c r="G1375" t="n">
-        <v>11.9143600463867</v>
+        <v>11.9143590927124</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>17.1660003662109</v>
       </c>
       <c r="G1378" t="n">
-        <v>12.5120439529419</v>
+        <v>12.5120449066162</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>17.4759998321533</v>
       </c>
       <c r="G1380" t="n">
-        <v>12.737998008728</v>
+        <v>12.7379989624023</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>17</v>
       </c>
       <c r="G1382" t="n">
-        <v>12.3910493850708</v>
+        <v>12.3910503387451</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1383" t="n">
-        <v>12.5003814697266</v>
+        <v>12.5003824234009</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>16.9680004119873</v>
       </c>
       <c r="G1384" t="n">
-        <v>12.3677244186401</v>
+        <v>12.3677253723145</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>16.8980007171631</v>
       </c>
       <c r="G1385" t="n">
-        <v>12.3167028427124</v>
+        <v>12.3167037963867</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1386" t="n">
-        <v>12.3181600570679</v>
+        <v>12.3181610107422</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1389" t="n">
-        <v>12.4056272506714</v>
+        <v>12.4056282043457</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>16.992000579834</v>
       </c>
       <c r="G1392" t="n">
-        <v>12.3852186203003</v>
+        <v>12.385217666626</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>16.8419990539551</v>
       </c>
       <c r="G1394" t="n">
-        <v>12.2758855819702</v>
+        <v>12.2758846282959</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>16.82200050354</v>
       </c>
       <c r="G1395" t="n">
-        <v>12.2613077163696</v>
+        <v>12.2613086700439</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>16.7019996643066</v>
       </c>
       <c r="G1397" t="n">
-        <v>12.1738414764404</v>
+        <v>12.1738405227661</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>16.931999206543</v>
       </c>
       <c r="G1399" t="n">
-        <v>12.3414840698242</v>
+        <v>12.3414850234985</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>16.5919990539551</v>
       </c>
       <c r="G1401" t="n">
-        <v>12.0936641693115</v>
+        <v>12.0936632156372</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1406" t="n">
-        <v>11.8370962142944</v>
+        <v>11.8370971679688</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>15.6859998703003</v>
       </c>
       <c r="G1408" t="n">
-        <v>11.4332942962646</v>
+        <v>11.4332933425903</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>15.1219997406006</v>
       </c>
       <c r="G1409" t="n">
-        <v>11.0222034454346</v>
+        <v>11.0222024917603</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1410" t="n">
-        <v>11.049901008606</v>
+        <v>11.0499000549316</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1411" t="n">
-        <v>11.4289207458496</v>
+        <v>11.4289216995239</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>15.5900001525879</v>
       </c>
       <c r="G1412" t="n">
-        <v>11.3633213043213</v>
+        <v>11.3633222579956</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>15.6879997253418</v>
       </c>
       <c r="G1415" t="n">
-        <v>11.4347515106201</v>
+        <v>11.4347524642944</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>17.4440002441406</v>
       </c>
       <c r="G1422" t="n">
-        <v>12.7146739959717</v>
+        <v>12.714674949646</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>17.8740005493164</v>
       </c>
       <c r="G1423" t="n">
-        <v>13.0280961990356</v>
+        <v>13.02809715271</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>17.996000289917</v>
       </c>
       <c r="G1424" t="n">
-        <v>13.1170206069946</v>
+        <v>13.117018699646</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>18.4979991912842</v>
       </c>
       <c r="G1427" t="n">
-        <v>13.4829196929932</v>
+        <v>13.4829187393188</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G1428" t="n">
-        <v>13.5645561218262</v>
+        <v>13.5645551681519</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>17.8439998626709</v>
       </c>
       <c r="G1430" t="n">
-        <v>13.0062284469604</v>
+        <v>13.0062294006348</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1432" t="n">
-        <v>12.6388711929321</v>
+        <v>12.6388702392578</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>17.2059993743896</v>
       </c>
       <c r="G1434" t="n">
-        <v>12.5411987304688</v>
+        <v>12.5411996841431</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>17.25</v>
       </c>
       <c r="G1435" t="n">
-        <v>12.5732698440552</v>
+        <v>12.5732707977295</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>16.931999206543</v>
       </c>
       <c r="G1440" t="n">
-        <v>12.3414840698242</v>
+        <v>12.3414850234985</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>17.1240005493164</v>
       </c>
       <c r="G1442" t="n">
-        <v>12.4814310073853</v>
+        <v>12.4814319610596</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>17.242000579834</v>
       </c>
       <c r="G1444" t="n">
-        <v>12.5674390792847</v>
+        <v>12.567440032959</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>17.0860004425049</v>
       </c>
       <c r="G1445" t="n">
-        <v>12.4537334442139</v>
+        <v>12.4537343978882</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>16.5979995727539</v>
       </c>
       <c r="G1446" t="n">
-        <v>12.0980377197266</v>
+        <v>12.0980367660522</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>16.7040004730225</v>
       </c>
       <c r="G1448" t="n">
-        <v>12.1752986907959</v>
+        <v>12.1752996444702</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1451" t="n">
-        <v>12.6388711929321</v>
+        <v>12.6388702392578</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G1452" t="n">
-        <v>12.6898927688599</v>
+        <v>12.6898918151855</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>16.8099994659424</v>
       </c>
       <c r="G1453" t="n">
-        <v>12.2525615692139</v>
+        <v>12.2525606155396</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>16.5520000457764</v>
       </c>
       <c r="G1456" t="n">
-        <v>12.0645093917847</v>
+        <v>12.0645084381104</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>16.7679996490479</v>
       </c>
       <c r="G1457" t="n">
-        <v>12.2219486236572</v>
+        <v>12.2219476699829</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>16.9360008239746</v>
       </c>
       <c r="G1459" t="n">
-        <v>12.3444004058838</v>
+        <v>12.3444013595581</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>16.431999206543</v>
       </c>
       <c r="G1460" t="n">
-        <v>11.9770421981812</v>
+        <v>11.9770412445068</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1461" t="n">
-        <v>12.1432285308838</v>
+        <v>12.1432275772095</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>16.5219993591309</v>
       </c>
       <c r="G1462" t="n">
-        <v>12.0426425933838</v>
+        <v>12.0426416397095</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>16.2679996490479</v>
       </c>
       <c r="G1463" t="n">
-        <v>11.8575057983398</v>
+        <v>11.8575038909912</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>16.1380004882812</v>
       </c>
       <c r="G1464" t="n">
-        <v>11.7627515792847</v>
+        <v>11.7627506256104</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>15.9659996032715</v>
       </c>
       <c r="G1466" t="n">
-        <v>11.6373825073242</v>
+        <v>11.6373815536499</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>16.57200050354</v>
       </c>
       <c r="G1467" t="n">
-        <v>12.0790872573853</v>
+        <v>12.0790863037109</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>16.673999786377</v>
       </c>
       <c r="G1468" t="n">
-        <v>12.1534328460693</v>
+        <v>12.1534337997437</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>16.8560009002686</v>
       </c>
       <c r="G1470" t="n">
-        <v>12.2860898971558</v>
+        <v>12.2860908508301</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>17.2059993743896</v>
       </c>
       <c r="G1473" t="n">
-        <v>12.5411987304688</v>
+        <v>12.5411996841431</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>16.8920001983643</v>
       </c>
       <c r="G1474" t="n">
-        <v>12.3123292922974</v>
+        <v>12.3123302459717</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1476" t="n">
-        <v>12.2598485946655</v>
+        <v>12.2598505020142</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>16.8540000915527</v>
       </c>
       <c r="G1477" t="n">
-        <v>12.284631729126</v>
+        <v>12.2846336364746</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>17.5139999389648</v>
       </c>
       <c r="G1479" t="n">
-        <v>12.7656955718994</v>
+        <v>12.765697479248</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>17.57200050354</v>
       </c>
       <c r="G1480" t="n">
-        <v>12.80797290802</v>
+        <v>12.8079719543457</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1481" t="n">
-        <v>12.7992248535156</v>
+        <v>12.7992258071899</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>17.25</v>
       </c>
       <c r="G1483" t="n">
-        <v>12.5732698440552</v>
+        <v>12.5732707977295</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>17.5359992980957</v>
       </c>
       <c r="G1489" t="n">
-        <v>12.7817316055298</v>
+        <v>12.7817306518555</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1490" t="n">
-        <v>12.7117595672607</v>
+        <v>12.7117605209351</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>17.8819999694824</v>
       </c>
       <c r="G1491" t="n">
-        <v>13.0339269638062</v>
+        <v>13.0339260101318</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>17.8859996795654</v>
       </c>
       <c r="G1492" t="n">
-        <v>13.0368423461914</v>
+        <v>13.0368413925171</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>17.8759994506836</v>
       </c>
       <c r="G1493" t="n">
-        <v>13.0295524597168</v>
+        <v>13.0295534133911</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>18.0900001525879</v>
       </c>
       <c r="G1495" t="n">
-        <v>13.1855354309082</v>
+        <v>13.1855344772339</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>17.9559993743896</v>
       </c>
       <c r="G1496" t="n">
-        <v>13.0878639221191</v>
+        <v>13.0878648757935</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>17.5139999389648</v>
       </c>
       <c r="G1498" t="n">
-        <v>12.7656955718994</v>
+        <v>12.765697479248</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>17.4580001831055</v>
       </c>
       <c r="G1499" t="n">
-        <v>12.7248802185059</v>
+        <v>12.7248792648315</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>16.8080005645752</v>
       </c>
       <c r="G1501" t="n">
-        <v>12.2511043548584</v>
+        <v>12.2511034011841</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>16.7080001831055</v>
       </c>
       <c r="G1502" t="n">
-        <v>12.1782150268555</v>
+        <v>12.1782159805298</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>15.5679998397827</v>
       </c>
       <c r="G1504" t="n">
-        <v>11.3472852706909</v>
+        <v>11.3472862243652</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>16</v>
       </c>
       <c r="G1506" t="n">
-        <v>11.662163734436</v>
+        <v>11.6621646881104</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>16.8719997406006</v>
       </c>
       <c r="G1510" t="n">
-        <v>12.2977523803711</v>
+        <v>12.2977514266968</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>16.4479999542236</v>
       </c>
       <c r="G1512" t="n">
-        <v>11.9887046813965</v>
+        <v>11.9887037277222</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G1515" t="n">
-        <v>11.8589639663696</v>
+        <v>11.8589630126953</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>16.3159999847412</v>
       </c>
       <c r="G1516" t="n">
-        <v>11.8924913406372</v>
+        <v>11.8924922943115</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>16.8540000915527</v>
       </c>
       <c r="G1517" t="n">
-        <v>12.284631729126</v>
+        <v>12.2846336364746</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>16.4139995574951</v>
       </c>
       <c r="G1518" t="n">
-        <v>11.9639225006104</v>
+        <v>11.963921546936</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1519" t="n">
-        <v>11.5309638977051</v>
+        <v>11.5309648513794</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>16.5979995727539</v>
       </c>
       <c r="G1522" t="n">
-        <v>12.0980377197266</v>
+        <v>12.0980367660522</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>16.8540000915527</v>
       </c>
       <c r="G1524" t="n">
-        <v>12.284631729126</v>
+        <v>12.2846336364746</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>16.7019996643066</v>
       </c>
       <c r="G1525" t="n">
-        <v>12.1738414764404</v>
+        <v>12.1738405227661</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>17.3279991149902</v>
       </c>
       <c r="G1527" t="n">
-        <v>12.6301221847534</v>
+        <v>12.6301231384277</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>18.0020008087158</v>
       </c>
       <c r="G1531" t="n">
-        <v>13.1213932037354</v>
+        <v>13.1213941574097</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>17.8640003204346</v>
       </c>
       <c r="G1532" t="n">
-        <v>13.0208072662354</v>
+        <v>13.0208053588867</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G1535" t="n">
-        <v>13.856107711792</v>
+        <v>13.8561086654663</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1537" t="n">
-        <v>13.9508628845215</v>
+        <v>13.9508638381958</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>19.0939998626709</v>
       </c>
       <c r="G1538" t="n">
-        <v>13.9173345565796</v>
+        <v>13.9173364639282</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G1539" t="n">
-        <v>13.8415307998657</v>
+        <v>13.8415298461914</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>18.7940006256104</v>
       </c>
       <c r="G1540" t="n">
-        <v>13.6986703872681</v>
+        <v>13.6986694335938</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>16.6019992828369</v>
       </c>
       <c r="G1543" t="n">
-        <v>12.1009521484375</v>
+        <v>12.1009531021118</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>17.4039993286133</v>
       </c>
       <c r="G1544" t="n">
-        <v>12.6855192184448</v>
+        <v>12.6855182647705</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>17.5419998168945</v>
       </c>
       <c r="G1545" t="n">
-        <v>12.7861061096191</v>
+        <v>12.7861051559448</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G1547" t="n">
-        <v>12.3691816329956</v>
+        <v>12.3691825866699</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>17.4759998321533</v>
       </c>
       <c r="G1549" t="n">
-        <v>12.737998008728</v>
+        <v>12.7379989624023</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>17.3740005493164</v>
       </c>
       <c r="G1550" t="n">
-        <v>12.6636524200439</v>
+        <v>12.6636533737183</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>16.4619998931885</v>
       </c>
       <c r="G1551" t="n">
-        <v>11.9989099502563</v>
+        <v>11.998908996582</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>16.3020000457764</v>
       </c>
       <c r="G1552" t="n">
-        <v>11.882287979126</v>
+        <v>11.8822870254517</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>16.4379997253418</v>
       </c>
       <c r="G1553" t="n">
-        <v>11.9814157485962</v>
+        <v>11.9814167022705</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1555" t="n">
-        <v>12.3618927001953</v>
+        <v>12.3618936538696</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G1556" t="n">
-        <v>12.223406791687</v>
+        <v>12.2234058380127</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>17.011999130249</v>
       </c>
       <c r="G1558" t="n">
-        <v>12.3997945785522</v>
+        <v>12.3997955322266</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>16.6919994354248</v>
       </c>
       <c r="G1561" t="n">
-        <v>12.1665534973145</v>
+        <v>12.1665525436401</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>16.3040008544922</v>
       </c>
       <c r="G1562" t="n">
-        <v>11.8837461471558</v>
+        <v>11.8837451934814</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>16.3460006713867</v>
       </c>
       <c r="G1563" t="n">
-        <v>11.9143600463867</v>
+        <v>11.9143590927124</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>12.9320001602173</v>
       </c>
       <c r="G1573" t="n">
-        <v>9.42594337463379</v>
+        <v>9.42594528198242</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1574" t="n">
-        <v>10.5834140777588</v>
+        <v>10.5834131240845</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>13.496000289917</v>
       </c>
       <c r="G1576" t="n">
-        <v>9.8370361328125</v>
+        <v>9.83703517913818</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>14</v>
       </c>
       <c r="G1577" t="n">
-        <v>10.2043943405151</v>
+        <v>10.2043933868408</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G1579" t="n">
-        <v>10.9770126342773</v>
+        <v>10.977011680603</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>14.6639995574951</v>
       </c>
       <c r="G1581" t="n">
-        <v>10.6883735656738</v>
+        <v>10.6883726119995</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>14.8219995498657</v>
       </c>
       <c r="G1583" t="n">
-        <v>10.8035364151001</v>
+        <v>10.8035373687744</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>14.4119997024536</v>
       </c>
       <c r="G1585" t="n">
-        <v>10.5046939849854</v>
+        <v>10.504693031311</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G1588" t="n">
-        <v>11.2321214675903</v>
+        <v>11.2321224212646</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>14.8879995346069</v>
       </c>
       <c r="G1592" t="n">
-        <v>10.8516445159912</v>
+        <v>10.8516435623169</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G1593" t="n">
-        <v>10.4522151947021</v>
+        <v>10.4522142410278</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>13.7659997940063</v>
       </c>
       <c r="G1596" t="n">
-        <v>10.0338354110718</v>
+        <v>10.0338344573975</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>13.9739999771118</v>
       </c>
       <c r="G1599" t="n">
-        <v>10.1854419708252</v>
+        <v>10.1854429244995</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>13.3479995727539</v>
       </c>
       <c r="G1601" t="n">
-        <v>10.5054626464844</v>
+        <v>10.5054616928101</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1603" t="n">
-        <v>10.6644458770752</v>
+        <v>10.6644449234009</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>12.7959995269775</v>
       </c>
       <c r="G1608" t="n">
-        <v>10.0710134506226</v>
+        <v>10.0710144042969</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>12.9820003509521</v>
       </c>
       <c r="G1609" t="n">
-        <v>10.2174053192139</v>
+        <v>10.2174043655396</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G1628" t="n">
-        <v>10.7903728485107</v>
+        <v>10.7903718948364</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>14.1759996414185</v>
       </c>
       <c r="G1632" t="n">
-        <v>11.1571350097656</v>
+        <v>11.1571340560913</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>13.7919998168945</v>
       </c>
       <c r="G1634" t="n">
-        <v>10.8549108505249</v>
+        <v>10.8549098968506</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>14.0579996109009</v>
       </c>
       <c r="G1635" t="n">
-        <v>11.064263343811</v>
+        <v>11.0642642974854</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>13.8879995346069</v>
       </c>
       <c r="G1636" t="n">
-        <v>10.9304656982422</v>
+        <v>10.9304666519165</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>12.9919996261597</v>
       </c>
       <c r="G1639" t="n">
-        <v>10.2252750396729</v>
+        <v>10.2252740859985</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1642" t="n">
-        <v>10.0977735519409</v>
+        <v>10.0977745056152</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>12.2360000610352</v>
       </c>
       <c r="G1644" t="n">
-        <v>9.63027095794678</v>
+        <v>9.63027000427246</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>12.3879995346069</v>
       </c>
       <c r="G1645" t="n">
-        <v>9.74990081787109</v>
+        <v>9.74989986419678</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>12.6979999542236</v>
       </c>
       <c r="G1646" t="n">
-        <v>9.99388313293457</v>
+        <v>9.99388408660889</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1647" t="n">
-        <v>9.82230758666992</v>
+        <v>9.82230854034424</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>12.4280004501343</v>
       </c>
       <c r="G1649" t="n">
-        <v>9.78138256072998</v>
+        <v>9.78138160705566</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1650" t="n">
-        <v>9.77508544921875</v>
+        <v>9.77508640289307</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1654" t="n">
-        <v>9.22415542602539</v>
+        <v>9.22415447235107</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1660" t="n">
-        <v>9.60193634033203</v>
+        <v>9.60193538665771</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>12.2980003356934</v>
       </c>
       <c r="G1661" t="n">
-        <v>9.67906761169434</v>
+        <v>9.67906665802002</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>11.6920003890991</v>
       </c>
       <c r="G1663" t="n">
-        <v>9.20211791992188</v>
+        <v>9.20211887359619</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>12.5679998397827</v>
       </c>
       <c r="G1668" t="n">
-        <v>9.89156723022461</v>
+        <v>9.89156818389893</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>14.423999786377</v>
       </c>
       <c r="G1677" t="n">
-        <v>11.3523216247559</v>
+        <v>11.3523225784302</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>14.7819995880127</v>
       </c>
       <c r="G1680" t="n">
-        <v>11.6340837478638</v>
+        <v>11.6340827941895</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>14.4060001373291</v>
       </c>
       <c r="G1681" t="n">
-        <v>11.3381547927856</v>
+        <v>11.33815574646</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>14.6859998703003</v>
       </c>
       <c r="G1683" t="n">
-        <v>11.5585279464722</v>
+        <v>11.5585269927979</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>14.8319997787476</v>
       </c>
       <c r="G1684" t="n">
-        <v>11.673436164856</v>
+        <v>11.6734352111816</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1685" t="n">
-        <v>11.7269554138184</v>
+        <v>11.726954460144</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>14.8719997406006</v>
       </c>
       <c r="G1687" t="n">
-        <v>11.7049179077148</v>
+        <v>11.7049169540405</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>13.8520002365112</v>
       </c>
       <c r="G1689" t="n">
-        <v>10.9021320343018</v>
+        <v>10.9021329879761</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G1692" t="n">
-        <v>11.089448928833</v>
+        <v>11.0894498825073</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G1693" t="n">
-        <v>10.8139839172363</v>
+        <v>10.813982963562</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>13.7559995651245</v>
       </c>
       <c r="G1694" t="n">
-        <v>10.8265771865845</v>
+        <v>10.8265762329102</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1697" t="n">
-        <v>10.3338871002197</v>
+        <v>10.333888053894</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>13.1379995346069</v>
       </c>
       <c r="G1701" t="n">
-        <v>10.3401832580566</v>
+        <v>10.340184211731</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>13.2919998168945</v>
       </c>
       <c r="G1703" t="n">
-        <v>10.4613876342773</v>
+        <v>10.4613885879517</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>13.6660003662109</v>
       </c>
       <c r="G1706" t="n">
-        <v>10.7557439804077</v>
+        <v>10.7557430267334</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G1709" t="n">
-        <v>10.6329641342163</v>
+        <v>10.632963180542</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1714" t="n">
-        <v>10.0111989974976</v>
+        <v>10.0111999511719</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>12.8339996337891</v>
       </c>
       <c r="G1715" t="n">
-        <v>10.1009216308594</v>
+        <v>10.1009225845337</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>12.2720003128052</v>
       </c>
       <c r="G1718" t="n">
-        <v>9.65860462188721</v>
+        <v>9.65860366821289</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>12.5139999389648</v>
       </c>
       <c r="G1719" t="n">
-        <v>9.84906768798828</v>
+        <v>9.8490686416626</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>12.6239995956421</v>
       </c>
       <c r="G1721" t="n">
-        <v>9.93564224243164</v>
+        <v>9.93564319610596</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>12.1840000152588</v>
       </c>
       <c r="G1724" t="n">
-        <v>9.5893440246582</v>
+        <v>9.58934307098389</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>12.1940002441406</v>
       </c>
       <c r="G1726" t="n">
-        <v>9.5972146987915</v>
+        <v>9.59721374511719</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>12.4860000610352</v>
       </c>
       <c r="G1727" t="n">
-        <v>9.82703113555908</v>
+        <v>9.82703018188477</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>12.8140001296997</v>
       </c>
       <c r="G1729" t="n">
-        <v>10.0851812362671</v>
+        <v>10.0851821899414</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>13.0220003128052</v>
       </c>
       <c r="G1730" t="n">
-        <v>10.2488870620728</v>
+        <v>10.2488861083984</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>13.6520004272461</v>
       </c>
       <c r="G1736" t="n">
-        <v>10.744725227356</v>
+        <v>10.7447233200073</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1739" t="n">
-        <v>10.7510204315186</v>
+        <v>10.7510194778442</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>13.7919998168945</v>
       </c>
       <c r="G1740" t="n">
-        <v>10.8549108505249</v>
+        <v>10.8549098968506</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>13.28600025177</v>
       </c>
       <c r="G1742" t="n">
-        <v>10.4566669464111</v>
+        <v>10.4566659927368</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G1745" t="n">
-        <v>10.7903728485107</v>
+        <v>10.7903718948364</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>14.25</v>
       </c>
       <c r="G1751" t="n">
-        <v>11.2153759002686</v>
+        <v>11.2153768539429</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>14.1079998016357</v>
       </c>
       <c r="G1752" t="n">
-        <v>11.1036157608032</v>
+        <v>11.1036167144775</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>14.46399974823</v>
       </c>
       <c r="G1756" t="n">
-        <v>11.3838033676147</v>
+        <v>11.3838043212891</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1758" t="n">
-        <v>11.5301942825317</v>
+        <v>11.5301933288574</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>14.4820003509521</v>
       </c>
       <c r="G1766" t="n">
-        <v>11.397970199585</v>
+        <v>11.3979711532593</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1770" t="n">
-        <v>10.8612060546875</v>
+        <v>10.8612070083618</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>13.8920001983643</v>
       </c>
       <c r="G1771" t="n">
-        <v>10.9336137771606</v>
+        <v>10.933614730835</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>13.1239995956421</v>
       </c>
       <c r="G1777" t="n">
-        <v>10.3291645050049</v>
+        <v>10.3291635513306</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>13.1579999923706</v>
       </c>
       <c r="G1779" t="n">
-        <v>10.3559236526489</v>
+        <v>10.3559246063232</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>13.1180000305176</v>
       </c>
       <c r="G1780" t="n">
-        <v>10.32444190979</v>
+        <v>10.3244428634644</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>13.3780002593994</v>
       </c>
       <c r="G1781" t="n">
-        <v>10.5290746688843</v>
+        <v>10.52907371521</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>13.6479997634888</v>
       </c>
       <c r="G1783" t="n">
-        <v>10.7415761947632</v>
+        <v>10.7415752410889</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>13.826000213623</v>
       </c>
       <c r="G1784" t="n">
-        <v>10.8816690444946</v>
+        <v>10.8816699981689</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>14.4460000991821</v>
       </c>
       <c r="G1787" t="n">
-        <v>11.3696365356445</v>
+        <v>11.3696374893188</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>14.6660003662109</v>
       </c>
       <c r="G1789" t="n">
-        <v>11.5427865982056</v>
+        <v>11.5427875518799</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>14.2679996490479</v>
       </c>
       <c r="G1795" t="n">
-        <v>11.2295427322388</v>
+        <v>11.2295417785645</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G1796" t="n">
-        <v>10.9477806091309</v>
+        <v>10.9477815628052</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>14.0539999008179</v>
       </c>
       <c r="G1801" t="n">
-        <v>11.0611152648926</v>
+        <v>11.0611162185669</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>14.1960000991821</v>
       </c>
       <c r="G1802" t="n">
-        <v>11.1728754043579</v>
+        <v>11.1728763580322</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>15.2080001831055</v>
       </c>
       <c r="G1806" t="n">
-        <v>11.9693651199341</v>
+        <v>11.9693641662598</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1807" t="n">
-        <v>11.9630689620972</v>
+        <v>11.9630680084229</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G1808" t="n">
-        <v>11.8686227798462</v>
+        <v>11.8686237335205</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>15.0880002975464</v>
       </c>
       <c r="G1809" t="n">
-        <v>11.8749198913574</v>
+        <v>11.8749189376831</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>15.1219997406006</v>
       </c>
       <c r="G1810" t="n">
-        <v>11.9016790390015</v>
+        <v>11.9016780853271</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>15.4119997024536</v>
       </c>
       <c r="G1812" t="n">
-        <v>12.1299209594727</v>
+        <v>12.129921913147</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>15.576000213623</v>
       </c>
       <c r="G1814" t="n">
-        <v>12.2589960098267</v>
+        <v>12.258996963501</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G1815" t="n">
-        <v>12.4903879165649</v>
+        <v>12.4903869628906</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1817" t="n">
-        <v>12.5533514022827</v>
+        <v>12.5533504486084</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>16.1380004882812</v>
       </c>
       <c r="G1818" t="n">
-        <v>12.7013158798218</v>
+        <v>12.7013149261475</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>15.8680000305176</v>
       </c>
       <c r="G1819" t="n">
-        <v>12.4888134002686</v>
+        <v>12.4888143539429</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>16.2180004119873</v>
       </c>
       <c r="G1820" t="n">
-        <v>12.7642793655396</v>
+        <v>12.7642784118652</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>16.6319999694824</v>
       </c>
       <c r="G1823" t="n">
-        <v>13.0901155471802</v>
+        <v>13.0901145935059</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>16.5540008544922</v>
       </c>
       <c r="G1824" t="n">
-        <v>13.0287265777588</v>
+        <v>13.0287256240845</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>17.0559997558594</v>
       </c>
       <c r="G1825" t="n">
-        <v>13.4238204956055</v>
+        <v>13.4238214492798</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>17.1720008850098</v>
       </c>
       <c r="G1826" t="n">
-        <v>13.515118598938</v>
+        <v>13.5151195526123</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>17.6679992675781</v>
       </c>
       <c r="G1827" t="n">
-        <v>13.9054918289185</v>
+        <v>13.9054927825928</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>17.576000213623</v>
       </c>
       <c r="G1828" t="n">
-        <v>13.8330850601196</v>
+        <v>13.8330860137939</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G1829" t="n">
-        <v>13.7968807220459</v>
+        <v>13.7968816757202</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>17.2019996643066</v>
       </c>
       <c r="G1831" t="n">
-        <v>13.5387296676636</v>
+        <v>13.5387306213379</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>16.3939990997314</v>
       </c>
       <c r="G1834" t="n">
-        <v>12.9027986526489</v>
+        <v>12.9027976989746</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>15.793999671936</v>
       </c>
       <c r="G1835" t="n">
-        <v>12.4305725097656</v>
+        <v>12.4305715560913</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>15.9160003662109</v>
       </c>
       <c r="G1836" t="n">
-        <v>12.5265913009644</v>
+        <v>12.5265922546387</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>15.7159996032715</v>
       </c>
       <c r="G1837" t="n">
-        <v>12.3691816329956</v>
+        <v>12.3691825866699</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>16.1860008239746</v>
       </c>
       <c r="G1839" t="n">
-        <v>12.7390947341919</v>
+        <v>12.7390937805176</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>16.1959991455078</v>
       </c>
       <c r="G1840" t="n">
-        <v>12.7469635009766</v>
+        <v>12.7469625473022</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>15.9020004272461</v>
       </c>
       <c r="G1842" t="n">
-        <v>12.5155735015869</v>
+        <v>12.5155725479126</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G1845" t="n">
-        <v>12.9153919219971</v>
+        <v>12.9153909683228</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G1848" t="n">
-        <v>13.120023727417</v>
+        <v>13.1200227737427</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>16.1140003204346</v>
       </c>
       <c r="G1850" t="n">
-        <v>12.6824264526367</v>
+        <v>12.682427406311</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>17.1639995574951</v>
       </c>
       <c r="G1855" t="n">
-        <v>13.5088214874268</v>
+        <v>13.5088224411011</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1859" t="n">
-        <v>12.6320543289185</v>
+        <v>12.6320552825928</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>3.83800005912781</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>35635457</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>3.88599991798401</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>3.7885000705719</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>3.81399989128113</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>3.87800002098083</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>3.87800002098083</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -427,7 +427,7 @@
         <v>7.70264196395874</v>
       </c>
       <c r="G2" t="n">
-        <v>4.02501440048218</v>
+        <v>4.02501392364502</v>
       </c>
       <c r="H2" t="n">
         <v>27068333</v>
@@ -456,7 +456,7 @@
         <v>7.90583992004395</v>
       </c>
       <c r="G3" t="n">
-        <v>4.13119506835938</v>
+        <v>4.13119459152222</v>
       </c>
       <c r="H3" t="n">
         <v>25131882</v>
@@ -485,7 +485,7 @@
         <v>7.49471807479858</v>
       </c>
       <c r="G4" t="n">
-        <v>3.91636300086975</v>
+        <v>3.91636323928833</v>
       </c>
       <c r="H4" t="n">
         <v>28467440</v>
@@ -514,7 +514,7 @@
         <v>7.24898910522461</v>
       </c>
       <c r="G5" t="n">
-        <v>3.78795790672302</v>
+        <v>3.78795766830444</v>
       </c>
       <c r="H5" t="n">
         <v>25910209</v>
@@ -543,7 +543,7 @@
         <v>6.95128011703491</v>
       </c>
       <c r="G6" t="n">
-        <v>3.63238978385925</v>
+        <v>3.63238954544067</v>
       </c>
       <c r="H6" t="n">
         <v>23954673</v>
@@ -572,7 +572,7 @@
         <v>6.92292594909668</v>
       </c>
       <c r="G7" t="n">
-        <v>3.61757349967957</v>
+        <v>3.61757326126099</v>
       </c>
       <c r="H7" t="n">
         <v>27133919</v>
@@ -601,7 +601,7 @@
         <v>7.11667394638062</v>
       </c>
       <c r="G8" t="n">
-        <v>3.71881651878357</v>
+        <v>3.71881675720215</v>
       </c>
       <c r="H8" t="n">
         <v>14686924</v>
@@ -659,7 +659,7 @@
         <v>6.46454811096191</v>
       </c>
       <c r="G10" t="n">
-        <v>3.37804841995239</v>
+        <v>3.37804818153381</v>
       </c>
       <c r="H10" t="n">
         <v>62457873</v>
@@ -775,7 +775,7 @@
         <v>5.85967779159546</v>
       </c>
       <c r="G14" t="n">
-        <v>3.06197309494019</v>
+        <v>3.06197357177734</v>
       </c>
       <c r="H14" t="n">
         <v>22052655</v>
@@ -833,7 +833,7 @@
         <v>6.36531209945679</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3261923789978</v>
+        <v>3.32619261741638</v>
       </c>
       <c r="H16" t="n">
         <v>20677475</v>
@@ -891,7 +891,7 @@
         <v>6.62521696090698</v>
       </c>
       <c r="G18" t="n">
-        <v>3.46200609207153</v>
+        <v>3.46200561523438</v>
       </c>
       <c r="H18" t="n">
         <v>29100832</v>
@@ -920,7 +920,7 @@
         <v>6.56851005554199</v>
       </c>
       <c r="G19" t="n">
-        <v>3.43237400054932</v>
+        <v>3.43237328529358</v>
       </c>
       <c r="H19" t="n">
         <v>46908275</v>
@@ -949,7 +949,7 @@
         <v>6.09595584869385</v>
       </c>
       <c r="G20" t="n">
-        <v>3.18544054031372</v>
+        <v>3.1854407787323</v>
       </c>
       <c r="H20" t="n">
         <v>37383419</v>
@@ -1007,7 +1007,7 @@
         <v>6.04869985580444</v>
       </c>
       <c r="G22" t="n">
-        <v>3.16074681282043</v>
+        <v>3.16074705123901</v>
       </c>
       <c r="H22" t="n">
         <v>15295313</v>
@@ -1123,7 +1123,7 @@
         <v>5.64230298995972</v>
       </c>
       <c r="G26" t="n">
-        <v>2.94838452339172</v>
+        <v>2.94838428497314</v>
       </c>
       <c r="H26" t="n">
         <v>30833975</v>
@@ -1152,7 +1152,7 @@
         <v>5.08468914031982</v>
       </c>
       <c r="G27" t="n">
-        <v>2.65700316429138</v>
+        <v>2.6570029258728</v>
       </c>
       <c r="H27" t="n">
         <v>33984093</v>
@@ -1181,7 +1181,7 @@
         <v>4.94292211532593</v>
       </c>
       <c r="G28" t="n">
-        <v>2.58292293548584</v>
+        <v>2.58292317390442</v>
       </c>
       <c r="H28" t="n">
         <v>34764384</v>
@@ -1210,7 +1210,7 @@
         <v>5.23118114471436</v>
       </c>
       <c r="G29" t="n">
-        <v>2.73355269432068</v>
+        <v>2.7335524559021</v>
       </c>
       <c r="H29" t="n">
         <v>29457120</v>
@@ -1268,7 +1268,7 @@
         <v>5.13667011260986</v>
       </c>
       <c r="G31" t="n">
-        <v>2.68416571617126</v>
+        <v>2.68416595458984</v>
       </c>
       <c r="H31" t="n">
         <v>22119082</v>
@@ -1297,7 +1297,7 @@
         <v>5.36349582672119</v>
       </c>
       <c r="G32" t="n">
-        <v>2.80269336700439</v>
+        <v>2.80269384384155</v>
       </c>
       <c r="H32" t="n">
         <v>21315364</v>
@@ -1326,7 +1326,7 @@
         <v>5.27843618392944</v>
       </c>
       <c r="G33" t="n">
-        <v>2.75824594497681</v>
+        <v>2.75824570655823</v>
       </c>
       <c r="H33" t="n">
         <v>22966997</v>
@@ -1355,7 +1355,7 @@
         <v>5.54779195785522</v>
       </c>
       <c r="G34" t="n">
-        <v>2.89899778366089</v>
+        <v>2.89899754524231</v>
       </c>
       <c r="H34" t="n">
         <v>21467582</v>
@@ -1413,7 +1413,7 @@
         <v>5.37767219543457</v>
       </c>
       <c r="G36" t="n">
-        <v>2.81010150909424</v>
+        <v>2.81010103225708</v>
       </c>
       <c r="H36" t="n">
         <v>14966595</v>
@@ -1442,7 +1442,7 @@
         <v>5.59977293014526</v>
       </c>
       <c r="G37" t="n">
-        <v>2.92615985870361</v>
+        <v>2.92616009712219</v>
       </c>
       <c r="H37" t="n">
         <v>15560828</v>
@@ -1471,7 +1471,7 @@
         <v>5.43437910079956</v>
       </c>
       <c r="G38" t="n">
-        <v>2.83973383903503</v>
+        <v>2.83973336219788</v>
       </c>
       <c r="H38" t="n">
         <v>15820069</v>
@@ -1500,7 +1500,7 @@
         <v>5.21700382232666</v>
       </c>
       <c r="G39" t="n">
-        <v>2.7261438369751</v>
+        <v>2.72614431381226</v>
       </c>
       <c r="H39" t="n">
         <v>23077078</v>
@@ -1529,7 +1529,7 @@
         <v>5.43437910079956</v>
       </c>
       <c r="G40" t="n">
-        <v>2.83973383903503</v>
+        <v>2.83973336219788</v>
       </c>
       <c r="H40" t="n">
         <v>26385500</v>
@@ -1558,7 +1558,7 @@
         <v>5.75099086761475</v>
       </c>
       <c r="G41" t="n">
-        <v>3.00517916679382</v>
+        <v>3.00517892837524</v>
       </c>
       <c r="H41" t="n">
         <v>30107591</v>
@@ -1587,7 +1587,7 @@
         <v>5.9967188835144</v>
       </c>
       <c r="G42" t="n">
-        <v>3.13358402252197</v>
+        <v>3.13358426094055</v>
       </c>
       <c r="H42" t="n">
         <v>30013061</v>
@@ -1616,7 +1616,7 @@
         <v>6.31333112716675</v>
       </c>
       <c r="G43" t="n">
-        <v>3.29902958869934</v>
+        <v>3.29902982711792</v>
       </c>
       <c r="H43" t="n">
         <v>35951217</v>
@@ -1645,7 +1645,7 @@
         <v>6.46454811096191</v>
       </c>
       <c r="G44" t="n">
-        <v>3.37804841995239</v>
+        <v>3.37804818153381</v>
       </c>
       <c r="H44" t="n">
         <v>30033851</v>
@@ -1674,7 +1674,7 @@
         <v>6.60631513595581</v>
       </c>
       <c r="G45" t="n">
-        <v>3.45212841033936</v>
+        <v>3.45212864875793</v>
       </c>
       <c r="H45" t="n">
         <v>25716643</v>
@@ -1732,7 +1732,7 @@
         <v>6.58741283416748</v>
       </c>
       <c r="G47" t="n">
-        <v>3.44225072860718</v>
+        <v>3.44225144386292</v>
       </c>
       <c r="H47" t="n">
         <v>19278573</v>
@@ -1761,7 +1761,7 @@
         <v>6.29442882537842</v>
       </c>
       <c r="G48" t="n">
-        <v>3.28915238380432</v>
+        <v>3.28915286064148</v>
       </c>
       <c r="H48" t="n">
         <v>24895913</v>
@@ -1790,7 +1790,7 @@
         <v>6.32750797271729</v>
       </c>
       <c r="G49" t="n">
-        <v>3.30643749237061</v>
+        <v>3.30643820762634</v>
       </c>
       <c r="H49" t="n">
         <v>22487975</v>
@@ -1819,7 +1819,7 @@
         <v>6.14321088790894</v>
       </c>
       <c r="G50" t="n">
-        <v>3.21013331413269</v>
+        <v>3.21013355255127</v>
       </c>
       <c r="H50" t="n">
         <v>37496819</v>
@@ -1877,7 +1877,7 @@
         <v>6.59686422348022</v>
       </c>
       <c r="G52" t="n">
-        <v>3.44718956947327</v>
+        <v>3.44719004631042</v>
       </c>
       <c r="H52" t="n">
         <v>21719280</v>
@@ -1906,7 +1906,7 @@
         <v>6.43146991729736</v>
       </c>
       <c r="G53" t="n">
-        <v>3.36076331138611</v>
+        <v>3.36076354980469</v>
       </c>
       <c r="H53" t="n">
         <v>16213374</v>
@@ -1935,7 +1935,7 @@
         <v>6.59213781356812</v>
       </c>
       <c r="G54" t="n">
-        <v>3.44472026824951</v>
+        <v>3.44471979141235</v>
       </c>
       <c r="H54" t="n">
         <v>18927252</v>
@@ -1964,7 +1964,7 @@
         <v>6.55433416366577</v>
       </c>
       <c r="G55" t="n">
-        <v>3.42496585845947</v>
+        <v>3.42496562004089</v>
       </c>
       <c r="H55" t="n">
         <v>20625461</v>
@@ -1993,7 +1993,7 @@
         <v>6.72917890548706</v>
       </c>
       <c r="G56" t="n">
-        <v>3.51633167266846</v>
+        <v>3.51633095741272</v>
       </c>
       <c r="H56" t="n">
         <v>22735682</v>
@@ -2022,7 +2022,7 @@
         <v>6.7008261680603</v>
       </c>
       <c r="G57" t="n">
-        <v>3.50151515007019</v>
+        <v>3.50151538848877</v>
       </c>
       <c r="H57" t="n">
         <v>16580612</v>
@@ -2051,7 +2051,7 @@
         <v>6.72445297241211</v>
       </c>
       <c r="G58" t="n">
-        <v>3.51386165618896</v>
+        <v>3.51386117935181</v>
       </c>
       <c r="H58" t="n">
         <v>15216180</v>
@@ -2080,7 +2080,7 @@
         <v>6.6535701751709</v>
       </c>
       <c r="G59" t="n">
-        <v>3.47682189941406</v>
+        <v>3.4768214225769</v>
       </c>
       <c r="H59" t="n">
         <v>16307668</v>
@@ -2109,7 +2109,7 @@
         <v>6.37948894500732</v>
       </c>
       <c r="G60" t="n">
-        <v>3.3336009979248</v>
+        <v>3.33360028266907</v>
       </c>
       <c r="H60" t="n">
         <v>16981342</v>
@@ -2138,7 +2138,7 @@
         <v>6.46454811096191</v>
       </c>
       <c r="G61" t="n">
-        <v>3.37804841995239</v>
+        <v>3.37804818153381</v>
       </c>
       <c r="H61" t="n">
         <v>11336845</v>
@@ -2167,7 +2167,7 @@
         <v>6.84259176254272</v>
       </c>
       <c r="G62" t="n">
-        <v>3.57559490203857</v>
+        <v>3.57559537887573</v>
       </c>
       <c r="H62" t="n">
         <v>28129056</v>
@@ -2196,7 +2196,7 @@
         <v>6.71027708053589</v>
       </c>
       <c r="G63" t="n">
-        <v>3.50645351409912</v>
+        <v>3.50645422935486</v>
       </c>
       <c r="H63" t="n">
         <v>21163552</v>
@@ -2225,7 +2225,7 @@
         <v>6.38421392440796</v>
       </c>
       <c r="G64" t="n">
-        <v>3.33606958389282</v>
+        <v>3.3360698223114</v>
       </c>
       <c r="H64" t="n">
         <v>24990642</v>
@@ -2254,7 +2254,7 @@
         <v>6.40784215927124</v>
       </c>
       <c r="G65" t="n">
-        <v>3.34841656684875</v>
+        <v>3.34841680526733</v>
       </c>
       <c r="H65" t="n">
         <v>17468544</v>
@@ -2283,7 +2283,7 @@
         <v>6.08650493621826</v>
       </c>
       <c r="G66" t="n">
-        <v>3.18050169944763</v>
+        <v>3.18050146102905</v>
       </c>
       <c r="H66" t="n">
         <v>23044825</v>
@@ -2312,7 +2312,7 @@
         <v>6.00616979598999</v>
       </c>
       <c r="G67" t="n">
-        <v>3.1385223865509</v>
+        <v>3.13852262496948</v>
       </c>
       <c r="H67" t="n">
         <v>24915748</v>
@@ -2370,7 +2370,7 @@
         <v>6.00144481658936</v>
       </c>
       <c r="G69" t="n">
-        <v>3.13605332374573</v>
+        <v>3.13605380058289</v>
       </c>
       <c r="H69" t="n">
         <v>16142642</v>
@@ -2399,7 +2399,7 @@
         <v>6.14793682098389</v>
       </c>
       <c r="G70" t="n">
-        <v>3.21260285377502</v>
+        <v>3.2126030921936</v>
       </c>
       <c r="H70" t="n">
         <v>16632629</v>
@@ -2428,7 +2428,7 @@
         <v>6.06287717819214</v>
       </c>
       <c r="G71" t="n">
-        <v>3.1681547164917</v>
+        <v>3.16815543174744</v>
       </c>
       <c r="H71" t="n">
         <v>13181604</v>
@@ -2515,7 +2515,7 @@
         <v>6.31333112716675</v>
       </c>
       <c r="G74" t="n">
-        <v>3.29902958869934</v>
+        <v>3.29902982711792</v>
       </c>
       <c r="H74" t="n">
         <v>17885182</v>
@@ -2544,7 +2544,7 @@
         <v>6.51180410385132</v>
       </c>
       <c r="G75" t="n">
-        <v>3.40274167060852</v>
+        <v>3.40274214744568</v>
       </c>
       <c r="H75" t="n">
         <v>15875228</v>
@@ -2573,7 +2573,7 @@
         <v>6.71027708053589</v>
       </c>
       <c r="G76" t="n">
-        <v>3.50645351409912</v>
+        <v>3.50645422935486</v>
       </c>
       <c r="H76" t="n">
         <v>20955582</v>
@@ -2631,7 +2631,7 @@
         <v>6.95128011703491</v>
       </c>
       <c r="G78" t="n">
-        <v>3.63238978385925</v>
+        <v>3.63238954544067</v>
       </c>
       <c r="H78" t="n">
         <v>28627119</v>
@@ -2660,7 +2660,7 @@
         <v>6.78588581085205</v>
       </c>
       <c r="G79" t="n">
-        <v>3.54596352577209</v>
+        <v>3.54596328735352</v>
       </c>
       <c r="H79" t="n">
         <v>24764558</v>
@@ -2689,7 +2689,7 @@
         <v>6.8284158706665</v>
       </c>
       <c r="G80" t="n">
-        <v>3.56818771362305</v>
+        <v>3.56818747520447</v>
       </c>
       <c r="H80" t="n">
         <v>20819593</v>
@@ -2718,7 +2718,7 @@
         <v>6.64884519577026</v>
       </c>
       <c r="G81" t="n">
-        <v>3.47435283660889</v>
+        <v>3.47435259819031</v>
       </c>
       <c r="H81" t="n">
         <v>38953938</v>
@@ -2747,7 +2747,7 @@
         <v>6.76225805282593</v>
       </c>
       <c r="G82" t="n">
-        <v>3.53361654281616</v>
+        <v>3.53361630439758</v>
       </c>
       <c r="H82" t="n">
         <v>15984734</v>
@@ -2776,7 +2776,7 @@
         <v>6.92292594909668</v>
       </c>
       <c r="G83" t="n">
-        <v>3.61757349967957</v>
+        <v>3.61757326126099</v>
       </c>
       <c r="H83" t="n">
         <v>19414695</v>
@@ -2805,7 +2805,7 @@
         <v>6.62521696090698</v>
       </c>
       <c r="G84" t="n">
-        <v>3.46200609207153</v>
+        <v>3.46200561523438</v>
       </c>
       <c r="H84" t="n">
         <v>27031716</v>
@@ -2834,7 +2834,7 @@
         <v>6.72917890548706</v>
       </c>
       <c r="G85" t="n">
-        <v>3.51633167266846</v>
+        <v>3.51633095741272</v>
       </c>
       <c r="H85" t="n">
         <v>16699771</v>
@@ -2892,7 +2892,7 @@
         <v>6.4739990234375</v>
       </c>
       <c r="G87" t="n">
-        <v>3.38298726081848</v>
+        <v>3.38298678398132</v>
       </c>
       <c r="H87" t="n">
         <v>18863492</v>
@@ -2921,7 +2921,7 @@
         <v>6.3086051940918</v>
       </c>
       <c r="G88" t="n">
-        <v>3.29656004905701</v>
+        <v>3.29656028747559</v>
       </c>
       <c r="H88" t="n">
         <v>17228666</v>
@@ -3008,7 +3008,7 @@
         <v>6.44092082977295</v>
       </c>
       <c r="G91" t="n">
-        <v>3.36570143699646</v>
+        <v>3.36570167541504</v>
       </c>
       <c r="H91" t="n">
         <v>16137773</v>
@@ -3037,7 +3037,7 @@
         <v>6.34640979766846</v>
       </c>
       <c r="G92" t="n">
-        <v>3.31631541252136</v>
+        <v>3.3163149356842</v>
       </c>
       <c r="H92" t="n">
         <v>15026251</v>
@@ -3066,7 +3066,7 @@
         <v>6.32750797271729</v>
       </c>
       <c r="G93" t="n">
-        <v>3.30643749237061</v>
+        <v>3.30643820762634</v>
       </c>
       <c r="H93" t="n">
         <v>12472161</v>
@@ -3095,7 +3095,7 @@
         <v>6.46927404403687</v>
       </c>
       <c r="G94" t="n">
-        <v>3.38051819801331</v>
+        <v>3.38051772117615</v>
       </c>
       <c r="H94" t="n">
         <v>14055300</v>
@@ -3124,7 +3124,7 @@
         <v>6.37476301193237</v>
       </c>
       <c r="G95" t="n">
-        <v>3.33113145828247</v>
+        <v>3.33113121986389</v>
       </c>
       <c r="H95" t="n">
         <v>9563240</v>
@@ -3153,7 +3153,7 @@
         <v>5.94946384429932</v>
       </c>
       <c r="G96" t="n">
-        <v>3.108891248703</v>
+        <v>3.10889101028442</v>
       </c>
       <c r="H96" t="n">
         <v>34740090</v>
@@ -3182,7 +3182,7 @@
         <v>5.95891523361206</v>
       </c>
       <c r="G97" t="n">
-        <v>3.11382985115051</v>
+        <v>3.11382961273193</v>
       </c>
       <c r="H97" t="n">
         <v>42285564</v>
@@ -3211,7 +3211,7 @@
         <v>5.93528699874878</v>
       </c>
       <c r="G98" t="n">
-        <v>3.10148334503174</v>
+        <v>3.10148310661316</v>
       </c>
       <c r="H98" t="n">
         <v>17904156</v>
@@ -3240,7 +3240,7 @@
         <v>5.9636402130127</v>
       </c>
       <c r="G99" t="n">
-        <v>3.11629915237427</v>
+        <v>3.11629891395569</v>
       </c>
       <c r="H99" t="n">
         <v>20701775</v>
@@ -3269,7 +3269,7 @@
         <v>5.69900989532471</v>
       </c>
       <c r="G100" t="n">
-        <v>2.97801637649536</v>
+        <v>2.97801613807678</v>
       </c>
       <c r="H100" t="n">
         <v>36088305</v>
@@ -3298,7 +3298,7 @@
         <v>5.87385511398315</v>
       </c>
       <c r="G101" t="n">
-        <v>3.06938123703003</v>
+        <v>3.06938147544861</v>
       </c>
       <c r="H101" t="n">
         <v>20548077</v>
@@ -3327,7 +3327,7 @@
         <v>6.04869985580444</v>
       </c>
       <c r="G102" t="n">
-        <v>3.16074681282043</v>
+        <v>3.16074705123901</v>
       </c>
       <c r="H102" t="n">
         <v>16430587</v>
@@ -3356,7 +3356,7 @@
         <v>5.97781705856323</v>
       </c>
       <c r="G103" t="n">
-        <v>3.12370705604553</v>
+        <v>3.12370681762695</v>
       </c>
       <c r="H103" t="n">
         <v>12927433</v>
@@ -3385,7 +3385,7 @@
         <v>5.87858104705811</v>
       </c>
       <c r="G104" t="n">
-        <v>3.0718514919281</v>
+        <v>3.07185101509094</v>
       </c>
       <c r="H104" t="n">
         <v>14384783</v>
@@ -3414,7 +3414,7 @@
         <v>6.04397487640381</v>
       </c>
       <c r="G105" t="n">
-        <v>3.15827775001526</v>
+        <v>3.15827751159668</v>
       </c>
       <c r="H105" t="n">
         <v>8345509</v>
@@ -3443,7 +3443,7 @@
         <v>6.06287717819214</v>
       </c>
       <c r="G106" t="n">
-        <v>3.1681547164917</v>
+        <v>3.16815543174744</v>
       </c>
       <c r="H106" t="n">
         <v>17125303</v>
@@ -3472,7 +3472,7 @@
         <v>5.88330602645874</v>
       </c>
       <c r="G107" t="n">
-        <v>3.07432007789612</v>
+        <v>3.07432055473328</v>
       </c>
       <c r="H107" t="n">
         <v>14273053</v>
@@ -3501,7 +3501,7 @@
         <v>6.00144481658936</v>
       </c>
       <c r="G108" t="n">
-        <v>3.13605332374573</v>
+        <v>3.13605380058289</v>
       </c>
       <c r="H108" t="n">
         <v>15841708</v>
@@ -3530,7 +3530,7 @@
         <v>5.82187414169312</v>
       </c>
       <c r="G109" t="n">
-        <v>3.04221892356873</v>
+        <v>3.04221868515015</v>
       </c>
       <c r="H109" t="n">
         <v>16014681</v>
@@ -3559,7 +3559,7 @@
         <v>5.81714820861816</v>
       </c>
       <c r="G110" t="n">
-        <v>3.03974962234497</v>
+        <v>3.03974938392639</v>
       </c>
       <c r="H110" t="n">
         <v>12333558</v>
@@ -3588,7 +3588,7 @@
         <v>6.06287717819214</v>
       </c>
       <c r="G111" t="n">
-        <v>3.1681547164917</v>
+        <v>3.16815543174744</v>
       </c>
       <c r="H111" t="n">
         <v>15403740</v>
@@ -3617,7 +3617,7 @@
         <v>6.02507209777832</v>
       </c>
       <c r="G112" t="n">
-        <v>3.14840054512024</v>
+        <v>3.14840030670166</v>
       </c>
       <c r="H112" t="n">
         <v>23618338</v>
@@ -3704,7 +3704,7 @@
         <v>5.60922384262085</v>
       </c>
       <c r="G115" t="n">
-        <v>2.93109822273254</v>
+        <v>2.9310986995697</v>
       </c>
       <c r="H115" t="n">
         <v>20043519</v>
@@ -3791,7 +3791,7 @@
         <v>5.47690916061401</v>
       </c>
       <c r="G118" t="n">
-        <v>2.86195731163025</v>
+        <v>2.86195755004883</v>
       </c>
       <c r="H118" t="n">
         <v>21847770</v>
@@ -3820,7 +3820,7 @@
         <v>5.6139497756958</v>
       </c>
       <c r="G119" t="n">
-        <v>2.93356800079346</v>
+        <v>2.93356847763062</v>
       </c>
       <c r="H119" t="n">
         <v>21282200</v>
@@ -3849,7 +3849,7 @@
         <v>5.92111015319824</v>
       </c>
       <c r="G120" t="n">
-        <v>3.09407472610474</v>
+        <v>3.09407496452332</v>
       </c>
       <c r="H120" t="n">
         <v>16973550</v>
@@ -3878,7 +3878,7 @@
         <v>5.90693378448486</v>
       </c>
       <c r="G121" t="n">
-        <v>3.08666682243347</v>
+        <v>3.08666658401489</v>
       </c>
       <c r="H121" t="n">
         <v>14606198</v>
@@ -3907,7 +3907,7 @@
         <v>5.83605098724365</v>
       </c>
       <c r="G122" t="n">
-        <v>3.04962730407715</v>
+        <v>3.04962754249573</v>
       </c>
       <c r="H122" t="n">
         <v>12203963</v>
@@ -3936,7 +3936,7 @@
         <v>5.95418882369995</v>
       </c>
       <c r="G123" t="n">
-        <v>3.11135983467102</v>
+        <v>3.1113600730896</v>
       </c>
       <c r="H123" t="n">
         <v>19064312</v>
@@ -3965,7 +3965,7 @@
         <v>5.39657497406006</v>
       </c>
       <c r="G124" t="n">
-        <v>2.81997895240784</v>
+        <v>2.81997919082642</v>
       </c>
       <c r="H124" t="n">
         <v>43250672</v>
@@ -3994,7 +3994,7 @@
         <v>5.06106090545654</v>
       </c>
       <c r="G125" t="n">
-        <v>2.64465665817261</v>
+        <v>2.64465641975403</v>
       </c>
       <c r="H125" t="n">
         <v>30578370</v>
@@ -4023,7 +4023,7 @@
         <v>5.13667011260986</v>
       </c>
       <c r="G126" t="n">
-        <v>2.68416571617126</v>
+        <v>2.68416595458984</v>
       </c>
       <c r="H126" t="n">
         <v>19933472</v>
@@ -4052,7 +4052,7 @@
         <v>5.09414005279541</v>
       </c>
       <c r="G127" t="n">
-        <v>2.66194200515747</v>
+        <v>2.66194176673889</v>
       </c>
       <c r="H127" t="n">
         <v>21487196</v>
@@ -4110,7 +4110,7 @@
         <v>5.30206394195557</v>
       </c>
       <c r="G129" t="n">
-        <v>2.770592212677</v>
+        <v>2.77059268951416</v>
       </c>
       <c r="H129" t="n">
         <v>22681420</v>
@@ -4139,7 +4139,7 @@
         <v>5.06106090545654</v>
       </c>
       <c r="G130" t="n">
-        <v>2.64465665817261</v>
+        <v>2.64465641975403</v>
       </c>
       <c r="H130" t="n">
         <v>15552079</v>
@@ -4168,7 +4168,7 @@
         <v>4.84841108322144</v>
       </c>
       <c r="G131" t="n">
-        <v>2.533536195755</v>
+        <v>2.53353595733643</v>
       </c>
       <c r="H131" t="n">
         <v>18483988</v>
@@ -4197,7 +4197,7 @@
         <v>4.82950878143311</v>
       </c>
       <c r="G132" t="n">
-        <v>2.52365875244141</v>
+        <v>2.52365851402283</v>
       </c>
       <c r="H132" t="n">
         <v>28392387</v>
@@ -4226,7 +4226,7 @@
         <v>4.87676382064819</v>
       </c>
       <c r="G133" t="n">
-        <v>2.54835176467896</v>
+        <v>2.54835200309753</v>
       </c>
       <c r="H133" t="n">
         <v>19621989</v>
@@ -4255,7 +4255,7 @@
         <v>5.23118114471436</v>
       </c>
       <c r="G134" t="n">
-        <v>2.73355269432068</v>
+        <v>2.7335524559021</v>
       </c>
       <c r="H134" t="n">
         <v>20083823</v>
@@ -4313,7 +4313,7 @@
         <v>5.67065620422363</v>
       </c>
       <c r="G136" t="n">
-        <v>2.96320009231567</v>
+        <v>2.96320033073425</v>
       </c>
       <c r="H136" t="n">
         <v>25011102</v>
@@ -4342,7 +4342,7 @@
         <v>5.57142019271851</v>
       </c>
       <c r="G137" t="n">
-        <v>2.91134452819824</v>
+        <v>2.9113450050354</v>
       </c>
       <c r="H137" t="n">
         <v>18167570</v>
@@ -4371,7 +4371,7 @@
         <v>5.73681402206421</v>
       </c>
       <c r="G138" t="n">
-        <v>2.99777102470398</v>
+        <v>2.9977707862854</v>
       </c>
       <c r="H138" t="n">
         <v>16879400</v>
@@ -4429,7 +4429,7 @@
         <v>5.85967779159546</v>
       </c>
       <c r="G140" t="n">
-        <v>3.06197309494019</v>
+        <v>3.06197357177734</v>
       </c>
       <c r="H140" t="n">
         <v>16667375</v>
@@ -4458,7 +4458,7 @@
         <v>5.66120481491089</v>
       </c>
       <c r="G141" t="n">
-        <v>2.95826172828674</v>
+        <v>2.95826125144958</v>
       </c>
       <c r="H141" t="n">
         <v>23600766</v>
@@ -4516,7 +4516,7 @@
         <v>5.94946384429932</v>
       </c>
       <c r="G143" t="n">
-        <v>3.108891248703</v>
+        <v>3.10889101028442</v>
       </c>
       <c r="H143" t="n">
         <v>23453575</v>
@@ -4545,7 +4545,7 @@
         <v>5.9116587638855</v>
       </c>
       <c r="G144" t="n">
-        <v>3.08913588523865</v>
+        <v>3.08913636207581</v>
       </c>
       <c r="H144" t="n">
         <v>13575162</v>
@@ -4574,7 +4574,7 @@
         <v>5.93056201934814</v>
       </c>
       <c r="G145" t="n">
-        <v>3.09901404380798</v>
+        <v>3.0990138053894</v>
       </c>
       <c r="H145" t="n">
         <v>15845076</v>
@@ -4632,7 +4632,7 @@
         <v>5.8691291809082</v>
       </c>
       <c r="G147" t="n">
-        <v>3.06691193580627</v>
+        <v>3.06691217422485</v>
       </c>
       <c r="H147" t="n">
         <v>47571097</v>
@@ -4661,7 +4661,7 @@
         <v>5.39657497406006</v>
       </c>
       <c r="G148" t="n">
-        <v>2.81997895240784</v>
+        <v>2.81997919082642</v>
       </c>
       <c r="H148" t="n">
         <v>41645170</v>
@@ -4690,7 +4690,7 @@
         <v>5.44383001327515</v>
       </c>
       <c r="G149" t="n">
-        <v>2.84467220306396</v>
+        <v>2.84467244148254</v>
       </c>
       <c r="H149" t="n">
         <v>19085528</v>
@@ -4748,7 +4748,7 @@
         <v>5.15084600448608</v>
       </c>
       <c r="G151" t="n">
-        <v>2.69157338142395</v>
+        <v>2.69157361984253</v>
       </c>
       <c r="H151" t="n">
         <v>22868288</v>
@@ -4835,7 +4835,7 @@
         <v>5.75099086761475</v>
       </c>
       <c r="G154" t="n">
-        <v>3.00517916679382</v>
+        <v>3.00517892837524</v>
       </c>
       <c r="H154" t="n">
         <v>18235708</v>
@@ -4864,7 +4864,7 @@
         <v>5.75099086761475</v>
       </c>
       <c r="G155" t="n">
-        <v>3.00517916679382</v>
+        <v>3.00517892837524</v>
       </c>
       <c r="H155" t="n">
         <v>11793612</v>
@@ -4922,7 +4922,7 @@
         <v>5.85967779159546</v>
       </c>
       <c r="G157" t="n">
-        <v>3.06197309494019</v>
+        <v>3.06197357177734</v>
       </c>
       <c r="H157" t="n">
         <v>12745349</v>
@@ -4951,7 +4951,7 @@
         <v>5.82187414169312</v>
       </c>
       <c r="G158" t="n">
-        <v>3.04221892356873</v>
+        <v>3.04221868515015</v>
       </c>
       <c r="H158" t="n">
         <v>12156476</v>
@@ -4980,7 +4980,7 @@
         <v>5.81714820861816</v>
       </c>
       <c r="G159" t="n">
-        <v>3.03974962234497</v>
+        <v>3.03974938392639</v>
       </c>
       <c r="H159" t="n">
         <v>12630022</v>
@@ -5009,7 +5009,7 @@
         <v>5.71791219711304</v>
       </c>
       <c r="G160" t="n">
-        <v>2.98789429664612</v>
+        <v>2.98789358139038</v>
       </c>
       <c r="H160" t="n">
         <v>14267856</v>
@@ -5096,7 +5096,7 @@
         <v>5.51943922042847</v>
       </c>
       <c r="G163" t="n">
-        <v>2.8841814994812</v>
+        <v>2.88418173789978</v>
       </c>
       <c r="H163" t="n">
         <v>12750149</v>
@@ -5125,7 +5125,7 @@
         <v>5.58559703826904</v>
       </c>
       <c r="G164" t="n">
-        <v>2.91875314712524</v>
+        <v>2.91875243186951</v>
       </c>
       <c r="H164" t="n">
         <v>11989677</v>
@@ -5154,7 +5154,7 @@
         <v>5.69900989532471</v>
       </c>
       <c r="G165" t="n">
-        <v>2.97801637649536</v>
+        <v>2.97801613807678</v>
       </c>
       <c r="H165" t="n">
         <v>11936237</v>
@@ -5212,7 +5212,7 @@
         <v>5.79824590682983</v>
       </c>
       <c r="G167" t="n">
-        <v>3.02987217903137</v>
+        <v>3.02987194061279</v>
       </c>
       <c r="H167" t="n">
         <v>17869525</v>
@@ -5241,7 +5241,7 @@
         <v>5.82659912109375</v>
       </c>
       <c r="G168" t="n">
-        <v>3.04468774795532</v>
+        <v>3.0446879863739</v>
       </c>
       <c r="H168" t="n">
         <v>9059933</v>
@@ -5270,7 +5270,7 @@
         <v>5.72736310958862</v>
       </c>
       <c r="G169" t="n">
-        <v>2.99283218383789</v>
+        <v>2.99283242225647</v>
       </c>
       <c r="H169" t="n">
         <v>10095115</v>
@@ -5299,7 +5299,7 @@
         <v>5.8691291809082</v>
       </c>
       <c r="G170" t="n">
-        <v>3.06691193580627</v>
+        <v>3.06691217422485</v>
       </c>
       <c r="H170" t="n">
         <v>11859192</v>
@@ -5328,7 +5328,7 @@
         <v>5.85495281219482</v>
       </c>
       <c r="G171" t="n">
-        <v>3.05950450897217</v>
+        <v>3.05950427055359</v>
       </c>
       <c r="H171" t="n">
         <v>13659997</v>
@@ -5357,7 +5357,7 @@
         <v>5.69428396224976</v>
       </c>
       <c r="G172" t="n">
-        <v>2.97554683685303</v>
+        <v>2.97554636001587</v>
       </c>
       <c r="H172" t="n">
         <v>28828993</v>
@@ -5415,7 +5415,7 @@
         <v>5.64702892303467</v>
       </c>
       <c r="G174" t="n">
-        <v>2.95085382461548</v>
+        <v>2.9508535861969</v>
       </c>
       <c r="H174" t="n">
         <v>11327362</v>
@@ -5444,7 +5444,7 @@
         <v>5.68010807037354</v>
       </c>
       <c r="G175" t="n">
-        <v>2.96813917160034</v>
+        <v>2.96813941001892</v>
       </c>
       <c r="H175" t="n">
         <v>16803940</v>
@@ -5473,7 +5473,7 @@
         <v>5.81714820861816</v>
       </c>
       <c r="G176" t="n">
-        <v>3.03974962234497</v>
+        <v>3.03974938392639</v>
       </c>
       <c r="H176" t="n">
         <v>15431752</v>
@@ -5531,7 +5531,7 @@
         <v>5.69428396224976</v>
       </c>
       <c r="G178" t="n">
-        <v>2.97554683685303</v>
+        <v>2.97554636001587</v>
       </c>
       <c r="H178" t="n">
         <v>10454962</v>
@@ -5560,7 +5560,7 @@
         <v>5.55724287033081</v>
       </c>
       <c r="G179" t="n">
-        <v>2.90393590927124</v>
+        <v>2.90393567085266</v>
       </c>
       <c r="H179" t="n">
         <v>17581614</v>
@@ -5618,7 +5618,7 @@
         <v>5.39657497406006</v>
       </c>
       <c r="G181" t="n">
-        <v>2.81997895240784</v>
+        <v>2.81997919082642</v>
       </c>
       <c r="H181" t="n">
         <v>17241177</v>
@@ -5676,7 +5676,7 @@
         <v>5.38712406158447</v>
       </c>
       <c r="G183" t="n">
-        <v>2.81504034996033</v>
+        <v>2.81504058837891</v>
       </c>
       <c r="H183" t="n">
         <v>19776409</v>
@@ -5734,7 +5734,7 @@
         <v>5.42020177841187</v>
       </c>
       <c r="G185" t="n">
-        <v>2.83232474327087</v>
+        <v>2.83232522010803</v>
       </c>
       <c r="H185" t="n">
         <v>9097857</v>
@@ -5763,7 +5763,7 @@
         <v>5.37767219543457</v>
       </c>
       <c r="G186" t="n">
-        <v>2.81010150909424</v>
+        <v>2.81010103225708</v>
       </c>
       <c r="H186" t="n">
         <v>12947255</v>
@@ -5792,7 +5792,7 @@
         <v>5.4863600730896</v>
       </c>
       <c r="G187" t="n">
-        <v>2.86689686775208</v>
+        <v>2.86689639091492</v>
       </c>
       <c r="H187" t="n">
         <v>11549870</v>
@@ -5821,7 +5821,7 @@
         <v>5.44383001327515</v>
       </c>
       <c r="G188" t="n">
-        <v>2.84467220306396</v>
+        <v>2.84467244148254</v>
       </c>
       <c r="H188" t="n">
         <v>8909677</v>
@@ -5879,7 +5879,7 @@
         <v>5.13667011260986</v>
       </c>
       <c r="G190" t="n">
-        <v>2.68416571617126</v>
+        <v>2.68416595458984</v>
       </c>
       <c r="H190" t="n">
         <v>17739843</v>
@@ -5908,7 +5908,7 @@
         <v>5.18392515182495</v>
       </c>
       <c r="G191" t="n">
-        <v>2.70885872840881</v>
+        <v>2.70885920524597</v>
       </c>
       <c r="H191" t="n">
         <v>10693015</v>
@@ -6024,7 +6024,7 @@
         <v>5.43910503387451</v>
       </c>
       <c r="G195" t="n">
-        <v>2.84220361709595</v>
+        <v>2.84220337867737</v>
       </c>
       <c r="H195" t="n">
         <v>12381882</v>
@@ -6053,7 +6053,7 @@
         <v>5.533616065979</v>
       </c>
       <c r="G196" t="n">
-        <v>2.89158964157104</v>
+        <v>2.8915901184082</v>
       </c>
       <c r="H196" t="n">
         <v>13835116</v>
@@ -6082,7 +6082,7 @@
         <v>5.49581098556519</v>
       </c>
       <c r="G197" t="n">
-        <v>2.87183547019958</v>
+        <v>2.87183475494385</v>
       </c>
       <c r="H197" t="n">
         <v>18838399</v>
@@ -6111,7 +6111,7 @@
         <v>5.4863600730896</v>
       </c>
       <c r="G198" t="n">
-        <v>2.86689686775208</v>
+        <v>2.86689639091492</v>
       </c>
       <c r="H198" t="n">
         <v>13540215</v>
@@ -6140,7 +6140,7 @@
         <v>5.58559703826904</v>
       </c>
       <c r="G199" t="n">
-        <v>2.91875314712524</v>
+        <v>2.91875243186951</v>
       </c>
       <c r="H199" t="n">
         <v>10269389</v>
@@ -6169,7 +6169,7 @@
         <v>5.5666937828064</v>
       </c>
       <c r="G200" t="n">
-        <v>2.90887427330017</v>
+        <v>2.90887451171875</v>
       </c>
       <c r="H200" t="n">
         <v>14397429</v>
@@ -6198,7 +6198,7 @@
         <v>5.4863600730896</v>
       </c>
       <c r="G201" t="n">
-        <v>2.86689686775208</v>
+        <v>2.86689639091492</v>
       </c>
       <c r="H201" t="n">
         <v>17084891</v>
@@ -6227,7 +6227,7 @@
         <v>5.29733800888062</v>
       </c>
       <c r="G202" t="n">
-        <v>2.76812314987183</v>
+        <v>2.76812219619751</v>
       </c>
       <c r="H202" t="n">
         <v>19611636</v>
@@ -6256,7 +6256,7 @@
         <v>5.42020177841187</v>
       </c>
       <c r="G203" t="n">
-        <v>2.83232474327087</v>
+        <v>2.83232522010803</v>
       </c>
       <c r="H203" t="n">
         <v>13593525</v>
@@ -6285,7 +6285,7 @@
         <v>5.43437910079956</v>
       </c>
       <c r="G204" t="n">
-        <v>2.83973383903503</v>
+        <v>2.83973336219788</v>
       </c>
       <c r="H204" t="n">
         <v>8767271</v>
@@ -6314,7 +6314,7 @@
         <v>5.40129995346069</v>
       </c>
       <c r="G205" t="n">
-        <v>2.82244849205017</v>
+        <v>2.82244801521301</v>
       </c>
       <c r="H205" t="n">
         <v>17189235</v>
@@ -6343,7 +6343,7 @@
         <v>5.43910503387451</v>
       </c>
       <c r="G206" t="n">
-        <v>2.84220361709595</v>
+        <v>2.84220337867737</v>
       </c>
       <c r="H206" t="n">
         <v>12130990</v>
@@ -6401,7 +6401,7 @@
         <v>5.47690916061401</v>
       </c>
       <c r="G208" t="n">
-        <v>2.86195731163025</v>
+        <v>2.86195755004883</v>
       </c>
       <c r="H208" t="n">
         <v>13595747</v>
@@ -6430,7 +6430,7 @@
         <v>5.57142019271851</v>
       </c>
       <c r="G209" t="n">
-        <v>2.91134452819824</v>
+        <v>2.9113450050354</v>
       </c>
       <c r="H209" t="n">
         <v>12171586</v>
@@ -6488,7 +6488,7 @@
         <v>5.8691291809082</v>
       </c>
       <c r="G211" t="n">
-        <v>3.06691193580627</v>
+        <v>3.06691217422485</v>
       </c>
       <c r="H211" t="n">
         <v>27688969</v>
@@ -6517,7 +6517,7 @@
         <v>6.22354507446289</v>
       </c>
       <c r="G212" t="n">
-        <v>3.25211191177368</v>
+        <v>3.25211238861084</v>
       </c>
       <c r="H212" t="n">
         <v>40077812</v>
@@ -6575,7 +6575,7 @@
         <v>6.30388021469116</v>
       </c>
       <c r="G214" t="n">
-        <v>3.29409122467041</v>
+        <v>3.29409170150757</v>
       </c>
       <c r="H214" t="n">
         <v>17239031</v>
@@ -6604,7 +6604,7 @@
         <v>6.23772192001343</v>
       </c>
       <c r="G215" t="n">
-        <v>3.25951981544495</v>
+        <v>3.2595202922821</v>
       </c>
       <c r="H215" t="n">
         <v>20237904</v>
@@ -6662,7 +6662,7 @@
         <v>5.80297183990479</v>
       </c>
       <c r="G217" t="n">
-        <v>3.03234171867371</v>
+        <v>3.03234195709229</v>
       </c>
       <c r="H217" t="n">
         <v>16057076</v>
@@ -6691,7 +6691,7 @@
         <v>5.7935209274292</v>
       </c>
       <c r="G218" t="n">
-        <v>3.0274031162262</v>
+        <v>3.02740335464478</v>
       </c>
       <c r="H218" t="n">
         <v>16831369</v>
@@ -6720,7 +6720,7 @@
         <v>6.09595584869385</v>
       </c>
       <c r="G219" t="n">
-        <v>3.18544054031372</v>
+        <v>3.1854407787323</v>
       </c>
       <c r="H219" t="n">
         <v>19809812</v>
@@ -6749,7 +6749,7 @@
         <v>6.05815076828003</v>
       </c>
       <c r="G220" t="n">
-        <v>3.16568493843079</v>
+        <v>3.16568517684937</v>
       </c>
       <c r="H220" t="n">
         <v>17046712</v>
@@ -6778,7 +6778,7 @@
         <v>5.92111015319824</v>
       </c>
       <c r="G221" t="n">
-        <v>3.09407472610474</v>
+        <v>3.09407496452332</v>
       </c>
       <c r="H221" t="n">
         <v>36627613</v>
@@ -6807,7 +6807,7 @@
         <v>6.38421392440796</v>
       </c>
       <c r="G222" t="n">
-        <v>3.33606958389282</v>
+        <v>3.3360698223114</v>
       </c>
       <c r="H222" t="n">
         <v>44570219</v>
@@ -6836,7 +6836,7 @@
         <v>6.74335622787476</v>
       </c>
       <c r="G223" t="n">
-        <v>3.52373933792114</v>
+        <v>3.52373957633972</v>
       </c>
       <c r="H223" t="n">
         <v>52480266</v>
@@ -6865,7 +6865,7 @@
         <v>6.55433416366577</v>
       </c>
       <c r="G224" t="n">
-        <v>3.42496585845947</v>
+        <v>3.42496562004089</v>
       </c>
       <c r="H224" t="n">
         <v>33513544</v>
@@ -6894,7 +6894,7 @@
         <v>6.50235319137573</v>
       </c>
       <c r="G225" t="n">
-        <v>3.39780330657959</v>
+        <v>3.39780306816101</v>
       </c>
       <c r="H225" t="n">
         <v>22697171</v>
@@ -6923,7 +6923,7 @@
         <v>6.64411878585815</v>
       </c>
       <c r="G226" t="n">
-        <v>3.47188305854797</v>
+        <v>3.47188329696655</v>
       </c>
       <c r="H226" t="n">
         <v>21799819</v>
@@ -6952,7 +6952,7 @@
         <v>6.62049102783203</v>
       </c>
       <c r="G227" t="n">
-        <v>3.45953607559204</v>
+        <v>3.45953631401062</v>
       </c>
       <c r="H227" t="n">
         <v>23176804</v>
@@ -6981,7 +6981,7 @@
         <v>6.65829610824585</v>
       </c>
       <c r="G228" t="n">
-        <v>3.4792914390564</v>
+        <v>3.47929096221924</v>
       </c>
       <c r="H228" t="n">
         <v>17400533</v>
@@ -7039,7 +7039,7 @@
         <v>6.7008261680603</v>
       </c>
       <c r="G230" t="n">
-        <v>3.50151515007019</v>
+        <v>3.50151538848877</v>
       </c>
       <c r="H230" t="n">
         <v>19469458</v>
@@ -7068,7 +7068,7 @@
         <v>6.80478811264038</v>
       </c>
       <c r="G231" t="n">
-        <v>3.55584025382996</v>
+        <v>3.55584049224854</v>
       </c>
       <c r="H231" t="n">
         <v>23054760</v>
@@ -7097,7 +7097,7 @@
         <v>6.92292594909668</v>
       </c>
       <c r="G232" t="n">
-        <v>3.61757349967957</v>
+        <v>3.61757326126099</v>
       </c>
       <c r="H232" t="n">
         <v>18450637</v>
@@ -7126,7 +7126,7 @@
         <v>6.86149406433105</v>
       </c>
       <c r="G233" t="n">
-        <v>3.58547306060791</v>
+        <v>3.58547186851501</v>
       </c>
       <c r="H233" t="n">
         <v>8648665</v>
@@ -7155,7 +7155,7 @@
         <v>6.83314085006714</v>
       </c>
       <c r="G234" t="n">
-        <v>3.57065653800964</v>
+        <v>3.57065582275391</v>
       </c>
       <c r="H234" t="n">
         <v>29540193</v>
@@ -7184,7 +7184,7 @@
         <v>6.81423902511597</v>
       </c>
       <c r="G235" t="n">
-        <v>3.56077909469604</v>
+        <v>3.56077861785889</v>
       </c>
       <c r="H235" t="n">
         <v>18580024</v>
@@ -7213,7 +7213,7 @@
         <v>6.88984823226929</v>
       </c>
       <c r="G236" t="n">
-        <v>3.60028839111328</v>
+        <v>3.60028886795044</v>
       </c>
       <c r="H236" t="n">
         <v>18859938</v>
@@ -7271,7 +7271,7 @@
         <v>6.80951309204102</v>
       </c>
       <c r="G238" t="n">
-        <v>3.55830907821655</v>
+        <v>3.55830931663513</v>
       </c>
       <c r="H238" t="n">
         <v>21362521</v>
@@ -7300,7 +7300,7 @@
         <v>7.12139892578125</v>
       </c>
       <c r="G239" t="n">
-        <v>3.72128558158875</v>
+        <v>3.72128510475159</v>
       </c>
       <c r="H239" t="n">
         <v>37981867</v>
@@ -7329,7 +7329,7 @@
         <v>7.29624509811401</v>
       </c>
       <c r="G240" t="n">
-        <v>3.81265115737915</v>
+        <v>3.81265139579773</v>
       </c>
       <c r="H240" t="n">
         <v>29477831</v>
@@ -7358,7 +7358,7 @@
         <v>7.38130521774292</v>
       </c>
       <c r="G241" t="n">
-        <v>3.8570990562439</v>
+        <v>3.85709929466248</v>
       </c>
       <c r="H241" t="n">
         <v>22963791</v>
@@ -7387,7 +7387,7 @@
         <v>7.52779722213745</v>
       </c>
       <c r="G242" t="n">
-        <v>3.93364858627319</v>
+        <v>3.93364906311035</v>
       </c>
       <c r="H242" t="n">
         <v>32960510</v>
@@ -7445,7 +7445,7 @@
         <v>7.6034049987793</v>
       </c>
       <c r="G244" t="n">
-        <v>3.97315764427185</v>
+        <v>3.97315788269043</v>
       </c>
       <c r="H244" t="n">
         <v>27934866</v>
@@ -7503,7 +7503,7 @@
         <v>7.63648414611816</v>
       </c>
       <c r="G246" t="n">
-        <v>3.99044370651245</v>
+        <v>3.99044322967529</v>
       </c>
       <c r="H246" t="n">
         <v>16004870</v>
@@ -7532,7 +7532,7 @@
         <v>7.9483699798584</v>
       </c>
       <c r="G247" t="n">
-        <v>4.15341901779175</v>
+        <v>4.15341949462891</v>
       </c>
       <c r="H247" t="n">
         <v>23716521</v>
@@ -7590,7 +7590,7 @@
         <v>8.07123470306396</v>
       </c>
       <c r="G249" t="n">
-        <v>4.21762180328369</v>
+        <v>4.21762228012085</v>
       </c>
       <c r="H249" t="n">
         <v>17069125</v>
@@ -7619,7 +7619,7 @@
         <v>8.22245216369629</v>
       </c>
       <c r="G250" t="n">
-        <v>4.29664039611816</v>
+        <v>4.29663991928101</v>
       </c>
       <c r="H250" t="n">
         <v>20386114</v>
@@ -7648,7 +7648,7 @@
         <v>8.24135398864746</v>
       </c>
       <c r="G251" t="n">
-        <v>4.30651760101318</v>
+        <v>4.30651807785034</v>
       </c>
       <c r="H251" t="n">
         <v>13417510</v>
@@ -7706,7 +7706,7 @@
         <v>8.16102027893066</v>
       </c>
       <c r="G253" t="n">
-        <v>4.26453971862793</v>
+        <v>4.26453876495361</v>
       </c>
       <c r="H253" t="n">
         <v>10633274</v>
@@ -7793,7 +7793,7 @@
         <v>8.16102027893066</v>
       </c>
       <c r="G256" t="n">
-        <v>4.26453971862793</v>
+        <v>4.26453876495361</v>
       </c>
       <c r="H256" t="n">
         <v>8948498</v>
@@ -7822,7 +7822,7 @@
         <v>8.18937301635742</v>
       </c>
       <c r="G257" t="n">
-        <v>4.2793550491333</v>
+        <v>4.27935552597046</v>
       </c>
       <c r="H257" t="n">
         <v>8424433</v>
@@ -7880,7 +7880,7 @@
         <v>8.62412357330322</v>
       </c>
       <c r="G259" t="n">
-        <v>4.5065336227417</v>
+        <v>4.50653409957886</v>
       </c>
       <c r="H259" t="n">
         <v>33051782</v>
@@ -8025,7 +8025,7 @@
         <v>9.59286117553711</v>
       </c>
       <c r="G264" t="n">
-        <v>5.01274824142456</v>
+        <v>5.01274728775024</v>
       </c>
       <c r="H264" t="n">
         <v>26411820</v>
@@ -8054,7 +8054,7 @@
         <v>9.89529609680176</v>
       </c>
       <c r="G265" t="n">
-        <v>5.17078447341919</v>
+        <v>5.17078495025635</v>
       </c>
       <c r="H265" t="n">
         <v>23432517</v>
@@ -8083,7 +8083,7 @@
         <v>8.29806137084961</v>
       </c>
       <c r="G266" t="n">
-        <v>4.33615064620972</v>
+        <v>4.33615016937256</v>
       </c>
       <c r="H266" t="n">
         <v>78378600</v>
@@ -8170,7 +8170,7 @@
         <v>8.40202331542969</v>
       </c>
       <c r="G269" t="n">
-        <v>4.39047574996948</v>
+        <v>4.39047527313232</v>
       </c>
       <c r="H269" t="n">
         <v>24628775</v>
@@ -8199,7 +8199,7 @@
         <v>8.44927787780762</v>
       </c>
       <c r="G270" t="n">
-        <v>4.41516828536987</v>
+        <v>4.41516876220703</v>
       </c>
       <c r="H270" t="n">
         <v>15138377</v>
@@ -8257,7 +8257,7 @@
         <v>8.88402938842773</v>
       </c>
       <c r="G272" t="n">
-        <v>4.64234781265259</v>
+        <v>4.64234733581543</v>
       </c>
       <c r="H272" t="n">
         <v>23917461</v>
@@ -8286,7 +8286,7 @@
         <v>9.03052139282227</v>
       </c>
       <c r="G273" t="n">
-        <v>4.71889734268188</v>
+        <v>4.71889686584473</v>
       </c>
       <c r="H273" t="n">
         <v>21788140</v>
@@ -8315,7 +8315,7 @@
         <v>9.56450843811035</v>
       </c>
       <c r="G274" t="n">
-        <v>4.99793195724487</v>
+        <v>4.99793148040771</v>
       </c>
       <c r="H274" t="n">
         <v>35863677</v>
@@ -8344,7 +8344,7 @@
         <v>9.64956665039062</v>
       </c>
       <c r="G275" t="n">
-        <v>5.04237937927246</v>
+        <v>5.04237842559814</v>
       </c>
       <c r="H275" t="n">
         <v>33413617</v>
@@ -8373,7 +8373,7 @@
         <v>9.76298046112061</v>
       </c>
       <c r="G276" t="n">
-        <v>5.10164403915405</v>
+        <v>5.10164356231689</v>
       </c>
       <c r="H276" t="n">
         <v>41520201</v>
@@ -8518,7 +8518,7 @@
         <v>9.57395935058594</v>
       </c>
       <c r="G281" t="n">
-        <v>5.00287055969238</v>
+        <v>5.00287103652954</v>
       </c>
       <c r="H281" t="n">
         <v>13889473</v>
@@ -8547,7 +8547,7 @@
         <v>9.65901756286621</v>
       </c>
       <c r="G282" t="n">
-        <v>5.04731750488281</v>
+        <v>5.04731702804565</v>
       </c>
       <c r="H282" t="n">
         <v>10415551</v>
@@ -8634,7 +8634,7 @@
         <v>9.37548637390137</v>
       </c>
       <c r="G285" t="n">
-        <v>4.89915800094604</v>
+        <v>4.89915895462036</v>
       </c>
       <c r="H285" t="n">
         <v>21847157</v>
@@ -8663,7 +8663,7 @@
         <v>9.62121391296387</v>
       </c>
       <c r="G286" t="n">
-        <v>5.02756309509277</v>
+        <v>5.02756357192993</v>
       </c>
       <c r="H286" t="n">
         <v>19397284</v>
@@ -8692,7 +8692,7 @@
         <v>9.59286117553711</v>
       </c>
       <c r="G287" t="n">
-        <v>5.01274824142456</v>
+        <v>5.01274728775024</v>
       </c>
       <c r="H287" t="n">
         <v>14648782</v>
@@ -8750,7 +8750,7 @@
         <v>10.2166328430176</v>
       </c>
       <c r="G289" t="n">
-        <v>5.33869981765747</v>
+        <v>5.33869886398315</v>
       </c>
       <c r="H289" t="n">
         <v>33645256</v>
@@ -8779,7 +8779,7 @@
         <v>10.2260837554932</v>
       </c>
       <c r="G290" t="n">
-        <v>5.34363794326782</v>
+        <v>5.34363746643066</v>
       </c>
       <c r="H290" t="n">
         <v>27659289</v>
@@ -8808,7 +8808,7 @@
         <v>10.1882801055908</v>
       </c>
       <c r="G291" t="n">
-        <v>5.32388401031494</v>
+        <v>5.32388353347778</v>
       </c>
       <c r="H291" t="n">
         <v>12528118</v>
@@ -8866,7 +8866,7 @@
         <v>10.1977310180664</v>
       </c>
       <c r="G293" t="n">
-        <v>5.32882213592529</v>
+        <v>5.32882261276245</v>
       </c>
       <c r="H293" t="n">
         <v>8752628</v>
@@ -8895,7 +8895,7 @@
         <v>10.2166328430176</v>
       </c>
       <c r="G294" t="n">
-        <v>5.33869981765747</v>
+        <v>5.33869886398315</v>
       </c>
       <c r="H294" t="n">
         <v>10806146</v>
@@ -8924,7 +8924,7 @@
         <v>10.1882801055908</v>
       </c>
       <c r="G295" t="n">
-        <v>5.32388401031494</v>
+        <v>5.32388353347778</v>
       </c>
       <c r="H295" t="n">
         <v>11623707</v>
@@ -8953,7 +8953,7 @@
         <v>9.90474700927734</v>
       </c>
       <c r="G296" t="n">
-        <v>5.17572259902954</v>
+        <v>5.17572355270386</v>
       </c>
       <c r="H296" t="n">
         <v>18015198</v>
@@ -8982,7 +8982,7 @@
         <v>9.59286117553711</v>
       </c>
       <c r="G297" t="n">
-        <v>5.01274824142456</v>
+        <v>5.01274728775024</v>
       </c>
       <c r="H297" t="n">
         <v>21475304</v>
@@ -9011,7 +9011,7 @@
         <v>9.8480396270752</v>
       </c>
       <c r="G298" t="n">
-        <v>5.14609098434448</v>
+        <v>5.14609146118164</v>
       </c>
       <c r="H298" t="n">
         <v>13183667</v>
@@ -9040,7 +9040,7 @@
         <v>9.76298046112061</v>
       </c>
       <c r="G299" t="n">
-        <v>5.10164403915405</v>
+        <v>5.10164356231689</v>
       </c>
       <c r="H299" t="n">
         <v>11905862</v>
@@ -9069,7 +9069,7 @@
         <v>9.92364883422852</v>
       </c>
       <c r="G300" t="n">
-        <v>5.18560075759888</v>
+        <v>5.18560028076172</v>
       </c>
       <c r="H300" t="n">
         <v>16834662</v>
@@ -9098,7 +9098,7 @@
         <v>9.92364883422852</v>
       </c>
       <c r="G301" t="n">
-        <v>5.18560075759888</v>
+        <v>5.18560028076172</v>
       </c>
       <c r="H301" t="n">
         <v>9610216</v>
@@ -9127,7 +9127,7 @@
         <v>9.91419792175293</v>
       </c>
       <c r="G302" t="n">
-        <v>5.18066263198853</v>
+        <v>5.18066167831421</v>
       </c>
       <c r="H302" t="n">
         <v>12321680</v>
@@ -9156,7 +9156,7 @@
         <v>9.81968688964844</v>
       </c>
       <c r="G303" t="n">
-        <v>5.13127517700195</v>
+        <v>5.13127613067627</v>
       </c>
       <c r="H303" t="n">
         <v>12046516</v>
@@ -9185,7 +9185,7 @@
         <v>9.82913780212402</v>
       </c>
       <c r="G304" t="n">
-        <v>5.13621377944946</v>
+        <v>5.13621282577515</v>
       </c>
       <c r="H304" t="n">
         <v>10303430</v>
@@ -9214,7 +9214,7 @@
         <v>9.88584518432617</v>
       </c>
       <c r="G305" t="n">
-        <v>5.16584587097168</v>
+        <v>5.165846824646</v>
       </c>
       <c r="H305" t="n">
         <v>16521299</v>
@@ -9272,7 +9272,7 @@
         <v>9.62121391296387</v>
       </c>
       <c r="G307" t="n">
-        <v>5.02756309509277</v>
+        <v>5.02756357192993</v>
       </c>
       <c r="H307" t="n">
         <v>10310340</v>
@@ -9301,7 +9301,7 @@
         <v>9.83858871459961</v>
       </c>
       <c r="G308" t="n">
-        <v>5.14115238189697</v>
+        <v>5.14115285873413</v>
       </c>
       <c r="H308" t="n">
         <v>13084990</v>
@@ -9388,7 +9388,7 @@
         <v>10.1882801055908</v>
       </c>
       <c r="G311" t="n">
-        <v>5.32388401031494</v>
+        <v>5.32388353347778</v>
       </c>
       <c r="H311" t="n">
         <v>16511332</v>
@@ -9446,7 +9446,7 @@
         <v>9.97090530395508</v>
       </c>
       <c r="G313" t="n">
-        <v>5.21029424667358</v>
+        <v>5.21029376983643</v>
       </c>
       <c r="H313" t="n">
         <v>8514700</v>
@@ -9475,7 +9475,7 @@
         <v>9.59286117553711</v>
       </c>
       <c r="G314" t="n">
-        <v>5.01274824142456</v>
+        <v>5.01274728775024</v>
       </c>
       <c r="H314" t="n">
         <v>22107792</v>
@@ -9504,7 +9504,7 @@
         <v>9.53615379333496</v>
       </c>
       <c r="G315" t="n">
-        <v>4.98311519622803</v>
+        <v>4.98311614990234</v>
       </c>
       <c r="H315" t="n">
         <v>27272382</v>
@@ -9533,7 +9533,7 @@
         <v>9.46054458618164</v>
       </c>
       <c r="G316" t="n">
-        <v>4.94360542297363</v>
+        <v>4.94360589981079</v>
       </c>
       <c r="H316" t="n">
         <v>23498979</v>
@@ -9562,7 +9562,7 @@
         <v>9.49835014343262</v>
       </c>
       <c r="G317" t="n">
-        <v>4.96335983276367</v>
+        <v>4.96336078643799</v>
       </c>
       <c r="H317" t="n">
         <v>12704721</v>
@@ -9591,7 +9591,7 @@
         <v>9.44164276123047</v>
       </c>
       <c r="G318" t="n">
-        <v>4.93372821807861</v>
+        <v>4.93372869491577</v>
       </c>
       <c r="H318" t="n">
         <v>15362502</v>
@@ -9620,7 +9620,7 @@
         <v>9.71572494506836</v>
       </c>
       <c r="G319" t="n">
-        <v>5.07694959640503</v>
+        <v>5.07695055007935</v>
       </c>
       <c r="H319" t="n">
         <v>12278352</v>
@@ -9649,7 +9649,7 @@
         <v>9.76298046112061</v>
       </c>
       <c r="G320" t="n">
-        <v>5.10164403915405</v>
+        <v>5.10164356231689</v>
       </c>
       <c r="H320" t="n">
         <v>15098559</v>
@@ -9678,7 +9678,7 @@
         <v>9.70627403259277</v>
       </c>
       <c r="G321" t="n">
-        <v>5.07201099395752</v>
+        <v>5.07201147079468</v>
       </c>
       <c r="H321" t="n">
         <v>8057059</v>
@@ -9736,7 +9736,7 @@
         <v>9.20536613464355</v>
       </c>
       <c r="G323" t="n">
-        <v>4.81026220321655</v>
+        <v>4.81026172637939</v>
       </c>
       <c r="H323" t="n">
         <v>25190469</v>
@@ -9794,7 +9794,7 @@
         <v>9.0777759552002</v>
       </c>
       <c r="G325" t="n">
-        <v>4.74359035491943</v>
+        <v>4.74358940124512</v>
       </c>
       <c r="H325" t="n">
         <v>19454758</v>
@@ -9852,7 +9852,7 @@
         <v>9.05887413024902</v>
       </c>
       <c r="G327" t="n">
-        <v>4.73371267318726</v>
+        <v>4.7337121963501</v>
       </c>
       <c r="H327" t="n">
         <v>14223880</v>
@@ -9881,7 +9881,7 @@
         <v>9.02579498291016</v>
       </c>
       <c r="G328" t="n">
-        <v>4.71642732620239</v>
+        <v>4.71642684936523</v>
       </c>
       <c r="H328" t="n">
         <v>11116251</v>
@@ -9910,7 +9910,7 @@
         <v>9.00689315795898</v>
       </c>
       <c r="G329" t="n">
-        <v>4.70654964447021</v>
+        <v>4.70655012130737</v>
       </c>
       <c r="H329" t="n">
         <v>21695958</v>
@@ -9968,7 +9968,7 @@
         <v>8.64775085449219</v>
       </c>
       <c r="G331" t="n">
-        <v>4.51887989044189</v>
+        <v>4.51888036727905</v>
       </c>
       <c r="H331" t="n">
         <v>22900023</v>
@@ -9997,7 +9997,7 @@
         <v>8.52016162872314</v>
       </c>
       <c r="G332" t="n">
-        <v>4.45220851898193</v>
+        <v>4.45220947265625</v>
       </c>
       <c r="H332" t="n">
         <v>18534807</v>
@@ -10026,7 +10026,7 @@
         <v>8.89348030090332</v>
       </c>
       <c r="G333" t="n">
-        <v>4.64728689193726</v>
+        <v>4.6472864151001</v>
       </c>
       <c r="H333" t="n">
         <v>17447863</v>
@@ -10113,7 +10113,7 @@
         <v>9.17228698730469</v>
       </c>
       <c r="G336" t="n">
-        <v>4.79297685623169</v>
+        <v>4.79297590255737</v>
       </c>
       <c r="H336" t="n">
         <v>17375618</v>
@@ -10142,7 +10142,7 @@
         <v>9.1628360748291</v>
       </c>
       <c r="G337" t="n">
-        <v>4.78803873062134</v>
+        <v>4.78803825378418</v>
       </c>
       <c r="H337" t="n">
         <v>10917033</v>
@@ -10200,7 +10200,7 @@
         <v>9.76298046112061</v>
       </c>
       <c r="G339" t="n">
-        <v>5.10164403915405</v>
+        <v>5.10164356231689</v>
       </c>
       <c r="H339" t="n">
         <v>22653203</v>
@@ -10229,7 +10229,7 @@
         <v>9.81968688964844</v>
       </c>
       <c r="G340" t="n">
-        <v>5.13127517700195</v>
+        <v>5.13127613067627</v>
       </c>
       <c r="H340" t="n">
         <v>12015952</v>
@@ -10258,7 +10258,7 @@
         <v>9.4085636138916</v>
       </c>
       <c r="G341" t="n">
-        <v>4.91644239425659</v>
+        <v>4.91644287109375</v>
       </c>
       <c r="H341" t="n">
         <v>27114233</v>
@@ -10287,7 +10287,7 @@
         <v>9.51725196838379</v>
       </c>
       <c r="G342" t="n">
-        <v>4.97323751449585</v>
+        <v>4.97323799133301</v>
       </c>
       <c r="H342" t="n">
         <v>15505239</v>
@@ -10345,7 +10345,7 @@
         <v>9.71572494506836</v>
       </c>
       <c r="G344" t="n">
-        <v>5.07694959640503</v>
+        <v>5.07695055007935</v>
       </c>
       <c r="H344" t="n">
         <v>12506882</v>
@@ -10374,7 +10374,7 @@
         <v>9.64011573791504</v>
       </c>
       <c r="G345" t="n">
-        <v>5.03744029998779</v>
+        <v>5.03744077682495</v>
       </c>
       <c r="H345" t="n">
         <v>10657369</v>
@@ -10403,7 +10403,7 @@
         <v>9.62121391296387</v>
       </c>
       <c r="G346" t="n">
-        <v>5.02756309509277</v>
+        <v>5.02756357192993</v>
       </c>
       <c r="H346" t="n">
         <v>11452499</v>
@@ -10461,7 +10461,7 @@
         <v>9.41329002380371</v>
       </c>
       <c r="G348" t="n">
-        <v>4.91891288757324</v>
+        <v>4.91891241073608</v>
       </c>
       <c r="H348" t="n">
         <v>15385667</v>
@@ -10548,7 +10548,7 @@
         <v>9.56450843811035</v>
       </c>
       <c r="G351" t="n">
-        <v>4.99793195724487</v>
+        <v>4.99793148040771</v>
       </c>
       <c r="H351" t="n">
         <v>10834105</v>
@@ -10577,7 +10577,7 @@
         <v>9.12503242492676</v>
       </c>
       <c r="G352" t="n">
-        <v>4.7682843208313</v>
+        <v>4.76828384399414</v>
       </c>
       <c r="H352" t="n">
         <v>28594627</v>
@@ -10722,7 +10722,7 @@
         <v>8.92183303833008</v>
       </c>
       <c r="G357" t="n">
-        <v>4.66210126876831</v>
+        <v>4.66210174560547</v>
       </c>
       <c r="H357" t="n">
         <v>26021303</v>
@@ -10751,7 +10751,7 @@
         <v>8.88402938842773</v>
       </c>
       <c r="G358" t="n">
-        <v>4.64234781265259</v>
+        <v>4.64234733581543</v>
       </c>
       <c r="H358" t="n">
         <v>13153983</v>
@@ -10838,7 +10838,7 @@
         <v>8.77061557769775</v>
       </c>
       <c r="G361" t="n">
-        <v>4.583083152771</v>
+        <v>4.58308410644531</v>
       </c>
       <c r="H361" t="n">
         <v>15527144</v>
@@ -10867,7 +10867,7 @@
         <v>8.8320484161377</v>
       </c>
       <c r="G362" t="n">
-        <v>4.61518526077271</v>
+        <v>4.61518478393555</v>
       </c>
       <c r="H362" t="n">
         <v>30274610</v>
@@ -10896,7 +10896,7 @@
         <v>9.27624893188477</v>
       </c>
       <c r="G363" t="n">
-        <v>4.84730243682861</v>
+        <v>4.8473014831543</v>
       </c>
       <c r="H363" t="n">
         <v>25316340</v>
@@ -10925,7 +10925,7 @@
         <v>9.2431697845459</v>
       </c>
       <c r="G364" t="n">
-        <v>4.83001661300659</v>
+        <v>4.83001613616943</v>
       </c>
       <c r="H364" t="n">
         <v>17050586</v>
@@ -10954,7 +10954,7 @@
         <v>9.1628360748291</v>
       </c>
       <c r="G365" t="n">
-        <v>4.78803873062134</v>
+        <v>4.78803825378418</v>
       </c>
       <c r="H365" t="n">
         <v>9153930</v>
@@ -10983,7 +10983,7 @@
         <v>9.09667778015137</v>
       </c>
       <c r="G366" t="n">
-        <v>4.75346708297729</v>
+        <v>4.75346660614014</v>
       </c>
       <c r="H366" t="n">
         <v>12587007</v>
@@ -11012,7 +11012,7 @@
         <v>9.19591522216797</v>
       </c>
       <c r="G367" t="n">
-        <v>4.80532312393188</v>
+        <v>4.80532360076904</v>
       </c>
       <c r="H367" t="n">
         <v>19037774</v>
@@ -11041,7 +11041,7 @@
         <v>9.09195327758789</v>
       </c>
       <c r="G368" t="n">
-        <v>4.75099754333496</v>
+        <v>4.75099849700928</v>
       </c>
       <c r="H368" t="n">
         <v>18285356</v>
@@ -11128,7 +11128,7 @@
         <v>9.44164276123047</v>
       </c>
       <c r="G371" t="n">
-        <v>4.93372821807861</v>
+        <v>4.93372869491577</v>
       </c>
       <c r="H371" t="n">
         <v>17882977</v>
@@ -11273,7 +11273,7 @@
         <v>9.02579498291016</v>
       </c>
       <c r="G376" t="n">
-        <v>4.71642732620239</v>
+        <v>4.71642684936523</v>
       </c>
       <c r="H376" t="n">
         <v>11980637</v>
@@ -11302,7 +11302,7 @@
         <v>9.05887413024902</v>
       </c>
       <c r="G377" t="n">
-        <v>4.73371267318726</v>
+        <v>4.7337121963501</v>
       </c>
       <c r="H377" t="n">
         <v>10978967</v>
@@ -11360,7 +11360,7 @@
         <v>9.17228698730469</v>
       </c>
       <c r="G379" t="n">
-        <v>4.79297685623169</v>
+        <v>4.79297590255737</v>
       </c>
       <c r="H379" t="n">
         <v>11815944</v>
@@ -11447,7 +11447,7 @@
         <v>9.11085510253906</v>
       </c>
       <c r="G382" t="n">
-        <v>4.76087522506714</v>
+        <v>4.7608757019043</v>
       </c>
       <c r="H382" t="n">
         <v>11984142</v>
@@ -11476,7 +11476,7 @@
         <v>8.8320484161377</v>
       </c>
       <c r="G383" t="n">
-        <v>4.61518526077271</v>
+        <v>4.61518478393555</v>
       </c>
       <c r="H383" t="n">
         <v>19945692</v>
@@ -11534,7 +11534,7 @@
         <v>9.29113101959229</v>
       </c>
       <c r="G385" t="n">
-        <v>4.85507822036743</v>
+        <v>4.85507869720459</v>
       </c>
       <c r="H385" t="n">
         <v>22841806</v>
@@ -11563,7 +11563,7 @@
         <v>9.30062103271484</v>
       </c>
       <c r="G386" t="n">
-        <v>4.86003732681274</v>
+        <v>4.86003637313843</v>
       </c>
       <c r="H386" t="n">
         <v>10205601</v>
@@ -11621,7 +11621,7 @@
         <v>9.23418807983398</v>
       </c>
       <c r="G388" t="n">
-        <v>4.82532262802124</v>
+        <v>4.82532358169556</v>
       </c>
       <c r="H388" t="n">
         <v>8752587</v>
@@ -11679,7 +11679,7 @@
         <v>9.3243465423584</v>
       </c>
       <c r="G390" t="n">
-        <v>4.87243556976318</v>
+        <v>4.87243413925171</v>
       </c>
       <c r="H390" t="n">
         <v>8826532</v>
@@ -11737,7 +11737,7 @@
         <v>9.56635284423828</v>
       </c>
       <c r="G392" t="n">
-        <v>4.99889516830444</v>
+        <v>4.99889612197876</v>
       </c>
       <c r="H392" t="n">
         <v>12609284</v>
@@ -11766,7 +11766,7 @@
         <v>9.93647956848145</v>
       </c>
       <c r="G393" t="n">
-        <v>5.19230651855469</v>
+        <v>5.19230508804321</v>
       </c>
       <c r="H393" t="n">
         <v>20354856</v>
@@ -11795,7 +11795,7 @@
         <v>9.86055660247803</v>
       </c>
       <c r="G394" t="n">
-        <v>5.15263080596924</v>
+        <v>5.15263223648071</v>
       </c>
       <c r="H394" t="n">
         <v>11378559</v>
@@ -11824,7 +11824,7 @@
         <v>9.89851760864258</v>
       </c>
       <c r="G395" t="n">
-        <v>5.17246770858765</v>
+        <v>5.17246866226196</v>
       </c>
       <c r="H395" t="n">
         <v>7763539</v>
@@ -11853,7 +11853,7 @@
         <v>9.77514266967773</v>
       </c>
       <c r="G396" t="n">
-        <v>5.10799837112427</v>
+        <v>5.10799884796143</v>
       </c>
       <c r="H396" t="n">
         <v>7635296</v>
@@ -11882,7 +11882,7 @@
         <v>9.90800857543945</v>
       </c>
       <c r="G397" t="n">
-        <v>5.17742776870728</v>
+        <v>5.17742729187012</v>
       </c>
       <c r="H397" t="n">
         <v>7049651</v>
@@ -11911,7 +11911,7 @@
         <v>9.77514266967773</v>
       </c>
       <c r="G398" t="n">
-        <v>5.10799837112427</v>
+        <v>5.10799884796143</v>
       </c>
       <c r="H398" t="n">
         <v>7661828</v>
@@ -11940,7 +11940,7 @@
         <v>9.51890087127686</v>
       </c>
       <c r="G399" t="n">
-        <v>4.97409963607788</v>
+        <v>4.97410011291504</v>
       </c>
       <c r="H399" t="n">
         <v>13029550</v>
@@ -11998,7 +11998,7 @@
         <v>9.54737186431885</v>
       </c>
       <c r="G401" t="n">
-        <v>4.98897790908813</v>
+        <v>4.98897695541382</v>
       </c>
       <c r="H401" t="n">
         <v>11150961</v>
@@ -12027,7 +12027,7 @@
         <v>9.64227676391602</v>
       </c>
       <c r="G402" t="n">
-        <v>5.03856992721558</v>
+        <v>5.03856945037842</v>
       </c>
       <c r="H402" t="n">
         <v>7509622</v>
@@ -12056,7 +12056,7 @@
         <v>9.63278579711914</v>
       </c>
       <c r="G403" t="n">
-        <v>5.03361034393311</v>
+        <v>5.03360939025879</v>
       </c>
       <c r="H403" t="n">
         <v>14703094</v>
@@ -12085,7 +12085,7 @@
         <v>9.64227676391602</v>
       </c>
       <c r="G404" t="n">
-        <v>5.03856992721558</v>
+        <v>5.03856945037842</v>
       </c>
       <c r="H404" t="n">
         <v>11405236</v>
@@ -12114,7 +12114,7 @@
         <v>9.68023777008057</v>
       </c>
       <c r="G405" t="n">
-        <v>5.05840635299683</v>
+        <v>5.05840682983398</v>
       </c>
       <c r="H405" t="n">
         <v>5302628</v>
@@ -12172,7 +12172,7 @@
         <v>9.54737186431885</v>
       </c>
       <c r="G407" t="n">
-        <v>4.98897790908813</v>
+        <v>4.98897695541382</v>
       </c>
       <c r="H407" t="n">
         <v>11063455</v>
@@ -12201,7 +12201,7 @@
         <v>9.62329578399658</v>
       </c>
       <c r="G408" t="n">
-        <v>5.02865171432495</v>
+        <v>5.02865123748779</v>
       </c>
       <c r="H408" t="n">
         <v>7872872</v>
@@ -12259,7 +12259,7 @@
         <v>9.68972873687744</v>
       </c>
       <c r="G410" t="n">
-        <v>5.06336545944214</v>
+        <v>5.06336498260498</v>
       </c>
       <c r="H410" t="n">
         <v>5148835</v>
@@ -12288,7 +12288,7 @@
         <v>9.68023777008057</v>
       </c>
       <c r="G411" t="n">
-        <v>5.05840635299683</v>
+        <v>5.05840682983398</v>
       </c>
       <c r="H411" t="n">
         <v>5720628</v>
@@ -12317,7 +12317,7 @@
         <v>9.47619438171387</v>
       </c>
       <c r="G412" t="n">
-        <v>4.95178318023682</v>
+        <v>4.95178365707397</v>
       </c>
       <c r="H412" t="n">
         <v>12537171</v>
@@ -12375,7 +12375,7 @@
         <v>9.31960201263428</v>
       </c>
       <c r="G414" t="n">
-        <v>4.86995601654053</v>
+        <v>4.86995649337769</v>
       </c>
       <c r="H414" t="n">
         <v>10086846</v>
@@ -12404,7 +12404,7 @@
         <v>10.0788373947144</v>
       </c>
       <c r="G415" t="n">
-        <v>5.26669406890869</v>
+        <v>5.26669311523438</v>
       </c>
       <c r="H415" t="n">
         <v>28810469</v>
@@ -12433,7 +12433,7 @@
         <v>10.3445692062378</v>
       </c>
       <c r="G416" t="n">
-        <v>5.40555238723755</v>
+        <v>5.40555191040039</v>
       </c>
       <c r="H416" t="n">
         <v>34742126</v>
@@ -12462,7 +12462,7 @@
         <v>10.2306833267212</v>
       </c>
       <c r="G417" t="n">
-        <v>5.34604215621948</v>
+        <v>5.34604167938232</v>
       </c>
       <c r="H417" t="n">
         <v>16900204</v>
@@ -12491,7 +12491,7 @@
         <v>10.1547603607178</v>
       </c>
       <c r="G418" t="n">
-        <v>5.30636739730835</v>
+        <v>5.30636787414551</v>
       </c>
       <c r="H418" t="n">
         <v>10053045</v>
@@ -12520,7 +12520,7 @@
         <v>10.8570518493652</v>
       </c>
       <c r="G419" t="n">
-        <v>5.67334985733032</v>
+        <v>5.67335081100464</v>
       </c>
       <c r="H419" t="n">
         <v>44007998</v>
@@ -12549,7 +12549,7 @@
         <v>10.8855228424072</v>
       </c>
       <c r="G420" t="n">
-        <v>5.68822717666626</v>
+        <v>5.68822765350342</v>
       </c>
       <c r="H420" t="n">
         <v>38801858</v>
@@ -12578,7 +12578,7 @@
         <v>11.5118913650513</v>
       </c>
       <c r="G421" t="n">
-        <v>6.01553630828857</v>
+        <v>6.01553678512573</v>
       </c>
       <c r="H421" t="n">
         <v>38649803</v>
@@ -12607,7 +12607,7 @@
         <v>11.8535470962524</v>
       </c>
       <c r="G422" t="n">
-        <v>6.19406890869141</v>
+        <v>6.19406843185425</v>
       </c>
       <c r="H422" t="n">
         <v>56385043</v>
@@ -12665,7 +12665,7 @@
         <v>11.7966041564941</v>
       </c>
       <c r="G424" t="n">
-        <v>6.1643123626709</v>
+        <v>6.16431283950806</v>
       </c>
       <c r="H424" t="n">
         <v>14811732</v>
@@ -12723,7 +12723,7 @@
         <v>11.7491521835327</v>
       </c>
       <c r="G426" t="n">
-        <v>6.13951683044434</v>
+        <v>6.13951778411865</v>
       </c>
       <c r="H426" t="n">
         <v>14260587</v>
@@ -12810,7 +12810,7 @@
         <v>12.4988956451416</v>
       </c>
       <c r="G429" t="n">
-        <v>6.53129625320435</v>
+        <v>6.53129482269287</v>
       </c>
       <c r="H429" t="n">
         <v>21767803</v>
@@ -12839,7 +12839,7 @@
         <v>12.4514436721802</v>
       </c>
       <c r="G430" t="n">
-        <v>6.50649976730347</v>
+        <v>6.50649881362915</v>
       </c>
       <c r="H430" t="n">
         <v>13643699</v>
@@ -12868,7 +12868,7 @@
         <v>12.9829082489014</v>
       </c>
       <c r="G431" t="n">
-        <v>6.78421545028687</v>
+        <v>6.78421592712402</v>
       </c>
       <c r="H431" t="n">
         <v>32111779</v>
@@ -12897,7 +12897,7 @@
         <v>12.8405523300171</v>
       </c>
       <c r="G432" t="n">
-        <v>6.70982837677002</v>
+        <v>6.70982789993286</v>
       </c>
       <c r="H432" t="n">
         <v>27563680</v>
@@ -12955,7 +12955,7 @@
         <v>12.9544372558594</v>
       </c>
       <c r="G434" t="n">
-        <v>6.76933765411377</v>
+        <v>6.76933813095093</v>
       </c>
       <c r="H434" t="n">
         <v>14217993</v>
@@ -12984,7 +12984,7 @@
         <v>12.9829082489014</v>
       </c>
       <c r="G435" t="n">
-        <v>6.78421545028687</v>
+        <v>6.78421592712402</v>
       </c>
       <c r="H435" t="n">
         <v>14229274</v>
@@ -13013,7 +13013,7 @@
         <v>13.0208702087402</v>
       </c>
       <c r="G436" t="n">
-        <v>6.80405235290527</v>
+        <v>6.80405282974243</v>
       </c>
       <c r="H436" t="n">
         <v>8799897</v>
@@ -13071,7 +13071,7 @@
         <v>13.1727170944214</v>
       </c>
       <c r="G438" t="n">
-        <v>6.88340091705322</v>
+        <v>6.88340044021606</v>
       </c>
       <c r="H438" t="n">
         <v>16431367</v>
@@ -13100,7 +13100,7 @@
         <v>13.3815059661865</v>
       </c>
       <c r="G439" t="n">
-        <v>6.99250364303589</v>
+        <v>6.99250268936157</v>
       </c>
       <c r="H439" t="n">
         <v>11398438</v>
@@ -13129,7 +13129,7 @@
         <v>13.5428438186646</v>
       </c>
       <c r="G440" t="n">
-        <v>7.07680940628052</v>
+        <v>7.07681035995483</v>
       </c>
       <c r="H440" t="n">
         <v>12272675</v>
@@ -13158,7 +13158,7 @@
         <v>13.6757097244263</v>
       </c>
       <c r="G441" t="n">
-        <v>7.14623832702637</v>
+        <v>7.14623975753784</v>
       </c>
       <c r="H441" t="n">
         <v>16517396</v>
@@ -13216,7 +13216,7 @@
         <v>14.2830972671509</v>
       </c>
       <c r="G443" t="n">
-        <v>7.46362924575806</v>
+        <v>7.46362972259521</v>
       </c>
       <c r="H443" t="n">
         <v>30225906</v>
@@ -13245,7 +13245,7 @@
         <v>13.998384475708</v>
       </c>
       <c r="G444" t="n">
-        <v>7.31485176086426</v>
+        <v>7.31485319137573</v>
       </c>
       <c r="H444" t="n">
         <v>23424229</v>
@@ -13274,7 +13274,7 @@
         <v>14.0363464355469</v>
       </c>
       <c r="G445" t="n">
-        <v>7.33469009399414</v>
+        <v>7.33468961715698</v>
       </c>
       <c r="H445" t="n">
         <v>16118823</v>
@@ -13332,7 +13332,7 @@
         <v>14.0932893753052</v>
       </c>
       <c r="G447" t="n">
-        <v>7.36444473266602</v>
+        <v>7.36444520950317</v>
       </c>
       <c r="H447" t="n">
         <v>8548100</v>
@@ -13361,7 +13361,7 @@
         <v>14.3874921798706</v>
       </c>
       <c r="G448" t="n">
-        <v>7.51818180084229</v>
+        <v>7.51818084716797</v>
       </c>
       <c r="H448" t="n">
         <v>17254730</v>
@@ -13419,7 +13419,7 @@
         <v>14.4729061126709</v>
       </c>
       <c r="G450" t="n">
-        <v>7.56281328201294</v>
+        <v>7.56281423568726</v>
       </c>
       <c r="H450" t="n">
         <v>9911424</v>
@@ -13448,7 +13448,7 @@
         <v>14.4254541397095</v>
       </c>
       <c r="G451" t="n">
-        <v>7.53801822662354</v>
+        <v>7.53801774978638</v>
       </c>
       <c r="H451" t="n">
         <v>17775976</v>
@@ -13506,7 +13506,7 @@
         <v>14.1787023544312</v>
       </c>
       <c r="G453" t="n">
-        <v>7.40907859802246</v>
+        <v>7.4090781211853</v>
       </c>
       <c r="H453" t="n">
         <v>10463213</v>
@@ -13535,7 +13535,7 @@
         <v>14.3969821929932</v>
       </c>
       <c r="G454" t="n">
-        <v>7.5231409072876</v>
+        <v>7.52313947677612</v>
       </c>
       <c r="H454" t="n">
         <v>9497222</v>
@@ -13564,7 +13564,7 @@
         <v>14.188193321228</v>
       </c>
       <c r="G455" t="n">
-        <v>7.41403770446777</v>
+        <v>7.41403722763062</v>
       </c>
       <c r="H455" t="n">
         <v>10897984</v>
@@ -13593,7 +13593,7 @@
         <v>14.3590211868286</v>
       </c>
       <c r="G456" t="n">
-        <v>7.50330352783203</v>
+        <v>7.50330305099487</v>
       </c>
       <c r="H456" t="n">
         <v>9173855</v>
@@ -13680,7 +13680,7 @@
         <v>14.1976833343506</v>
       </c>
       <c r="G459" t="n">
-        <v>7.41899728775024</v>
+        <v>7.41899585723877</v>
       </c>
       <c r="H459" t="n">
         <v>5992592</v>
@@ -13709,7 +13709,7 @@
         <v>13.9888944625854</v>
       </c>
       <c r="G460" t="n">
-        <v>7.30989503860474</v>
+        <v>7.30989408493042</v>
       </c>
       <c r="H460" t="n">
         <v>10094456</v>
@@ -13738,7 +13738,7 @@
         <v>14.1217603683472</v>
       </c>
       <c r="G461" t="n">
-        <v>7.37932300567627</v>
+        <v>7.37932205200195</v>
       </c>
       <c r="H461" t="n">
         <v>7266075</v>
@@ -13796,7 +13796,7 @@
         <v>13.5048818588257</v>
       </c>
       <c r="G463" t="n">
-        <v>7.05697298049927</v>
+        <v>7.05697250366211</v>
       </c>
       <c r="H463" t="n">
         <v>19255008</v>
@@ -13825,7 +13825,7 @@
         <v>13.4384489059448</v>
       </c>
       <c r="G464" t="n">
-        <v>7.02225828170776</v>
+        <v>7.02225780487061</v>
       </c>
       <c r="H464" t="n">
         <v>14071301</v>
@@ -13854,7 +13854,7 @@
         <v>14.1217603683472</v>
       </c>
       <c r="G465" t="n">
-        <v>7.37932300567627</v>
+        <v>7.37932205200195</v>
       </c>
       <c r="H465" t="n">
         <v>24350184</v>
@@ -13883,7 +13883,7 @@
         <v>13.6662187576294</v>
       </c>
       <c r="G466" t="n">
-        <v>7.14128017425537</v>
+        <v>7.14127922058105</v>
       </c>
       <c r="H466" t="n">
         <v>18153330</v>
@@ -13912,7 +13912,7 @@
         <v>14.0648174285889</v>
       </c>
       <c r="G467" t="n">
-        <v>7.34956741333008</v>
+        <v>7.34956693649292</v>
       </c>
       <c r="H467" t="n">
         <v>17861971</v>
@@ -13941,7 +13941,7 @@
         <v>13.9888944625854</v>
       </c>
       <c r="G468" t="n">
-        <v>7.30989503860474</v>
+        <v>7.30989408493042</v>
       </c>
       <c r="H468" t="n">
         <v>13673672</v>
@@ -13970,7 +13970,7 @@
         <v>14.0837984085083</v>
       </c>
       <c r="G469" t="n">
-        <v>7.35948610305786</v>
+        <v>7.35948657989502</v>
       </c>
       <c r="H469" t="n">
         <v>12364779</v>
@@ -13999,7 +13999,7 @@
         <v>14.0837984085083</v>
       </c>
       <c r="G470" t="n">
-        <v>7.35948610305786</v>
+        <v>7.35948657989502</v>
       </c>
       <c r="H470" t="n">
         <v>7702286</v>
@@ -14028,7 +14028,7 @@
         <v>14.3780012130737</v>
       </c>
       <c r="G471" t="n">
-        <v>7.5132212638855</v>
+        <v>7.51322078704834</v>
       </c>
       <c r="H471" t="n">
         <v>14147271</v>
@@ -14086,7 +14086,7 @@
         <v>14.8620128631592</v>
       </c>
       <c r="G473" t="n">
-        <v>7.76614236831665</v>
+        <v>7.76614141464233</v>
       </c>
       <c r="H473" t="n">
         <v>19743917</v>
@@ -14144,7 +14144,7 @@
         <v>14.6627140045166</v>
       </c>
       <c r="G475" t="n">
-        <v>7.6619987487793</v>
+        <v>7.66199731826782</v>
       </c>
       <c r="H475" t="n">
         <v>8638786</v>
@@ -14202,7 +14202,7 @@
         <v>13.9319505691528</v>
       </c>
       <c r="G477" t="n">
-        <v>7.28013706207275</v>
+        <v>7.28013753890991</v>
       </c>
       <c r="H477" t="n">
         <v>12283271</v>
@@ -14231,7 +14231,7 @@
         <v>14.0458364486694</v>
       </c>
       <c r="G478" t="n">
-        <v>7.33964872360229</v>
+        <v>7.33964824676514</v>
       </c>
       <c r="H478" t="n">
         <v>11839175</v>
@@ -14260,7 +14260,7 @@
         <v>14.0363464355469</v>
       </c>
       <c r="G479" t="n">
-        <v>7.33469009399414</v>
+        <v>7.33468961715698</v>
       </c>
       <c r="H479" t="n">
         <v>7466140</v>
@@ -14289,7 +14289,7 @@
         <v>14.1122694015503</v>
       </c>
       <c r="G480" t="n">
-        <v>7.37436294555664</v>
+        <v>7.37436246871948</v>
       </c>
       <c r="H480" t="n">
         <v>8990997</v>
@@ -14318,7 +14318,7 @@
         <v>13.8750085830688</v>
       </c>
       <c r="G481" t="n">
-        <v>7.25038290023804</v>
+        <v>7.2503833770752</v>
       </c>
       <c r="H481" t="n">
         <v>11176699</v>
@@ -14347,7 +14347,7 @@
         <v>14.1217603683472</v>
       </c>
       <c r="G482" t="n">
-        <v>7.37932300567627</v>
+        <v>7.37932205200195</v>
       </c>
       <c r="H482" t="n">
         <v>10722979</v>
@@ -14376,7 +14376,7 @@
         <v>13.9888944625854</v>
       </c>
       <c r="G483" t="n">
-        <v>7.30989503860474</v>
+        <v>7.30989408493042</v>
       </c>
       <c r="H483" t="n">
         <v>7066875</v>
@@ -14405,7 +14405,7 @@
         <v>14.2261552810669</v>
       </c>
       <c r="G484" t="n">
-        <v>7.4338755607605</v>
+        <v>7.43387317657471</v>
       </c>
       <c r="H484" t="n">
         <v>8139443</v>
@@ -14434,7 +14434,7 @@
         <v>14.463415145874</v>
       </c>
       <c r="G485" t="n">
-        <v>7.55785512924194</v>
+        <v>7.55785465240479</v>
       </c>
       <c r="H485" t="n">
         <v>9555422</v>
@@ -14463,7 +14463,7 @@
         <v>14.188193321228</v>
       </c>
       <c r="G486" t="n">
-        <v>7.41403770446777</v>
+        <v>7.41403722763062</v>
       </c>
       <c r="H486" t="n">
         <v>8569877</v>
@@ -14492,7 +14492,7 @@
         <v>14.0932893753052</v>
       </c>
       <c r="G487" t="n">
-        <v>7.36444473266602</v>
+        <v>7.36444520950317</v>
       </c>
       <c r="H487" t="n">
         <v>5002470</v>
@@ -14521,7 +14521,7 @@
         <v>13.9888944625854</v>
       </c>
       <c r="G488" t="n">
-        <v>7.30989503860474</v>
+        <v>7.30989408493042</v>
       </c>
       <c r="H488" t="n">
         <v>6344904</v>
@@ -14550,7 +14550,7 @@
         <v>13.8560276031494</v>
       </c>
       <c r="G489" t="n">
-        <v>7.24046516418457</v>
+        <v>7.24046468734741</v>
       </c>
       <c r="H489" t="n">
         <v>19858980</v>
@@ -14608,7 +14608,7 @@
         <v>13.7231616973877</v>
       </c>
       <c r="G491" t="n">
-        <v>7.17103481292725</v>
+        <v>7.17103576660156</v>
       </c>
       <c r="H491" t="n">
         <v>9180585</v>
@@ -14637,7 +14637,7 @@
         <v>13.6851997375488</v>
       </c>
       <c r="G492" t="n">
-        <v>7.15119934082031</v>
+        <v>7.15119791030884</v>
       </c>
       <c r="H492" t="n">
         <v>12799230</v>
@@ -14695,7 +14695,7 @@
         <v>13.8465366363525</v>
       </c>
       <c r="G494" t="n">
-        <v>7.2355055809021</v>
+        <v>7.23550462722778</v>
       </c>
       <c r="H494" t="n">
         <v>12888480</v>
@@ -14724,7 +14724,7 @@
         <v>13.8750085830688</v>
       </c>
       <c r="G495" t="n">
-        <v>7.25038290023804</v>
+        <v>7.2503833770752</v>
       </c>
       <c r="H495" t="n">
         <v>8099387</v>
@@ -14753,7 +14753,7 @@
         <v>13.6757097244263</v>
       </c>
       <c r="G496" t="n">
-        <v>7.14623832702637</v>
+        <v>7.14623975753784</v>
       </c>
       <c r="H496" t="n">
         <v>8595908</v>
@@ -14840,7 +14840,7 @@
         <v>14.4159631729126</v>
       </c>
       <c r="G499" t="n">
-        <v>7.53305816650391</v>
+        <v>7.53305912017822</v>
       </c>
       <c r="H499" t="n">
         <v>10224728</v>
@@ -14869,7 +14869,7 @@
         <v>14.40647315979</v>
       </c>
       <c r="G500" t="n">
-        <v>7.52809858322144</v>
+        <v>7.52809906005859</v>
       </c>
       <c r="H500" t="n">
         <v>7629668</v>
@@ -14898,7 +14898,7 @@
         <v>14.3685111999512</v>
       </c>
       <c r="G501" t="n">
-        <v>7.50826263427734</v>
+        <v>7.5082631111145</v>
       </c>
       <c r="H501" t="n">
         <v>7724096</v>
@@ -14956,7 +14956,7 @@
         <v>14.2546262741089</v>
       </c>
       <c r="G503" t="n">
-        <v>7.44875288009644</v>
+        <v>7.44875240325928</v>
       </c>
       <c r="H503" t="n">
         <v>9833784</v>
@@ -15014,7 +15014,7 @@
         <v>14.6437330245972</v>
       </c>
       <c r="G505" t="n">
-        <v>7.6520791053772</v>
+        <v>7.65207958221436</v>
       </c>
       <c r="H505" t="n">
         <v>7658264</v>
@@ -15043,7 +15043,7 @@
         <v>14.6247529983521</v>
       </c>
       <c r="G506" t="n">
-        <v>7.64216184616089</v>
+        <v>7.64216232299805</v>
       </c>
       <c r="H506" t="n">
         <v>8511432</v>
@@ -15072,7 +15072,7 @@
         <v>14.7196569442749</v>
       </c>
       <c r="G507" t="n">
-        <v>7.69175338745117</v>
+        <v>7.69175386428833</v>
       </c>
       <c r="H507" t="n">
         <v>5529243</v>
@@ -15101,7 +15101,7 @@
         <v>14.6627140045166</v>
       </c>
       <c r="G508" t="n">
-        <v>7.6619987487793</v>
+        <v>7.66199731826782</v>
       </c>
       <c r="H508" t="n">
         <v>4135624</v>
@@ -15159,7 +15159,7 @@
         <v>14.434944152832</v>
       </c>
       <c r="G510" t="n">
-        <v>7.54297685623169</v>
+        <v>7.54297733306885</v>
       </c>
       <c r="H510" t="n">
         <v>5783158</v>
@@ -15217,7 +15217,7 @@
         <v>14.3874921798706</v>
       </c>
       <c r="G512" t="n">
-        <v>7.51818180084229</v>
+        <v>7.51818084716797</v>
       </c>
       <c r="H512" t="n">
         <v>13920115</v>
@@ -15246,7 +15246,7 @@
         <v>14.7576189041138</v>
       </c>
       <c r="G513" t="n">
-        <v>7.71159172058105</v>
+        <v>7.71159029006958</v>
       </c>
       <c r="H513" t="n">
         <v>11687502</v>
@@ -15304,7 +15304,7 @@
         <v>17.0068511962891</v>
       </c>
       <c r="G515" t="n">
-        <v>8.88692569732666</v>
+        <v>8.88692760467529</v>
       </c>
       <c r="H515" t="n">
         <v>31586911</v>
@@ -15391,7 +15391,7 @@
         <v>17.6332187652588</v>
       </c>
       <c r="G518" t="n">
-        <v>9.21423435211182</v>
+        <v>9.2142333984375</v>
       </c>
       <c r="H518" t="n">
         <v>17813494</v>
@@ -15420,7 +15420,7 @@
         <v>18.0318164825439</v>
       </c>
       <c r="G519" t="n">
-        <v>9.42252254486084</v>
+        <v>9.42252159118652</v>
       </c>
       <c r="H519" t="n">
         <v>23083991</v>
@@ -15507,7 +15507,7 @@
         <v>17.7755756378174</v>
       </c>
       <c r="G522" t="n">
-        <v>9.28862380981445</v>
+        <v>9.28862285614014</v>
       </c>
       <c r="H522" t="n">
         <v>22620200</v>
@@ -15536,7 +15536,7 @@
         <v>17.8514995574951</v>
       </c>
       <c r="G523" t="n">
-        <v>9.32829666137695</v>
+        <v>9.32829761505127</v>
       </c>
       <c r="H523" t="n">
         <v>21548480</v>
@@ -15565,7 +15565,7 @@
         <v>18.1836643218994</v>
       </c>
       <c r="G524" t="n">
-        <v>9.50187015533447</v>
+        <v>9.50186824798584</v>
       </c>
       <c r="H524" t="n">
         <v>18294717</v>
@@ -15594,7 +15594,7 @@
         <v>18.5537910461426</v>
       </c>
       <c r="G525" t="n">
-        <v>9.69528007507324</v>
+        <v>9.69528102874756</v>
       </c>
       <c r="H525" t="n">
         <v>17908846</v>
@@ -15623,7 +15623,7 @@
         <v>18.6866569519043</v>
       </c>
       <c r="G526" t="n">
-        <v>9.76470756530762</v>
+        <v>9.76470947265625</v>
       </c>
       <c r="H526" t="n">
         <v>9959218</v>
@@ -15652,7 +15652,7 @@
         <v>18.5727710723877</v>
       </c>
       <c r="G527" t="n">
-        <v>9.70519733428955</v>
+        <v>9.70519924163818</v>
       </c>
       <c r="H527" t="n">
         <v>17211089</v>
@@ -15710,7 +15710,7 @@
         <v>18.4304141998291</v>
       </c>
       <c r="G529" t="n">
-        <v>9.63080978393555</v>
+        <v>9.63080883026123</v>
       </c>
       <c r="H529" t="n">
         <v>36495372</v>
@@ -15739,7 +15739,7 @@
         <v>18.791051864624</v>
       </c>
       <c r="G530" t="n">
-        <v>9.81925964355469</v>
+        <v>9.819260597229</v>
       </c>
       <c r="H530" t="n">
         <v>10279617</v>
@@ -15797,7 +15797,7 @@
         <v>18.5310134887695</v>
       </c>
       <c r="G532" t="n">
-        <v>9.68337821960449</v>
+        <v>9.68337631225586</v>
       </c>
       <c r="H532" t="n">
         <v>16795139</v>
@@ -15855,7 +15855,7 @@
         <v>18.2538928985596</v>
       </c>
       <c r="G534" t="n">
-        <v>9.53856658935547</v>
+        <v>9.53856754302979</v>
       </c>
       <c r="H534" t="n">
         <v>16075846</v>
@@ -15884,7 +15884,7 @@
         <v>17.834415435791</v>
       </c>
       <c r="G535" t="n">
-        <v>9.31937026977539</v>
+        <v>9.31937122344971</v>
       </c>
       <c r="H535" t="n">
         <v>15302703</v>
@@ -15942,7 +15942,7 @@
         <v>16.7600994110107</v>
       </c>
       <c r="G537" t="n">
-        <v>8.7579870223999</v>
+        <v>8.75798511505127</v>
       </c>
       <c r="H537" t="n">
         <v>28865088</v>
@@ -15971,7 +15971,7 @@
         <v>17.8951549530029</v>
       </c>
       <c r="G538" t="n">
-        <v>9.35110950469971</v>
+        <v>9.35110855102539</v>
       </c>
       <c r="H538" t="n">
         <v>22997887</v>
@@ -16029,7 +16029,7 @@
         <v>16.5285339355469</v>
       </c>
       <c r="G540" t="n">
-        <v>8.63698196411133</v>
+        <v>8.63698101043701</v>
       </c>
       <c r="H540" t="n">
         <v>20165759</v>
@@ -16058,7 +16058,7 @@
         <v>16.7506084442139</v>
       </c>
       <c r="G541" t="n">
-        <v>8.75302791595459</v>
+        <v>8.75302696228027</v>
       </c>
       <c r="H541" t="n">
         <v>12327961</v>
@@ -16087,7 +16087,7 @@
         <v>16.410852432251</v>
       </c>
       <c r="G542" t="n">
-        <v>8.57548713684082</v>
+        <v>8.57548809051514</v>
       </c>
       <c r="H542" t="n">
         <v>9909876</v>
@@ -16145,7 +16145,7 @@
         <v>16.8929653167725</v>
       </c>
       <c r="G544" t="n">
-        <v>8.82741546630859</v>
+        <v>8.82741641998291</v>
       </c>
       <c r="H544" t="n">
         <v>15515850</v>
@@ -16174,7 +16174,7 @@
         <v>17.2308254241943</v>
       </c>
       <c r="G545" t="n">
-        <v>9.00396347045898</v>
+        <v>9.0039644241333</v>
       </c>
       <c r="H545" t="n">
         <v>12613157</v>
@@ -16232,7 +16232,7 @@
         <v>17.120735168457</v>
       </c>
       <c r="G547" t="n">
-        <v>8.94643688201904</v>
+        <v>8.94643592834473</v>
       </c>
       <c r="H547" t="n">
         <v>7621239</v>
@@ -16261,7 +16261,7 @@
         <v>17.2023544311523</v>
       </c>
       <c r="G548" t="n">
-        <v>8.98908615112305</v>
+        <v>8.98908710479736</v>
       </c>
       <c r="H548" t="n">
         <v>7526967</v>
@@ -16290,7 +16290,7 @@
         <v>16.8588008880615</v>
       </c>
       <c r="G549" t="n">
-        <v>8.80956363677979</v>
+        <v>8.80956268310547</v>
       </c>
       <c r="H549" t="n">
         <v>10799807</v>
@@ -16319,7 +16319,7 @@
         <v>16.7221374511719</v>
       </c>
       <c r="G550" t="n">
-        <v>8.73814964294434</v>
+        <v>8.73815059661865</v>
       </c>
       <c r="H550" t="n">
         <v>8960581</v>
@@ -16348,7 +16348,7 @@
         <v>16.6310291290283</v>
       </c>
       <c r="G551" t="n">
-        <v>8.69053936004639</v>
+        <v>8.6905403137207</v>
       </c>
       <c r="H551" t="n">
         <v>8546640</v>
@@ -16377,7 +16377,7 @@
         <v>16.8512077331543</v>
       </c>
       <c r="G552" t="n">
-        <v>8.8055944442749</v>
+        <v>8.80559539794922</v>
       </c>
       <c r="H552" t="n">
         <v>12261872</v>
@@ -16406,7 +16406,7 @@
         <v>16.6765842437744</v>
       </c>
       <c r="G553" t="n">
-        <v>8.71434593200684</v>
+        <v>8.71434497833252</v>
       </c>
       <c r="H553" t="n">
         <v>8830311</v>
@@ -16464,7 +16464,7 @@
         <v>15.2890825271606</v>
       </c>
       <c r="G555" t="n">
-        <v>7.98930835723877</v>
+        <v>7.98930740356445</v>
       </c>
       <c r="H555" t="n">
         <v>24124958</v>
@@ -16493,7 +16493,7 @@
         <v>15.3365354537964</v>
       </c>
       <c r="G556" t="n">
-        <v>8.01410293579102</v>
+        <v>8.01410388946533</v>
       </c>
       <c r="H556" t="n">
         <v>15242024</v>
@@ -16522,7 +16522,7 @@
         <v>16.2058582305908</v>
       </c>
       <c r="G557" t="n">
-        <v>8.4683666229248</v>
+        <v>8.46836757659912</v>
       </c>
       <c r="H557" t="n">
         <v>19613827</v>
@@ -16551,7 +16551,7 @@
         <v>16.3747882843018</v>
       </c>
       <c r="G558" t="n">
-        <v>8.55664253234863</v>
+        <v>8.55664157867432</v>
       </c>
       <c r="H558" t="n">
         <v>15356677</v>
@@ -16667,7 +16667,7 @@
         <v>16.3254375457764</v>
       </c>
       <c r="G562" t="n">
-        <v>8.53085517883301</v>
+        <v>8.53085422515869</v>
       </c>
       <c r="H562" t="n">
         <v>7438041</v>
@@ -16696,7 +16696,7 @@
         <v>16.1375274658203</v>
       </c>
       <c r="G563" t="n">
-        <v>8.43266201019287</v>
+        <v>8.43266105651855</v>
       </c>
       <c r="H563" t="n">
         <v>8209905</v>
@@ -16725,7 +16725,7 @@
         <v>16.327335357666</v>
       </c>
       <c r="G564" t="n">
-        <v>8.53184509277344</v>
+        <v>8.53184604644775</v>
       </c>
       <c r="H564" t="n">
         <v>9408768</v>
@@ -16783,7 +16783,7 @@
         <v>15.9970693588257</v>
       </c>
       <c r="G566" t="n">
-        <v>8.35926532745361</v>
+        <v>8.3592643737793</v>
       </c>
       <c r="H566" t="n">
         <v>8405353</v>
@@ -16812,7 +16812,7 @@
         <v>16.3899726867676</v>
       </c>
       <c r="G567" t="n">
-        <v>8.56457805633545</v>
+        <v>8.56457614898682</v>
       </c>
       <c r="H567" t="n">
         <v>9938343</v>
@@ -16841,7 +16841,7 @@
         <v>16.6822776794434</v>
       </c>
       <c r="G568" t="n">
-        <v>8.71732044219971</v>
+        <v>8.71732139587402</v>
       </c>
       <c r="H568" t="n">
         <v>11088370</v>
@@ -16899,7 +16899,7 @@
         <v>15.7901773452759</v>
       </c>
       <c r="G570" t="n">
-        <v>8.25115394592285</v>
+        <v>8.25115489959717</v>
       </c>
       <c r="H570" t="n">
         <v>11871422</v>
@@ -16957,7 +16957,7 @@
         <v>15.9325342178345</v>
       </c>
       <c r="G572" t="n">
-        <v>8.32554340362549</v>
+        <v>8.32554149627686</v>
       </c>
       <c r="H572" t="n">
         <v>10767354</v>
@@ -17073,7 +17073,7 @@
         <v>16.7164421081543</v>
       </c>
       <c r="G576" t="n">
-        <v>8.73517322540283</v>
+        <v>8.73517227172852</v>
       </c>
       <c r="H576" t="n">
         <v>19899347</v>
@@ -17131,7 +17131,7 @@
         <v>17.3655891418457</v>
       </c>
       <c r="G578" t="n">
-        <v>9.07438373565674</v>
+        <v>9.07438468933105</v>
       </c>
       <c r="H578" t="n">
         <v>12479906</v>
@@ -17160,7 +17160,7 @@
         <v>17.5857677459717</v>
       </c>
       <c r="G579" t="n">
-        <v>9.18943881988525</v>
+        <v>9.18943786621094</v>
       </c>
       <c r="H579" t="n">
         <v>9029715</v>
@@ -17218,7 +17218,7 @@
         <v>17.6559963226318</v>
       </c>
       <c r="G581" t="n">
-        <v>9.22613620758057</v>
+        <v>9.22613716125488</v>
       </c>
       <c r="H581" t="n">
         <v>15478215</v>
@@ -17247,7 +17247,7 @@
         <v>18.003345489502</v>
       </c>
       <c r="G582" t="n">
-        <v>9.40764427185059</v>
+        <v>9.4076452255249</v>
       </c>
       <c r="H582" t="n">
         <v>9564230</v>
@@ -17363,7 +17363,7 @@
         <v>18.6923503875732</v>
       </c>
       <c r="G586" t="n">
-        <v>9.76768493652344</v>
+        <v>9.7676830291748</v>
       </c>
       <c r="H586" t="n">
         <v>16750129</v>
@@ -17392,7 +17392,7 @@
         <v>18.4323139190674</v>
       </c>
       <c r="G587" t="n">
-        <v>9.63180255889893</v>
+        <v>9.63180065155029</v>
       </c>
       <c r="H587" t="n">
         <v>9123975</v>
@@ -17595,7 +17595,7 @@
         <v>17.6237297058105</v>
       </c>
       <c r="G594" t="n">
-        <v>9.20927619934082</v>
+        <v>9.20927715301514</v>
       </c>
       <c r="H594" t="n">
         <v>11102300</v>
@@ -17624,7 +17624,7 @@
         <v>18.0602874755859</v>
       </c>
       <c r="G595" t="n">
-        <v>9.43739891052246</v>
+        <v>9.43740081787109</v>
       </c>
       <c r="H595" t="n">
         <v>14912590</v>
@@ -17653,7 +17653,7 @@
         <v>17.640811920166</v>
       </c>
       <c r="G596" t="n">
-        <v>9.21820259094238</v>
+        <v>9.2182035446167</v>
       </c>
       <c r="H596" t="n">
         <v>12884696</v>
@@ -17682,7 +17682,7 @@
         <v>18.2121353149414</v>
       </c>
       <c r="G597" t="n">
-        <v>9.51674652099609</v>
+        <v>9.51674747467041</v>
       </c>
       <c r="H597" t="n">
         <v>13040119</v>
@@ -17740,7 +17740,7 @@
         <v>18.1419067382812</v>
       </c>
       <c r="G599" t="n">
-        <v>9.4800500869751</v>
+        <v>9.48004913330078</v>
       </c>
       <c r="H599" t="n">
         <v>11091447</v>
@@ -17769,7 +17769,7 @@
         <v>17.7888622283936</v>
       </c>
       <c r="G600" t="n">
-        <v>9.29556560516357</v>
+        <v>9.29556655883789</v>
       </c>
       <c r="H600" t="n">
         <v>9446584</v>
@@ -17827,7 +17827,7 @@
         <v>18.0451030731201</v>
       </c>
       <c r="G602" t="n">
-        <v>9.42946434020996</v>
+        <v>9.42946624755859</v>
       </c>
       <c r="H602" t="n">
         <v>7123162</v>
@@ -17856,7 +17856,7 @@
         <v>18.0223274230957</v>
       </c>
       <c r="G603" t="n">
-        <v>9.41756343841553</v>
+        <v>9.41756439208984</v>
       </c>
       <c r="H603" t="n">
         <v>7532212</v>
@@ -17885,7 +17885,7 @@
         <v>17.9255237579346</v>
       </c>
       <c r="G604" t="n">
-        <v>9.36697864532471</v>
+        <v>9.36697769165039</v>
       </c>
       <c r="H604" t="n">
         <v>6825439</v>
@@ -17914,7 +17914,7 @@
         <v>17.8116397857666</v>
       </c>
       <c r="G605" t="n">
-        <v>9.30746936798096</v>
+        <v>9.30746841430664</v>
       </c>
       <c r="H605" t="n">
         <v>9635740</v>
@@ -17943,7 +17943,7 @@
         <v>17.9274215698242</v>
       </c>
       <c r="G606" t="n">
-        <v>9.36797046661377</v>
+        <v>9.36796951293945</v>
       </c>
       <c r="H606" t="n">
         <v>9059025</v>
@@ -17972,7 +17972,7 @@
         <v>17.6047477722168</v>
       </c>
       <c r="G607" t="n">
-        <v>9.1993579864502</v>
+        <v>9.19935703277588</v>
       </c>
       <c r="H607" t="n">
         <v>11340871</v>
@@ -18001,7 +18001,7 @@
         <v>18.0640850067139</v>
       </c>
       <c r="G608" t="n">
-        <v>9.4393835067749</v>
+        <v>9.43938255310059</v>
       </c>
       <c r="H608" t="n">
         <v>11657118</v>
@@ -18030,7 +18030,7 @@
         <v>18.3639812469482</v>
       </c>
       <c r="G609" t="n">
-        <v>9.59609508514404</v>
+        <v>9.59609413146973</v>
       </c>
       <c r="H609" t="n">
         <v>12355340</v>
@@ -18059,7 +18059,7 @@
         <v>18.1532955169678</v>
       </c>
       <c r="G610" t="n">
-        <v>9.48600101470947</v>
+        <v>9.48600006103516</v>
       </c>
       <c r="H610" t="n">
         <v>10783060</v>
@@ -18117,7 +18117,7 @@
         <v>17.8078422546387</v>
       </c>
       <c r="G612" t="n">
-        <v>9.30548572540283</v>
+        <v>9.3054838180542</v>
       </c>
       <c r="H612" t="n">
         <v>14183264</v>
@@ -18146,7 +18146,7 @@
         <v>17.4301242828369</v>
       </c>
       <c r="G613" t="n">
-        <v>9.10810852050781</v>
+        <v>9.1081075668335</v>
       </c>
       <c r="H613" t="n">
         <v>7368939</v>
@@ -18175,7 +18175,7 @@
         <v>17.346607208252</v>
       </c>
       <c r="G614" t="n">
-        <v>9.06446647644043</v>
+        <v>9.06446552276611</v>
       </c>
       <c r="H614" t="n">
         <v>14175802</v>
@@ -18204,7 +18204,7 @@
         <v>18.0413074493408</v>
       </c>
       <c r="G615" t="n">
-        <v>9.42748165130615</v>
+        <v>9.42748069763184</v>
       </c>
       <c r="H615" t="n">
         <v>15274197</v>
@@ -18233,7 +18233,7 @@
         <v>18.411434173584</v>
       </c>
       <c r="G616" t="n">
-        <v>9.62089157104492</v>
+        <v>9.62089061737061</v>
       </c>
       <c r="H616" t="n">
         <v>18298834</v>
@@ -18262,7 +18262,7 @@
         <v>17.5781745910645</v>
       </c>
       <c r="G617" t="n">
-        <v>9.185471534729</v>
+        <v>9.18547058105469</v>
       </c>
       <c r="H617" t="n">
         <v>33395512</v>
@@ -18320,7 +18320,7 @@
         <v>16.9859714508057</v>
       </c>
       <c r="G619" t="n">
-        <v>8.87601470947266</v>
+        <v>8.87601566314697</v>
       </c>
       <c r="H619" t="n">
         <v>12670293</v>
@@ -18349,7 +18349,7 @@
         <v>16.9593982696533</v>
       </c>
       <c r="G620" t="n">
-        <v>8.86212921142578</v>
+        <v>8.86213111877441</v>
       </c>
       <c r="H620" t="n">
         <v>10107896</v>
@@ -18407,7 +18407,7 @@
         <v>17.0448112487793</v>
       </c>
       <c r="G622" t="n">
-        <v>8.90676212310791</v>
+        <v>8.90676307678223</v>
       </c>
       <c r="H622" t="n">
         <v>10384066</v>
@@ -18523,7 +18523,7 @@
         <v>17.3086452484131</v>
       </c>
       <c r="G626" t="n">
-        <v>9.04462718963623</v>
+        <v>9.04462814331055</v>
       </c>
       <c r="H626" t="n">
         <v>12168092</v>
@@ -18552,7 +18552,7 @@
         <v>16.9821758270264</v>
       </c>
       <c r="G627" t="n">
-        <v>8.87403297424316</v>
+        <v>8.87403202056885</v>
       </c>
       <c r="H627" t="n">
         <v>12008671</v>
@@ -18581,7 +18581,7 @@
         <v>17.0789775848389</v>
       </c>
       <c r="G628" t="n">
-        <v>8.92461490631104</v>
+        <v>8.92461585998535</v>
       </c>
       <c r="H628" t="n">
         <v>6192351</v>
@@ -18639,7 +18639,7 @@
         <v>16.7449150085449</v>
       </c>
       <c r="G630" t="n">
-        <v>8.7500524520874</v>
+        <v>8.75005149841309</v>
       </c>
       <c r="H630" t="n">
         <v>7559671</v>
@@ -18668,7 +18668,7 @@
         <v>16.0464191436768</v>
       </c>
       <c r="G631" t="n">
-        <v>8.38505363464355</v>
+        <v>8.38505268096924</v>
       </c>
       <c r="H631" t="n">
         <v>15821302</v>
@@ -18697,7 +18697,7 @@
         <v>15.6573114395142</v>
       </c>
       <c r="G632" t="n">
-        <v>8.18172550201416</v>
+        <v>8.18172359466553</v>
       </c>
       <c r="H632" t="n">
         <v>14104317</v>
@@ -18726,7 +18726,7 @@
         <v>15.1751976013184</v>
       </c>
       <c r="G633" t="n">
-        <v>7.92979621887207</v>
+        <v>7.92979669570923</v>
       </c>
       <c r="H633" t="n">
         <v>9489084</v>
@@ -18784,7 +18784,7 @@
         <v>15.7711973190308</v>
       </c>
       <c r="G635" t="n">
-        <v>8.24123668670654</v>
+        <v>8.24123573303223</v>
       </c>
       <c r="H635" t="n">
         <v>10024907</v>
@@ -18842,7 +18842,7 @@
         <v>15.5016679763794</v>
       </c>
       <c r="G637" t="n">
-        <v>8.10039329528809</v>
+        <v>8.1003942489624</v>
       </c>
       <c r="H637" t="n">
         <v>18010771</v>
@@ -18900,7 +18900,7 @@
         <v>15.5016679763794</v>
       </c>
       <c r="G639" t="n">
-        <v>8.10039329528809</v>
+        <v>8.1003942489624</v>
       </c>
       <c r="H639" t="n">
         <v>6671029</v>
@@ -19074,7 +19074,7 @@
         <v>15.8129549026489</v>
       </c>
       <c r="G645" t="n">
-        <v>8.26305675506592</v>
+        <v>8.2630558013916</v>
       </c>
       <c r="H645" t="n">
         <v>7986360</v>
@@ -19132,7 +19132,7 @@
         <v>15.7920761108398</v>
       </c>
       <c r="G647" t="n">
-        <v>8.25214767456055</v>
+        <v>8.25214576721191</v>
       </c>
       <c r="H647" t="n">
         <v>4573934</v>
@@ -19190,7 +19190,7 @@
         <v>15.7863807678223</v>
       </c>
       <c r="G649" t="n">
-        <v>8.24917030334473</v>
+        <v>8.24916934967041</v>
       </c>
       <c r="H649" t="n">
         <v>5261525</v>
@@ -19219,7 +19219,7 @@
         <v>15.7351331710815</v>
       </c>
       <c r="G650" t="n">
-        <v>8.22239112854004</v>
+        <v>8.22239017486572</v>
       </c>
       <c r="H650" t="n">
         <v>7491771</v>
@@ -19248,7 +19248,7 @@
         <v>15.9477186203003</v>
       </c>
       <c r="G651" t="n">
-        <v>8.33347702026367</v>
+        <v>8.33347606658936</v>
       </c>
       <c r="H651" t="n">
         <v>6210341</v>
@@ -19306,7 +19306,7 @@
         <v>15.3460254669189</v>
       </c>
       <c r="G653" t="n">
-        <v>8.01906204223633</v>
+        <v>8.01906299591064</v>
       </c>
       <c r="H653" t="n">
         <v>20651563</v>
@@ -19509,7 +19509,7 @@
         <v>13.4877986907959</v>
       </c>
       <c r="G660" t="n">
-        <v>7.04804658889771</v>
+        <v>7.04804611206055</v>
       </c>
       <c r="H660" t="n">
         <v>10692697</v>
@@ -19567,7 +19567,7 @@
         <v>13.8617219924927</v>
       </c>
       <c r="G662" t="n">
-        <v>7.24343872070312</v>
+        <v>7.24343967437744</v>
       </c>
       <c r="H662" t="n">
         <v>13895019</v>
@@ -19596,7 +19596,7 @@
         <v>13.8427410125732</v>
       </c>
       <c r="G663" t="n">
-        <v>7.23352193832397</v>
+        <v>7.23352098464966</v>
       </c>
       <c r="H663" t="n">
         <v>6180662</v>
@@ -19625,7 +19625,7 @@
         <v>13.7839012145996</v>
       </c>
       <c r="G664" t="n">
-        <v>7.20277404785156</v>
+        <v>7.20277500152588</v>
       </c>
       <c r="H664" t="n">
         <v>7400362</v>
@@ -19654,7 +19654,7 @@
         <v>13.8712120056152</v>
       </c>
       <c r="G665" t="n">
-        <v>7.24839925765991</v>
+        <v>7.24839878082275</v>
       </c>
       <c r="H665" t="n">
         <v>7719008</v>
@@ -19683,7 +19683,7 @@
         <v>13.7307538986206</v>
       </c>
       <c r="G666" t="n">
-        <v>7.17500352859497</v>
+        <v>7.17500257492065</v>
       </c>
       <c r="H666" t="n">
         <v>5663137</v>
@@ -19712,7 +19712,7 @@
         <v>13.4802074432373</v>
       </c>
       <c r="G667" t="n">
-        <v>7.04408025741577</v>
+        <v>7.04407930374146</v>
       </c>
       <c r="H667" t="n">
         <v>7471037</v>
@@ -19741,7 +19741,7 @@
         <v>13.3511371612549</v>
       </c>
       <c r="G668" t="n">
-        <v>6.97663354873657</v>
+        <v>6.97663402557373</v>
       </c>
       <c r="H668" t="n">
         <v>6078170</v>
@@ -19799,7 +19799,7 @@
         <v>13.0284624099731</v>
       </c>
       <c r="G670" t="n">
-        <v>6.808021068573</v>
+        <v>6.80801963806152</v>
       </c>
       <c r="H670" t="n">
         <v>8740511</v>
@@ -19828,7 +19828,7 @@
         <v>13.0113792419434</v>
       </c>
       <c r="G671" t="n">
-        <v>6.7990927696228</v>
+        <v>6.79909372329712</v>
       </c>
       <c r="H671" t="n">
         <v>9954709</v>
@@ -19857,7 +19857,7 @@
         <v>13.4289579391479</v>
       </c>
       <c r="G672" t="n">
-        <v>7.01729869842529</v>
+        <v>7.01729965209961</v>
       </c>
       <c r="H672" t="n">
         <v>8669950</v>
@@ -19886,7 +19886,7 @@
         <v>13.6301555633545</v>
       </c>
       <c r="G673" t="n">
-        <v>7.12243604660034</v>
+        <v>7.12243556976318</v>
       </c>
       <c r="H673" t="n">
         <v>6773484</v>
@@ -19973,7 +19973,7 @@
         <v>13.7516326904297</v>
       </c>
       <c r="G676" t="n">
-        <v>7.18591260910034</v>
+        <v>7.1859130859375</v>
       </c>
       <c r="H676" t="n">
         <v>9674767</v>
@@ -20002,7 +20002,7 @@
         <v>14.2280530929565</v>
       </c>
       <c r="G677" t="n">
-        <v>7.43486642837524</v>
+        <v>7.43486595153809</v>
       </c>
       <c r="H677" t="n">
         <v>10052209</v>
@@ -20060,7 +20060,7 @@
         <v>14.1976833343506</v>
       </c>
       <c r="G679" t="n">
-        <v>7.41899728775024</v>
+        <v>7.41899585723877</v>
       </c>
       <c r="H679" t="n">
         <v>10125499</v>
@@ -20118,7 +20118,7 @@
         <v>13.8180656433105</v>
       </c>
       <c r="G681" t="n">
-        <v>7.220627784729</v>
+        <v>7.22062730789185</v>
       </c>
       <c r="H681" t="n">
         <v>8184826</v>
@@ -20147,7 +20147,7 @@
         <v>13.9091739654541</v>
       </c>
       <c r="G682" t="n">
-        <v>7.26823663711548</v>
+        <v>7.26823472976685</v>
       </c>
       <c r="H682" t="n">
         <v>5651801</v>
@@ -20205,7 +20205,7 @@
         <v>13.8294553756714</v>
       </c>
       <c r="G684" t="n">
-        <v>7.22657823562622</v>
+        <v>7.22657918930054</v>
       </c>
       <c r="H684" t="n">
         <v>9722473</v>
@@ -20234,7 +20234,7 @@
         <v>13.6662187576294</v>
       </c>
       <c r="G685" t="n">
-        <v>7.14128017425537</v>
+        <v>7.14127922058105</v>
       </c>
       <c r="H685" t="n">
         <v>6688217</v>
@@ -20263,7 +20263,7 @@
         <v>13.6757097244263</v>
       </c>
       <c r="G686" t="n">
-        <v>7.14623832702637</v>
+        <v>7.14623975753784</v>
       </c>
       <c r="H686" t="n">
         <v>5369251</v>
@@ -20292,7 +20292,7 @@
         <v>13.808575630188</v>
       </c>
       <c r="G687" t="n">
-        <v>7.21566724777222</v>
+        <v>7.21566915512085</v>
       </c>
       <c r="H687" t="n">
         <v>8267436</v>
@@ -20321,7 +20321,7 @@
         <v>13.7155685424805</v>
       </c>
       <c r="G688" t="n">
-        <v>7.16706657409668</v>
+        <v>7.16706705093384</v>
       </c>
       <c r="H688" t="n">
         <v>6718361</v>
@@ -20350,7 +20350,7 @@
         <v>14.3191614151001</v>
       </c>
       <c r="G689" t="n">
-        <v>7.48247385025024</v>
+        <v>7.48247575759888</v>
       </c>
       <c r="H689" t="n">
         <v>16301224</v>
@@ -20379,7 +20379,7 @@
         <v>14.1730079650879</v>
       </c>
       <c r="G690" t="n">
-        <v>7.40610218048096</v>
+        <v>7.40610265731812</v>
       </c>
       <c r="H690" t="n">
         <v>6873337</v>
@@ -20408,7 +20408,7 @@
         <v>14.2147655487061</v>
       </c>
       <c r="G691" t="n">
-        <v>7.42792320251465</v>
+        <v>7.42792224884033</v>
       </c>
       <c r="H691" t="n">
         <v>6033692</v>
@@ -20495,7 +20495,7 @@
         <v>14.5810966491699</v>
       </c>
       <c r="G694" t="n">
-        <v>7.61934900283813</v>
+        <v>7.61934852600098</v>
       </c>
       <c r="H694" t="n">
         <v>11327806</v>
@@ -20524,7 +20524,7 @@
         <v>14.7993774414062</v>
       </c>
       <c r="G695" t="n">
-        <v>7.7334098815918</v>
+        <v>7.73341178894043</v>
       </c>
       <c r="H695" t="n">
         <v>11563827</v>
@@ -20553,7 +20553,7 @@
         <v>14.7576189041138</v>
       </c>
       <c r="G696" t="n">
-        <v>7.71159172058105</v>
+        <v>7.71159029006958</v>
       </c>
       <c r="H696" t="n">
         <v>9486490</v>
@@ -20582,7 +20582,7 @@
         <v>14.6247529983521</v>
       </c>
       <c r="G697" t="n">
-        <v>7.64216184616089</v>
+        <v>7.64216232299805</v>
       </c>
       <c r="H697" t="n">
         <v>5332962</v>
@@ -20698,7 +20698,7 @@
         <v>14.3723068237305</v>
       </c>
       <c r="G701" t="n">
-        <v>7.51024627685547</v>
+        <v>7.51024580001831</v>
       </c>
       <c r="H701" t="n">
         <v>8767872</v>
@@ -20727,7 +20727,7 @@
         <v>14.7025737762451</v>
       </c>
       <c r="G702" t="n">
-        <v>7.68282651901245</v>
+        <v>7.68282699584961</v>
       </c>
       <c r="H702" t="n">
         <v>10330063</v>
@@ -20756,7 +20756,7 @@
         <v>14.7234525680542</v>
       </c>
       <c r="G703" t="n">
-        <v>7.69373655319214</v>
+        <v>7.6937370300293</v>
       </c>
       <c r="H703" t="n">
         <v>10764860</v>
@@ -20785,7 +20785,7 @@
         <v>14.6209564208984</v>
       </c>
       <c r="G704" t="n">
-        <v>7.64017724990845</v>
+        <v>7.64017772674561</v>
       </c>
       <c r="H704" t="n">
         <v>5908880</v>
@@ -20814,7 +20814,7 @@
         <v>14.5013771057129</v>
       </c>
       <c r="G705" t="n">
-        <v>7.57769060134888</v>
+        <v>7.57769155502319</v>
       </c>
       <c r="H705" t="n">
         <v>6986701</v>
@@ -20843,7 +20843,7 @@
         <v>14.3912878036499</v>
       </c>
       <c r="G706" t="n">
-        <v>7.52016401290894</v>
+        <v>7.52016448974609</v>
       </c>
       <c r="H706" t="n">
         <v>6378357</v>
@@ -20872,7 +20872,7 @@
         <v>14.0553274154663</v>
       </c>
       <c r="G707" t="n">
-        <v>7.34460830688477</v>
+        <v>7.34460926055908</v>
       </c>
       <c r="H707" t="n">
         <v>8869980</v>
@@ -20901,7 +20901,7 @@
         <v>14.2033777236938</v>
       </c>
       <c r="G708" t="n">
-        <v>7.42197179794312</v>
+        <v>7.42197227478027</v>
       </c>
       <c r="H708" t="n">
         <v>8377877</v>
@@ -20930,7 +20930,7 @@
         <v>13.4156723022461</v>
       </c>
       <c r="G709" t="n">
-        <v>7.01035642623901</v>
+        <v>7.01035737991333</v>
       </c>
       <c r="H709" t="n">
         <v>15105489</v>
@@ -20959,7 +20959,7 @@
         <v>13.3245639801025</v>
       </c>
       <c r="G710" t="n">
-        <v>6.9627480506897</v>
+        <v>6.96274709701538</v>
       </c>
       <c r="H710" t="n">
         <v>13805588</v>
@@ -21046,7 +21046,7 @@
         <v>13.7364482879639</v>
       </c>
       <c r="G713" t="n">
-        <v>7.17797756195068</v>
+        <v>7.17797899246216</v>
       </c>
       <c r="H713" t="n">
         <v>9194882</v>
@@ -21104,7 +21104,7 @@
         <v>13.0626277923584</v>
       </c>
       <c r="G715" t="n">
-        <v>6.82587432861328</v>
+        <v>6.82587337493896</v>
       </c>
       <c r="H715" t="n">
         <v>8065238</v>
@@ -21133,7 +21133,7 @@
         <v>12.7570362091064</v>
       </c>
       <c r="G716" t="n">
-        <v>6.66618680953979</v>
+        <v>6.66618728637695</v>
       </c>
       <c r="H716" t="n">
         <v>16683638</v>
@@ -21162,7 +21162,7 @@
         <v>13.1366529464722</v>
       </c>
       <c r="G717" t="n">
-        <v>6.86455535888672</v>
+        <v>6.86455488204956</v>
       </c>
       <c r="H717" t="n">
         <v>15045078</v>
@@ -21191,7 +21191,7 @@
         <v>13.3036851882935</v>
       </c>
       <c r="G718" t="n">
-        <v>6.95183801651001</v>
+        <v>6.95183706283569</v>
       </c>
       <c r="H718" t="n">
         <v>10102453</v>
@@ -21220,7 +21220,7 @@
         <v>12.9753160476685</v>
       </c>
       <c r="G719" t="n">
-        <v>6.78024816513062</v>
+        <v>6.78024911880493</v>
       </c>
       <c r="H719" t="n">
         <v>13122592</v>
@@ -21249,7 +21249,7 @@
         <v>13.4156723022461</v>
       </c>
       <c r="G720" t="n">
-        <v>7.01035642623901</v>
+        <v>7.01035737991333</v>
       </c>
       <c r="H720" t="n">
         <v>11044345</v>
@@ -21307,7 +21307,7 @@
         <v>13.4859008789062</v>
       </c>
       <c r="G722" t="n">
-        <v>7.04705429077148</v>
+        <v>7.0470552444458</v>
       </c>
       <c r="H722" t="n">
         <v>13158928</v>
@@ -21336,7 +21336,7 @@
         <v>13.0512390136719</v>
       </c>
       <c r="G723" t="n">
-        <v>6.81992292404175</v>
+        <v>6.81992149353027</v>
       </c>
       <c r="H723" t="n">
         <v>21047437</v>
@@ -21365,7 +21365,7 @@
         <v>12.7646284103394</v>
       </c>
       <c r="G724" t="n">
-        <v>6.67015504837036</v>
+        <v>6.67015409469604</v>
       </c>
       <c r="H724" t="n">
         <v>29510414</v>
@@ -21394,7 +21394,7 @@
         <v>12.9221687316895</v>
       </c>
       <c r="G725" t="n">
-        <v>6.75247573852539</v>
+        <v>6.75247621536255</v>
       </c>
       <c r="H725" t="n">
         <v>12118944</v>
@@ -21423,7 +21423,7 @@
         <v>13.4517345428467</v>
       </c>
       <c r="G726" t="n">
-        <v>7.02920007705688</v>
+        <v>7.02920150756836</v>
       </c>
       <c r="H726" t="n">
         <v>19284748</v>
@@ -21481,7 +21481,7 @@
         <v>13.5808048248291</v>
       </c>
       <c r="G728" t="n">
-        <v>7.09664678573608</v>
+        <v>7.09664630889893</v>
       </c>
       <c r="H728" t="n">
         <v>7457464</v>
@@ -21510,7 +21510,7 @@
         <v>13.8958883285522</v>
       </c>
       <c r="G729" t="n">
-        <v>7.26129388809204</v>
+        <v>7.26129341125488</v>
       </c>
       <c r="H729" t="n">
         <v>11061346</v>
@@ -21597,7 +21597,7 @@
         <v>13.4289579391479</v>
       </c>
       <c r="G732" t="n">
-        <v>7.01729869842529</v>
+        <v>7.01729965209961</v>
       </c>
       <c r="H732" t="n">
         <v>5500628</v>
@@ -21626,7 +21626,7 @@
         <v>13.9775047302246</v>
       </c>
       <c r="G733" t="n">
-        <v>7.30394268035889</v>
+        <v>7.3039436340332</v>
       </c>
       <c r="H733" t="n">
         <v>8313493</v>
@@ -21655,7 +21655,7 @@
         <v>13.83704662323</v>
       </c>
       <c r="G734" t="n">
-        <v>7.23054456710815</v>
+        <v>7.23054552078247</v>
       </c>
       <c r="H734" t="n">
         <v>9171125</v>
@@ -21684,7 +21684,7 @@
         <v>13.6510343551636</v>
       </c>
       <c r="G735" t="n">
-        <v>7.13334512710571</v>
+        <v>7.13334465026855</v>
       </c>
       <c r="H735" t="n">
         <v>6786796</v>
@@ -21713,7 +21713,7 @@
         <v>13.6301555633545</v>
       </c>
       <c r="G736" t="n">
-        <v>7.12243604660034</v>
+        <v>7.12243556976318</v>
       </c>
       <c r="H736" t="n">
         <v>6289756</v>
@@ -21742,7 +21742,7 @@
         <v>13.641544342041</v>
       </c>
       <c r="G737" t="n">
-        <v>7.12838649749756</v>
+        <v>7.1283860206604</v>
       </c>
       <c r="H737" t="n">
         <v>5555239</v>
@@ -21771,7 +21771,7 @@
         <v>13.2866020202637</v>
       </c>
       <c r="G738" t="n">
-        <v>6.94291067123413</v>
+        <v>6.94291114807129</v>
       </c>
       <c r="H738" t="n">
         <v>8332316</v>
@@ -21800,7 +21800,7 @@
         <v>13.4194679260254</v>
       </c>
       <c r="G739" t="n">
-        <v>7.01233959197998</v>
+        <v>7.0123405456543</v>
       </c>
       <c r="H739" t="n">
         <v>7431434</v>
@@ -21829,7 +21829,7 @@
         <v>13.261926651001</v>
       </c>
       <c r="G740" t="n">
-        <v>6.93001699447632</v>
+        <v>6.93001651763916</v>
       </c>
       <c r="H740" t="n">
         <v>5223946</v>
@@ -21858,7 +21858,7 @@
         <v>13.3777103424072</v>
       </c>
       <c r="G741" t="n">
-        <v>6.99051952362061</v>
+        <v>6.99052000045776</v>
       </c>
       <c r="H741" t="n">
         <v>4854577</v>
@@ -21887,7 +21887,7 @@
         <v>14.0439376831055</v>
       </c>
       <c r="G742" t="n">
-        <v>7.33865737915039</v>
+        <v>7.33865785598755</v>
       </c>
       <c r="H742" t="n">
         <v>12266889</v>
@@ -21916,7 +21916,7 @@
         <v>14.0610208511353</v>
       </c>
       <c r="G743" t="n">
-        <v>7.34758329391479</v>
+        <v>7.34758424758911</v>
       </c>
       <c r="H743" t="n">
         <v>9520996</v>
@@ -21974,7 +21974,7 @@
         <v>13.9794025421143</v>
       </c>
       <c r="G745" t="n">
-        <v>7.30493402481079</v>
+        <v>7.30493354797363</v>
       </c>
       <c r="H745" t="n">
         <v>6134185</v>
@@ -22003,7 +22003,7 @@
         <v>13.8294553756714</v>
       </c>
       <c r="G746" t="n">
-        <v>7.22657823562622</v>
+        <v>7.22657918930054</v>
       </c>
       <c r="H746" t="n">
         <v>8491393</v>
@@ -22032,7 +22032,7 @@
         <v>14.3457336425781</v>
       </c>
       <c r="G747" t="n">
-        <v>7.49635887145996</v>
+        <v>7.49636030197144</v>
       </c>
       <c r="H747" t="n">
         <v>14817897</v>
@@ -22061,7 +22061,7 @@
         <v>14.0629186630249</v>
       </c>
       <c r="G748" t="n">
-        <v>7.34857559204102</v>
+        <v>7.34857511520386</v>
       </c>
       <c r="H748" t="n">
         <v>7175606</v>
@@ -22090,7 +22090,7 @@
         <v>13.8446388244629</v>
       </c>
       <c r="G749" t="n">
-        <v>7.23451280593872</v>
+        <v>7.23451328277588</v>
       </c>
       <c r="H749" t="n">
         <v>6130678</v>
@@ -22148,7 +22148,7 @@
         <v>13.0607299804688</v>
       </c>
       <c r="G751" t="n">
-        <v>6.82488203048706</v>
+        <v>6.8248815536499</v>
       </c>
       <c r="H751" t="n">
         <v>8837709</v>
@@ -22177,7 +22177,7 @@
         <v>12.6507425308228</v>
       </c>
       <c r="G752" t="n">
-        <v>6.6106424331665</v>
+        <v>6.61064338684082</v>
       </c>
       <c r="H752" t="n">
         <v>10554883</v>
@@ -22235,7 +22235,7 @@
         <v>13.2353544235229</v>
       </c>
       <c r="G754" t="n">
-        <v>6.91613101959229</v>
+        <v>6.91613245010376</v>
       </c>
       <c r="H754" t="n">
         <v>9267027</v>
@@ -22264,7 +22264,7 @@
         <v>13.2467422485352</v>
       </c>
       <c r="G755" t="n">
-        <v>6.9220814704895</v>
+        <v>6.92208290100098</v>
       </c>
       <c r="H755" t="n">
         <v>8700607</v>
@@ -22293,7 +22293,7 @@
         <v>13.1442451477051</v>
       </c>
       <c r="G756" t="n">
-        <v>6.86852264404297</v>
+        <v>6.86852359771729</v>
       </c>
       <c r="H756" t="n">
         <v>8964768</v>
@@ -22322,7 +22322,7 @@
         <v>13.0683221817017</v>
       </c>
       <c r="G757" t="n">
-        <v>6.82884979248047</v>
+        <v>6.82884883880615</v>
       </c>
       <c r="H757" t="n">
         <v>6851792</v>
@@ -22380,7 +22380,7 @@
         <v>13.261926651001</v>
       </c>
       <c r="G759" t="n">
-        <v>6.93001699447632</v>
+        <v>6.93001651763916</v>
       </c>
       <c r="H759" t="n">
         <v>8103049</v>
@@ -22438,7 +22438,7 @@
         <v>12.4552402496338</v>
       </c>
       <c r="G761" t="n">
-        <v>6.50848293304443</v>
+        <v>6.50848340988159</v>
       </c>
       <c r="H761" t="n">
         <v>14612321</v>
@@ -22467,7 +22467,7 @@
         <v>11.9750242233276</v>
       </c>
       <c r="G762" t="n">
-        <v>6.25754690170288</v>
+        <v>6.25754642486572</v>
       </c>
       <c r="H762" t="n">
         <v>14168419</v>
@@ -22496,7 +22496,7 @@
         <v>12.0357627868652</v>
       </c>
       <c r="G763" t="n">
-        <v>6.28928470611572</v>
+        <v>6.28928565979004</v>
       </c>
       <c r="H763" t="n">
         <v>8593330</v>
@@ -22554,7 +22554,7 @@
         <v>11.783317565918</v>
       </c>
       <c r="G765" t="n">
-        <v>6.15737056732178</v>
+        <v>6.15737009048462</v>
       </c>
       <c r="H765" t="n">
         <v>8008267</v>
@@ -22641,7 +22641,7 @@
         <v>12.6849088668823</v>
       </c>
       <c r="G768" t="n">
-        <v>6.6284966468811</v>
+        <v>6.62849569320679</v>
       </c>
       <c r="H768" t="n">
         <v>10069766</v>
@@ -22699,7 +22699,7 @@
         <v>13.1594295501709</v>
       </c>
       <c r="G770" t="n">
-        <v>6.87645578384399</v>
+        <v>6.87645721435547</v>
       </c>
       <c r="H770" t="n">
         <v>10348718</v>
@@ -22728,7 +22728,7 @@
         <v>13.4877986907959</v>
       </c>
       <c r="G771" t="n">
-        <v>7.04804658889771</v>
+        <v>7.04804611206055</v>
       </c>
       <c r="H771" t="n">
         <v>11161105</v>
@@ -22844,7 +22844,7 @@
         <v>13.7990846633911</v>
       </c>
       <c r="G775" t="n">
-        <v>7.21070957183838</v>
+        <v>7.21070909500122</v>
       </c>
       <c r="H775" t="n">
         <v>6211918</v>
@@ -22873,7 +22873,7 @@
         <v>13.998384475708</v>
       </c>
       <c r="G776" t="n">
-        <v>7.31485176086426</v>
+        <v>7.31485319137573</v>
       </c>
       <c r="H776" t="n">
         <v>7523614</v>
@@ -22989,7 +22989,7 @@
         <v>13.808575630188</v>
       </c>
       <c r="G780" t="n">
-        <v>7.21566724777222</v>
+        <v>7.21566915512085</v>
       </c>
       <c r="H780" t="n">
         <v>8773268</v>
@@ -23018,7 +23018,7 @@
         <v>13.9072761535645</v>
       </c>
       <c r="G781" t="n">
-        <v>7.26724529266357</v>
+        <v>7.2672438621521</v>
       </c>
       <c r="H781" t="n">
         <v>6220740</v>
@@ -23076,7 +23076,7 @@
         <v>13.7592248916626</v>
       </c>
       <c r="G783" t="n">
-        <v>7.18987989425659</v>
+        <v>7.18988037109375</v>
       </c>
       <c r="H783" t="n">
         <v>6344388</v>
@@ -23105,7 +23105,7 @@
         <v>13.9414415359497</v>
       </c>
       <c r="G784" t="n">
-        <v>7.2850980758667</v>
+        <v>7.28509712219238</v>
       </c>
       <c r="H784" t="n">
         <v>5199734</v>
@@ -23163,7 +23163,7 @@
         <v>14.3020782470703</v>
       </c>
       <c r="G786" t="n">
-        <v>7.47354698181152</v>
+        <v>7.47354793548584</v>
       </c>
       <c r="H786" t="n">
         <v>10698830</v>
@@ -23192,7 +23192,7 @@
         <v>14.0648174285889</v>
       </c>
       <c r="G787" t="n">
-        <v>7.34956741333008</v>
+        <v>7.34956693649292</v>
       </c>
       <c r="H787" t="n">
         <v>6640516</v>
@@ -23221,7 +23221,7 @@
         <v>14.4045753479004</v>
       </c>
       <c r="G788" t="n">
-        <v>7.52710723876953</v>
+        <v>7.52710771560669</v>
       </c>
       <c r="H788" t="n">
         <v>7592460</v>
@@ -23250,7 +23250,7 @@
         <v>14.463415145874</v>
       </c>
       <c r="G789" t="n">
-        <v>7.55785512924194</v>
+        <v>7.55785465240479</v>
       </c>
       <c r="H789" t="n">
         <v>7863580</v>
@@ -23308,7 +23308,7 @@
         <v>12.329966545105</v>
       </c>
       <c r="G791" t="n">
-        <v>6.44302129745483</v>
+        <v>6.44302034378052</v>
       </c>
       <c r="H791" t="n">
         <v>18166573</v>
@@ -23337,7 +23337,7 @@
         <v>12.2825136184692</v>
       </c>
       <c r="G792" t="n">
-        <v>6.41822481155396</v>
+        <v>6.4182243347168</v>
       </c>
       <c r="H792" t="n">
         <v>14019969</v>
@@ -23366,7 +23366,7 @@
         <v>12.242654800415</v>
       </c>
       <c r="G793" t="n">
-        <v>6.3973970413208</v>
+        <v>6.39739656448364</v>
       </c>
       <c r="H793" t="n">
         <v>10474835</v>
@@ -23395,7 +23395,7 @@
         <v>12.4343614578247</v>
       </c>
       <c r="G794" t="n">
-        <v>6.49757289886475</v>
+        <v>6.49757242202759</v>
       </c>
       <c r="H794" t="n">
         <v>7940460</v>
@@ -23482,7 +23482,7 @@
         <v>12.3413553237915</v>
       </c>
       <c r="G797" t="n">
-        <v>6.44897317886353</v>
+        <v>6.44897365570068</v>
       </c>
       <c r="H797" t="n">
         <v>7336696</v>
@@ -23511,7 +23511,7 @@
         <v>12.3470487594604</v>
       </c>
       <c r="G798" t="n">
-        <v>6.45194721221924</v>
+        <v>6.4519476890564</v>
       </c>
       <c r="H798" t="n">
         <v>6190600</v>
@@ -23540,7 +23540,7 @@
         <v>12.5862083435059</v>
       </c>
       <c r="G799" t="n">
-        <v>6.57692050933838</v>
+        <v>6.57692003250122</v>
       </c>
       <c r="H799" t="n">
         <v>15152984</v>
@@ -23569,7 +23569,7 @@
         <v>12.4419536590576</v>
       </c>
       <c r="G800" t="n">
-        <v>6.50154066085815</v>
+        <v>6.50153970718384</v>
       </c>
       <c r="H800" t="n">
         <v>11998185</v>
@@ -23598,7 +23598,7 @@
         <v>12.4609346389771</v>
       </c>
       <c r="G801" t="n">
-        <v>6.51145935058594</v>
+        <v>6.5114598274231</v>
       </c>
       <c r="H801" t="n">
         <v>8556211</v>
@@ -23627,7 +23627,7 @@
         <v>12.5273675918579</v>
       </c>
       <c r="G802" t="n">
-        <v>6.5461745262146</v>
+        <v>6.54617357254028</v>
       </c>
       <c r="H802" t="n">
         <v>9906002</v>
@@ -23656,7 +23656,7 @@
         <v>12.4419536590576</v>
       </c>
       <c r="G803" t="n">
-        <v>6.50154066085815</v>
+        <v>6.50153970718384</v>
       </c>
       <c r="H803" t="n">
         <v>9445802</v>
@@ -23685,7 +23685,7 @@
         <v>12.3546419143677</v>
       </c>
       <c r="G804" t="n">
-        <v>6.4559154510498</v>
+        <v>6.45591449737549</v>
       </c>
       <c r="H804" t="n">
         <v>8359228</v>
@@ -23743,7 +23743,7 @@
         <v>12.271125793457</v>
       </c>
       <c r="G806" t="n">
-        <v>6.41227436065674</v>
+        <v>6.4122748374939</v>
       </c>
       <c r="H806" t="n">
         <v>8618454</v>
@@ -23772,7 +23772,7 @@
         <v>12.1762218475342</v>
       </c>
       <c r="G807" t="n">
-        <v>6.36268138885498</v>
+        <v>6.3626823425293</v>
       </c>
       <c r="H807" t="n">
         <v>9713023</v>
@@ -23801,7 +23801,7 @@
         <v>12.2768201828003</v>
       </c>
       <c r="G808" t="n">
-        <v>6.41525077819824</v>
+        <v>6.41524887084961</v>
       </c>
       <c r="H808" t="n">
         <v>9511991</v>
@@ -23830,7 +23830,7 @@
         <v>12.7247676849365</v>
       </c>
       <c r="G809" t="n">
-        <v>6.64932489395142</v>
+        <v>6.64932537078857</v>
       </c>
       <c r="H809" t="n">
         <v>24281661</v>
@@ -23859,7 +23859,7 @@
         <v>12.4343614578247</v>
       </c>
       <c r="G810" t="n">
-        <v>6.49757289886475</v>
+        <v>6.49757242202759</v>
       </c>
       <c r="H810" t="n">
         <v>12067683</v>
@@ -23888,7 +23888,7 @@
         <v>12.1078910827637</v>
       </c>
       <c r="G811" t="n">
-        <v>6.32697629928589</v>
+        <v>6.32697582244873</v>
       </c>
       <c r="H811" t="n">
         <v>16807051</v>
@@ -23946,7 +23946,7 @@
         <v>12.168628692627</v>
       </c>
       <c r="G813" t="n">
-        <v>6.35871410369873</v>
+        <v>6.35871458053589</v>
       </c>
       <c r="H813" t="n">
         <v>7543066</v>
@@ -23975,7 +23975,7 @@
         <v>12.0642347335815</v>
       </c>
       <c r="G814" t="n">
-        <v>6.30416297912598</v>
+        <v>6.30416250228882</v>
       </c>
       <c r="H814" t="n">
         <v>8829340</v>
@@ -24004,7 +24004,7 @@
         <v>11.9769229888916</v>
       </c>
       <c r="G815" t="n">
-        <v>6.25853776931763</v>
+        <v>6.25853872299194</v>
       </c>
       <c r="H815" t="n">
         <v>8459401</v>
@@ -24033,7 +24033,7 @@
         <v>11.9902086257935</v>
       </c>
       <c r="G816" t="n">
-        <v>6.26548099517822</v>
+        <v>6.26548147201538</v>
       </c>
       <c r="H816" t="n">
         <v>10382476</v>
@@ -24091,7 +24091,7 @@
         <v>12.7000932693481</v>
       </c>
       <c r="G818" t="n">
-        <v>6.6364312171936</v>
+        <v>6.63643217086792</v>
       </c>
       <c r="H818" t="n">
         <v>22601173</v>
@@ -24120,7 +24120,7 @@
         <v>12.38121509552</v>
       </c>
       <c r="G819" t="n">
-        <v>6.469801902771</v>
+        <v>6.46980142593384</v>
       </c>
       <c r="H819" t="n">
         <v>20806055</v>
@@ -24149,7 +24149,7 @@
         <v>12.4324626922607</v>
       </c>
       <c r="G820" t="n">
-        <v>6.49658107757568</v>
+        <v>6.49658155441284</v>
       </c>
       <c r="H820" t="n">
         <v>10274653</v>
@@ -24178,7 +24178,7 @@
         <v>12.1249732971191</v>
       </c>
       <c r="G821" t="n">
-        <v>6.33590173721313</v>
+        <v>6.33590221405029</v>
       </c>
       <c r="H821" t="n">
         <v>10466970</v>
@@ -24207,7 +24207,7 @@
         <v>12.3698263168335</v>
       </c>
       <c r="G822" t="n">
-        <v>6.46384954452515</v>
+        <v>6.46385049819946</v>
       </c>
       <c r="H822" t="n">
         <v>13630606</v>
@@ -24294,7 +24294,7 @@
         <v>12.489405632019</v>
       </c>
       <c r="G825" t="n">
-        <v>6.52633619308472</v>
+        <v>6.52633714675903</v>
       </c>
       <c r="H825" t="n">
         <v>10762420</v>
@@ -24323,7 +24323,7 @@
         <v>12.5956993103027</v>
       </c>
       <c r="G826" t="n">
-        <v>6.58188056945801</v>
+        <v>6.58188009262085</v>
       </c>
       <c r="H826" t="n">
         <v>12110367</v>
@@ -24352,7 +24352,7 @@
         <v>12.8974943161011</v>
       </c>
       <c r="G827" t="n">
-        <v>6.73958301544189</v>
+        <v>6.73958349227905</v>
       </c>
       <c r="H827" t="n">
         <v>13350137</v>
@@ -24381,7 +24381,7 @@
         <v>13.0246658325195</v>
       </c>
       <c r="G828" t="n">
-        <v>6.80603551864624</v>
+        <v>6.80603647232056</v>
       </c>
       <c r="H828" t="n">
         <v>23141392</v>
@@ -24410,7 +24410,7 @@
         <v>13.0512390136719</v>
       </c>
       <c r="G829" t="n">
-        <v>6.81992292404175</v>
+        <v>6.81992149353027</v>
       </c>
       <c r="H829" t="n">
         <v>13973303</v>
@@ -24439,7 +24439,7 @@
         <v>13.0303602218628</v>
       </c>
       <c r="G830" t="n">
-        <v>6.80901193618774</v>
+        <v>6.80901145935059</v>
       </c>
       <c r="H830" t="n">
         <v>9526935</v>
@@ -24468,7 +24468,7 @@
         <v>13.0322580337524</v>
       </c>
       <c r="G831" t="n">
-        <v>6.81000375747681</v>
+        <v>6.81000423431396</v>
       </c>
       <c r="H831" t="n">
         <v>7823093</v>
@@ -24497,7 +24497,7 @@
         <v>13.2790098190308</v>
       </c>
       <c r="G832" t="n">
-        <v>6.93894338607788</v>
+        <v>6.93894386291504</v>
       </c>
       <c r="H832" t="n">
         <v>11972110</v>
@@ -24526,7 +24526,7 @@
         <v>13.1309585571289</v>
       </c>
       <c r="G833" t="n">
-        <v>6.86157846450806</v>
+        <v>6.86157989501953</v>
       </c>
       <c r="H833" t="n">
         <v>10628349</v>
@@ -24555,7 +24555,7 @@
         <v>13.1879005432129</v>
       </c>
       <c r="G834" t="n">
-        <v>6.89133405685425</v>
+        <v>6.89133358001709</v>
       </c>
       <c r="H834" t="n">
         <v>12846522</v>
@@ -24584,7 +24584,7 @@
         <v>13.1898002624512</v>
       </c>
       <c r="G835" t="n">
-        <v>6.8923282623291</v>
+        <v>6.89232730865479</v>
       </c>
       <c r="H835" t="n">
         <v>8365656</v>
@@ -24613,7 +24613,7 @@
         <v>13.4783086776733</v>
       </c>
       <c r="G836" t="n">
-        <v>7.04308652877808</v>
+        <v>7.04308700561523</v>
       </c>
       <c r="H836" t="n">
         <v>14841620</v>
@@ -24642,7 +24642,7 @@
         <v>13.5751113891602</v>
       </c>
       <c r="G837" t="n">
-        <v>7.09367179870605</v>
+        <v>7.0936713218689</v>
       </c>
       <c r="H837" t="n">
         <v>8827788</v>
@@ -24729,7 +24729,7 @@
         <v>13.9091739654541</v>
       </c>
       <c r="G840" t="n">
-        <v>7.26823663711548</v>
+        <v>7.26823472976685</v>
       </c>
       <c r="H840" t="n">
         <v>11973943</v>
@@ -24758,7 +24758,7 @@
         <v>13.2884998321533</v>
       </c>
       <c r="G841" t="n">
-        <v>7.28431224822998</v>
+        <v>7.28431129455566</v>
       </c>
       <c r="H841" t="n">
         <v>11265801</v>
@@ -24816,7 +24816,7 @@
         <v>13.0322580337524</v>
       </c>
       <c r="G843" t="n">
-        <v>7.14384794235229</v>
+        <v>7.14384841918945</v>
       </c>
       <c r="H843" t="n">
         <v>6582788</v>
@@ -24845,7 +24845,7 @@
         <v>13.1518383026123</v>
       </c>
       <c r="G844" t="n">
-        <v>7.20939826965332</v>
+        <v>7.20939874649048</v>
       </c>
       <c r="H844" t="n">
         <v>8537298</v>
@@ -24874,7 +24874,7 @@
         <v>13.1195697784424</v>
       </c>
       <c r="G845" t="n">
-        <v>7.19170999526978</v>
+        <v>7.19170951843262</v>
       </c>
       <c r="H845" t="n">
         <v>4309815</v>
@@ -24903,7 +24903,7 @@
         <v>13.0341567993164</v>
       </c>
       <c r="G846" t="n">
-        <v>7.14488935470581</v>
+        <v>7.14488840103149</v>
       </c>
       <c r="H846" t="n">
         <v>6218047</v>
@@ -24932,7 +24932,7 @@
         <v>12.8595333099365</v>
       </c>
       <c r="G847" t="n">
-        <v>7.04916715621948</v>
+        <v>7.04916667938232</v>
       </c>
       <c r="H847" t="n">
         <v>12748455</v>
@@ -24961,7 +24961,7 @@
         <v>13.4517345428467</v>
       </c>
       <c r="G848" t="n">
-        <v>7.3737907409668</v>
+        <v>7.37379169464111</v>
       </c>
       <c r="H848" t="n">
         <v>26077111</v>
@@ -24990,7 +24990,7 @@
         <v>13.1518383026123</v>
       </c>
       <c r="G849" t="n">
-        <v>7.20939826965332</v>
+        <v>7.20939874649048</v>
       </c>
       <c r="H849" t="n">
         <v>12539772</v>
@@ -25019,7 +25019,7 @@
         <v>12.9753160476685</v>
       </c>
       <c r="G850" t="n">
-        <v>7.11263465881348</v>
+        <v>7.11263561248779</v>
       </c>
       <c r="H850" t="n">
         <v>9037764</v>
@@ -25048,7 +25048,7 @@
         <v>12.9012899398804</v>
       </c>
       <c r="G851" t="n">
-        <v>7.07205629348755</v>
+        <v>7.07205533981323</v>
       </c>
       <c r="H851" t="n">
         <v>7338014</v>
@@ -25077,7 +25077,7 @@
         <v>12.4172792434692</v>
       </c>
       <c r="G852" t="n">
-        <v>6.80673742294312</v>
+        <v>6.80673789978027</v>
       </c>
       <c r="H852" t="n">
         <v>12707250</v>
@@ -25135,7 +25135,7 @@
         <v>12.0604381561279</v>
       </c>
       <c r="G854" t="n">
-        <v>6.61112928390503</v>
+        <v>6.61112976074219</v>
       </c>
       <c r="H854" t="n">
         <v>10847699</v>
@@ -25164,7 +25164,7 @@
         <v>12.2464513778687</v>
       </c>
       <c r="G855" t="n">
-        <v>6.71309566497803</v>
+        <v>6.71309471130371</v>
       </c>
       <c r="H855" t="n">
         <v>7854157</v>
@@ -25222,7 +25222,7 @@
         <v>12.5691251754761</v>
       </c>
       <c r="G857" t="n">
-        <v>6.88997507095337</v>
+        <v>6.88997459411621</v>
       </c>
       <c r="H857" t="n">
         <v>8691096</v>
@@ -25251,7 +25251,7 @@
         <v>12.686806678772</v>
       </c>
       <c r="G858" t="n">
-        <v>6.95448350906372</v>
+        <v>6.95448398590088</v>
       </c>
       <c r="H858" t="n">
         <v>15894410</v>
@@ -25280,7 +25280,7 @@
         <v>11.3524522781372</v>
       </c>
       <c r="G859" t="n">
-        <v>6.93350172042847</v>
+        <v>6.93350124359131</v>
       </c>
       <c r="H859" t="n">
         <v>15924075</v>
@@ -25309,7 +25309,7 @@
         <v>11.2708349227905</v>
       </c>
       <c r="G860" t="n">
-        <v>6.88365459442139</v>
+        <v>6.88365364074707</v>
       </c>
       <c r="H860" t="n">
         <v>7714819</v>
@@ -25338,7 +25338,7 @@
         <v>11.177827835083</v>
       </c>
       <c r="G861" t="n">
-        <v>6.82684946060181</v>
+        <v>6.82684993743896</v>
       </c>
       <c r="H861" t="n">
         <v>7598910</v>
@@ -25396,7 +25396,7 @@
         <v>10.8722362518311</v>
       </c>
       <c r="G863" t="n">
-        <v>6.64020967483521</v>
+        <v>6.64021062850952</v>
       </c>
       <c r="H863" t="n">
         <v>6991145</v>
@@ -25425,7 +25425,7 @@
         <v>11.7396621704102</v>
       </c>
       <c r="G864" t="n">
-        <v>7.16998958587646</v>
+        <v>7.16998910903931</v>
       </c>
       <c r="H864" t="n">
         <v>60224625</v>
@@ -25454,7 +25454,7 @@
         <v>11.6352672576904</v>
       </c>
       <c r="G865" t="n">
-        <v>7.10623025894165</v>
+        <v>7.10622978210449</v>
       </c>
       <c r="H865" t="n">
         <v>22205120</v>
@@ -25483,7 +25483,7 @@
         <v>11.4929113388062</v>
       </c>
       <c r="G866" t="n">
-        <v>7.01928663253784</v>
+        <v>7.01928615570068</v>
       </c>
       <c r="H866" t="n">
         <v>17340802</v>
@@ -25512,7 +25512,7 @@
         <v>11.398006439209</v>
       </c>
       <c r="G867" t="n">
-        <v>6.96132278442383</v>
+        <v>6.96132373809814</v>
       </c>
       <c r="H867" t="n">
         <v>9839102</v>
@@ -25541,7 +25541,7 @@
         <v>10.8551540374756</v>
       </c>
       <c r="G868" t="n">
-        <v>6.62977647781372</v>
+        <v>6.62977695465088</v>
       </c>
       <c r="H868" t="n">
         <v>28158505</v>
@@ -25570,7 +25570,7 @@
         <v>10.794415473938</v>
       </c>
       <c r="G869" t="n">
-        <v>6.59268140792847</v>
+        <v>6.59268093109131</v>
       </c>
       <c r="H869" t="n">
         <v>13751352</v>
@@ -25599,7 +25599,7 @@
         <v>11.2119941711426</v>
       </c>
       <c r="G870" t="n">
-        <v>6.84771680831909</v>
+        <v>6.84771728515625</v>
       </c>
       <c r="H870" t="n">
         <v>16304416</v>
@@ -25628,7 +25628,7 @@
         <v>11.1038026809692</v>
       </c>
       <c r="G871" t="n">
-        <v>6.78163957595825</v>
+        <v>6.78163909912109</v>
       </c>
       <c r="H871" t="n">
         <v>9556509</v>
@@ -25657,7 +25657,7 @@
         <v>11.1132926940918</v>
       </c>
       <c r="G872" t="n">
-        <v>6.78743457794189</v>
+        <v>6.78743505477905</v>
       </c>
       <c r="H872" t="n">
         <v>23597285</v>
@@ -25686,7 +25686,7 @@
         <v>11.0753316879272</v>
       </c>
       <c r="G873" t="n">
-        <v>6.7642502784729</v>
+        <v>6.76425075531006</v>
       </c>
       <c r="H873" t="n">
         <v>8606841</v>
@@ -25773,7 +25773,7 @@
         <v>11.1949110031128</v>
       </c>
       <c r="G876" t="n">
-        <v>6.83728408813477</v>
+        <v>6.83728313446045</v>
       </c>
       <c r="H876" t="n">
         <v>7756257</v>
@@ -25831,7 +25831,7 @@
         <v>11.236668586731</v>
       </c>
       <c r="G878" t="n">
-        <v>6.86278629302979</v>
+        <v>6.86278676986694</v>
       </c>
       <c r="H878" t="n">
         <v>5229858</v>
@@ -25860,7 +25860,7 @@
         <v>11.3372678756714</v>
       </c>
       <c r="G879" t="n">
-        <v>6.92422676086426</v>
+        <v>6.92422723770142</v>
       </c>
       <c r="H879" t="n">
         <v>5923658</v>
@@ -25889,7 +25889,7 @@
         <v>11.4378662109375</v>
       </c>
       <c r="G880" t="n">
-        <v>6.98566865921021</v>
+        <v>6.98566770553589</v>
       </c>
       <c r="H880" t="n">
         <v>10165151</v>
@@ -25918,7 +25918,7 @@
         <v>11.5669355392456</v>
       </c>
       <c r="G881" t="n">
-        <v>7.0644965171814</v>
+        <v>7.06449747085571</v>
       </c>
       <c r="H881" t="n">
         <v>9682969</v>
@@ -25947,7 +25947,7 @@
         <v>11.7073936462402</v>
       </c>
       <c r="G882" t="n">
-        <v>7.15028238296509</v>
+        <v>7.15028285980225</v>
       </c>
       <c r="H882" t="n">
         <v>13384556</v>
@@ -26005,7 +26005,7 @@
         <v>11.6941080093384</v>
       </c>
       <c r="G884" t="n">
-        <v>7.14216804504395</v>
+        <v>7.14216709136963</v>
       </c>
       <c r="H884" t="n">
         <v>5686660</v>
@@ -26034,7 +26034,7 @@
         <v>11.4967069625854</v>
       </c>
       <c r="G885" t="n">
-        <v>7.02160596847534</v>
+        <v>7.02160501480103</v>
       </c>
       <c r="H885" t="n">
         <v>5951436</v>
@@ -26121,7 +26121,7 @@
         <v>11.6409606933594</v>
       </c>
       <c r="G888" t="n">
-        <v>7.10970830917358</v>
+        <v>7.10970783233643</v>
       </c>
       <c r="H888" t="n">
         <v>6813411</v>
@@ -26150,7 +26150,7 @@
         <v>11.7187833786011</v>
       </c>
       <c r="G889" t="n">
-        <v>7.15723752975464</v>
+        <v>7.15723848342896</v>
       </c>
       <c r="H889" t="n">
         <v>7399451</v>
@@ -26179,7 +26179,7 @@
         <v>11.6751270294189</v>
       </c>
       <c r="G890" t="n">
-        <v>7.13057470321655</v>
+        <v>7.13057565689087</v>
       </c>
       <c r="H890" t="n">
         <v>8437718</v>
@@ -26208,7 +26208,7 @@
         <v>12.0034961700439</v>
       </c>
       <c r="G891" t="n">
-        <v>7.33112668991089</v>
+        <v>7.33112621307373</v>
       </c>
       <c r="H891" t="n">
         <v>12485858</v>
@@ -26266,7 +26266,7 @@
         <v>11.9940052032471</v>
       </c>
       <c r="G893" t="n">
-        <v>7.32532930374146</v>
+        <v>7.32533025741577</v>
       </c>
       <c r="H893" t="n">
         <v>4682690</v>
@@ -26295,7 +26295,7 @@
         <v>11.9351654052734</v>
       </c>
       <c r="G894" t="n">
-        <v>7.28939342498779</v>
+        <v>7.28939390182495</v>
       </c>
       <c r="H894" t="n">
         <v>5081986</v>
@@ -26324,7 +26324,7 @@
         <v>11.8041973114014</v>
       </c>
       <c r="G895" t="n">
-        <v>7.20940494537354</v>
+        <v>7.20940446853638</v>
       </c>
       <c r="H895" t="n">
         <v>6925731</v>
@@ -26353,7 +26353,7 @@
         <v>11.7966041564941</v>
       </c>
       <c r="G896" t="n">
-        <v>7.20476627349854</v>
+        <v>7.20476675033569</v>
       </c>
       <c r="H896" t="n">
         <v>6462180</v>
@@ -26382,7 +26382,7 @@
         <v>11.7073936462402</v>
       </c>
       <c r="G897" t="n">
-        <v>7.15028238296509</v>
+        <v>7.15028285980225</v>
       </c>
       <c r="H897" t="n">
         <v>7278375</v>
@@ -26411,7 +26411,7 @@
         <v>11.9313688278198</v>
       </c>
       <c r="G898" t="n">
-        <v>7.28707361221313</v>
+        <v>7.28707408905029</v>
       </c>
       <c r="H898" t="n">
         <v>10782814</v>
@@ -26440,7 +26440,7 @@
         <v>11.9294700622559</v>
       </c>
       <c r="G899" t="n">
-        <v>7.2859148979187</v>
+        <v>7.28591442108154</v>
       </c>
       <c r="H899" t="n">
         <v>8199234</v>
@@ -26469,7 +26469,7 @@
         <v>11.559344291687</v>
       </c>
       <c r="G900" t="n">
-        <v>7.05986022949219</v>
+        <v>7.05986070632935</v>
       </c>
       <c r="H900" t="n">
         <v>21597824</v>
@@ -26498,7 +26498,7 @@
         <v>11.5669355392456</v>
       </c>
       <c r="G901" t="n">
-        <v>7.0644965171814</v>
+        <v>7.06449747085571</v>
       </c>
       <c r="H901" t="n">
         <v>10779552</v>
@@ -26527,7 +26527,7 @@
         <v>11.5840187072754</v>
       </c>
       <c r="G902" t="n">
-        <v>7.07493114471436</v>
+        <v>7.07493019104004</v>
       </c>
       <c r="H902" t="n">
         <v>7964489</v>
@@ -26585,7 +26585,7 @@
         <v>11.398006439209</v>
       </c>
       <c r="G904" t="n">
-        <v>6.96132278442383</v>
+        <v>6.96132373809814</v>
       </c>
       <c r="H904" t="n">
         <v>6307481</v>
@@ -26643,7 +26643,7 @@
         <v>11.971227645874</v>
       </c>
       <c r="G906" t="n">
-        <v>7.31141757965088</v>
+        <v>7.31141805648804</v>
       </c>
       <c r="H906" t="n">
         <v>11014422</v>
@@ -26672,7 +26672,7 @@
         <v>11.7795219421387</v>
       </c>
       <c r="G907" t="n">
-        <v>7.19433450698853</v>
+        <v>7.19433403015137</v>
       </c>
       <c r="H907" t="n">
         <v>12045507</v>
@@ -26701,7 +26701,7 @@
         <v>11.7187833786011</v>
       </c>
       <c r="G908" t="n">
-        <v>7.15723752975464</v>
+        <v>7.15723848342896</v>
       </c>
       <c r="H908" t="n">
         <v>7115760</v>
@@ -26730,7 +26730,7 @@
         <v>11.6048984527588</v>
       </c>
       <c r="G909" t="n">
-        <v>7.08768320083618</v>
+        <v>7.08768367767334</v>
       </c>
       <c r="H909" t="n">
         <v>5469067</v>
@@ -26759,7 +26759,7 @@
         <v>11.1038026809692</v>
       </c>
       <c r="G910" t="n">
-        <v>6.78163957595825</v>
+        <v>6.78163909912109</v>
       </c>
       <c r="H910" t="n">
         <v>18606256</v>
@@ -26788,7 +26788,7 @@
         <v>11.4226808547974</v>
       </c>
       <c r="G911" t="n">
-        <v>6.97639322280884</v>
+        <v>6.97639274597168</v>
       </c>
       <c r="H911" t="n">
         <v>18475377</v>
@@ -26817,7 +26817,7 @@
         <v>11.4587450027466</v>
       </c>
       <c r="G912" t="n">
-        <v>6.99842023849487</v>
+        <v>6.99841976165771</v>
       </c>
       <c r="H912" t="n">
         <v>7746554</v>
@@ -26846,7 +26846,7 @@
         <v>11.1132926940918</v>
       </c>
       <c r="G913" t="n">
-        <v>6.78743457794189</v>
+        <v>6.78743505477905</v>
       </c>
       <c r="H913" t="n">
         <v>14204815</v>
@@ -26904,7 +26904,7 @@
         <v>11.1645421981812</v>
       </c>
       <c r="G915" t="n">
-        <v>6.81873512268066</v>
+        <v>6.81873607635498</v>
       </c>
       <c r="H915" t="n">
         <v>13526423</v>
@@ -26933,7 +26933,7 @@
         <v>11.1038026809692</v>
       </c>
       <c r="G916" t="n">
-        <v>6.78163957595825</v>
+        <v>6.78163909912109</v>
       </c>
       <c r="H916" t="n">
         <v>8534339</v>
@@ -26962,7 +26962,7 @@
         <v>11.2461585998535</v>
       </c>
       <c r="G917" t="n">
-        <v>6.86858320236206</v>
+        <v>6.8685827255249</v>
       </c>
       <c r="H917" t="n">
         <v>5015432</v>
@@ -26991,7 +26991,7 @@
         <v>11.0145931243896</v>
       </c>
       <c r="G918" t="n">
-        <v>6.72715377807617</v>
+        <v>6.72715425491333</v>
       </c>
       <c r="H918" t="n">
         <v>7228084</v>
@@ -27020,7 +27020,7 @@
         <v>11.0088987350464</v>
       </c>
       <c r="G919" t="n">
-        <v>6.7236762046814</v>
+        <v>6.72367668151855</v>
       </c>
       <c r="H919" t="n">
         <v>5218718</v>
@@ -27078,7 +27078,7 @@
         <v>10.7830257415771</v>
       </c>
       <c r="G921" t="n">
-        <v>6.5857253074646</v>
+        <v>6.58572435379028</v>
       </c>
       <c r="H921" t="n">
         <v>7995093</v>
@@ -27107,7 +27107,7 @@
         <v>10.4907207489014</v>
       </c>
       <c r="G922" t="n">
-        <v>6.4072003364563</v>
+        <v>6.40719938278198</v>
       </c>
       <c r="H922" t="n">
         <v>15734219</v>
@@ -27136,7 +27136,7 @@
         <v>10.6862239837646</v>
       </c>
       <c r="G923" t="n">
-        <v>6.52660274505615</v>
+        <v>6.52660322189331</v>
       </c>
       <c r="H923" t="n">
         <v>8919160</v>
@@ -27252,7 +27252,7 @@
         <v>10.7165927886963</v>
       </c>
       <c r="G927" t="n">
-        <v>6.54515027999878</v>
+        <v>6.54515171051025</v>
       </c>
       <c r="H927" t="n">
         <v>8356968</v>
@@ -27310,7 +27310,7 @@
         <v>11.0088987350464</v>
       </c>
       <c r="G929" t="n">
-        <v>6.7236762046814</v>
+        <v>6.72367668151855</v>
       </c>
       <c r="H929" t="n">
         <v>7288298</v>
@@ -27339,7 +27339,7 @@
         <v>11.0430641174316</v>
       </c>
       <c r="G930" t="n">
-        <v>6.74454307556152</v>
+        <v>6.74454259872437</v>
       </c>
       <c r="H930" t="n">
         <v>7687713</v>
@@ -27368,7 +27368,7 @@
         <v>11.1417646408081</v>
       </c>
       <c r="G931" t="n">
-        <v>6.8048243522644</v>
+        <v>6.80482339859009</v>
       </c>
       <c r="H931" t="n">
         <v>8405039</v>
@@ -27426,7 +27426,7 @@
         <v>11.2385673522949</v>
       </c>
       <c r="G933" t="n">
-        <v>6.86394691467285</v>
+        <v>6.86394596099854</v>
       </c>
       <c r="H933" t="n">
         <v>2988232</v>
@@ -27455,7 +27455,7 @@
         <v>11.3372678756714</v>
       </c>
       <c r="G934" t="n">
-        <v>6.92422676086426</v>
+        <v>6.92422723770142</v>
       </c>
       <c r="H934" t="n">
         <v>10036990</v>
@@ -27484,7 +27484,7 @@
         <v>11.5973052978516</v>
       </c>
       <c r="G935" t="n">
-        <v>7.0830454826355</v>
+        <v>7.08304595947266</v>
       </c>
       <c r="H935" t="n">
         <v>12048310</v>
@@ -27513,7 +27513,7 @@
         <v>11.9370632171631</v>
       </c>
       <c r="G936" t="n">
-        <v>7.29055213928223</v>
+        <v>7.29055118560791</v>
       </c>
       <c r="H936" t="n">
         <v>12407160</v>
@@ -27571,7 +27571,7 @@
         <v>12.0718269348145</v>
       </c>
       <c r="G938" t="n">
-        <v>7.37285947799683</v>
+        <v>7.37285900115967</v>
       </c>
       <c r="H938" t="n">
         <v>9164685</v>
@@ -27629,7 +27629,7 @@
         <v>11.7795219421387</v>
       </c>
       <c r="G940" t="n">
-        <v>7.19433450698853</v>
+        <v>7.19433403015137</v>
       </c>
       <c r="H940" t="n">
         <v>10017690</v>
@@ -27658,7 +27658,7 @@
         <v>11.9313688278198</v>
       </c>
       <c r="G941" t="n">
-        <v>7.28707361221313</v>
+        <v>7.28707408905029</v>
       </c>
       <c r="H941" t="n">
         <v>10641382</v>
@@ -27687,7 +27687,7 @@
         <v>11.9218778610229</v>
       </c>
       <c r="G942" t="n">
-        <v>7.28127765655518</v>
+        <v>7.28127813339233</v>
       </c>
       <c r="H942" t="n">
         <v>5712763</v>
@@ -27745,7 +27745,7 @@
         <v>11.7586431503296</v>
       </c>
       <c r="G944" t="n">
-        <v>7.1815824508667</v>
+        <v>7.18158292770386</v>
       </c>
       <c r="H944" t="n">
         <v>7605053</v>
@@ -27774,7 +27774,7 @@
         <v>11.7586431503296</v>
       </c>
       <c r="G945" t="n">
-        <v>7.1815824508667</v>
+        <v>7.18158292770386</v>
       </c>
       <c r="H945" t="n">
         <v>7649590</v>
@@ -27832,7 +27832,7 @@
         <v>11.7073936462402</v>
       </c>
       <c r="G947" t="n">
-        <v>7.15028238296509</v>
+        <v>7.15028285980225</v>
       </c>
       <c r="H947" t="n">
         <v>8019289</v>
@@ -27861,7 +27861,7 @@
         <v>11.5764255523682</v>
       </c>
       <c r="G948" t="n">
-        <v>7.07029390335083</v>
+        <v>7.07029294967651</v>
       </c>
       <c r="H948" t="n">
         <v>8415376</v>
@@ -27948,7 +27948,7 @@
         <v>11.208197593689</v>
       </c>
       <c r="G951" t="n">
-        <v>6.84539794921875</v>
+        <v>6.84539890289307</v>
       </c>
       <c r="H951" t="n">
         <v>6266730</v>
@@ -27977,7 +27977,7 @@
         <v>11.2613439559937</v>
       </c>
       <c r="G952" t="n">
-        <v>6.87785720825195</v>
+        <v>6.87785673141479</v>
       </c>
       <c r="H952" t="n">
         <v>3876072</v>
@@ -28035,7 +28035,7 @@
         <v>11.1588468551636</v>
       </c>
       <c r="G954" t="n">
-        <v>6.81525802612305</v>
+        <v>6.81525707244873</v>
       </c>
       <c r="H954" t="n">
         <v>6266902</v>
@@ -28064,7 +28064,7 @@
         <v>10.8570518493652</v>
       </c>
       <c r="G955" t="n">
-        <v>6.63093709945679</v>
+        <v>6.63093566894531</v>
       </c>
       <c r="H955" t="n">
         <v>11840992</v>
@@ -28093,7 +28093,7 @@
         <v>10.7090005874634</v>
       </c>
       <c r="G956" t="n">
-        <v>6.54051399230957</v>
+        <v>6.54051446914673</v>
       </c>
       <c r="H956" t="n">
         <v>10188023</v>
@@ -28122,7 +28122,7 @@
         <v>10.6957139968872</v>
       </c>
       <c r="G957" t="n">
-        <v>6.53239965438843</v>
+        <v>6.53239870071411</v>
       </c>
       <c r="H957" t="n">
         <v>9541843</v>
@@ -28151,7 +28151,7 @@
         <v>10.7659435272217</v>
       </c>
       <c r="G958" t="n">
-        <v>6.57529163360596</v>
+        <v>6.57529211044312</v>
       </c>
       <c r="H958" t="n">
         <v>5181589</v>
@@ -28180,7 +28180,7 @@
         <v>10.6577529907227</v>
       </c>
       <c r="G959" t="n">
-        <v>6.50921440124512</v>
+        <v>6.50921487808228</v>
       </c>
       <c r="H959" t="n">
         <v>7014502</v>
@@ -28209,7 +28209,7 @@
         <v>10.7222881317139</v>
       </c>
       <c r="G960" t="n">
-        <v>6.54862880706787</v>
+        <v>6.54862976074219</v>
       </c>
       <c r="H960" t="n">
         <v>8304332</v>
@@ -28267,7 +28267,7 @@
         <v>11.2575483322144</v>
       </c>
       <c r="G962" t="n">
-        <v>6.87553882598877</v>
+        <v>6.87553977966309</v>
       </c>
       <c r="H962" t="n">
         <v>11291785</v>
@@ -28296,7 +28296,7 @@
         <v>11.3277769088745</v>
       </c>
       <c r="G963" t="n">
-        <v>6.91843175888062</v>
+        <v>6.91843128204346</v>
       </c>
       <c r="H963" t="n">
         <v>7461695</v>
@@ -28325,7 +28325,7 @@
         <v>11.4587450027466</v>
       </c>
       <c r="G964" t="n">
-        <v>6.99842023849487</v>
+        <v>6.99841976165771</v>
       </c>
       <c r="H964" t="n">
         <v>10041863</v>
@@ -28383,7 +28383,7 @@
         <v>11.5251779556274</v>
       </c>
       <c r="G966" t="n">
-        <v>7.03899431228638</v>
+        <v>7.03899335861206</v>
       </c>
       <c r="H966" t="n">
         <v>9543633</v>
@@ -28441,7 +28441,7 @@
         <v>11.3904142379761</v>
       </c>
       <c r="G968" t="n">
-        <v>6.95668745040894</v>
+        <v>6.95668649673462</v>
       </c>
       <c r="H968" t="n">
         <v>11598281</v>
@@ -28499,7 +28499,7 @@
         <v>11.236668586731</v>
       </c>
       <c r="G970" t="n">
-        <v>6.86278629302979</v>
+        <v>6.86278676986694</v>
       </c>
       <c r="H970" t="n">
         <v>6269190</v>
@@ -28557,7 +28557,7 @@
         <v>11.2442607879639</v>
       </c>
       <c r="G972" t="n">
-        <v>6.86742353439331</v>
+        <v>6.86742305755615</v>
       </c>
       <c r="H972" t="n">
         <v>5396727</v>
@@ -28586,7 +28586,7 @@
         <v>11.3031015396118</v>
       </c>
       <c r="G973" t="n">
-        <v>6.90336036682129</v>
+        <v>6.90336084365845</v>
       </c>
       <c r="H973" t="n">
         <v>10515673</v>
@@ -28615,7 +28615,7 @@
         <v>11.1512546539307</v>
       </c>
       <c r="G974" t="n">
-        <v>6.81062126159668</v>
+        <v>6.81062078475952</v>
       </c>
       <c r="H974" t="n">
         <v>11762724</v>
@@ -28673,7 +28673,7 @@
         <v>13.2182712554932</v>
       </c>
       <c r="G976" t="n">
-        <v>8.07304954528809</v>
+        <v>8.07304859161377</v>
       </c>
       <c r="H976" t="n">
         <v>73306102</v>
@@ -28702,7 +28702,7 @@
         <v>13.2960920333862</v>
       </c>
       <c r="G977" t="n">
-        <v>8.12057685852051</v>
+        <v>8.12057781219482</v>
       </c>
       <c r="H977" t="n">
         <v>27936738</v>
@@ -28731,7 +28731,7 @@
         <v>13.6358499526978</v>
       </c>
       <c r="G978" t="n">
-        <v>8.32808589935303</v>
+        <v>8.32808494567871</v>
       </c>
       <c r="H978" t="n">
         <v>26086439</v>
@@ -28847,7 +28847,7 @@
         <v>13.888295173645</v>
       </c>
       <c r="G982" t="n">
-        <v>8.48226642608643</v>
+        <v>8.48226547241211</v>
       </c>
       <c r="H982" t="n">
         <v>9871220</v>
@@ -28876,7 +28876,7 @@
         <v>13.7706136703491</v>
       </c>
       <c r="G983" t="n">
-        <v>8.41039276123047</v>
+        <v>8.41039085388184</v>
       </c>
       <c r="H983" t="n">
         <v>8348142</v>
@@ -28905,7 +28905,7 @@
         <v>13.9357471466064</v>
       </c>
       <c r="G984" t="n">
-        <v>8.51124572753906</v>
+        <v>8.51124668121338</v>
       </c>
       <c r="H984" t="n">
         <v>10051345</v>
@@ -28963,7 +28963,7 @@
         <v>13.7668180465698</v>
       </c>
       <c r="G986" t="n">
-        <v>8.40807437896729</v>
+        <v>8.40807342529297</v>
       </c>
       <c r="H986" t="n">
         <v>6878905</v>
@@ -28992,7 +28992,7 @@
         <v>13.7895946502686</v>
       </c>
       <c r="G987" t="n">
-        <v>8.4219856262207</v>
+        <v>8.42198467254639</v>
       </c>
       <c r="H987" t="n">
         <v>7697920</v>
@@ -29050,7 +29050,7 @@
         <v>13.4137735366821</v>
       </c>
       <c r="G989" t="n">
-        <v>8.19245147705078</v>
+        <v>8.1924524307251</v>
       </c>
       <c r="H989" t="n">
         <v>8664505</v>
@@ -29108,7 +29108,7 @@
         <v>12.7551383972168</v>
       </c>
       <c r="G991" t="n">
-        <v>7.79019165039062</v>
+        <v>7.79019069671631</v>
       </c>
       <c r="H991" t="n">
         <v>29829158</v>
@@ -29137,7 +29137,7 @@
         <v>12.6830110549927</v>
       </c>
       <c r="G992" t="n">
-        <v>7.74613857269287</v>
+        <v>7.7461404800415</v>
       </c>
       <c r="H992" t="n">
         <v>10755842</v>
@@ -29166,7 +29166,7 @@
         <v>12.9050874710083</v>
       </c>
       <c r="G993" t="n">
-        <v>7.88177156448364</v>
+        <v>7.88177299499512</v>
       </c>
       <c r="H993" t="n">
         <v>6869746</v>
@@ -29224,7 +29224,7 @@
         <v>12.9202709197998</v>
       </c>
       <c r="G995" t="n">
-        <v>7.89104604721069</v>
+        <v>7.89104509353638</v>
       </c>
       <c r="H995" t="n">
         <v>6259587</v>
@@ -29282,7 +29282,7 @@
         <v>12.7361574172974</v>
       </c>
       <c r="G997" t="n">
-        <v>7.77859973907471</v>
+        <v>7.77859878540039</v>
       </c>
       <c r="H997" t="n">
         <v>4566360</v>
@@ -29311,7 +29311,7 @@
         <v>12.6146793365479</v>
       </c>
       <c r="G998" t="n">
-        <v>7.70440626144409</v>
+        <v>7.70440530776978</v>
       </c>
       <c r="H998" t="n">
         <v>10026295</v>
@@ -29340,7 +29340,7 @@
         <v>12.5292663574219</v>
       </c>
       <c r="G999" t="n">
-        <v>7.6522388458252</v>
+        <v>7.65223932266235</v>
       </c>
       <c r="H999" t="n">
         <v>7457729</v>
@@ -29427,7 +29427,7 @@
         <v>12.5862083435059</v>
       </c>
       <c r="G1002" t="n">
-        <v>7.68701791763306</v>
+        <v>7.68701648712158</v>
       </c>
       <c r="H1002" t="n">
         <v>6633338</v>
@@ -29572,7 +29572,7 @@
         <v>12.6469469070435</v>
       </c>
       <c r="G1007" t="n">
-        <v>7.72411298751831</v>
+        <v>7.72411346435547</v>
       </c>
       <c r="H1007" t="n">
         <v>12352255</v>
@@ -29601,7 +29601,7 @@
         <v>12.7836093902588</v>
       </c>
       <c r="G1008" t="n">
-        <v>7.80757904052734</v>
+        <v>7.80758047103882</v>
       </c>
       <c r="H1008" t="n">
         <v>7178859</v>
@@ -29630,7 +29630,7 @@
         <v>12.9050874710083</v>
       </c>
       <c r="G1009" t="n">
-        <v>7.88177156448364</v>
+        <v>7.88177299499512</v>
       </c>
       <c r="H1009" t="n">
         <v>9982091</v>
@@ -29688,7 +29688,7 @@
         <v>12.9088830947876</v>
       </c>
       <c r="G1011" t="n">
-        <v>7.8840913772583</v>
+        <v>7.88408994674683</v>
       </c>
       <c r="H1011" t="n">
         <v>12182873</v>
@@ -29746,7 +29746,7 @@
         <v>12.817774772644</v>
       </c>
       <c r="G1013" t="n">
-        <v>7.82844638824463</v>
+        <v>7.82844591140747</v>
       </c>
       <c r="H1013" t="n">
         <v>6012672</v>
@@ -29775,7 +29775,7 @@
         <v>12.7456474304199</v>
       </c>
       <c r="G1014" t="n">
-        <v>7.78439426422119</v>
+        <v>7.78439378738403</v>
       </c>
       <c r="H1014" t="n">
         <v>6456581</v>
@@ -29833,7 +29833,7 @@
         <v>12.6754179000854</v>
       </c>
       <c r="G1016" t="n">
-        <v>7.74150228500366</v>
+        <v>7.74150133132935</v>
       </c>
       <c r="H1016" t="n">
         <v>6162266</v>
@@ -29862,7 +29862,7 @@
         <v>12.4115839004517</v>
       </c>
       <c r="G1017" t="n">
-        <v>7.5803656578064</v>
+        <v>7.58036613464355</v>
       </c>
       <c r="H1017" t="n">
         <v>11057906</v>
@@ -29920,7 +29920,7 @@
         <v>12.299596786499</v>
       </c>
       <c r="G1019" t="n">
-        <v>7.51196956634521</v>
+        <v>7.51197004318237</v>
       </c>
       <c r="H1019" t="n">
         <v>7565735</v>
@@ -29949,7 +29949,7 @@
         <v>12.1439542770386</v>
       </c>
       <c r="G1020" t="n">
-        <v>7.41691064834595</v>
+        <v>7.41691160202026</v>
       </c>
       <c r="H1020" t="n">
         <v>11683621</v>
@@ -29978,7 +29978,7 @@
         <v>12.1781196594238</v>
       </c>
       <c r="G1021" t="n">
-        <v>7.43777799606323</v>
+        <v>7.43777751922607</v>
       </c>
       <c r="H1021" t="n">
         <v>8721406</v>
@@ -30007,7 +30007,7 @@
         <v>12.1762218475342</v>
       </c>
       <c r="G1022" t="n">
-        <v>7.43661880493164</v>
+        <v>7.43661737442017</v>
       </c>
       <c r="H1022" t="n">
         <v>8590564</v>
@@ -30036,7 +30036,7 @@
         <v>12.1002979278564</v>
       </c>
       <c r="G1023" t="n">
-        <v>7.39024782180786</v>
+        <v>7.39024829864502</v>
       </c>
       <c r="H1023" t="n">
         <v>8910297</v>
@@ -30065,7 +30065,7 @@
         <v>12.0642347335815</v>
       </c>
       <c r="G1024" t="n">
-        <v>7.36822128295898</v>
+        <v>7.3682222366333</v>
       </c>
       <c r="H1024" t="n">
         <v>8662160</v>
@@ -30094,7 +30094,7 @@
         <v>11.8364639282227</v>
       </c>
       <c r="G1025" t="n">
-        <v>7.22911167144775</v>
+        <v>7.2291111946106</v>
       </c>
       <c r="H1025" t="n">
         <v>10457038</v>
@@ -30152,7 +30152,7 @@
         <v>11.7985019683838</v>
       </c>
       <c r="G1027" t="n">
-        <v>7.2059268951416</v>
+        <v>7.20592641830444</v>
       </c>
       <c r="H1027" t="n">
         <v>6600020</v>
@@ -30181,7 +30181,7 @@
         <v>11.8231782913208</v>
       </c>
       <c r="G1028" t="n">
-        <v>7.22099733352661</v>
+        <v>7.22099685668945</v>
       </c>
       <c r="H1028" t="n">
         <v>4612748</v>
@@ -30210,7 +30210,7 @@
         <v>11.7017002105713</v>
       </c>
       <c r="G1029" t="n">
-        <v>7.146803855896</v>
+        <v>7.14680528640747</v>
       </c>
       <c r="H1029" t="n">
         <v>7233535</v>
@@ -30239,7 +30239,7 @@
         <v>11.5973052978516</v>
       </c>
       <c r="G1030" t="n">
-        <v>7.0830454826355</v>
+        <v>7.08304595947266</v>
       </c>
       <c r="H1030" t="n">
         <v>9372736</v>
@@ -30355,7 +30355,7 @@
         <v>11.4018020629883</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.96364259719849</v>
+        <v>6.96364212036133</v>
       </c>
       <c r="H1034" t="n">
         <v>8651481</v>
@@ -30384,7 +30384,7 @@
         <v>11.5118913650513</v>
       </c>
       <c r="G1035" t="n">
-        <v>7.0308780670166</v>
+        <v>7.03087997436523</v>
       </c>
       <c r="H1035" t="n">
         <v>7967142</v>
@@ -30413,7 +30413,7 @@
         <v>11.318286895752</v>
       </c>
       <c r="G1036" t="n">
-        <v>6.91263437271118</v>
+        <v>6.9126353263855</v>
       </c>
       <c r="H1036" t="n">
         <v>11133203</v>
@@ -30500,7 +30500,7 @@
         <v>11.398006439209</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.96132278442383</v>
+        <v>6.96132373809814</v>
       </c>
       <c r="H1039" t="n">
         <v>10806337</v>
@@ -30558,7 +30558,7 @@
         <v>11.777624130249</v>
       </c>
       <c r="G1041" t="n">
-        <v>7.19317388534546</v>
+        <v>7.19317579269409</v>
       </c>
       <c r="H1041" t="n">
         <v>17420557</v>
@@ -30703,7 +30703,7 @@
         <v>11.7985019683838</v>
       </c>
       <c r="G1046" t="n">
-        <v>7.2059268951416</v>
+        <v>7.20592641830444</v>
       </c>
       <c r="H1046" t="n">
         <v>7757263</v>
@@ -30732,7 +30732,7 @@
         <v>11.6371650695801</v>
       </c>
       <c r="G1047" t="n">
-        <v>7.10738945007324</v>
+        <v>7.1073899269104</v>
       </c>
       <c r="H1047" t="n">
         <v>7845003</v>
@@ -30790,7 +30790,7 @@
         <v>11.5840187072754</v>
       </c>
       <c r="G1049" t="n">
-        <v>7.07493114471436</v>
+        <v>7.07493019104004</v>
       </c>
       <c r="H1049" t="n">
         <v>7295141</v>
@@ -30848,7 +30848,7 @@
         <v>11.6504516601562</v>
       </c>
       <c r="G1051" t="n">
-        <v>7.11550426483154</v>
+        <v>7.11550521850586</v>
       </c>
       <c r="H1051" t="n">
         <v>8917979</v>
@@ -30877,7 +30877,7 @@
         <v>11.4644393920898</v>
       </c>
       <c r="G1052" t="n">
-        <v>7.00189733505249</v>
+        <v>7.00189781188965</v>
       </c>
       <c r="H1052" t="n">
         <v>11179493</v>
@@ -30906,7 +30906,7 @@
         <v>10.7621469497681</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.57297420501709</v>
+        <v>6.57297277450562</v>
       </c>
       <c r="H1053" t="n">
         <v>25864410</v>
@@ -30935,7 +30935,7 @@
         <v>10.684326171875</v>
       </c>
       <c r="G1054" t="n">
-        <v>6.52544403076172</v>
+        <v>6.52544355392456</v>
       </c>
       <c r="H1054" t="n">
         <v>16163015</v>
@@ -31022,7 +31022,7 @@
         <v>10.6691408157349</v>
       </c>
       <c r="G1057" t="n">
-        <v>6.51617002487183</v>
+        <v>6.51616954803467</v>
       </c>
       <c r="H1057" t="n">
         <v>22197980</v>
@@ -31051,7 +31051,7 @@
         <v>10.2762365341187</v>
       </c>
       <c r="G1058" t="n">
-        <v>6.27620267868042</v>
+        <v>6.27620458602905</v>
       </c>
       <c r="H1058" t="n">
         <v>21913609</v>
@@ -31138,7 +31138,7 @@
         <v>10.2895240783691</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.28431940078735</v>
+        <v>6.2843189239502</v>
       </c>
       <c r="H1061" t="n">
         <v>11481641</v>
@@ -31196,7 +31196,7 @@
         <v>8.90392112731934</v>
       </c>
       <c r="G1063" t="n">
-        <v>5.438063621521</v>
+        <v>5.43806314468384</v>
       </c>
       <c r="H1063" t="n">
         <v>30088498</v>
@@ -31254,7 +31254,7 @@
         <v>9.03678703308105</v>
       </c>
       <c r="G1065" t="n">
-        <v>5.51921081542969</v>
+        <v>5.51921129226685</v>
       </c>
       <c r="H1065" t="n">
         <v>14724221</v>
@@ -31312,7 +31312,7 @@
         <v>7.95392894744873</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.85785627365112</v>
+        <v>4.85785579681396</v>
       </c>
       <c r="H1067" t="n">
         <v>25562426</v>
@@ -31370,7 +31370,7 @@
         <v>6.5151801109314</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.97914147377014</v>
+        <v>3.97914123535156</v>
       </c>
       <c r="H1069" t="n">
         <v>27201181</v>
@@ -31399,7 +31399,7 @@
         <v>5.8081431388855</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.54731893539429</v>
+        <v>3.54731941223145</v>
       </c>
       <c r="H1070" t="n">
         <v>18643241</v>
@@ -31428,7 +31428,7 @@
         <v>5.51014280319214</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.36531543731689</v>
+        <v>3.36531567573547</v>
       </c>
       <c r="H1071" t="n">
         <v>27261923</v>
@@ -31457,7 +31457,7 @@
         <v>5.83092021942139</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.56123018264771</v>
+        <v>3.56122994422913</v>
       </c>
       <c r="H1072" t="n">
         <v>31113817</v>
@@ -31515,7 +31515,7 @@
         <v>6.30164480209351</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.84872460365295</v>
+        <v>3.84872508049011</v>
       </c>
       <c r="H1074" t="n">
         <v>20477817</v>
@@ -31573,7 +31573,7 @@
         <v>6.53985500335693</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.99421095848083</v>
+        <v>3.99421143531799</v>
       </c>
       <c r="H1076" t="n">
         <v>13580103</v>
@@ -31602,7 +31602,7 @@
         <v>6.14790010452271</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.75482559204102</v>
+        <v>3.75482511520386</v>
       </c>
       <c r="H1077" t="n">
         <v>12042575</v>
@@ -31631,7 +31631,7 @@
         <v>5.98846101760864</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.65744781494141</v>
+        <v>3.65744733810425</v>
       </c>
       <c r="H1078" t="n">
         <v>11504283</v>
@@ -31660,7 +31660,7 @@
         <v>6.23711013793945</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.8093101978302</v>
+        <v>3.80930995941162</v>
       </c>
       <c r="H1079" t="n">
         <v>13657132</v>
@@ -31689,7 +31689,7 @@
         <v>6.00079917907715</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.66498351097107</v>
+        <v>3.66498398780823</v>
       </c>
       <c r="H1080" t="n">
         <v>10059147</v>
@@ -31718,7 +31718,7 @@
         <v>5.96473503112793</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.64295744895935</v>
+        <v>3.64295721054077</v>
       </c>
       <c r="H1081" t="n">
         <v>10832835</v>
@@ -31805,7 +31805,7 @@
         <v>6.68505907058716</v>
       </c>
       <c r="G1084" t="n">
-        <v>4.08289432525635</v>
+        <v>4.08289480209351</v>
       </c>
       <c r="H1084" t="n">
         <v>18328643</v>
@@ -31834,7 +31834,7 @@
         <v>6.7562370300293</v>
       </c>
       <c r="G1085" t="n">
-        <v>4.12636661529541</v>
+        <v>4.12636709213257</v>
       </c>
       <c r="H1085" t="n">
         <v>8123955</v>
@@ -31892,7 +31892,7 @@
         <v>7.07986116409302</v>
       </c>
       <c r="G1087" t="n">
-        <v>4.32402038574219</v>
+        <v>4.32401943206787</v>
       </c>
       <c r="H1087" t="n">
         <v>13540727</v>
@@ -31950,7 +31950,7 @@
         <v>6.74674606323242</v>
       </c>
       <c r="G1089" t="n">
-        <v>4.12057018280029</v>
+        <v>4.12056970596313</v>
       </c>
       <c r="H1089" t="n">
         <v>8283080</v>
@@ -32037,7 +32037,7 @@
         <v>6.73630714416504</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.11419486999512</v>
+        <v>4.11419439315796</v>
       </c>
       <c r="H1092" t="n">
         <v>6799525</v>
@@ -32066,7 +32066,7 @@
         <v>6.88056087493896</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.20229768753052</v>
+        <v>4.20229721069336</v>
       </c>
       <c r="H1093" t="n">
         <v>6105844</v>
@@ -32095,7 +32095,7 @@
         <v>7.12256717681885</v>
       </c>
       <c r="G1094" t="n">
-        <v>4.35010194778442</v>
+        <v>4.35010242462158</v>
       </c>
       <c r="H1094" t="n">
         <v>6164407</v>
@@ -32124,7 +32124,7 @@
         <v>6.97546577453613</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.26026010513306</v>
+        <v>4.26026058197021</v>
       </c>
       <c r="H1095" t="n">
         <v>5839222</v>
@@ -32240,7 +32240,7 @@
         <v>7.60752820968628</v>
       </c>
       <c r="G1099" t="n">
-        <v>4.64629125595093</v>
+        <v>4.64629173278809</v>
       </c>
       <c r="H1099" t="n">
         <v>12707049</v>
@@ -32269,7 +32269,7 @@
         <v>7.17856121063232</v>
       </c>
       <c r="G1100" t="n">
-        <v>4.38430070877075</v>
+        <v>4.38430118560791</v>
       </c>
       <c r="H1100" t="n">
         <v>11877207</v>
@@ -32298,7 +32298,7 @@
         <v>7.28390502929688</v>
       </c>
       <c r="G1101" t="n">
-        <v>4.44863939285278</v>
+        <v>4.44863986968994</v>
       </c>
       <c r="H1101" t="n">
         <v>7811329</v>
@@ -32385,7 +32385,7 @@
         <v>7.37406396865845</v>
       </c>
       <c r="G1104" t="n">
-        <v>4.50370359420776</v>
+        <v>4.50370407104492</v>
       </c>
       <c r="H1104" t="n">
         <v>4807661</v>
@@ -32443,7 +32443,7 @@
         <v>7.20513391494751</v>
       </c>
       <c r="G1106" t="n">
-        <v>4.4005298614502</v>
+        <v>4.40053033828735</v>
       </c>
       <c r="H1106" t="n">
         <v>6205144</v>
@@ -32588,7 +32588,7 @@
         <v>7.06088018417358</v>
       </c>
       <c r="G1111" t="n">
-        <v>4.31242704391479</v>
+        <v>4.31242752075195</v>
       </c>
       <c r="H1111" t="n">
         <v>18686809</v>
@@ -32675,7 +32675,7 @@
         <v>7.0381031036377</v>
       </c>
       <c r="G1114" t="n">
-        <v>4.29851627349854</v>
+        <v>4.29851675033569</v>
       </c>
       <c r="H1114" t="n">
         <v>13430529</v>
@@ -32704,7 +32704,7 @@
         <v>7.28390502929688</v>
       </c>
       <c r="G1115" t="n">
-        <v>4.44863939285278</v>
+        <v>4.44863986968994</v>
       </c>
       <c r="H1115" t="n">
         <v>7503292</v>
@@ -32733,7 +32733,7 @@
         <v>7.53065586090088</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.59934234619141</v>
+        <v>4.59934282302856</v>
       </c>
       <c r="H1116" t="n">
         <v>14110902</v>
@@ -32791,7 +32791,7 @@
         <v>7.82960510253906</v>
       </c>
       <c r="G1118" t="n">
-        <v>4.78192567825317</v>
+        <v>4.78192520141602</v>
       </c>
       <c r="H1118" t="n">
         <v>11798728</v>
@@ -32820,7 +32820,7 @@
         <v>7.53729915618896</v>
       </c>
       <c r="G1119" t="n">
-        <v>4.60340023040771</v>
+        <v>4.60339975357056</v>
       </c>
       <c r="H1119" t="n">
         <v>14883017</v>
@@ -32878,7 +32878,7 @@
         <v>7.91311979293823</v>
       </c>
       <c r="G1121" t="n">
-        <v>4.832932472229</v>
+        <v>4.83293199539185</v>
       </c>
       <c r="H1121" t="n">
         <v>11148650</v>
@@ -32907,7 +32907,7 @@
         <v>8.32120895385742</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.08217239379883</v>
+        <v>5.08217144012451</v>
       </c>
       <c r="H1122" t="n">
         <v>16050436</v>
@@ -33023,7 +33023,7 @@
         <v>8.53569316864014</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.21316814422607</v>
+        <v>5.21316862106323</v>
       </c>
       <c r="H1126" t="n">
         <v>18143907</v>
@@ -33052,7 +33052,7 @@
         <v>8.30507469177246</v>
       </c>
       <c r="G1127" t="n">
-        <v>5.0723180770874</v>
+        <v>5.07231855392456</v>
       </c>
       <c r="H1127" t="n">
         <v>12941351</v>
@@ -33081,7 +33081,7 @@
         <v>7.6654200553894</v>
       </c>
       <c r="G1128" t="n">
-        <v>4.68164920806885</v>
+        <v>4.68164968490601</v>
       </c>
       <c r="H1128" t="n">
         <v>24615597</v>
@@ -33110,7 +33110,7 @@
         <v>7.77550888061523</v>
       </c>
       <c r="G1129" t="n">
-        <v>4.74888563156128</v>
+        <v>4.7488865852356</v>
       </c>
       <c r="H1129" t="n">
         <v>15936016</v>
@@ -33139,7 +33139,7 @@
         <v>7.77835607528687</v>
       </c>
       <c r="G1130" t="n">
-        <v>4.75062465667725</v>
+        <v>4.7506251335144</v>
       </c>
       <c r="H1130" t="n">
         <v>10945752</v>
@@ -33168,7 +33168,7 @@
         <v>8.00043201446533</v>
       </c>
       <c r="G1131" t="n">
-        <v>4.88625764846802</v>
+        <v>4.88625812530518</v>
       </c>
       <c r="H1131" t="n">
         <v>13131338</v>
@@ -33197,7 +33197,7 @@
         <v>7.97006320953369</v>
       </c>
       <c r="G1132" t="n">
-        <v>4.86770915985107</v>
+        <v>4.86771011352539</v>
       </c>
       <c r="H1132" t="n">
         <v>13268054</v>
@@ -33255,7 +33255,7 @@
         <v>8.02225971221924</v>
       </c>
       <c r="G1134" t="n">
-        <v>4.89958906173706</v>
+        <v>4.8995885848999</v>
       </c>
       <c r="H1134" t="n">
         <v>15743164</v>
@@ -33284,7 +33284,7 @@
         <v>8.1314001083374</v>
       </c>
       <c r="G1135" t="n">
-        <v>4.96624660491943</v>
+        <v>4.96624612808228</v>
       </c>
       <c r="H1135" t="n">
         <v>11120772</v>
@@ -33313,7 +33313,7 @@
         <v>8.602126121521</v>
       </c>
       <c r="G1136" t="n">
-        <v>5.25374174118042</v>
+        <v>5.25374221801758</v>
       </c>
       <c r="H1136" t="n">
         <v>19919897</v>
@@ -33342,7 +33342,7 @@
         <v>8.22345733642578</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.02247047424316</v>
+        <v>5.02246999740601</v>
       </c>
       <c r="H1137" t="n">
         <v>14767769</v>
@@ -33371,7 +33371,7 @@
         <v>8.34303665161133</v>
       </c>
       <c r="G1138" t="n">
-        <v>5.09550333023071</v>
+        <v>5.09550285339355</v>
       </c>
       <c r="H1138" t="n">
         <v>11215982</v>
@@ -33400,7 +33400,7 @@
         <v>8.19498634338379</v>
       </c>
       <c r="G1139" t="n">
-        <v>5.00508165359497</v>
+        <v>5.00508213043213</v>
       </c>
       <c r="H1139" t="n">
         <v>8543580</v>
@@ -33487,7 +33487,7 @@
         <v>8.33829212188721</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.09260511398315</v>
+        <v>5.09260559082031</v>
       </c>
       <c r="H1142" t="n">
         <v>9813243</v>
@@ -33603,7 +33603,7 @@
         <v>8.52525329589844</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.20679140090942</v>
+        <v>5.20679187774658</v>
       </c>
       <c r="H1146" t="n">
         <v>7735786</v>
@@ -33632,7 +33632,7 @@
         <v>8.34778213500977</v>
       </c>
       <c r="G1147" t="n">
-        <v>5.09840154647827</v>
+        <v>5.09840202331543</v>
       </c>
       <c r="H1147" t="n">
         <v>7472601</v>
@@ -33661,7 +33661,7 @@
         <v>8.19118976593018</v>
       </c>
       <c r="G1148" t="n">
-        <v>5.00276279449463</v>
+        <v>5.00276327133179</v>
       </c>
       <c r="H1148" t="n">
         <v>6870047</v>
@@ -33777,7 +33777,7 @@
         <v>8.60781955718994</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.25721979141235</v>
+        <v>5.2572193145752</v>
       </c>
       <c r="H1152" t="n">
         <v>9989493</v>
@@ -33806,7 +33806,7 @@
         <v>8.70557117462158</v>
       </c>
       <c r="G1153" t="n">
-        <v>5.3169207572937</v>
+        <v>5.31692123413086</v>
       </c>
       <c r="H1153" t="n">
         <v>8382162</v>
@@ -33835,7 +33835,7 @@
         <v>8.6951322555542</v>
       </c>
       <c r="G1154" t="n">
-        <v>5.31054544448853</v>
+        <v>5.31054496765137</v>
       </c>
       <c r="H1154" t="n">
         <v>8332593</v>
@@ -33864,7 +33864,7 @@
         <v>8.74637985229492</v>
       </c>
       <c r="G1155" t="n">
-        <v>5.34184551239014</v>
+        <v>5.34184408187866</v>
       </c>
       <c r="H1155" t="n">
         <v>6000919</v>
@@ -33922,7 +33922,7 @@
         <v>8.69133567810059</v>
       </c>
       <c r="G1157" t="n">
-        <v>5.30822706222534</v>
+        <v>5.30822658538818</v>
       </c>
       <c r="H1157" t="n">
         <v>11227734</v>
@@ -33951,7 +33951,7 @@
         <v>8.7454309463501</v>
       </c>
       <c r="G1158" t="n">
-        <v>5.34126472473145</v>
+        <v>5.34126567840576</v>
       </c>
       <c r="H1158" t="n">
         <v>9864564</v>
@@ -33980,7 +33980,7 @@
         <v>8.6135139465332</v>
       </c>
       <c r="G1159" t="n">
-        <v>5.26069736480713</v>
+        <v>5.26069784164429</v>
       </c>
       <c r="H1159" t="n">
         <v>7140068</v>
@@ -34009,7 +34009,7 @@
         <v>8.61066722869873</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.25895881652832</v>
+        <v>5.25895833969116</v>
       </c>
       <c r="H1160" t="n">
         <v>7304019</v>
@@ -34038,7 +34038,7 @@
         <v>8.80047607421875</v>
       </c>
       <c r="G1161" t="n">
-        <v>5.3748836517334</v>
+        <v>5.37488412857056</v>
       </c>
       <c r="H1161" t="n">
         <v>12332748</v>
@@ -34096,7 +34096,7 @@
         <v>8.34778213500977</v>
       </c>
       <c r="G1163" t="n">
-        <v>5.09840154647827</v>
+        <v>5.09840202331543</v>
       </c>
       <c r="H1163" t="n">
         <v>12421425</v>
@@ -34212,7 +34212,7 @@
         <v>8.91910552978516</v>
       </c>
       <c r="G1167" t="n">
-        <v>5.44733715057373</v>
+        <v>5.44733667373657</v>
       </c>
       <c r="H1167" t="n">
         <v>9652262</v>
@@ -34241,7 +34241,7 @@
         <v>8.8242015838623</v>
       </c>
       <c r="G1168" t="n">
-        <v>5.38937473297119</v>
+        <v>5.38937377929688</v>
       </c>
       <c r="H1168" t="n">
         <v>11368887</v>
@@ -34299,7 +34299,7 @@
         <v>8.96371078491211</v>
       </c>
       <c r="G1170" t="n">
-        <v>5.47457981109619</v>
+        <v>5.47457933425903</v>
       </c>
       <c r="H1170" t="n">
         <v>5068327</v>
@@ -34328,7 +34328,7 @@
         <v>9.43633365631104</v>
       </c>
       <c r="G1171" t="n">
-        <v>5.76323366165161</v>
+        <v>5.76323318481445</v>
       </c>
       <c r="H1171" t="n">
         <v>16161596</v>
@@ -34357,7 +34357,7 @@
         <v>9.40122032165527</v>
       </c>
       <c r="G1172" t="n">
-        <v>5.74178838729858</v>
+        <v>5.74178791046143</v>
       </c>
       <c r="H1172" t="n">
         <v>11463330</v>
@@ -34386,7 +34386,7 @@
         <v>9.26265907287598</v>
       </c>
       <c r="G1173" t="n">
-        <v>5.6571626663208</v>
+        <v>5.65716171264648</v>
       </c>
       <c r="H1173" t="n">
         <v>5880122</v>
@@ -34415,7 +34415,7 @@
         <v>9.19622611999512</v>
       </c>
       <c r="G1174" t="n">
-        <v>5.61658811569214</v>
+        <v>5.61658763885498</v>
       </c>
       <c r="H1174" t="n">
         <v>5783149</v>
@@ -34444,7 +34444,7 @@
         <v>9.15826511383057</v>
       </c>
       <c r="G1175" t="n">
-        <v>5.59340286254883</v>
+        <v>5.59340333938599</v>
       </c>
       <c r="H1175" t="n">
         <v>4010991</v>
@@ -34473,7 +34473,7 @@
         <v>9.11745643615723</v>
       </c>
       <c r="G1176" t="n">
-        <v>5.56848001480103</v>
+        <v>5.56847953796387</v>
       </c>
       <c r="H1176" t="n">
         <v>6484263</v>
@@ -34531,7 +34531,7 @@
         <v>8.9665584564209</v>
       </c>
       <c r="G1178" t="n">
-        <v>5.47631931304932</v>
+        <v>5.47631883621216</v>
       </c>
       <c r="H1178" t="n">
         <v>7032977</v>
@@ -34589,7 +34589,7 @@
         <v>9.13643741607666</v>
       </c>
       <c r="G1180" t="n">
-        <v>5.58007192611694</v>
+        <v>5.58007287979126</v>
       </c>
       <c r="H1180" t="n">
         <v>7199279</v>
@@ -34705,7 +34705,7 @@
         <v>8.93523979187012</v>
       </c>
       <c r="G1184" t="n">
-        <v>5.457190990448</v>
+        <v>5.45719146728516</v>
       </c>
       <c r="H1184" t="n">
         <v>6926510</v>
@@ -34763,7 +34763,7 @@
         <v>8.65717029571533</v>
       </c>
       <c r="G1186" t="n">
-        <v>5.28736019134521</v>
+        <v>5.28736066818237</v>
       </c>
       <c r="H1186" t="n">
         <v>8371595</v>
@@ -34792,7 +34792,7 @@
         <v>8.70652008056641</v>
       </c>
       <c r="G1187" t="n">
-        <v>5.31750059127808</v>
+        <v>5.31750106811523</v>
       </c>
       <c r="H1187" t="n">
         <v>7873413</v>
@@ -34821,7 +34821,7 @@
         <v>8.80617046356201</v>
       </c>
       <c r="G1188" t="n">
-        <v>5.37836170196533</v>
+        <v>5.37836217880249</v>
       </c>
       <c r="H1188" t="n">
         <v>14198366</v>
@@ -34908,7 +34908,7 @@
         <v>9.12125205993652</v>
       </c>
       <c r="G1191" t="n">
-        <v>5.57079744338989</v>
+        <v>5.57079839706421</v>
       </c>
       <c r="H1191" t="n">
         <v>6203598</v>
@@ -34937,7 +34937,7 @@
         <v>9.12220096588135</v>
       </c>
       <c r="G1192" t="n">
-        <v>5.57137727737427</v>
+        <v>5.57137775421143</v>
       </c>
       <c r="H1192" t="n">
         <v>6745287</v>
@@ -34995,7 +34995,7 @@
         <v>9.40881156921387</v>
       </c>
       <c r="G1194" t="n">
-        <v>5.74642515182495</v>
+        <v>5.74642467498779</v>
       </c>
       <c r="H1194" t="n">
         <v>7537470</v>
@@ -35024,7 +35024,7 @@
         <v>9.4742956161499</v>
       </c>
       <c r="G1195" t="n">
-        <v>5.78641891479492</v>
+        <v>5.78641939163208</v>
       </c>
       <c r="H1195" t="n">
         <v>9848029</v>
@@ -35053,7 +35053,7 @@
         <v>10.327486038208</v>
       </c>
       <c r="G1196" t="n">
-        <v>6.30750417709351</v>
+        <v>6.30750513076782</v>
       </c>
       <c r="H1196" t="n">
         <v>43218612</v>
@@ -35082,7 +35082,7 @@
         <v>10.2610530853271</v>
       </c>
       <c r="G1197" t="n">
-        <v>6.26693105697632</v>
+        <v>6.26693058013916</v>
       </c>
       <c r="H1197" t="n">
         <v>15867956</v>
@@ -35140,7 +35140,7 @@
         <v>9.8491678237915</v>
       </c>
       <c r="G1199" t="n">
-        <v>6.01537132263184</v>
+        <v>6.01537179946899</v>
       </c>
       <c r="H1199" t="n">
         <v>13428051</v>
@@ -35169,7 +35169,7 @@
         <v>9.43064022064209</v>
       </c>
       <c r="G1200" t="n">
-        <v>5.75975704193115</v>
+        <v>5.75975608825684</v>
       </c>
       <c r="H1200" t="n">
         <v>13765233</v>
@@ -35198,7 +35198,7 @@
         <v>9.69732093811035</v>
       </c>
       <c r="G1201" t="n">
-        <v>5.92263221740723</v>
+        <v>5.92263078689575</v>
       </c>
       <c r="H1201" t="n">
         <v>11313802</v>
@@ -35227,7 +35227,7 @@
         <v>9.86055660247803</v>
       </c>
       <c r="G1202" t="n">
-        <v>6.02232694625854</v>
+        <v>6.02232789993286</v>
       </c>
       <c r="H1202" t="n">
         <v>14822309</v>
@@ -35256,7 +35256,7 @@
         <v>9.84347438812256</v>
       </c>
       <c r="G1203" t="n">
-        <v>6.01189422607422</v>
+        <v>6.01189470291138</v>
       </c>
       <c r="H1203" t="n">
         <v>10445207</v>
@@ -35285,7 +35285,7 @@
         <v>9.70870971679688</v>
       </c>
       <c r="G1204" t="n">
-        <v>5.92958784103394</v>
+        <v>5.92958736419678</v>
       </c>
       <c r="H1204" t="n">
         <v>9479863</v>
@@ -35314,7 +35314,7 @@
         <v>10.0940208435059</v>
       </c>
       <c r="G1205" t="n">
-        <v>6.16491556167603</v>
+        <v>6.16491603851318</v>
       </c>
       <c r="H1205" t="n">
         <v>14814702</v>
@@ -35343,7 +35343,7 @@
         <v>9.85865879058838</v>
       </c>
       <c r="G1206" t="n">
-        <v>6.02116823196411</v>
+        <v>6.02116775512695</v>
       </c>
       <c r="H1206" t="n">
         <v>8215276</v>
@@ -35372,7 +35372,7 @@
         <v>9.9345817565918</v>
       </c>
       <c r="G1207" t="n">
-        <v>6.06753730773926</v>
+        <v>6.06753826141357</v>
       </c>
       <c r="H1207" t="n">
         <v>10072710</v>
@@ -35401,7 +35401,7 @@
         <v>9.8491678237915</v>
       </c>
       <c r="G1208" t="n">
-        <v>6.01537132263184</v>
+        <v>6.01537179946899</v>
       </c>
       <c r="H1208" t="n">
         <v>10638058</v>
@@ -35430,7 +35430,7 @@
         <v>9.82259464263916</v>
       </c>
       <c r="G1209" t="n">
-        <v>5.99914121627808</v>
+        <v>5.99914216995239</v>
       </c>
       <c r="H1209" t="n">
         <v>5637822</v>
@@ -35459,7 +35459,7 @@
         <v>9.94976711273193</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.07681226730347</v>
+        <v>6.07681274414062</v>
       </c>
       <c r="H1210" t="n">
         <v>6832677</v>
@@ -35546,7 +35546,7 @@
         <v>10.1357793807983</v>
       </c>
       <c r="G1213" t="n">
-        <v>6.19041919708252</v>
+        <v>6.19042062759399</v>
       </c>
       <c r="H1213" t="n">
         <v>8045845</v>
@@ -35575,7 +35575,7 @@
         <v>9.99532127380371</v>
       </c>
       <c r="G1214" t="n">
-        <v>6.1046347618103</v>
+        <v>6.10463523864746</v>
       </c>
       <c r="H1214" t="n">
         <v>12751104</v>
@@ -35604,7 +35604,7 @@
         <v>10.0921230316162</v>
       </c>
       <c r="G1215" t="n">
-        <v>6.16375732421875</v>
+        <v>6.16375637054443</v>
       </c>
       <c r="H1215" t="n">
         <v>7530729</v>
@@ -35633,7 +35633,7 @@
         <v>9.92319297790527</v>
       </c>
       <c r="G1216" t="n">
-        <v>6.06058263778687</v>
+        <v>6.06058216094971</v>
       </c>
       <c r="H1216" t="n">
         <v>5579872</v>
@@ -35662,7 +35662,7 @@
         <v>10.0313844680786</v>
       </c>
       <c r="G1217" t="n">
-        <v>6.12666082382202</v>
+        <v>6.12665987014771</v>
       </c>
       <c r="H1217" t="n">
         <v>6967421</v>
@@ -35720,7 +35720,7 @@
         <v>10.2325811386108</v>
       </c>
       <c r="G1219" t="n">
-        <v>6.24954080581665</v>
+        <v>6.24954175949097</v>
       </c>
       <c r="H1219" t="n">
         <v>16232401</v>
@@ -35778,7 +35778,7 @@
         <v>10.2287845611572</v>
       </c>
       <c r="G1221" t="n">
-        <v>6.24722146987915</v>
+        <v>6.24722337722778</v>
       </c>
       <c r="H1221" t="n">
         <v>9049658</v>
@@ -35807,7 +35807,7 @@
         <v>10.1604537963867</v>
       </c>
       <c r="G1222" t="n">
-        <v>6.20548915863037</v>
+        <v>6.20548963546753</v>
       </c>
       <c r="H1222" t="n">
         <v>6666023</v>
@@ -35836,7 +35836,7 @@
         <v>10.4091033935547</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.3573522567749</v>
+        <v>6.35735177993774</v>
       </c>
       <c r="H1223" t="n">
         <v>10980762</v>
@@ -35865,7 +35865,7 @@
         <v>10.5343770980835</v>
       </c>
       <c r="G1224" t="n">
-        <v>6.43386268615723</v>
+        <v>6.43386220932007</v>
       </c>
       <c r="H1224" t="n">
         <v>10923733</v>
@@ -35894,7 +35894,7 @@
         <v>10.6103010177612</v>
       </c>
       <c r="G1225" t="n">
-        <v>6.48023271560669</v>
+        <v>6.48023319244385</v>
       </c>
       <c r="H1225" t="n">
         <v>23024056</v>
@@ -35923,7 +35923,7 @@
         <v>10.4337787628174</v>
       </c>
       <c r="G1226" t="n">
-        <v>6.37242317199707</v>
+        <v>6.37242269515991</v>
       </c>
       <c r="H1226" t="n">
         <v>11951147</v>
@@ -36010,7 +36010,7 @@
         <v>10.0048112869263</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.1104302406311</v>
+        <v>6.11043071746826</v>
       </c>
       <c r="H1229" t="n">
         <v>8566779</v>
@@ -36039,7 +36039,7 @@
         <v>10.2686452865601</v>
       </c>
       <c r="G1230" t="n">
-        <v>6.27156734466553</v>
+        <v>6.27156686782837</v>
       </c>
       <c r="H1230" t="n">
         <v>10507665</v>
@@ -36068,7 +36068,7 @@
         <v>10.4451665878296</v>
       </c>
       <c r="G1231" t="n">
-        <v>6.3793773651123</v>
+        <v>6.37937784194946</v>
       </c>
       <c r="H1231" t="n">
         <v>12114251</v>
@@ -36097,7 +36097,7 @@
         <v>10.6008100509644</v>
       </c>
       <c r="G1232" t="n">
-        <v>6.47443675994873</v>
+        <v>6.47443628311157</v>
       </c>
       <c r="H1232" t="n">
         <v>13120481</v>
@@ -36155,7 +36155,7 @@
         <v>10.6634473800659</v>
       </c>
       <c r="G1234" t="n">
-        <v>6.51269340515137</v>
+        <v>6.51269245147705</v>
       </c>
       <c r="H1234" t="n">
         <v>14734096</v>
@@ -36184,7 +36184,7 @@
         <v>11.3144912719727</v>
       </c>
       <c r="G1235" t="n">
-        <v>6.91031694412231</v>
+        <v>6.91031789779663</v>
       </c>
       <c r="H1235" t="n">
         <v>26097768</v>
@@ -36213,7 +36213,7 @@
         <v>11.5973052978516</v>
       </c>
       <c r="G1236" t="n">
-        <v>7.0830454826355</v>
+        <v>7.08304595947266</v>
       </c>
       <c r="H1236" t="n">
         <v>16773983</v>
@@ -36242,7 +36242,7 @@
         <v>11.6941080093384</v>
       </c>
       <c r="G1237" t="n">
-        <v>7.14216804504395</v>
+        <v>7.14216709136963</v>
       </c>
       <c r="H1237" t="n">
         <v>12790303</v>
@@ -36271,7 +36271,7 @@
         <v>11.4473571777344</v>
       </c>
       <c r="G1238" t="n">
-        <v>6.99146366119385</v>
+        <v>6.99146509170532</v>
       </c>
       <c r="H1238" t="n">
         <v>12168076</v>
@@ -36300,7 +36300,7 @@
         <v>11.5897130966187</v>
       </c>
       <c r="G1239" t="n">
-        <v>7.07840871810913</v>
+        <v>7.07840824127197</v>
       </c>
       <c r="H1239" t="n">
         <v>8208393</v>
@@ -36358,7 +36358,7 @@
         <v>11.9826173782349</v>
       </c>
       <c r="G1241" t="n">
-        <v>7.31837463378906</v>
+        <v>7.3183741569519</v>
       </c>
       <c r="H1241" t="n">
         <v>11783900</v>
@@ -36445,7 +36445,7 @@
         <v>12.2236738204956</v>
       </c>
       <c r="G1244" t="n">
-        <v>7.46559906005859</v>
+        <v>7.46559953689575</v>
       </c>
       <c r="H1244" t="n">
         <v>9449671</v>
@@ -36474,7 +36474,7 @@
         <v>12.1933040618896</v>
       </c>
       <c r="G1245" t="n">
-        <v>7.44705152511597</v>
+        <v>7.44705104827881</v>
       </c>
       <c r="H1245" t="n">
         <v>8543660</v>
@@ -36503,7 +36503,7 @@
         <v>12.4267692565918</v>
       </c>
       <c r="G1246" t="n">
-        <v>7.58964109420776</v>
+        <v>7.58964014053345</v>
       </c>
       <c r="H1246" t="n">
         <v>11547460</v>
@@ -36532,7 +36532,7 @@
         <v>12.5121831893921</v>
       </c>
       <c r="G1247" t="n">
-        <v>7.64180660247803</v>
+        <v>7.64180707931519</v>
       </c>
       <c r="H1247" t="n">
         <v>12635167</v>
@@ -36561,7 +36561,7 @@
         <v>12.4210748672485</v>
       </c>
       <c r="G1248" t="n">
-        <v>7.58616161346436</v>
+        <v>7.5861611366272</v>
       </c>
       <c r="H1248" t="n">
         <v>5569708</v>
@@ -36590,7 +36590,7 @@
         <v>12.5520429611206</v>
       </c>
       <c r="G1249" t="n">
-        <v>7.66615056991577</v>
+        <v>7.66615104675293</v>
       </c>
       <c r="H1249" t="n">
         <v>8245905</v>
@@ -36648,7 +36648,7 @@
         <v>12.5539407730103</v>
       </c>
       <c r="G1251" t="n">
-        <v>7.66730976104736</v>
+        <v>7.66731023788452</v>
       </c>
       <c r="H1251" t="n">
         <v>8910574</v>
@@ -36706,7 +36706,7 @@
         <v>12.5558385848999</v>
       </c>
       <c r="G1253" t="n">
-        <v>7.66846990585327</v>
+        <v>7.66846895217896</v>
       </c>
       <c r="H1253" t="n">
         <v>8361176</v>
@@ -36735,7 +36735,7 @@
         <v>12.8595333099365</v>
       </c>
       <c r="G1254" t="n">
-        <v>7.85395097732544</v>
+        <v>7.85394954681396</v>
       </c>
       <c r="H1254" t="n">
         <v>13541806</v>
@@ -36793,7 +36793,7 @@
         <v>12.7228698730469</v>
       </c>
       <c r="G1256" t="n">
-        <v>7.77048301696777</v>
+        <v>7.77048254013062</v>
       </c>
       <c r="H1256" t="n">
         <v>5417455</v>
@@ -36822,7 +36822,7 @@
         <v>13.0740156173706</v>
       </c>
       <c r="G1257" t="n">
-        <v>7.98494577407837</v>
+        <v>7.98494529724121</v>
       </c>
       <c r="H1257" t="n">
         <v>14379979</v>
@@ -36880,7 +36880,7 @@
         <v>12.9449462890625</v>
       </c>
       <c r="G1259" t="n">
-        <v>7.90611600875854</v>
+        <v>7.90611553192139</v>
       </c>
       <c r="H1259" t="n">
         <v>8808025</v>
@@ -36909,7 +36909,7 @@
         <v>13.1157741546631</v>
       </c>
       <c r="G1260" t="n">
-        <v>8.01044845581055</v>
+        <v>8.01045036315918</v>
       </c>
       <c r="H1260" t="n">
         <v>13771240</v>
@@ -36938,7 +36938,7 @@
         <v>13.4061813354492</v>
       </c>
       <c r="G1261" t="n">
-        <v>8.18781661987305</v>
+        <v>8.18781471252441</v>
       </c>
       <c r="H1261" t="n">
         <v>10065125</v>
@@ -36967,7 +36967,7 @@
         <v>13.5846014022827</v>
       </c>
       <c r="G1262" t="n">
-        <v>8.29678440093994</v>
+        <v>8.29678535461426</v>
       </c>
       <c r="H1262" t="n">
         <v>13487197</v>
@@ -36996,7 +36996,7 @@
         <v>13.670015335083</v>
       </c>
       <c r="G1263" t="n">
-        <v>8.348952293396</v>
+        <v>8.34895133972168</v>
       </c>
       <c r="H1263" t="n">
         <v>10369090</v>
@@ -37025,7 +37025,7 @@
         <v>13.7876968383789</v>
       </c>
       <c r="G1264" t="n">
-        <v>8.42082500457764</v>
+        <v>8.42082595825195</v>
       </c>
       <c r="H1264" t="n">
         <v>14080432</v>
@@ -37054,7 +37054,7 @@
         <v>13.5238628387451</v>
       </c>
       <c r="G1265" t="n">
-        <v>8.25968933105469</v>
+        <v>8.25968837738037</v>
       </c>
       <c r="H1265" t="n">
         <v>19283533</v>
@@ -37141,7 +37141,7 @@
         <v>14.0325498580933</v>
       </c>
       <c r="G1268" t="n">
-        <v>8.57036876678467</v>
+        <v>8.57036972045898</v>
       </c>
       <c r="H1268" t="n">
         <v>7784092</v>
@@ -37170,7 +37170,7 @@
         <v>13.9395437240601</v>
       </c>
       <c r="G1269" t="n">
-        <v>8.51356601715088</v>
+        <v>8.51356506347656</v>
       </c>
       <c r="H1269" t="n">
         <v>10033435</v>
@@ -37199,7 +37199,7 @@
         <v>13.9129695892334</v>
       </c>
       <c r="G1270" t="n">
-        <v>8.49733543395996</v>
+        <v>8.49733638763428</v>
       </c>
       <c r="H1270" t="n">
         <v>6249016</v>
@@ -37228,7 +37228,7 @@
         <v>14.1217603683472</v>
       </c>
       <c r="G1271" t="n">
-        <v>8.62485408782959</v>
+        <v>8.62485504150391</v>
       </c>
       <c r="H1271" t="n">
         <v>19895535</v>
@@ -37257,7 +37257,7 @@
         <v>14.0837984085083</v>
       </c>
       <c r="G1272" t="n">
-        <v>8.60166931152344</v>
+        <v>8.60167026519775</v>
       </c>
       <c r="H1272" t="n">
         <v>16854394</v>
@@ -37286,7 +37286,7 @@
         <v>13.7876968383789</v>
       </c>
       <c r="G1273" t="n">
-        <v>8.42082500457764</v>
+        <v>8.42082595825195</v>
       </c>
       <c r="H1273" t="n">
         <v>15230817</v>
@@ -37315,7 +37315,7 @@
         <v>14.0344476699829</v>
       </c>
       <c r="G1274" t="n">
-        <v>8.57152843475342</v>
+        <v>8.5715274810791</v>
       </c>
       <c r="H1274" t="n">
         <v>12920368</v>
@@ -37344,7 +37344,7 @@
         <v>13.7744102478027</v>
       </c>
       <c r="G1275" t="n">
-        <v>8.41271018981934</v>
+        <v>8.41271114349365</v>
       </c>
       <c r="H1275" t="n">
         <v>20044688</v>
@@ -37402,7 +37402,7 @@
         <v>13.9262571334839</v>
       </c>
       <c r="G1277" t="n">
-        <v>8.50545120239258</v>
+        <v>8.50545024871826</v>
       </c>
       <c r="H1277" t="n">
         <v>12728976</v>
@@ -37431,7 +37431,7 @@
         <v>13.8674163818359</v>
       </c>
       <c r="G1278" t="n">
-        <v>8.46951389312744</v>
+        <v>8.46951293945312</v>
       </c>
       <c r="H1278" t="n">
         <v>15059110</v>
@@ -37460,7 +37460,7 @@
         <v>12.4723234176636</v>
       </c>
       <c r="G1279" t="n">
-        <v>8.78280925750732</v>
+        <v>8.78281021118164</v>
       </c>
       <c r="H1279" t="n">
         <v>22700747</v>
@@ -37605,7 +37605,7 @@
         <v>12.9506406784058</v>
       </c>
       <c r="G1284" t="n">
-        <v>9.1196346282959</v>
+        <v>9.11963367462158</v>
       </c>
       <c r="H1284" t="n">
         <v>19585832</v>
@@ -37663,7 +37663,7 @@
         <v>11.9807186126709</v>
       </c>
       <c r="G1286" t="n">
-        <v>8.43663024902344</v>
+        <v>8.43662929534912</v>
       </c>
       <c r="H1286" t="n">
         <v>21308618</v>
@@ -37692,7 +37692,7 @@
         <v>12.2160806655884</v>
       </c>
       <c r="G1287" t="n">
-        <v>8.60236930847168</v>
+        <v>8.60236835479736</v>
       </c>
       <c r="H1287" t="n">
         <v>15668469</v>
@@ -37779,7 +37779,7 @@
         <v>11.8915090560913</v>
       </c>
       <c r="G1290" t="n">
-        <v>8.37381076812744</v>
+        <v>8.37380981445312</v>
       </c>
       <c r="H1290" t="n">
         <v>13953977</v>
@@ -37837,7 +37837,7 @@
         <v>12.328067779541</v>
       </c>
       <c r="G1292" t="n">
-        <v>8.68122863769531</v>
+        <v>8.681227684021</v>
       </c>
       <c r="H1292" t="n">
         <v>16271807</v>
@@ -37866,7 +37866,7 @@
         <v>12.3508462905884</v>
       </c>
       <c r="G1293" t="n">
-        <v>8.69726943969727</v>
+        <v>8.69726848602295</v>
       </c>
       <c r="H1293" t="n">
         <v>17417693</v>
@@ -37924,7 +37924,7 @@
         <v>12.6830110549927</v>
       </c>
       <c r="G1295" t="n">
-        <v>8.93117237091064</v>
+        <v>8.93117332458496</v>
       </c>
       <c r="H1295" t="n">
         <v>17565417</v>
@@ -37982,7 +37982,7 @@
         <v>12.8063859939575</v>
       </c>
       <c r="G1297" t="n">
-        <v>9.01805210113525</v>
+        <v>9.01805114746094</v>
       </c>
       <c r="H1297" t="n">
         <v>9491937</v>
@@ -38011,7 +38011,7 @@
         <v>12.5577373504639</v>
       </c>
       <c r="G1298" t="n">
-        <v>8.84295654296875</v>
+        <v>8.84295749664307</v>
       </c>
       <c r="H1298" t="n">
         <v>11453401</v>
@@ -38040,7 +38040,7 @@
         <v>12.489405632019</v>
       </c>
       <c r="G1299" t="n">
-        <v>8.79483890533447</v>
+        <v>8.79483985900879</v>
       </c>
       <c r="H1299" t="n">
         <v>7444190</v>
@@ -38127,7 +38127,7 @@
         <v>12.8120803833008</v>
       </c>
       <c r="G1302" t="n">
-        <v>9.02206134796143</v>
+        <v>9.02206230163574</v>
       </c>
       <c r="H1302" t="n">
         <v>8396731</v>
@@ -38272,7 +38272,7 @@
         <v>12.5956993103027</v>
       </c>
       <c r="G1307" t="n">
-        <v>8.86968994140625</v>
+        <v>8.86969089508057</v>
       </c>
       <c r="H1307" t="n">
         <v>12231243</v>
@@ -38301,7 +38301,7 @@
         <v>12.8880043029785</v>
       </c>
       <c r="G1308" t="n">
-        <v>9.07552623748779</v>
+        <v>9.07552719116211</v>
       </c>
       <c r="H1308" t="n">
         <v>12674024</v>
@@ -38330,7 +38330,7 @@
         <v>12.8671245574951</v>
       </c>
       <c r="G1309" t="n">
-        <v>9.06082344055176</v>
+        <v>9.06082248687744</v>
       </c>
       <c r="H1309" t="n">
         <v>9826027</v>
@@ -38359,7 +38359,7 @@
         <v>12.7494440078735</v>
       </c>
       <c r="G1310" t="n">
-        <v>8.97795486450195</v>
+        <v>8.97795391082764</v>
       </c>
       <c r="H1310" t="n">
         <v>15936005</v>
@@ -38417,7 +38417,7 @@
         <v>13.1860027313232</v>
       </c>
       <c r="G1312" t="n">
-        <v>9.28537178039551</v>
+        <v>9.28537273406982</v>
       </c>
       <c r="H1312" t="n">
         <v>14812722</v>
@@ -38446,7 +38446,7 @@
         <v>13.1613283157349</v>
       </c>
       <c r="G1313" t="n">
-        <v>9.2679967880249</v>
+        <v>9.26799583435059</v>
       </c>
       <c r="H1313" t="n">
         <v>24447891</v>
@@ -38504,7 +38504,7 @@
         <v>12.984806060791</v>
       </c>
       <c r="G1315" t="n">
-        <v>9.14369297027588</v>
+        <v>9.14369201660156</v>
       </c>
       <c r="H1315" t="n">
         <v>15879176</v>
@@ -38620,7 +38620,7 @@
         <v>14.4501285552979</v>
       </c>
       <c r="G1319" t="n">
-        <v>10.1755485534668</v>
+        <v>10.1755495071411</v>
       </c>
       <c r="H1319" t="n">
         <v>22471190</v>
@@ -38649,7 +38649,7 @@
         <v>14.6494283676147</v>
       </c>
       <c r="G1320" t="n">
-        <v>10.3158922195435</v>
+        <v>10.3158931732178</v>
       </c>
       <c r="H1320" t="n">
         <v>19043847</v>
@@ -38678,7 +38678,7 @@
         <v>14.8579998016357</v>
       </c>
       <c r="G1321" t="n">
-        <v>10.6027088165283</v>
+        <v>10.602707862854</v>
       </c>
       <c r="H1321" t="n">
         <v>18918059</v>
@@ -38736,7 +38736,7 @@
         <v>14.9460000991821</v>
       </c>
       <c r="G1323" t="n">
-        <v>10.6655054092407</v>
+        <v>10.6655044555664</v>
       </c>
       <c r="H1323" t="n">
         <v>12742978</v>
@@ -38794,7 +38794,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1325" t="n">
-        <v>10.5970001220703</v>
+        <v>10.596999168396</v>
       </c>
       <c r="H1325" t="n">
         <v>28239181</v>
@@ -38910,7 +38910,7 @@
         <v>14.4060001373291</v>
       </c>
       <c r="G1329" t="n">
-        <v>10.280158996582</v>
+        <v>10.2801599502563</v>
       </c>
       <c r="H1329" t="n">
         <v>12824494</v>
@@ -38968,7 +38968,7 @@
         <v>14.6619997024536</v>
       </c>
       <c r="G1331" t="n">
-        <v>10.4628419876099</v>
+        <v>10.4628410339355</v>
       </c>
       <c r="H1331" t="n">
         <v>8470881</v>
@@ -39055,7 +39055,7 @@
         <v>15.1359996795654</v>
       </c>
       <c r="G1334" t="n">
-        <v>10.8010892868042</v>
+        <v>10.8010902404785</v>
       </c>
       <c r="H1334" t="n">
         <v>8000397</v>
@@ -39084,7 +39084,7 @@
         <v>15.2919998168945</v>
       </c>
       <c r="G1335" t="n">
-        <v>10.912410736084</v>
+        <v>10.9124116897583</v>
       </c>
       <c r="H1335" t="n">
         <v>17012730</v>
@@ -39142,7 +39142,7 @@
         <v>14.9280004501343</v>
       </c>
       <c r="G1337" t="n">
-        <v>10.6526613235474</v>
+        <v>10.652660369873</v>
       </c>
       <c r="H1337" t="n">
         <v>13073820</v>
@@ -39200,7 +39200,7 @@
         <v>14.9379997253418</v>
       </c>
       <c r="G1339" t="n">
-        <v>10.6597957611084</v>
+        <v>10.6597967147827</v>
       </c>
       <c r="H1339" t="n">
         <v>7134497</v>
@@ -39229,7 +39229,7 @@
         <v>15.1459999084473</v>
       </c>
       <c r="G1340" t="n">
-        <v>10.8082246780396</v>
+        <v>10.8082256317139</v>
       </c>
       <c r="H1340" t="n">
         <v>10689036</v>
@@ -39316,7 +39316,7 @@
         <v>15.2620000839233</v>
       </c>
       <c r="G1343" t="n">
-        <v>10.8910036087036</v>
+        <v>10.8910026550293</v>
       </c>
       <c r="H1343" t="n">
         <v>14462123</v>
@@ -39461,7 +39461,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G1348" t="n">
-        <v>10.4886598587036</v>
+        <v>10.4886589050293</v>
       </c>
       <c r="H1348" t="n">
         <v>5991456</v>
@@ -39490,7 +39490,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1349" t="n">
-        <v>10.4667921066284</v>
+        <v>10.4667911529541</v>
       </c>
       <c r="H1349" t="n">
         <v>6149041</v>
@@ -39577,7 +39577,7 @@
         <v>13.8439998626709</v>
       </c>
       <c r="G1352" t="n">
-        <v>10.0906867980957</v>
+        <v>10.09068775177</v>
       </c>
       <c r="H1352" t="n">
         <v>16997183</v>
@@ -39606,7 +39606,7 @@
         <v>13.8240003585815</v>
       </c>
       <c r="G1353" t="n">
-        <v>10.0761108398438</v>
+        <v>10.0761098861694</v>
       </c>
       <c r="H1353" t="n">
         <v>9599854</v>
@@ -39635,7 +39635,7 @@
         <v>14.0220003128052</v>
       </c>
       <c r="G1354" t="n">
-        <v>10.2204294204712</v>
+        <v>10.2204303741455</v>
       </c>
       <c r="H1354" t="n">
         <v>7464291</v>
@@ -39664,7 +39664,7 @@
         <v>13.8879995346069</v>
       </c>
       <c r="G1355" t="n">
-        <v>10.1227588653564</v>
+        <v>10.1227579116821</v>
       </c>
       <c r="H1355" t="n">
         <v>9455650</v>
@@ -39722,7 +39722,7 @@
         <v>14.9139995574951</v>
       </c>
       <c r="G1357" t="n">
-        <v>10.8705949783325</v>
+        <v>10.8705940246582</v>
       </c>
       <c r="H1357" t="n">
         <v>14377159</v>
@@ -39751,7 +39751,7 @@
         <v>14.9420003890991</v>
       </c>
       <c r="G1358" t="n">
-        <v>10.8910045623779</v>
+        <v>10.8910036087036</v>
       </c>
       <c r="H1358" t="n">
         <v>9822912</v>
@@ -39809,7 +39809,7 @@
         <v>14.6619997024536</v>
       </c>
       <c r="G1360" t="n">
-        <v>10.6869163513184</v>
+        <v>10.686915397644</v>
       </c>
       <c r="H1360" t="n">
         <v>13399672</v>
@@ -39925,7 +39925,7 @@
         <v>15.0979995727539</v>
       </c>
       <c r="G1364" t="n">
-        <v>11.0047092437744</v>
+        <v>11.0047101974487</v>
       </c>
       <c r="H1364" t="n">
         <v>12737338</v>
@@ -39983,7 +39983,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G1366" t="n">
-        <v>10.7364797592163</v>
+        <v>10.7364807128906</v>
       </c>
       <c r="H1366" t="n">
         <v>13476236</v>
@@ -40041,7 +40041,7 @@
         <v>15.3159999847412</v>
       </c>
       <c r="G1368" t="n">
-        <v>11.1636075973511</v>
+        <v>11.1636066436768</v>
       </c>
       <c r="H1368" t="n">
         <v>18987807</v>
@@ -40186,7 +40186,7 @@
         <v>16.1060009002686</v>
       </c>
       <c r="G1373" t="n">
-        <v>11.7394256591797</v>
+        <v>11.739426612854</v>
       </c>
       <c r="H1373" t="n">
         <v>14181999</v>
@@ -40418,7 +40418,7 @@
         <v>17.2320003509521</v>
       </c>
       <c r="G1381" t="n">
-        <v>12.5601501464844</v>
+        <v>12.5601511001587</v>
       </c>
       <c r="H1381" t="n">
         <v>10798544</v>
@@ -40563,7 +40563,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1386" t="n">
-        <v>12.3181610107422</v>
+        <v>12.3181600570679</v>
       </c>
       <c r="H1386" t="n">
         <v>12774845</v>
@@ -40679,7 +40679,7 @@
         <v>16.9860000610352</v>
       </c>
       <c r="G1390" t="n">
-        <v>12.3808450698853</v>
+        <v>12.3808441162109</v>
       </c>
       <c r="H1390" t="n">
         <v>7752292</v>
@@ -40737,7 +40737,7 @@
         <v>16.992000579834</v>
       </c>
       <c r="G1392" t="n">
-        <v>12.3852186203003</v>
+        <v>12.3852195739746</v>
       </c>
       <c r="H1392" t="n">
         <v>9194651</v>
@@ -40766,7 +40766,7 @@
         <v>17.0620002746582</v>
       </c>
       <c r="G1393" t="n">
-        <v>12.436240196228</v>
+        <v>12.4362411499023</v>
       </c>
       <c r="H1393" t="n">
         <v>7418861</v>
@@ -40824,7 +40824,7 @@
         <v>16.82200050354</v>
       </c>
       <c r="G1395" t="n">
-        <v>12.2613086700439</v>
+        <v>12.2613077163696</v>
       </c>
       <c r="H1395" t="n">
         <v>6672159</v>
@@ -40882,7 +40882,7 @@
         <v>16.7019996643066</v>
       </c>
       <c r="G1397" t="n">
-        <v>12.1738414764404</v>
+        <v>12.1738405227661</v>
       </c>
       <c r="H1397" t="n">
         <v>7156812</v>
@@ -40969,7 +40969,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1400" t="n">
-        <v>12.1942501068115</v>
+        <v>12.1942491531372</v>
       </c>
       <c r="H1400" t="n">
         <v>13243160</v>
@@ -40998,7 +40998,7 @@
         <v>16.5919990539551</v>
       </c>
       <c r="G1401" t="n">
-        <v>12.0936632156372</v>
+        <v>12.0936641693115</v>
       </c>
       <c r="H1401" t="n">
         <v>11656240</v>
@@ -41027,7 +41027,7 @@
         <v>16.0359992980957</v>
       </c>
       <c r="G1402" t="n">
-        <v>11.688404083252</v>
+        <v>11.6884031295776</v>
       </c>
       <c r="H1402" t="n">
         <v>19081376</v>
@@ -41201,7 +41201,7 @@
         <v>15.6859998703003</v>
       </c>
       <c r="G1408" t="n">
-        <v>11.4332942962646</v>
+        <v>11.4332933425903</v>
       </c>
       <c r="H1408" t="n">
         <v>8195845</v>
@@ -41375,7 +41375,7 @@
         <v>15.8859996795654</v>
       </c>
       <c r="G1414" t="n">
-        <v>11.5790700912476</v>
+        <v>11.5790710449219</v>
       </c>
       <c r="H1414" t="n">
         <v>6106773</v>
@@ -41404,7 +41404,7 @@
         <v>15.6879997253418</v>
       </c>
       <c r="G1415" t="n">
-        <v>11.4347524642944</v>
+        <v>11.4347515106201</v>
       </c>
       <c r="H1415" t="n">
         <v>5624955</v>
@@ -41549,7 +41549,7 @@
         <v>17.0620002746582</v>
       </c>
       <c r="G1420" t="n">
-        <v>12.436240196228</v>
+        <v>12.4362411499023</v>
       </c>
       <c r="H1420" t="n">
         <v>22351876</v>
@@ -41607,7 +41607,7 @@
         <v>17.4440002441406</v>
       </c>
       <c r="G1422" t="n">
-        <v>12.714674949646</v>
+        <v>12.7146739959717</v>
       </c>
       <c r="H1422" t="n">
         <v>12451584</v>
@@ -41665,7 +41665,7 @@
         <v>17.996000289917</v>
       </c>
       <c r="G1424" t="n">
-        <v>13.117018699646</v>
+        <v>13.1170196533203</v>
       </c>
       <c r="H1424" t="n">
         <v>9916408</v>
@@ -41694,7 +41694,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1425" t="n">
-        <v>13.0834903717041</v>
+        <v>13.0834913253784</v>
       </c>
       <c r="H1425" t="n">
         <v>8331189</v>
@@ -41723,7 +41723,7 @@
         <v>18.0179996490479</v>
       </c>
       <c r="G1426" t="n">
-        <v>13.1330547332764</v>
+        <v>13.1330537796021</v>
       </c>
       <c r="H1426" t="n">
         <v>7782123</v>
@@ -41752,7 +41752,7 @@
         <v>18.4979991912842</v>
       </c>
       <c r="G1427" t="n">
-        <v>13.4829177856445</v>
+        <v>13.4829168319702</v>
       </c>
       <c r="H1427" t="n">
         <v>12643699</v>
@@ -41810,7 +41810,7 @@
         <v>18.3419990539551</v>
       </c>
       <c r="G1429" t="n">
-        <v>13.369213104248</v>
+        <v>13.3692140579224</v>
       </c>
       <c r="H1429" t="n">
         <v>8899377</v>
@@ -41868,7 +41868,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1431" t="n">
-        <v>13.1053562164307</v>
+        <v>13.105357170105</v>
       </c>
       <c r="H1431" t="n">
         <v>7911926</v>
@@ -41955,7 +41955,7 @@
         <v>17.2059993743896</v>
       </c>
       <c r="G1434" t="n">
-        <v>12.5411996841431</v>
+        <v>12.5412006378174</v>
       </c>
       <c r="H1434" t="n">
         <v>8801811</v>
@@ -41984,7 +41984,7 @@
         <v>17.25</v>
       </c>
       <c r="G1435" t="n">
-        <v>12.5732717514038</v>
+        <v>12.5732707977295</v>
       </c>
       <c r="H1435" t="n">
         <v>7032288</v>
@@ -42042,7 +42042,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G1437" t="n">
-        <v>12.485803604126</v>
+        <v>12.4858045578003</v>
       </c>
       <c r="H1437" t="n">
         <v>9665894</v>
@@ -42071,7 +42071,7 @@
         <v>17.1639995574951</v>
       </c>
       <c r="G1438" t="n">
-        <v>12.5105867385864</v>
+        <v>12.5105857849121</v>
       </c>
       <c r="H1438" t="n">
         <v>5985747</v>
@@ -42216,7 +42216,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G1443" t="n">
-        <v>12.485803604126</v>
+        <v>12.4858045578003</v>
       </c>
       <c r="H1443" t="n">
         <v>9948006</v>
@@ -42361,7 +42361,7 @@
         <v>16.7040004730225</v>
       </c>
       <c r="G1448" t="n">
-        <v>12.1753005981445</v>
+        <v>12.1752996444702</v>
       </c>
       <c r="H1448" t="n">
         <v>12892650</v>
@@ -42506,7 +42506,7 @@
         <v>16.8099994659424</v>
       </c>
       <c r="G1453" t="n">
-        <v>12.2525606155396</v>
+        <v>12.2525615692139</v>
       </c>
       <c r="H1453" t="n">
         <v>84696171</v>
@@ -42622,7 +42622,7 @@
         <v>16.7679996490479</v>
       </c>
       <c r="G1457" t="n">
-        <v>12.2219486236572</v>
+        <v>12.2219476699829</v>
       </c>
       <c r="H1457" t="n">
         <v>13181642</v>
@@ -42738,7 +42738,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1461" t="n">
-        <v>12.1432275772095</v>
+        <v>12.1432285308838</v>
       </c>
       <c r="H1461" t="n">
         <v>9582369</v>
@@ -42767,7 +42767,7 @@
         <v>16.5219993591309</v>
       </c>
       <c r="G1462" t="n">
-        <v>12.0426425933838</v>
+        <v>12.0426416397095</v>
       </c>
       <c r="H1462" t="n">
         <v>11491288</v>
@@ -42825,7 +42825,7 @@
         <v>16.1380004882812</v>
       </c>
       <c r="G1464" t="n">
-        <v>11.762749671936</v>
+        <v>11.7627506256104</v>
       </c>
       <c r="H1464" t="n">
         <v>8363713</v>
@@ -43028,7 +43028,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G1471" t="n">
-        <v>12.2671384811401</v>
+        <v>12.2671394348145</v>
       </c>
       <c r="H1471" t="n">
         <v>12943620</v>
@@ -43086,7 +43086,7 @@
         <v>17.2059993743896</v>
       </c>
       <c r="G1473" t="n">
-        <v>12.5411996841431</v>
+        <v>12.5412006378174</v>
       </c>
       <c r="H1473" t="n">
         <v>9442031</v>
@@ -43144,7 +43144,7 @@
         <v>16.7779998779297</v>
       </c>
       <c r="G1475" t="n">
-        <v>12.2292366027832</v>
+        <v>12.2292375564575</v>
       </c>
       <c r="H1475" t="n">
         <v>7838678</v>
@@ -43318,7 +43318,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1481" t="n">
-        <v>12.7992258071899</v>
+        <v>12.7992248535156</v>
       </c>
       <c r="H1481" t="n">
         <v>11351659</v>
@@ -43376,7 +43376,7 @@
         <v>17.25</v>
       </c>
       <c r="G1483" t="n">
-        <v>12.5732717514038</v>
+        <v>12.5732707977295</v>
       </c>
       <c r="H1483" t="n">
         <v>11777883</v>
@@ -43405,7 +43405,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1484" t="n">
-        <v>12.7190475463867</v>
+        <v>12.719048500061</v>
       </c>
       <c r="H1484" t="n">
         <v>8713760</v>
@@ -43434,7 +43434,7 @@
         <v>17.4680004119873</v>
       </c>
       <c r="G1485" t="n">
-        <v>12.7321681976318</v>
+        <v>12.7321672439575</v>
       </c>
       <c r="H1485" t="n">
         <v>8006195</v>
@@ -43550,7 +43550,7 @@
         <v>17.5359992980957</v>
       </c>
       <c r="G1489" t="n">
-        <v>12.7817316055298</v>
+        <v>12.7817325592041</v>
       </c>
       <c r="H1489" t="n">
         <v>8625008</v>
@@ -43579,7 +43579,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1490" t="n">
-        <v>12.7117595672607</v>
+        <v>12.7117605209351</v>
       </c>
       <c r="H1490" t="n">
         <v>10009713</v>
@@ -43637,7 +43637,7 @@
         <v>17.8859996795654</v>
       </c>
       <c r="G1492" t="n">
-        <v>13.0368423461914</v>
+        <v>13.0368413925171</v>
       </c>
       <c r="H1492" t="n">
         <v>9421866</v>
@@ -43695,7 +43695,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1494" t="n">
-        <v>13.0834903717041</v>
+        <v>13.0834913253784</v>
       </c>
       <c r="H1494" t="n">
         <v>8750371</v>
@@ -43753,7 +43753,7 @@
         <v>17.9559993743896</v>
       </c>
       <c r="G1496" t="n">
-        <v>13.0878639221191</v>
+        <v>13.0878648757935</v>
       </c>
       <c r="H1496" t="n">
         <v>8661810</v>
@@ -43840,7 +43840,7 @@
         <v>17.4580001831055</v>
       </c>
       <c r="G1499" t="n">
-        <v>12.7248792648315</v>
+        <v>12.7248802185059</v>
       </c>
       <c r="H1499" t="n">
         <v>8060360</v>
@@ -43869,7 +43869,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1500" t="n">
-        <v>12.3983383178711</v>
+        <v>12.3983392715454</v>
       </c>
       <c r="H1500" t="n">
         <v>9956145</v>
@@ -43898,7 +43898,7 @@
         <v>16.8080005645752</v>
       </c>
       <c r="G1501" t="n">
-        <v>12.2511043548584</v>
+        <v>12.2511034011841</v>
       </c>
       <c r="H1501" t="n">
         <v>11525744</v>
@@ -43927,7 +43927,7 @@
         <v>16.7080001831055</v>
       </c>
       <c r="G1502" t="n">
-        <v>12.1782150268555</v>
+        <v>12.1782159805298</v>
       </c>
       <c r="H1502" t="n">
         <v>8940028</v>
@@ -43956,7 +43956,7 @@
         <v>15.5659999847412</v>
       </c>
       <c r="G1503" t="n">
-        <v>11.3458280563354</v>
+        <v>11.3458271026611</v>
       </c>
       <c r="H1503" t="n">
         <v>20502015</v>
@@ -44072,7 +44072,7 @@
         <v>15.9280004501343</v>
       </c>
       <c r="G1507" t="n">
-        <v>11.6096839904785</v>
+        <v>11.6096849441528</v>
       </c>
       <c r="H1507" t="n">
         <v>12111703</v>
@@ -44159,7 +44159,7 @@
         <v>16.8719997406006</v>
       </c>
       <c r="G1510" t="n">
-        <v>12.2977523803711</v>
+        <v>12.2977514266968</v>
       </c>
       <c r="H1510" t="n">
         <v>15259763</v>
@@ -44188,7 +44188,7 @@
         <v>16.681999206543</v>
       </c>
       <c r="G1511" t="n">
-        <v>12.1592636108398</v>
+        <v>12.1592626571655</v>
       </c>
       <c r="H1511" t="n">
         <v>10273796</v>
@@ -44246,7 +44246,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G1513" t="n">
-        <v>12.0193176269531</v>
+        <v>12.0193185806274</v>
       </c>
       <c r="H1513" t="n">
         <v>9130267</v>
@@ -44333,7 +44333,7 @@
         <v>16.3159999847412</v>
       </c>
       <c r="G1516" t="n">
-        <v>11.8924922943115</v>
+        <v>11.8924913406372</v>
       </c>
       <c r="H1516" t="n">
         <v>7393498</v>
@@ -44420,7 +44420,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1519" t="n">
-        <v>11.5309648513794</v>
+        <v>11.5309638977051</v>
       </c>
       <c r="H1519" t="n">
         <v>12556793</v>
@@ -44594,7 +44594,7 @@
         <v>16.7019996643066</v>
       </c>
       <c r="G1525" t="n">
-        <v>12.1738414764404</v>
+        <v>12.1738405227661</v>
       </c>
       <c r="H1525" t="n">
         <v>4705186</v>
@@ -44797,7 +44797,7 @@
         <v>17.8640003204346</v>
       </c>
       <c r="G1532" t="n">
-        <v>13.0208053588867</v>
+        <v>13.020806312561</v>
       </c>
       <c r="H1532" t="n">
         <v>9088781</v>
@@ -44913,7 +44913,7 @@
         <v>18.9740009307861</v>
       </c>
       <c r="G1536" t="n">
-        <v>13.8298692703247</v>
+        <v>13.829870223999</v>
       </c>
       <c r="H1536" t="n">
         <v>12639580</v>
@@ -45000,7 +45000,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G1539" t="n">
-        <v>13.8415298461914</v>
+        <v>13.84153175354</v>
       </c>
       <c r="H1539" t="n">
         <v>11809912</v>
@@ -45029,7 +45029,7 @@
         <v>18.7940006256104</v>
       </c>
       <c r="G1540" t="n">
-        <v>13.6986684799194</v>
+        <v>13.6986703872681</v>
       </c>
       <c r="H1540" t="n">
         <v>18772137</v>
@@ -45174,7 +45174,7 @@
         <v>17.5419998168945</v>
       </c>
       <c r="G1545" t="n">
-        <v>12.7861051559448</v>
+        <v>12.7861061096191</v>
       </c>
       <c r="H1545" t="n">
         <v>14202828</v>
@@ -45348,7 +45348,7 @@
         <v>16.4619998931885</v>
       </c>
       <c r="G1551" t="n">
-        <v>11.9989080429077</v>
+        <v>11.9989099502563</v>
       </c>
       <c r="H1551" t="n">
         <v>20977707</v>
@@ -45406,7 +45406,7 @@
         <v>16.4379997253418</v>
       </c>
       <c r="G1553" t="n">
-        <v>11.9814167022705</v>
+        <v>11.9814157485962</v>
       </c>
       <c r="H1553" t="n">
         <v>10198211</v>
@@ -45464,7 +45464,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1555" t="n">
-        <v>12.3618927001953</v>
+        <v>12.3618936538696</v>
       </c>
       <c r="H1555" t="n">
         <v>11428071</v>
@@ -45522,7 +45522,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1557" t="n">
-        <v>11.9099855422974</v>
+        <v>11.9099864959717</v>
       </c>
       <c r="H1557" t="n">
         <v>16408259</v>
@@ -45551,7 +45551,7 @@
         <v>17.011999130249</v>
       </c>
       <c r="G1558" t="n">
-        <v>12.3997955322266</v>
+        <v>12.3997945785522</v>
       </c>
       <c r="H1558" t="n">
         <v>12740314</v>
@@ -45754,7 +45754,7 @@
         <v>16.0340003967285</v>
       </c>
       <c r="G1565" t="n">
-        <v>11.6869468688965</v>
+        <v>11.6869459152222</v>
       </c>
       <c r="H1565" t="n">
         <v>27661075</v>
@@ -45899,7 +45899,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G1570" t="n">
-        <v>10.9041242599487</v>
+        <v>10.9041233062744</v>
       </c>
       <c r="H1570" t="n">
         <v>17317291</v>
@@ -45928,7 +45928,7 @@
         <v>13.8219995498657</v>
       </c>
       <c r="G1571" t="n">
-        <v>10.074652671814</v>
+        <v>10.0746517181396</v>
       </c>
       <c r="H1571" t="n">
         <v>27863742</v>
@@ -45986,7 +45986,7 @@
         <v>12.9320001602173</v>
       </c>
       <c r="G1573" t="n">
-        <v>9.42594432830811</v>
+        <v>9.42594337463379</v>
       </c>
       <c r="H1573" t="n">
         <v>23437500</v>
@@ -46015,7 +46015,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1574" t="n">
-        <v>10.5834140777588</v>
+        <v>10.5834150314331</v>
       </c>
       <c r="H1574" t="n">
         <v>24728697</v>
@@ -46363,7 +46363,7 @@
         <v>14.4340000152588</v>
       </c>
       <c r="G1586" t="n">
-        <v>10.5207290649414</v>
+        <v>10.5207300186157</v>
       </c>
       <c r="H1586" t="n">
         <v>8201329</v>
@@ -46392,7 +46392,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1587" t="n">
-        <v>10.5323915481567</v>
+        <v>10.5323925018311</v>
       </c>
       <c r="H1587" t="n">
         <v>11175290</v>
@@ -46508,7 +46508,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G1591" t="n">
-        <v>10.7802124023438</v>
+        <v>10.7802133560181</v>
       </c>
       <c r="H1591" t="n">
         <v>11448264</v>
@@ -46537,7 +46537,7 @@
         <v>14.8879995346069</v>
       </c>
       <c r="G1592" t="n">
-        <v>10.8516435623169</v>
+        <v>10.8516426086426</v>
       </c>
       <c r="H1592" t="n">
         <v>10698097</v>
@@ -46595,7 +46595,7 @@
         <v>13.7019996643066</v>
       </c>
       <c r="G1594" t="n">
-        <v>9.98718547821045</v>
+        <v>9.98718643188477</v>
       </c>
       <c r="H1594" t="n">
         <v>24669291</v>
@@ -46624,7 +46624,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1595" t="n">
-        <v>9.86910724639893</v>
+        <v>9.86910629272461</v>
       </c>
       <c r="H1595" t="n">
         <v>11808221</v>
@@ -46653,7 +46653,7 @@
         <v>13.7659997940063</v>
       </c>
       <c r="G1596" t="n">
-        <v>10.0338344573975</v>
+        <v>10.0338354110718</v>
       </c>
       <c r="H1596" t="n">
         <v>11644663</v>
@@ -46682,7 +46682,7 @@
         <v>13.9219999313354</v>
       </c>
       <c r="G1597" t="n">
-        <v>10.1475410461426</v>
+        <v>10.1475400924683</v>
       </c>
       <c r="H1597" t="n">
         <v>9999354</v>
@@ -46740,7 +46740,7 @@
         <v>13.9739999771118</v>
       </c>
       <c r="G1599" t="n">
-        <v>10.1854429244995</v>
+        <v>10.1854419708252</v>
       </c>
       <c r="H1599" t="n">
         <v>15693607</v>
@@ -46827,7 +46827,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1602" t="n">
-        <v>10.5621309280396</v>
+        <v>10.5621299743652</v>
       </c>
       <c r="H1602" t="n">
         <v>11110836</v>
@@ -46972,7 +46972,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1607" t="n">
-        <v>9.9482364654541</v>
+        <v>9.94823551177979</v>
       </c>
       <c r="H1607" t="n">
         <v>13554190</v>
@@ -47146,7 +47146,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G1613" t="n">
-        <v>10.0190687179565</v>
+        <v>10.0190696716309</v>
       </c>
       <c r="H1613" t="n">
         <v>19205981</v>
@@ -47233,7 +47233,7 @@
         <v>12.8479995727539</v>
       </c>
       <c r="G1616" t="n">
-        <v>10.1119394302368</v>
+        <v>10.1119403839111</v>
       </c>
       <c r="H1616" t="n">
         <v>12445007</v>
@@ -47291,7 +47291,7 @@
         <v>13.253999710083</v>
       </c>
       <c r="G1618" t="n">
-        <v>10.4314804077148</v>
+        <v>10.4314794540405</v>
       </c>
       <c r="H1618" t="n">
         <v>14249318</v>
@@ -47320,7 +47320,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G1619" t="n">
-        <v>10.8375949859619</v>
+        <v>10.8375959396362</v>
       </c>
       <c r="H1619" t="n">
         <v>15173714</v>
@@ -47813,7 +47813,7 @@
         <v>13.8879995346069</v>
       </c>
       <c r="G1636" t="n">
-        <v>10.9304666519165</v>
+        <v>10.9304656982422</v>
       </c>
       <c r="H1636" t="n">
         <v>7108409</v>
@@ -47958,7 +47958,7 @@
         <v>12.4779996871948</v>
       </c>
       <c r="G1641" t="n">
-        <v>9.82073402404785</v>
+        <v>9.82073497772217</v>
       </c>
       <c r="H1641" t="n">
         <v>10537828</v>
@@ -48045,7 +48045,7 @@
         <v>12.2360000610352</v>
       </c>
       <c r="G1644" t="n">
-        <v>9.63027000427246</v>
+        <v>9.63026905059814</v>
       </c>
       <c r="H1644" t="n">
         <v>18533131</v>
@@ -48103,7 +48103,7 @@
         <v>12.6979999542236</v>
       </c>
       <c r="G1646" t="n">
-        <v>9.99388313293457</v>
+        <v>9.99388408660889</v>
       </c>
       <c r="H1646" t="n">
         <v>7844175</v>
@@ -48219,7 +48219,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1650" t="n">
-        <v>9.77508640289307</v>
+        <v>9.77508544921875</v>
       </c>
       <c r="H1650" t="n">
         <v>9393955</v>
@@ -48451,7 +48451,7 @@
         <v>11.9980001449585</v>
       </c>
       <c r="G1658" t="n">
-        <v>9.44295310974121</v>
+        <v>9.44295406341553</v>
       </c>
       <c r="H1658" t="n">
         <v>14373601</v>
@@ -48538,7 +48538,7 @@
         <v>12.2980003356934</v>
       </c>
       <c r="G1661" t="n">
-        <v>9.67906665802002</v>
+        <v>9.67906761169434</v>
       </c>
       <c r="H1661" t="n">
         <v>11261520</v>
@@ -48654,7 +48654,7 @@
         <v>12.253999710083</v>
       </c>
       <c r="G1665" t="n">
-        <v>9.64443683624268</v>
+        <v>9.64443588256836</v>
       </c>
       <c r="H1665" t="n">
         <v>9922342</v>
@@ -48712,7 +48712,7 @@
         <v>12.6420001983643</v>
       </c>
       <c r="G1667" t="n">
-        <v>9.94980907440186</v>
+        <v>9.94981002807617</v>
       </c>
       <c r="H1667" t="n">
         <v>12157434</v>
@@ -48915,7 +48915,7 @@
         <v>13.9219999313354</v>
       </c>
       <c r="G1674" t="n">
-        <v>10.9572257995605</v>
+        <v>10.9572248458862</v>
       </c>
       <c r="H1674" t="n">
         <v>13107465</v>
@@ -48973,7 +48973,7 @@
         <v>14.2819995880127</v>
       </c>
       <c r="G1676" t="n">
-        <v>11.2405614852905</v>
+        <v>11.2405605316162</v>
       </c>
       <c r="H1676" t="n">
         <v>14546655</v>
@@ -49002,7 +49002,7 @@
         <v>14.423999786377</v>
       </c>
       <c r="G1677" t="n">
-        <v>11.3523225784302</v>
+        <v>11.3523216247559</v>
       </c>
       <c r="H1677" t="n">
         <v>15285395</v>
@@ -49060,7 +49060,7 @@
         <v>14.3319997787476</v>
       </c>
       <c r="G1679" t="n">
-        <v>11.2799129486084</v>
+        <v>11.2799139022827</v>
       </c>
       <c r="H1679" t="n">
         <v>9001478</v>
@@ -49089,7 +49089,7 @@
         <v>14.7819995880127</v>
       </c>
       <c r="G1680" t="n">
-        <v>11.6340827941895</v>
+        <v>11.6340837478638</v>
       </c>
       <c r="H1680" t="n">
         <v>14175564</v>
@@ -49118,7 +49118,7 @@
         <v>14.4060001373291</v>
       </c>
       <c r="G1681" t="n">
-        <v>11.3381547927856</v>
+        <v>11.33815574646</v>
       </c>
       <c r="H1681" t="n">
         <v>11966080</v>
@@ -49176,7 +49176,7 @@
         <v>14.6859998703003</v>
       </c>
       <c r="G1683" t="n">
-        <v>11.5585269927979</v>
+        <v>11.5585279464722</v>
       </c>
       <c r="H1683" t="n">
         <v>7311994</v>
@@ -49263,7 +49263,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1686" t="n">
-        <v>11.5223226547241</v>
+        <v>11.5223236083984</v>
       </c>
       <c r="H1686" t="n">
         <v>10556642</v>
@@ -49292,7 +49292,7 @@
         <v>14.8719997406006</v>
       </c>
       <c r="G1687" t="n">
-        <v>11.7049169540405</v>
+        <v>11.7049179077148</v>
       </c>
       <c r="H1687" t="n">
         <v>7441245</v>
@@ -49350,7 +49350,7 @@
         <v>13.8520002365112</v>
       </c>
       <c r="G1689" t="n">
-        <v>10.9021329879761</v>
+        <v>10.9021339416504</v>
       </c>
       <c r="H1689" t="n">
         <v>11980241</v>
@@ -49437,7 +49437,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G1692" t="n">
-        <v>11.0894498825073</v>
+        <v>11.089448928833</v>
       </c>
       <c r="H1692" t="n">
         <v>10161956</v>
@@ -49785,7 +49785,7 @@
         <v>13.7379999160767</v>
       </c>
       <c r="G1704" t="n">
-        <v>10.8124103546143</v>
+        <v>10.8124094009399</v>
       </c>
       <c r="H1704" t="n">
         <v>11457955</v>
@@ -49872,7 +49872,7 @@
         <v>13.6840000152588</v>
       </c>
       <c r="G1707" t="n">
-        <v>10.7699089050293</v>
+        <v>10.7699098587036</v>
       </c>
       <c r="H1707" t="n">
         <v>8404248</v>
@@ -49901,7 +49901,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1708" t="n">
-        <v>10.5463876724243</v>
+        <v>10.5463886260986</v>
       </c>
       <c r="H1708" t="n">
         <v>19048773</v>
@@ -50017,7 +50017,7 @@
         <v>13.0080003738403</v>
       </c>
       <c r="G1712" t="n">
-        <v>10.237868309021</v>
+        <v>10.2378673553467</v>
       </c>
       <c r="H1712" t="n">
         <v>8544502</v>
@@ -50075,7 +50075,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1714" t="n">
-        <v>10.0111999511719</v>
+        <v>10.0111989974976</v>
       </c>
       <c r="H1714" t="n">
         <v>10150594</v>
@@ -50278,7 +50278,7 @@
         <v>12.6239995956421</v>
       </c>
       <c r="G1721" t="n">
-        <v>9.93564319610596</v>
+        <v>9.93564224243164</v>
       </c>
       <c r="H1721" t="n">
         <v>12463118</v>
@@ -50307,7 +50307,7 @@
         <v>12.5340003967285</v>
       </c>
       <c r="G1722" t="n">
-        <v>9.8648099899292</v>
+        <v>9.86480903625488</v>
       </c>
       <c r="H1722" t="n">
         <v>8128712</v>
@@ -50336,7 +50336,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1723" t="n">
-        <v>9.68064117431641</v>
+        <v>9.68064022064209</v>
       </c>
       <c r="H1723" t="n">
         <v>9175837</v>
@@ -50423,7 +50423,7 @@
         <v>12.1940002441406</v>
       </c>
       <c r="G1726" t="n">
-        <v>9.59721374511719</v>
+        <v>9.5972146987915</v>
       </c>
       <c r="H1726" t="n">
         <v>11106779</v>
@@ -50568,7 +50568,7 @@
         <v>12.9680004119873</v>
       </c>
       <c r="G1731" t="n">
-        <v>10.2063856124878</v>
+        <v>10.2063865661621</v>
       </c>
       <c r="H1731" t="n">
         <v>6824383</v>
@@ -50626,7 +50626,7 @@
         <v>13.0740003585815</v>
       </c>
       <c r="G1733" t="n">
-        <v>10.289813041687</v>
+        <v>10.2898120880127</v>
       </c>
       <c r="H1733" t="n">
         <v>9054649</v>
@@ -51003,7 +51003,7 @@
         <v>13.706000328064</v>
       </c>
       <c r="G1746" t="n">
-        <v>10.7872257232666</v>
+        <v>10.7872247695923</v>
       </c>
       <c r="H1746" t="n">
         <v>5584421</v>
@@ -51177,7 +51177,7 @@
         <v>14.1079998016357</v>
       </c>
       <c r="G1752" t="n">
-        <v>11.1036167144775</v>
+        <v>11.1036157608032</v>
       </c>
       <c r="H1752" t="n">
         <v>8112234</v>
@@ -51206,7 +51206,7 @@
         <v>14.4099998474121</v>
       </c>
       <c r="G1753" t="n">
-        <v>11.3413028717041</v>
+        <v>11.3413038253784</v>
       </c>
       <c r="H1753" t="n">
         <v>9935411</v>
@@ -51235,7 +51235,7 @@
         <v>14.5419998168945</v>
       </c>
       <c r="G1754" t="n">
-        <v>11.4451932907104</v>
+        <v>11.4451923370361</v>
       </c>
       <c r="H1754" t="n">
         <v>6841134</v>
@@ -51293,7 +51293,7 @@
         <v>14.46399974823</v>
       </c>
       <c r="G1756" t="n">
-        <v>11.3838043212891</v>
+        <v>11.3838033676147</v>
       </c>
       <c r="H1756" t="n">
         <v>6889669</v>
@@ -51322,7 +51322,7 @@
         <v>14.6540002822876</v>
       </c>
       <c r="G1757" t="n">
-        <v>11.5333414077759</v>
+        <v>11.5333423614502</v>
       </c>
       <c r="H1757" t="n">
         <v>4996884</v>
@@ -51496,7 +51496,7 @@
         <v>14.6020002365112</v>
       </c>
       <c r="G1763" t="n">
-        <v>11.4924154281616</v>
+        <v>11.4924163818359</v>
       </c>
       <c r="H1763" t="n">
         <v>10869461</v>
@@ -51525,7 +51525,7 @@
         <v>14.6579999923706</v>
       </c>
       <c r="G1764" t="n">
-        <v>11.5364904403687</v>
+        <v>11.5364894866943</v>
       </c>
       <c r="H1764" t="n">
         <v>7750958</v>
@@ -51757,7 +51757,7 @@
         <v>13.5539999008179</v>
       </c>
       <c r="G1772" t="n">
-        <v>10.6675939559937</v>
+        <v>10.6675930023193</v>
       </c>
       <c r="H1772" t="n">
         <v>14317406</v>
@@ -51844,7 +51844,7 @@
         <v>13.253999710083</v>
       </c>
       <c r="G1775" t="n">
-        <v>10.4314804077148</v>
+        <v>10.4314794540405</v>
       </c>
       <c r="H1775" t="n">
         <v>8853439</v>
@@ -51989,7 +51989,7 @@
         <v>13.1180000305176</v>
       </c>
       <c r="G1780" t="n">
-        <v>10.32444190979</v>
+        <v>10.3244428634644</v>
       </c>
       <c r="H1780" t="n">
         <v>6572127</v>
@@ -52134,7 +52134,7 @@
         <v>14.1920003890991</v>
       </c>
       <c r="G1785" t="n">
-        <v>11.1697282791138</v>
+        <v>11.1697273254395</v>
       </c>
       <c r="H1785" t="n">
         <v>11205279</v>
@@ -52337,7 +52337,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G1792" t="n">
-        <v>11.199634552002</v>
+        <v>11.1996355056763</v>
       </c>
       <c r="H1792" t="n">
         <v>19979779</v>
@@ -52366,7 +52366,7 @@
         <v>14.3159999847412</v>
       </c>
       <c r="G1793" t="n">
-        <v>11.2673206329346</v>
+        <v>11.2673215866089</v>
       </c>
       <c r="H1793" t="n">
         <v>7749051</v>
@@ -52424,7 +52424,7 @@
         <v>14.2679996490479</v>
       </c>
       <c r="G1795" t="n">
-        <v>11.2295417785645</v>
+        <v>11.2295427322388</v>
       </c>
       <c r="H1795" t="n">
         <v>8387240</v>
@@ -52453,7 +52453,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G1796" t="n">
-        <v>10.9477815628052</v>
+        <v>10.9477806091309</v>
       </c>
       <c r="H1796" t="n">
         <v>11640060</v>
@@ -52482,7 +52482,7 @@
         <v>14.0240001678467</v>
       </c>
       <c r="G1797" t="n">
-        <v>11.037504196167</v>
+        <v>11.0375032424927</v>
       </c>
       <c r="H1797" t="n">
         <v>11167514</v>
@@ -52627,7 +52627,7 @@
         <v>14.1960000991821</v>
       </c>
       <c r="G1802" t="n">
-        <v>11.1728763580322</v>
+        <v>11.1728754043579</v>
       </c>
       <c r="H1802" t="n">
         <v>9375416</v>
@@ -52656,7 +52656,7 @@
         <v>14.0240001678467</v>
       </c>
       <c r="G1803" t="n">
-        <v>11.037504196167</v>
+        <v>11.0375032424927</v>
       </c>
       <c r="H1803" t="n">
         <v>10925629</v>
@@ -52685,7 +52685,7 @@
         <v>14.3760004043579</v>
       </c>
       <c r="G1804" t="n">
-        <v>11.3145446777344</v>
+        <v>11.3145437240601</v>
       </c>
       <c r="H1804" t="n">
         <v>14827578</v>
@@ -52743,7 +52743,7 @@
         <v>15.2080001831055</v>
       </c>
       <c r="G1806" t="n">
-        <v>11.9693641662598</v>
+        <v>11.9693651199341</v>
       </c>
       <c r="H1806" t="n">
         <v>21413544</v>
@@ -52801,7 +52801,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G1808" t="n">
-        <v>11.8686237335205</v>
+        <v>11.8686227798462</v>
       </c>
       <c r="H1808" t="n">
         <v>9224277</v>
@@ -52888,7 +52888,7 @@
         <v>15.6780004501343</v>
       </c>
       <c r="G1811" t="n">
-        <v>12.3392763137817</v>
+        <v>12.3392753601074</v>
       </c>
       <c r="H1811" t="n">
         <v>14231457</v>
@@ -52917,7 +52917,7 @@
         <v>15.4119997024536</v>
       </c>
       <c r="G1812" t="n">
-        <v>12.129921913147</v>
+        <v>12.1299209594727</v>
       </c>
       <c r="H1812" t="n">
         <v>11119452</v>
@@ -53120,7 +53120,7 @@
         <v>15.8680000305176</v>
       </c>
       <c r="G1819" t="n">
-        <v>12.4888134002686</v>
+        <v>12.4888124465942</v>
       </c>
       <c r="H1819" t="n">
         <v>11435162</v>
@@ -53178,7 +53178,7 @@
         <v>16.8040008544922</v>
       </c>
       <c r="G1821" t="n">
-        <v>13.2254877090454</v>
+        <v>13.2254867553711</v>
       </c>
       <c r="H1821" t="n">
         <v>36181727</v>
@@ -53381,7 +53381,7 @@
         <v>17.576000213623</v>
       </c>
       <c r="G1828" t="n">
-        <v>13.8330850601196</v>
+        <v>13.8330841064453</v>
       </c>
       <c r="H1828" t="n">
         <v>9883487</v>
@@ -53410,7 +53410,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G1829" t="n">
-        <v>13.7968816757202</v>
+        <v>13.7968807220459</v>
       </c>
       <c r="H1829" t="n">
         <v>6385858</v>
@@ -53439,7 +53439,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G1830" t="n">
-        <v>13.7653980255127</v>
+        <v>13.765398979187</v>
       </c>
       <c r="H1830" t="n">
         <v>9111642</v>
@@ -53671,7 +53671,7 @@
         <v>15.8459997177124</v>
       </c>
       <c r="G1838" t="n">
-        <v>12.4714994430542</v>
+        <v>12.4714984893799</v>
       </c>
       <c r="H1838" t="n">
         <v>11999902</v>
@@ -53787,7 +53787,7 @@
         <v>15.9020004272461</v>
       </c>
       <c r="G1842" t="n">
-        <v>12.5155725479126</v>
+        <v>12.5155735015869</v>
       </c>
       <c r="H1842" t="n">
         <v>10262336</v>
@@ -53816,7 +53816,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G1843" t="n">
-        <v>12.7737236022949</v>
+        <v>12.7737226486206</v>
       </c>
       <c r="H1843" t="n">
         <v>5646418</v>
@@ -53845,7 +53845,7 @@
         <v>16.2520008087158</v>
       </c>
       <c r="G1844" t="n">
-        <v>12.7910394668579</v>
+        <v>12.7910385131836</v>
       </c>
       <c r="H1844" t="n">
         <v>5909643</v>
@@ -54019,7 +54019,7 @@
         <v>16.1140003204346</v>
       </c>
       <c r="G1850" t="n">
-        <v>12.682427406311</v>
+        <v>12.6824264526367</v>
       </c>
       <c r="H1850" t="n">
         <v>9491339</v>
@@ -54135,7 +54135,7 @@
         <v>16.8279991149902</v>
       </c>
       <c r="G1854" t="n">
-        <v>13.2443742752075</v>
+        <v>13.2443752288818</v>
       </c>
       <c r="H1854" t="n">
         <v>8015666</v>
@@ -54164,7 +54164,7 @@
         <v>17.1639995574951</v>
       </c>
       <c r="G1855" t="n">
-        <v>13.5088224411011</v>
+        <v>13.5088214874268</v>
       </c>
       <c r="H1855" t="n">
         <v>12119073</v>
@@ -54280,7 +54280,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1859" t="n">
-        <v>12.6320552825928</v>
+        <v>12.6320543289185</v>
       </c>
       <c r="H1859" t="n">
         <v>30007381</v>
@@ -80096,6 +80096,35 @@
         <v>73172503</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>3.61350011825562</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>3.70149993896484</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>3.61350011825562</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>3.69099998474121</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>3.69099998474121</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>44376828</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -427,7 +427,7 @@
         <v>7.70264196395874</v>
       </c>
       <c r="G2" t="n">
-        <v>4.02501344680786</v>
+        <v>4.02501392364502</v>
       </c>
       <c r="H2" t="n">
         <v>27068333</v>
@@ -485,7 +485,7 @@
         <v>7.49471807479858</v>
       </c>
       <c r="G4" t="n">
-        <v>3.91636276245117</v>
+        <v>3.91636300086975</v>
       </c>
       <c r="H4" t="n">
         <v>28467440</v>
@@ -514,7 +514,7 @@
         <v>7.24898910522461</v>
       </c>
       <c r="G5" t="n">
-        <v>3.78795766830444</v>
+        <v>3.7879581451416</v>
       </c>
       <c r="H5" t="n">
         <v>25910209</v>
@@ -572,7 +572,7 @@
         <v>6.92292594909668</v>
       </c>
       <c r="G7" t="n">
-        <v>3.61757326126099</v>
+        <v>3.61757349967957</v>
       </c>
       <c r="H7" t="n">
         <v>27133919</v>
@@ -630,7 +630,7 @@
         <v>7.02216291427612</v>
       </c>
       <c r="G9" t="n">
-        <v>3.66942930221558</v>
+        <v>3.66942977905273</v>
       </c>
       <c r="H9" t="n">
         <v>18895772</v>
@@ -688,7 +688,7 @@
         <v>6.28497791290283</v>
       </c>
       <c r="G11" t="n">
-        <v>3.28421425819397</v>
+        <v>3.28421401977539</v>
       </c>
       <c r="H11" t="n">
         <v>29332592</v>
@@ -717,7 +717,7 @@
         <v>6.10068082809448</v>
       </c>
       <c r="G12" t="n">
-        <v>3.18790936470032</v>
+        <v>3.1879096031189</v>
       </c>
       <c r="H12" t="n">
         <v>20540951</v>
@@ -746,7 +746,7 @@
         <v>6.25662422180176</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2693977355957</v>
+        <v>3.26939725875854</v>
       </c>
       <c r="H13" t="n">
         <v>18721047</v>
@@ -775,7 +775,7 @@
         <v>5.85967779159546</v>
       </c>
       <c r="G14" t="n">
-        <v>3.06197309494019</v>
+        <v>3.06197333335876</v>
       </c>
       <c r="H14" t="n">
         <v>22052655</v>
@@ -804,7 +804,7 @@
         <v>6.23299694061279</v>
       </c>
       <c r="G15" t="n">
-        <v>3.25705170631409</v>
+        <v>3.25705099105835</v>
       </c>
       <c r="H15" t="n">
         <v>26115263</v>
@@ -891,7 +891,7 @@
         <v>6.62521696090698</v>
       </c>
       <c r="G18" t="n">
-        <v>3.4620053768158</v>
+        <v>3.46200609207153</v>
       </c>
       <c r="H18" t="n">
         <v>29100832</v>
@@ -920,7 +920,7 @@
         <v>6.56851005554199</v>
       </c>
       <c r="G19" t="n">
-        <v>3.43237376213074</v>
+        <v>3.43237352371216</v>
       </c>
       <c r="H19" t="n">
         <v>46908275</v>
@@ -949,7 +949,7 @@
         <v>6.09595584869385</v>
       </c>
       <c r="G20" t="n">
-        <v>3.18544006347656</v>
+        <v>3.18544030189514</v>
       </c>
       <c r="H20" t="n">
         <v>37383419</v>
@@ -978,7 +978,7 @@
         <v>6.05342578887939</v>
       </c>
       <c r="G21" t="n">
-        <v>3.16321635246277</v>
+        <v>3.16321611404419</v>
       </c>
       <c r="H21" t="n">
         <v>27726657</v>
@@ -1007,7 +1007,7 @@
         <v>6.04869985580444</v>
       </c>
       <c r="G22" t="n">
-        <v>3.16074681282043</v>
+        <v>3.16074657440186</v>
       </c>
       <c r="H22" t="n">
         <v>15295313</v>
@@ -1036,7 +1036,7 @@
         <v>5.88803195953369</v>
       </c>
       <c r="G23" t="n">
-        <v>3.07679009437561</v>
+        <v>3.07678985595703</v>
       </c>
       <c r="H23" t="n">
         <v>26378999</v>
@@ -1065,7 +1065,7 @@
         <v>5.6517539024353</v>
       </c>
       <c r="G24" t="n">
-        <v>2.9533224105835</v>
+        <v>2.95332312583923</v>
       </c>
       <c r="H24" t="n">
         <v>29355123</v>
@@ -1094,7 +1094,7 @@
         <v>5.58087110519409</v>
       </c>
       <c r="G25" t="n">
-        <v>2.91628313064575</v>
+        <v>2.91628336906433</v>
       </c>
       <c r="H25" t="n">
         <v>32836946</v>
@@ -1152,7 +1152,7 @@
         <v>5.08468914031982</v>
       </c>
       <c r="G27" t="n">
-        <v>2.65700316429138</v>
+        <v>2.65700340270996</v>
       </c>
       <c r="H27" t="n">
         <v>33984093</v>
@@ -1181,7 +1181,7 @@
         <v>4.94292211532593</v>
       </c>
       <c r="G28" t="n">
-        <v>2.58292293548584</v>
+        <v>2.58292245864868</v>
       </c>
       <c r="H28" t="n">
         <v>34764384</v>
@@ -1210,7 +1210,7 @@
         <v>5.23118114471436</v>
       </c>
       <c r="G29" t="n">
-        <v>2.7335524559021</v>
+        <v>2.73355269432068</v>
       </c>
       <c r="H29" t="n">
         <v>29457120</v>
@@ -1268,7 +1268,7 @@
         <v>5.13667011260986</v>
       </c>
       <c r="G31" t="n">
-        <v>2.68416595458984</v>
+        <v>2.68416547775269</v>
       </c>
       <c r="H31" t="n">
         <v>22119082</v>
@@ -1297,7 +1297,7 @@
         <v>5.36349582672119</v>
       </c>
       <c r="G32" t="n">
-        <v>2.80269360542297</v>
+        <v>2.80269384384155</v>
       </c>
       <c r="H32" t="n">
         <v>21315364</v>
@@ -1326,7 +1326,7 @@
         <v>5.27843618392944</v>
       </c>
       <c r="G33" t="n">
-        <v>2.75824570655823</v>
+        <v>2.75824546813965</v>
       </c>
       <c r="H33" t="n">
         <v>22966997</v>
@@ -1355,7 +1355,7 @@
         <v>5.54779195785522</v>
       </c>
       <c r="G34" t="n">
-        <v>2.89899778366089</v>
+        <v>2.89899754524231</v>
       </c>
       <c r="H34" t="n">
         <v>21467582</v>
@@ -1384,7 +1384,7 @@
         <v>5.50998783111572</v>
       </c>
       <c r="G35" t="n">
-        <v>2.87924289703369</v>
+        <v>2.87924337387085</v>
       </c>
       <c r="H35" t="n">
         <v>24357504</v>
@@ -1413,7 +1413,7 @@
         <v>5.37767219543457</v>
       </c>
       <c r="G36" t="n">
-        <v>2.81010150909424</v>
+        <v>2.81010127067566</v>
       </c>
       <c r="H36" t="n">
         <v>14966595</v>
@@ -1442,7 +1442,7 @@
         <v>5.59977293014526</v>
       </c>
       <c r="G37" t="n">
-        <v>2.92616009712219</v>
+        <v>2.92615962028503</v>
       </c>
       <c r="H37" t="n">
         <v>15560828</v>
@@ -1471,7 +1471,7 @@
         <v>5.43437910079956</v>
       </c>
       <c r="G38" t="n">
-        <v>2.83973336219788</v>
+        <v>2.83973383903503</v>
       </c>
       <c r="H38" t="n">
         <v>15820069</v>
@@ -1529,7 +1529,7 @@
         <v>5.43437910079956</v>
       </c>
       <c r="G40" t="n">
-        <v>2.83973336219788</v>
+        <v>2.83973383903503</v>
       </c>
       <c r="H40" t="n">
         <v>26385500</v>
@@ -1558,7 +1558,7 @@
         <v>5.75099086761475</v>
       </c>
       <c r="G41" t="n">
-        <v>3.00517916679382</v>
+        <v>3.00517892837524</v>
       </c>
       <c r="H41" t="n">
         <v>30107591</v>
@@ -1587,7 +1587,7 @@
         <v>5.9967188835144</v>
       </c>
       <c r="G42" t="n">
-        <v>3.13358449935913</v>
+        <v>3.13358402252197</v>
       </c>
       <c r="H42" t="n">
         <v>30013061</v>
@@ -1616,7 +1616,7 @@
         <v>6.31333112716675</v>
       </c>
       <c r="G43" t="n">
-        <v>3.29902982711792</v>
+        <v>3.29903030395508</v>
       </c>
       <c r="H43" t="n">
         <v>35951217</v>
@@ -1674,7 +1674,7 @@
         <v>6.60631513595581</v>
       </c>
       <c r="G45" t="n">
-        <v>3.45212888717651</v>
+        <v>3.45212841033936</v>
       </c>
       <c r="H45" t="n">
         <v>25716643</v>
@@ -1703,7 +1703,7 @@
         <v>6.62994289398193</v>
       </c>
       <c r="G46" t="n">
-        <v>3.46447467803955</v>
+        <v>3.46447539329529</v>
       </c>
       <c r="H46" t="n">
         <v>20407937</v>
@@ -1732,7 +1732,7 @@
         <v>6.58741283416748</v>
       </c>
       <c r="G47" t="n">
-        <v>3.44225120544434</v>
+        <v>3.44225072860718</v>
       </c>
       <c r="H47" t="n">
         <v>19278573</v>
@@ -1761,7 +1761,7 @@
         <v>6.29442882537842</v>
       </c>
       <c r="G48" t="n">
-        <v>3.28915214538574</v>
+        <v>3.28915238380432</v>
       </c>
       <c r="H48" t="n">
         <v>24895913</v>
@@ -1819,7 +1819,7 @@
         <v>6.14321088790894</v>
       </c>
       <c r="G50" t="n">
-        <v>3.21013379096985</v>
+        <v>3.21013283729553</v>
       </c>
       <c r="H50" t="n">
         <v>37496819</v>
@@ -1848,7 +1848,7 @@
         <v>6.41256713867188</v>
       </c>
       <c r="G51" t="n">
-        <v>3.35088539123535</v>
+        <v>3.35088610649109</v>
       </c>
       <c r="H51" t="n">
         <v>19479032</v>
@@ -1877,7 +1877,7 @@
         <v>6.59686422348022</v>
       </c>
       <c r="G52" t="n">
-        <v>3.447190284729</v>
+        <v>3.44719004631042</v>
       </c>
       <c r="H52" t="n">
         <v>21719280</v>
@@ -1935,7 +1935,7 @@
         <v>6.59213781356812</v>
       </c>
       <c r="G54" t="n">
-        <v>3.44472050666809</v>
+        <v>3.44472026824951</v>
       </c>
       <c r="H54" t="n">
         <v>18927252</v>
@@ -1964,7 +1964,7 @@
         <v>6.55433416366577</v>
       </c>
       <c r="G55" t="n">
-        <v>3.42496609687805</v>
+        <v>3.42496585845947</v>
       </c>
       <c r="H55" t="n">
         <v>20625461</v>
@@ -1993,7 +1993,7 @@
         <v>6.72917890548706</v>
       </c>
       <c r="G56" t="n">
-        <v>3.51633071899414</v>
+        <v>3.51633095741272</v>
       </c>
       <c r="H56" t="n">
         <v>22735682</v>
@@ -2051,7 +2051,7 @@
         <v>6.72445297241211</v>
       </c>
       <c r="G58" t="n">
-        <v>3.51386141777039</v>
+        <v>3.51386165618896</v>
       </c>
       <c r="H58" t="n">
         <v>15216180</v>
@@ -2080,7 +2080,7 @@
         <v>6.6535701751709</v>
       </c>
       <c r="G59" t="n">
-        <v>3.47682189941406</v>
+        <v>3.4768214225769</v>
       </c>
       <c r="H59" t="n">
         <v>16307668</v>
@@ -2109,7 +2109,7 @@
         <v>6.37948894500732</v>
       </c>
       <c r="G60" t="n">
-        <v>3.33360052108765</v>
+        <v>3.33360075950623</v>
       </c>
       <c r="H60" t="n">
         <v>16981342</v>
@@ -2196,7 +2196,7 @@
         <v>6.71027708053589</v>
       </c>
       <c r="G63" t="n">
-        <v>3.50645351409912</v>
+        <v>3.50645399093628</v>
       </c>
       <c r="H63" t="n">
         <v>21163552</v>
@@ -2225,7 +2225,7 @@
         <v>6.38421392440796</v>
       </c>
       <c r="G64" t="n">
-        <v>3.33607006072998</v>
+        <v>3.33606934547424</v>
       </c>
       <c r="H64" t="n">
         <v>24990642</v>
@@ -2254,7 +2254,7 @@
         <v>6.40784215927124</v>
       </c>
       <c r="G65" t="n">
-        <v>3.34841704368591</v>
+        <v>3.34841656684875</v>
       </c>
       <c r="H65" t="n">
         <v>17468544</v>
@@ -2283,7 +2283,7 @@
         <v>6.08650493621826</v>
       </c>
       <c r="G66" t="n">
-        <v>3.18050193786621</v>
+        <v>3.18050217628479</v>
       </c>
       <c r="H66" t="n">
         <v>23044825</v>
@@ -2341,7 +2341,7 @@
         <v>5.76989316940308</v>
       </c>
       <c r="G68" t="n">
-        <v>3.01505613327026</v>
+        <v>3.01505637168884</v>
       </c>
       <c r="H68" t="n">
         <v>19779589</v>
@@ -2399,7 +2399,7 @@
         <v>6.14793682098389</v>
       </c>
       <c r="G70" t="n">
-        <v>3.2126030921936</v>
+        <v>3.21260333061218</v>
       </c>
       <c r="H70" t="n">
         <v>16632629</v>
@@ -2428,7 +2428,7 @@
         <v>6.06287717819214</v>
       </c>
       <c r="G71" t="n">
-        <v>3.1681547164917</v>
+        <v>3.16815519332886</v>
       </c>
       <c r="H71" t="n">
         <v>13181604</v>
@@ -2486,7 +2486,7 @@
         <v>6.41729307174683</v>
       </c>
       <c r="G73" t="n">
-        <v>3.35335445404053</v>
+        <v>3.35335540771484</v>
       </c>
       <c r="H73" t="n">
         <v>13482225</v>
@@ -2515,7 +2515,7 @@
         <v>6.31333112716675</v>
       </c>
       <c r="G74" t="n">
-        <v>3.29902982711792</v>
+        <v>3.29903030395508</v>
       </c>
       <c r="H74" t="n">
         <v>17885182</v>
@@ -2573,7 +2573,7 @@
         <v>6.71027708053589</v>
       </c>
       <c r="G76" t="n">
-        <v>3.50645351409912</v>
+        <v>3.50645399093628</v>
       </c>
       <c r="H76" t="n">
         <v>20955582</v>
@@ -2602,7 +2602,7 @@
         <v>6.82368993759155</v>
       </c>
       <c r="G77" t="n">
-        <v>3.56571745872498</v>
+        <v>3.56571769714355</v>
       </c>
       <c r="H77" t="n">
         <v>15831519</v>
@@ -2689,7 +2689,7 @@
         <v>6.8284158706665</v>
       </c>
       <c r="G80" t="n">
-        <v>3.56818675994873</v>
+        <v>3.56818699836731</v>
       </c>
       <c r="H80" t="n">
         <v>20819593</v>
@@ -2776,7 +2776,7 @@
         <v>6.92292594909668</v>
       </c>
       <c r="G83" t="n">
-        <v>3.61757326126099</v>
+        <v>3.61757349967957</v>
       </c>
       <c r="H83" t="n">
         <v>19414695</v>
@@ -2805,7 +2805,7 @@
         <v>6.62521696090698</v>
       </c>
       <c r="G84" t="n">
-        <v>3.4620053768158</v>
+        <v>3.46200609207153</v>
       </c>
       <c r="H84" t="n">
         <v>27031716</v>
@@ -2834,7 +2834,7 @@
         <v>6.72917890548706</v>
       </c>
       <c r="G85" t="n">
-        <v>3.51633071899414</v>
+        <v>3.51633095741272</v>
       </c>
       <c r="H85" t="n">
         <v>16699771</v>
@@ -2863,7 +2863,7 @@
         <v>6.52598094940186</v>
       </c>
       <c r="G86" t="n">
-        <v>3.41014981269836</v>
+        <v>3.41015005111694</v>
       </c>
       <c r="H86" t="n">
         <v>28041065</v>
@@ -2892,7 +2892,7 @@
         <v>6.4739990234375</v>
       </c>
       <c r="G87" t="n">
-        <v>3.38298654556274</v>
+        <v>3.38298678398132</v>
       </c>
       <c r="H87" t="n">
         <v>18863492</v>
@@ -2921,7 +2921,7 @@
         <v>6.3086051940918</v>
       </c>
       <c r="G88" t="n">
-        <v>3.29656028747559</v>
+        <v>3.29656100273132</v>
       </c>
       <c r="H88" t="n">
         <v>17228666</v>
@@ -2979,7 +2979,7 @@
         <v>6.25189876556396</v>
       </c>
       <c r="G90" t="n">
-        <v>3.26692843437195</v>
+        <v>3.26692819595337</v>
       </c>
       <c r="H90" t="n">
         <v>14993361</v>
@@ -3008,7 +3008,7 @@
         <v>6.44092082977295</v>
       </c>
       <c r="G91" t="n">
-        <v>3.36570191383362</v>
+        <v>3.36570167541504</v>
       </c>
       <c r="H91" t="n">
         <v>16137773</v>
@@ -3124,7 +3124,7 @@
         <v>6.37476301193237</v>
       </c>
       <c r="G95" t="n">
-        <v>3.33113098144531</v>
+        <v>3.33113121986389</v>
       </c>
       <c r="H95" t="n">
         <v>9563240</v>
@@ -3153,7 +3153,7 @@
         <v>5.94946384429932</v>
       </c>
       <c r="G96" t="n">
-        <v>3.108891248703</v>
+        <v>3.10889077186584</v>
       </c>
       <c r="H96" t="n">
         <v>34740090</v>
@@ -3211,7 +3211,7 @@
         <v>5.93528699874878</v>
       </c>
       <c r="G98" t="n">
-        <v>3.10148334503174</v>
+        <v>3.10148310661316</v>
       </c>
       <c r="H98" t="n">
         <v>17904156</v>
@@ -3240,7 +3240,7 @@
         <v>5.9636402130127</v>
       </c>
       <c r="G99" t="n">
-        <v>3.11629891395569</v>
+        <v>3.11629867553711</v>
       </c>
       <c r="H99" t="n">
         <v>20701775</v>
@@ -3298,7 +3298,7 @@
         <v>5.87385511398315</v>
       </c>
       <c r="G101" t="n">
-        <v>3.06938195228577</v>
+        <v>3.06938171386719</v>
       </c>
       <c r="H101" t="n">
         <v>20548077</v>
@@ -3327,7 +3327,7 @@
         <v>6.04869985580444</v>
       </c>
       <c r="G102" t="n">
-        <v>3.16074681282043</v>
+        <v>3.16074657440186</v>
       </c>
       <c r="H102" t="n">
         <v>16430587</v>
@@ -3414,7 +3414,7 @@
         <v>6.04397487640381</v>
       </c>
       <c r="G105" t="n">
-        <v>3.15827775001526</v>
+        <v>3.15827798843384</v>
       </c>
       <c r="H105" t="n">
         <v>8345509</v>
@@ -3443,7 +3443,7 @@
         <v>6.06287717819214</v>
       </c>
       <c r="G106" t="n">
-        <v>3.1681547164917</v>
+        <v>3.16815519332886</v>
       </c>
       <c r="H106" t="n">
         <v>17125303</v>
@@ -3559,7 +3559,7 @@
         <v>5.81714820861816</v>
       </c>
       <c r="G110" t="n">
-        <v>3.03974962234497</v>
+        <v>3.03974914550781</v>
       </c>
       <c r="H110" t="n">
         <v>12333558</v>
@@ -3588,7 +3588,7 @@
         <v>6.06287717819214</v>
       </c>
       <c r="G111" t="n">
-        <v>3.1681547164917</v>
+        <v>3.16815519332886</v>
       </c>
       <c r="H111" t="n">
         <v>15403740</v>
@@ -3617,7 +3617,7 @@
         <v>6.02507209777832</v>
       </c>
       <c r="G112" t="n">
-        <v>3.14840006828308</v>
+        <v>3.1483998298645</v>
       </c>
       <c r="H112" t="n">
         <v>23618338</v>
@@ -3646,7 +3646,7 @@
         <v>5.97309112548828</v>
       </c>
       <c r="G113" t="n">
-        <v>3.12123703956604</v>
+        <v>3.1212375164032</v>
       </c>
       <c r="H113" t="n">
         <v>12213718</v>
@@ -3675,7 +3675,7 @@
         <v>5.76989316940308</v>
       </c>
       <c r="G114" t="n">
-        <v>3.01505613327026</v>
+        <v>3.01505637168884</v>
       </c>
       <c r="H114" t="n">
         <v>16255019</v>
@@ -3704,7 +3704,7 @@
         <v>5.60922384262085</v>
       </c>
       <c r="G115" t="n">
-        <v>2.9310986995697</v>
+        <v>2.93109846115112</v>
       </c>
       <c r="H115" t="n">
         <v>20043519</v>
@@ -3733,7 +3733,7 @@
         <v>5.50526189804077</v>
       </c>
       <c r="G116" t="n">
-        <v>2.87677311897278</v>
+        <v>2.87677335739136</v>
       </c>
       <c r="H116" t="n">
         <v>16882703</v>
@@ -3762,7 +3762,7 @@
         <v>5.54306697845459</v>
       </c>
       <c r="G117" t="n">
-        <v>2.89652848243713</v>
+        <v>2.89652872085571</v>
       </c>
       <c r="H117" t="n">
         <v>15787045</v>
@@ -3791,7 +3791,7 @@
         <v>5.47690916061401</v>
       </c>
       <c r="G118" t="n">
-        <v>2.86195778846741</v>
+        <v>2.86195755004883</v>
       </c>
       <c r="H118" t="n">
         <v>21847770</v>
@@ -3820,7 +3820,7 @@
         <v>5.6139497756958</v>
       </c>
       <c r="G119" t="n">
-        <v>2.93356776237488</v>
+        <v>2.93356800079346</v>
       </c>
       <c r="H119" t="n">
         <v>21282200</v>
@@ -3878,7 +3878,7 @@
         <v>5.90693378448486</v>
       </c>
       <c r="G121" t="n">
-        <v>3.08666658401489</v>
+        <v>3.08666706085205</v>
       </c>
       <c r="H121" t="n">
         <v>14606198</v>
@@ -3936,7 +3936,7 @@
         <v>5.95418882369995</v>
       </c>
       <c r="G123" t="n">
-        <v>3.1113600730896</v>
+        <v>3.11136031150818</v>
       </c>
       <c r="H123" t="n">
         <v>19064312</v>
@@ -4023,7 +4023,7 @@
         <v>5.13667011260986</v>
       </c>
       <c r="G126" t="n">
-        <v>2.68416595458984</v>
+        <v>2.68416547775269</v>
       </c>
       <c r="H126" t="n">
         <v>19933472</v>
@@ -4052,7 +4052,7 @@
         <v>5.09414005279541</v>
       </c>
       <c r="G127" t="n">
-        <v>2.66194224357605</v>
+        <v>2.66194200515747</v>
       </c>
       <c r="H127" t="n">
         <v>21487196</v>
@@ -4110,7 +4110,7 @@
         <v>5.30206394195557</v>
       </c>
       <c r="G129" t="n">
-        <v>2.77059197425842</v>
+        <v>2.77059245109558</v>
       </c>
       <c r="H129" t="n">
         <v>22681420</v>
@@ -4168,7 +4168,7 @@
         <v>4.84841108322144</v>
       </c>
       <c r="G131" t="n">
-        <v>2.533536195755</v>
+        <v>2.53353643417358</v>
       </c>
       <c r="H131" t="n">
         <v>18483988</v>
@@ -4226,7 +4226,7 @@
         <v>4.87676382064819</v>
       </c>
       <c r="G133" t="n">
-        <v>2.54835176467896</v>
+        <v>2.54835152626038</v>
       </c>
       <c r="H133" t="n">
         <v>19621989</v>
@@ -4255,7 +4255,7 @@
         <v>5.23118114471436</v>
       </c>
       <c r="G134" t="n">
-        <v>2.7335524559021</v>
+        <v>2.73355269432068</v>
       </c>
       <c r="H134" t="n">
         <v>20083823</v>
@@ -4284,7 +4284,7 @@
         <v>5.4485559463501</v>
       </c>
       <c r="G135" t="n">
-        <v>2.8471417427063</v>
+        <v>2.84714150428772</v>
       </c>
       <c r="H135" t="n">
         <v>25144301</v>
@@ -4313,7 +4313,7 @@
         <v>5.67065620422363</v>
       </c>
       <c r="G136" t="n">
-        <v>2.96319961547852</v>
+        <v>2.96320009231567</v>
       </c>
       <c r="H136" t="n">
         <v>25011102</v>
@@ -4371,7 +4371,7 @@
         <v>5.73681402206421</v>
       </c>
       <c r="G138" t="n">
-        <v>2.9977707862854</v>
+        <v>2.99777102470398</v>
       </c>
       <c r="H138" t="n">
         <v>16879400</v>
@@ -4400,7 +4400,7 @@
         <v>5.74626493453979</v>
       </c>
       <c r="G139" t="n">
-        <v>3.00270986557007</v>
+        <v>3.00270962715149</v>
       </c>
       <c r="H139" t="n">
         <v>16004327</v>
@@ -4429,7 +4429,7 @@
         <v>5.85967779159546</v>
       </c>
       <c r="G140" t="n">
-        <v>3.06197309494019</v>
+        <v>3.06197333335876</v>
       </c>
       <c r="H140" t="n">
         <v>16667375</v>
@@ -4458,7 +4458,7 @@
         <v>5.66120481491089</v>
       </c>
       <c r="G141" t="n">
-        <v>2.95826148986816</v>
+        <v>2.95826125144958</v>
       </c>
       <c r="H141" t="n">
         <v>23600766</v>
@@ -4487,7 +4487,7 @@
         <v>5.88803195953369</v>
       </c>
       <c r="G142" t="n">
-        <v>3.07679009437561</v>
+        <v>3.07678985595703</v>
       </c>
       <c r="H142" t="n">
         <v>24263741</v>
@@ -4516,7 +4516,7 @@
         <v>5.94946384429932</v>
       </c>
       <c r="G143" t="n">
-        <v>3.108891248703</v>
+        <v>3.10889077186584</v>
       </c>
       <c r="H143" t="n">
         <v>23453575</v>
@@ -4574,7 +4574,7 @@
         <v>5.93056201934814</v>
       </c>
       <c r="G145" t="n">
-        <v>3.09901404380798</v>
+        <v>3.0990138053894</v>
       </c>
       <c r="H145" t="n">
         <v>15845076</v>
@@ -4632,7 +4632,7 @@
         <v>5.8691291809082</v>
       </c>
       <c r="G147" t="n">
-        <v>3.06691217422485</v>
+        <v>3.06691265106201</v>
       </c>
       <c r="H147" t="n">
         <v>47571097</v>
@@ -4690,7 +4690,7 @@
         <v>5.44383001327515</v>
       </c>
       <c r="G149" t="n">
-        <v>2.84467196464539</v>
+        <v>2.84467220306396</v>
       </c>
       <c r="H149" t="n">
         <v>19085528</v>
@@ -4719,7 +4719,7 @@
         <v>5.38239812850952</v>
       </c>
       <c r="G150" t="n">
-        <v>2.81257081031799</v>
+        <v>2.81257104873657</v>
       </c>
       <c r="H150" t="n">
         <v>12894185</v>
@@ -4777,7 +4777,7 @@
         <v>5.57614517211914</v>
       </c>
       <c r="G152" t="n">
-        <v>2.913813829422</v>
+        <v>2.91381359100342</v>
       </c>
       <c r="H152" t="n">
         <v>50108190</v>
@@ -4806,7 +4806,7 @@
         <v>5.5241641998291</v>
       </c>
       <c r="G153" t="n">
-        <v>2.88665103912354</v>
+        <v>2.88665080070496</v>
       </c>
       <c r="H153" t="n">
         <v>15664650</v>
@@ -4835,7 +4835,7 @@
         <v>5.75099086761475</v>
       </c>
       <c r="G154" t="n">
-        <v>3.00517916679382</v>
+        <v>3.00517892837524</v>
       </c>
       <c r="H154" t="n">
         <v>18235708</v>
@@ -4864,7 +4864,7 @@
         <v>5.75099086761475</v>
       </c>
       <c r="G155" t="n">
-        <v>3.00517916679382</v>
+        <v>3.00517892837524</v>
       </c>
       <c r="H155" t="n">
         <v>11793612</v>
@@ -4922,7 +4922,7 @@
         <v>5.85967779159546</v>
       </c>
       <c r="G157" t="n">
-        <v>3.06197309494019</v>
+        <v>3.06197333335876</v>
       </c>
       <c r="H157" t="n">
         <v>12745349</v>
@@ -4980,7 +4980,7 @@
         <v>5.81714820861816</v>
       </c>
       <c r="G159" t="n">
-        <v>3.03974962234497</v>
+        <v>3.03974914550781</v>
       </c>
       <c r="H159" t="n">
         <v>12630022</v>
@@ -5038,7 +5038,7 @@
         <v>5.665931224823</v>
       </c>
       <c r="G161" t="n">
-        <v>2.96073079109192</v>
+        <v>2.9607310295105</v>
       </c>
       <c r="H161" t="n">
         <v>14170437</v>
@@ -5067,7 +5067,7 @@
         <v>5.68955898284912</v>
       </c>
       <c r="G162" t="n">
-        <v>2.97307753562927</v>
+        <v>2.97307777404785</v>
       </c>
       <c r="H162" t="n">
         <v>9614265</v>
@@ -5096,7 +5096,7 @@
         <v>5.51943922042847</v>
       </c>
       <c r="G163" t="n">
-        <v>2.8841814994812</v>
+        <v>2.88418197631836</v>
       </c>
       <c r="H163" t="n">
         <v>12750149</v>
@@ -5183,7 +5183,7 @@
         <v>5.80769681930542</v>
       </c>
       <c r="G166" t="n">
-        <v>3.03481078147888</v>
+        <v>3.0348105430603</v>
       </c>
       <c r="H166" t="n">
         <v>13516735</v>
@@ -5212,7 +5212,7 @@
         <v>5.79824590682983</v>
       </c>
       <c r="G167" t="n">
-        <v>3.02987194061279</v>
+        <v>3.02987217903137</v>
       </c>
       <c r="H167" t="n">
         <v>17869525</v>
@@ -5241,7 +5241,7 @@
         <v>5.82659912109375</v>
       </c>
       <c r="G168" t="n">
-        <v>3.04468774795532</v>
+        <v>3.0446879863739</v>
       </c>
       <c r="H168" t="n">
         <v>9059933</v>
@@ -5270,7 +5270,7 @@
         <v>5.72736310958862</v>
       </c>
       <c r="G169" t="n">
-        <v>2.99283242225647</v>
+        <v>2.99283218383789</v>
       </c>
       <c r="H169" t="n">
         <v>10095115</v>
@@ -5299,7 +5299,7 @@
         <v>5.8691291809082</v>
       </c>
       <c r="G170" t="n">
-        <v>3.06691217422485</v>
+        <v>3.06691265106201</v>
       </c>
       <c r="H170" t="n">
         <v>11859192</v>
@@ -5328,7 +5328,7 @@
         <v>5.85495281219482</v>
       </c>
       <c r="G171" t="n">
-        <v>3.05950427055359</v>
+        <v>3.05950450897217</v>
       </c>
       <c r="H171" t="n">
         <v>13659997</v>
@@ -5357,7 +5357,7 @@
         <v>5.69428396224976</v>
       </c>
       <c r="G172" t="n">
-        <v>2.97554707527161</v>
+        <v>2.97554683685303</v>
       </c>
       <c r="H172" t="n">
         <v>28828993</v>
@@ -5386,7 +5386,7 @@
         <v>5.6517539024353</v>
       </c>
       <c r="G173" t="n">
-        <v>2.9533224105835</v>
+        <v>2.95332312583923</v>
       </c>
       <c r="H173" t="n">
         <v>29895335</v>
@@ -5473,7 +5473,7 @@
         <v>5.81714820861816</v>
       </c>
       <c r="G176" t="n">
-        <v>3.03974962234497</v>
+        <v>3.03974914550781</v>
       </c>
       <c r="H176" t="n">
         <v>15431752</v>
@@ -5502,7 +5502,7 @@
         <v>5.74626493453979</v>
       </c>
       <c r="G177" t="n">
-        <v>3.00270986557007</v>
+        <v>3.00270962715149</v>
       </c>
       <c r="H177" t="n">
         <v>25223271</v>
@@ -5531,7 +5531,7 @@
         <v>5.69428396224976</v>
       </c>
       <c r="G178" t="n">
-        <v>2.97554707527161</v>
+        <v>2.97554683685303</v>
       </c>
       <c r="H178" t="n">
         <v>10454962</v>
@@ -5589,7 +5589,7 @@
         <v>5.48163509368896</v>
       </c>
       <c r="G180" t="n">
-        <v>2.86442708969116</v>
+        <v>2.86442732810974</v>
       </c>
       <c r="H180" t="n">
         <v>12157462</v>
@@ -5647,7 +5647,7 @@
         <v>5.50053691864014</v>
       </c>
       <c r="G182" t="n">
-        <v>2.87430429458618</v>
+        <v>2.8743040561676</v>
       </c>
       <c r="H182" t="n">
         <v>15886777</v>
@@ -5676,7 +5676,7 @@
         <v>5.38712406158447</v>
       </c>
       <c r="G183" t="n">
-        <v>2.81504058837891</v>
+        <v>2.81504034996033</v>
       </c>
       <c r="H183" t="n">
         <v>19776409</v>
@@ -5705,7 +5705,7 @@
         <v>5.55251789093018</v>
       </c>
       <c r="G184" t="n">
-        <v>2.90146732330322</v>
+        <v>2.90146684646606</v>
       </c>
       <c r="H184" t="n">
         <v>13153922</v>
@@ -5734,7 +5734,7 @@
         <v>5.42020177841187</v>
       </c>
       <c r="G185" t="n">
-        <v>2.83232545852661</v>
+        <v>2.83232522010803</v>
       </c>
       <c r="H185" t="n">
         <v>9097857</v>
@@ -5763,7 +5763,7 @@
         <v>5.37767219543457</v>
       </c>
       <c r="G186" t="n">
-        <v>2.81010150909424</v>
+        <v>2.81010127067566</v>
       </c>
       <c r="H186" t="n">
         <v>12947255</v>
@@ -5792,7 +5792,7 @@
         <v>5.4863600730896</v>
       </c>
       <c r="G187" t="n">
-        <v>2.86689639091492</v>
+        <v>2.86689615249634</v>
       </c>
       <c r="H187" t="n">
         <v>11549870</v>
@@ -5821,7 +5821,7 @@
         <v>5.44383001327515</v>
       </c>
       <c r="G188" t="n">
-        <v>2.84467196464539</v>
+        <v>2.84467220306396</v>
       </c>
       <c r="H188" t="n">
         <v>8909677</v>
@@ -5850,7 +5850,7 @@
         <v>5.24535703659058</v>
       </c>
       <c r="G189" t="n">
-        <v>2.74096012115479</v>
+        <v>2.74096035957336</v>
       </c>
       <c r="H189" t="n">
         <v>12874770</v>
@@ -5879,7 +5879,7 @@
         <v>5.13667011260986</v>
       </c>
       <c r="G190" t="n">
-        <v>2.68416595458984</v>
+        <v>2.68416547775269</v>
       </c>
       <c r="H190" t="n">
         <v>17739843</v>
@@ -5908,7 +5908,7 @@
         <v>5.18392515182495</v>
       </c>
       <c r="G191" t="n">
-        <v>2.70885896682739</v>
+        <v>2.70885920524597</v>
       </c>
       <c r="H191" t="n">
         <v>10693015</v>
@@ -5937,7 +5937,7 @@
         <v>5.24535703659058</v>
       </c>
       <c r="G192" t="n">
-        <v>2.74096012115479</v>
+        <v>2.74096035957336</v>
       </c>
       <c r="H192" t="n">
         <v>9582580</v>
@@ -5995,7 +5995,7 @@
         <v>5.40602588653564</v>
       </c>
       <c r="G194" t="n">
-        <v>2.82491779327393</v>
+        <v>2.82491755485535</v>
       </c>
       <c r="H194" t="n">
         <v>13383472</v>
@@ -6024,7 +6024,7 @@
         <v>5.43910503387451</v>
       </c>
       <c r="G195" t="n">
-        <v>2.84220337867737</v>
+        <v>2.84220314025879</v>
       </c>
       <c r="H195" t="n">
         <v>12381882</v>
@@ -6082,7 +6082,7 @@
         <v>5.49581098556519</v>
       </c>
       <c r="G197" t="n">
-        <v>2.87183451652527</v>
+        <v>2.87183499336243</v>
       </c>
       <c r="H197" t="n">
         <v>18838399</v>
@@ -6111,7 +6111,7 @@
         <v>5.4863600730896</v>
       </c>
       <c r="G198" t="n">
-        <v>2.86689639091492</v>
+        <v>2.86689615249634</v>
       </c>
       <c r="H198" t="n">
         <v>13540215</v>
@@ -6169,7 +6169,7 @@
         <v>5.5666937828064</v>
       </c>
       <c r="G200" t="n">
-        <v>2.90887475013733</v>
+        <v>2.90887427330017</v>
       </c>
       <c r="H200" t="n">
         <v>14397429</v>
@@ -6198,7 +6198,7 @@
         <v>5.4863600730896</v>
       </c>
       <c r="G201" t="n">
-        <v>2.86689639091492</v>
+        <v>2.86689615249634</v>
       </c>
       <c r="H201" t="n">
         <v>17084891</v>
@@ -6227,7 +6227,7 @@
         <v>5.29733800888062</v>
       </c>
       <c r="G202" t="n">
-        <v>2.76812267303467</v>
+        <v>2.76812291145325</v>
       </c>
       <c r="H202" t="n">
         <v>19611636</v>
@@ -6256,7 +6256,7 @@
         <v>5.42020177841187</v>
       </c>
       <c r="G203" t="n">
-        <v>2.83232545852661</v>
+        <v>2.83232522010803</v>
       </c>
       <c r="H203" t="n">
         <v>13593525</v>
@@ -6285,7 +6285,7 @@
         <v>5.43437910079956</v>
       </c>
       <c r="G204" t="n">
-        <v>2.83973336219788</v>
+        <v>2.83973383903503</v>
       </c>
       <c r="H204" t="n">
         <v>8767271</v>
@@ -6314,7 +6314,7 @@
         <v>5.40129995346069</v>
       </c>
       <c r="G205" t="n">
-        <v>2.82244849205017</v>
+        <v>2.82244801521301</v>
       </c>
       <c r="H205" t="n">
         <v>17189235</v>
@@ -6343,7 +6343,7 @@
         <v>5.43910503387451</v>
       </c>
       <c r="G206" t="n">
-        <v>2.84220337867737</v>
+        <v>2.84220314025879</v>
       </c>
       <c r="H206" t="n">
         <v>12130990</v>
@@ -6372,7 +6372,7 @@
         <v>5.47218322753906</v>
       </c>
       <c r="G207" t="n">
-        <v>2.85948824882507</v>
+        <v>2.85948777198792</v>
       </c>
       <c r="H207" t="n">
         <v>13055073</v>
@@ -6401,7 +6401,7 @@
         <v>5.47690916061401</v>
       </c>
       <c r="G208" t="n">
-        <v>2.86195778846741</v>
+        <v>2.86195755004883</v>
       </c>
       <c r="H208" t="n">
         <v>13595747</v>
@@ -6459,7 +6459,7 @@
         <v>5.62340116500854</v>
       </c>
       <c r="G210" t="n">
-        <v>2.93850660324097</v>
+        <v>2.93850708007812</v>
       </c>
       <c r="H210" t="n">
         <v>41594087</v>
@@ -6488,7 +6488,7 @@
         <v>5.8691291809082</v>
       </c>
       <c r="G211" t="n">
-        <v>3.06691217422485</v>
+        <v>3.06691265106201</v>
       </c>
       <c r="H211" t="n">
         <v>27688969</v>
@@ -6517,7 +6517,7 @@
         <v>6.22354507446289</v>
       </c>
       <c r="G212" t="n">
-        <v>3.25211191177368</v>
+        <v>3.25211215019226</v>
       </c>
       <c r="H212" t="n">
         <v>40077812</v>
@@ -6546,7 +6546,7 @@
         <v>6.23299694061279</v>
       </c>
       <c r="G213" t="n">
-        <v>3.25705170631409</v>
+        <v>3.25705099105835</v>
       </c>
       <c r="H213" t="n">
         <v>30876599</v>
@@ -6575,7 +6575,7 @@
         <v>6.30388021469116</v>
       </c>
       <c r="G214" t="n">
-        <v>3.29409146308899</v>
+        <v>3.29409098625183</v>
       </c>
       <c r="H214" t="n">
         <v>17239031</v>
@@ -6604,7 +6604,7 @@
         <v>6.23772192001343</v>
       </c>
       <c r="G215" t="n">
-        <v>3.2595202922821</v>
+        <v>3.25952053070068</v>
       </c>
       <c r="H215" t="n">
         <v>20237904</v>
@@ -6662,7 +6662,7 @@
         <v>5.80297183990479</v>
       </c>
       <c r="G217" t="n">
-        <v>3.03234171867371</v>
+        <v>3.03234195709229</v>
       </c>
       <c r="H217" t="n">
         <v>16057076</v>
@@ -6691,7 +6691,7 @@
         <v>5.7935209274292</v>
       </c>
       <c r="G218" t="n">
-        <v>3.02740335464478</v>
+        <v>3.02740287780762</v>
       </c>
       <c r="H218" t="n">
         <v>16831369</v>
@@ -6720,7 +6720,7 @@
         <v>6.09595584869385</v>
       </c>
       <c r="G219" t="n">
-        <v>3.18544006347656</v>
+        <v>3.18544030189514</v>
       </c>
       <c r="H219" t="n">
         <v>19809812</v>
@@ -6749,7 +6749,7 @@
         <v>6.05815076828003</v>
       </c>
       <c r="G220" t="n">
-        <v>3.16568517684937</v>
+        <v>3.16568565368652</v>
       </c>
       <c r="H220" t="n">
         <v>17046712</v>
@@ -6807,7 +6807,7 @@
         <v>6.38421392440796</v>
       </c>
       <c r="G222" t="n">
-        <v>3.33607006072998</v>
+        <v>3.33606934547424</v>
       </c>
       <c r="H222" t="n">
         <v>44570219</v>
@@ -6836,7 +6836,7 @@
         <v>6.74335622787476</v>
       </c>
       <c r="G223" t="n">
-        <v>3.5237398147583</v>
+        <v>3.52373933792114</v>
       </c>
       <c r="H223" t="n">
         <v>52480266</v>
@@ -6865,7 +6865,7 @@
         <v>6.55433416366577</v>
       </c>
       <c r="G224" t="n">
-        <v>3.42496609687805</v>
+        <v>3.42496585845947</v>
       </c>
       <c r="H224" t="n">
         <v>33513544</v>
@@ -6981,7 +6981,7 @@
         <v>6.65829610824585</v>
       </c>
       <c r="G228" t="n">
-        <v>3.47929096221924</v>
+        <v>3.47929120063782</v>
       </c>
       <c r="H228" t="n">
         <v>17400533</v>
@@ -7010,7 +7010,7 @@
         <v>6.68664884567261</v>
       </c>
       <c r="G229" t="n">
-        <v>3.49410653114319</v>
+        <v>3.49410676956177</v>
       </c>
       <c r="H229" t="n">
         <v>15927440</v>
@@ -7097,7 +7097,7 @@
         <v>6.92292594909668</v>
       </c>
       <c r="G232" t="n">
-        <v>3.61757326126099</v>
+        <v>3.61757349967957</v>
       </c>
       <c r="H232" t="n">
         <v>18450637</v>
@@ -7126,7 +7126,7 @@
         <v>6.86149406433105</v>
       </c>
       <c r="G233" t="n">
-        <v>3.58547210693359</v>
+        <v>3.58547258377075</v>
       </c>
       <c r="H233" t="n">
         <v>8648665</v>
@@ -7155,7 +7155,7 @@
         <v>6.83314085006714</v>
       </c>
       <c r="G234" t="n">
-        <v>3.57065629959106</v>
+        <v>3.57065606117249</v>
       </c>
       <c r="H234" t="n">
         <v>29540193</v>
@@ -7184,7 +7184,7 @@
         <v>6.81423902511597</v>
       </c>
       <c r="G235" t="n">
-        <v>3.5607795715332</v>
+        <v>3.56077885627747</v>
       </c>
       <c r="H235" t="n">
         <v>18580024</v>
@@ -7213,7 +7213,7 @@
         <v>6.88984823226929</v>
       </c>
       <c r="G236" t="n">
-        <v>3.60028910636902</v>
+        <v>3.60028862953186</v>
       </c>
       <c r="H236" t="n">
         <v>18859938</v>
@@ -7242,7 +7242,7 @@
         <v>6.93237781524658</v>
       </c>
       <c r="G237" t="n">
-        <v>3.62251234054565</v>
+        <v>3.62251257896423</v>
       </c>
       <c r="H237" t="n">
         <v>25160124</v>
@@ -7271,7 +7271,7 @@
         <v>6.80951309204102</v>
       </c>
       <c r="G238" t="n">
-        <v>3.55830931663513</v>
+        <v>3.55830955505371</v>
       </c>
       <c r="H238" t="n">
         <v>21362521</v>
@@ -7300,7 +7300,7 @@
         <v>7.12139892578125</v>
       </c>
       <c r="G239" t="n">
-        <v>3.72128510475159</v>
+        <v>3.72128534317017</v>
       </c>
       <c r="H239" t="n">
         <v>37981867</v>
@@ -7329,7 +7329,7 @@
         <v>7.29624509811401</v>
       </c>
       <c r="G240" t="n">
-        <v>3.81265139579773</v>
+        <v>3.81265163421631</v>
       </c>
       <c r="H240" t="n">
         <v>29477831</v>
@@ -7358,7 +7358,7 @@
         <v>7.38130521774292</v>
       </c>
       <c r="G241" t="n">
-        <v>3.85709953308105</v>
+        <v>3.85709977149963</v>
       </c>
       <c r="H241" t="n">
         <v>22963791</v>
@@ -7387,7 +7387,7 @@
         <v>7.52779722213745</v>
       </c>
       <c r="G242" t="n">
-        <v>3.93364858627319</v>
+        <v>3.93364906311035</v>
       </c>
       <c r="H242" t="n">
         <v>32960510</v>
@@ -7416,7 +7416,7 @@
         <v>7.52307081222534</v>
       </c>
       <c r="G243" t="n">
-        <v>3.93117904663086</v>
+        <v>3.93117928504944</v>
       </c>
       <c r="H243" t="n">
         <v>23930374</v>
@@ -7445,7 +7445,7 @@
         <v>7.6034049987793</v>
       </c>
       <c r="G244" t="n">
-        <v>3.97315764427185</v>
+        <v>3.97315788269043</v>
       </c>
       <c r="H244" t="n">
         <v>27934866</v>
@@ -7474,7 +7474,7 @@
         <v>7.66483688354492</v>
       </c>
       <c r="G245" t="n">
-        <v>4.00525903701782</v>
+        <v>4.00525856018066</v>
       </c>
       <c r="H245" t="n">
         <v>20624551</v>
@@ -7532,7 +7532,7 @@
         <v>7.9483699798584</v>
       </c>
       <c r="G247" t="n">
-        <v>4.15341949462891</v>
+        <v>4.15341901779175</v>
       </c>
       <c r="H247" t="n">
         <v>23716521</v>
@@ -7561,7 +7561,7 @@
         <v>8.02870464324951</v>
       </c>
       <c r="G248" t="n">
-        <v>4.19539785385132</v>
+        <v>4.19539737701416</v>
       </c>
       <c r="H248" t="n">
         <v>29373279</v>
@@ -7619,7 +7619,7 @@
         <v>8.22245216369629</v>
       </c>
       <c r="G250" t="n">
-        <v>4.29664087295532</v>
+        <v>4.29664039611816</v>
       </c>
       <c r="H250" t="n">
         <v>20386114</v>
@@ -7648,7 +7648,7 @@
         <v>8.24135398864746</v>
       </c>
       <c r="G251" t="n">
-        <v>4.30651807785034</v>
+        <v>4.30651760101318</v>
       </c>
       <c r="H251" t="n">
         <v>13417510</v>
@@ -7677,7 +7677,7 @@
         <v>7.99090003967285</v>
       </c>
       <c r="G252" t="n">
-        <v>4.17564296722412</v>
+        <v>4.17564344406128</v>
       </c>
       <c r="H252" t="n">
         <v>19882785</v>
@@ -7735,7 +7735,7 @@
         <v>8.25553131103516</v>
       </c>
       <c r="G254" t="n">
-        <v>4.31392574310303</v>
+        <v>4.31392669677734</v>
       </c>
       <c r="H254" t="n">
         <v>8367756</v>
@@ -7851,7 +7851,7 @@
         <v>8.46345520019531</v>
       </c>
       <c r="G258" t="n">
-        <v>4.42257690429688</v>
+        <v>4.42257642745972</v>
       </c>
       <c r="H258" t="n">
         <v>12638696</v>
@@ -7880,7 +7880,7 @@
         <v>8.62412357330322</v>
       </c>
       <c r="G259" t="n">
-        <v>4.5065336227417</v>
+        <v>4.50653409957886</v>
       </c>
       <c r="H259" t="n">
         <v>33051782</v>
@@ -7967,7 +7967,7 @@
         <v>9.35658264160156</v>
       </c>
       <c r="G262" t="n">
-        <v>4.88928127288818</v>
+        <v>4.88927984237671</v>
       </c>
       <c r="H262" t="n">
         <v>42428855</v>
@@ -7996,7 +7996,7 @@
         <v>9.48889923095703</v>
       </c>
       <c r="G263" t="n">
-        <v>4.95842218399048</v>
+        <v>4.95842266082764</v>
       </c>
       <c r="H263" t="n">
         <v>45326336</v>
@@ -8025,7 +8025,7 @@
         <v>9.59286117553711</v>
       </c>
       <c r="G264" t="n">
-        <v>5.01274728775024</v>
+        <v>5.0127477645874</v>
       </c>
       <c r="H264" t="n">
         <v>26411820</v>
@@ -8083,7 +8083,7 @@
         <v>8.29806137084961</v>
       </c>
       <c r="G266" t="n">
-        <v>4.3361496925354</v>
+        <v>4.33615016937256</v>
       </c>
       <c r="H266" t="n">
         <v>78378600</v>
@@ -8141,7 +8141,7 @@
         <v>8.31696319580078</v>
       </c>
       <c r="G268" t="n">
-        <v>4.34602689743042</v>
+        <v>4.34602785110474</v>
       </c>
       <c r="H268" t="n">
         <v>36341964</v>
@@ -8228,7 +8228,7 @@
         <v>8.85567474365234</v>
       </c>
       <c r="G271" t="n">
-        <v>4.62753057479858</v>
+        <v>4.62753105163574</v>
       </c>
       <c r="H271" t="n">
         <v>28701758</v>
@@ -8257,7 +8257,7 @@
         <v>8.88402938842773</v>
       </c>
       <c r="G272" t="n">
-        <v>4.64234733581543</v>
+        <v>4.64234781265259</v>
       </c>
       <c r="H272" t="n">
         <v>23917461</v>
@@ -8286,7 +8286,7 @@
         <v>9.03052139282227</v>
       </c>
       <c r="G273" t="n">
-        <v>4.71889638900757</v>
+        <v>4.71889734268188</v>
       </c>
       <c r="H273" t="n">
         <v>21788140</v>
@@ -8402,7 +8402,7 @@
         <v>9.81023597717285</v>
       </c>
       <c r="G277" t="n">
-        <v>5.12633657455444</v>
+        <v>5.1263370513916</v>
       </c>
       <c r="H277" t="n">
         <v>18693528</v>
@@ -8431,7 +8431,7 @@
         <v>9.47944831848145</v>
       </c>
       <c r="G278" t="n">
-        <v>4.95348358154297</v>
+        <v>4.95348405838013</v>
       </c>
       <c r="H278" t="n">
         <v>16906258</v>
@@ -8460,7 +8460,7 @@
         <v>9.54560470581055</v>
       </c>
       <c r="G279" t="n">
-        <v>4.9880542755127</v>
+        <v>4.98805332183838</v>
       </c>
       <c r="H279" t="n">
         <v>21017641</v>
@@ -8605,7 +8605,7 @@
         <v>9.14865875244141</v>
       </c>
       <c r="G284" t="n">
-        <v>4.78062963485718</v>
+        <v>4.78063011169434</v>
       </c>
       <c r="H284" t="n">
         <v>26981116</v>
@@ -8634,7 +8634,7 @@
         <v>9.37548637390137</v>
       </c>
       <c r="G285" t="n">
-        <v>4.8991584777832</v>
+        <v>4.89915895462036</v>
       </c>
       <c r="H285" t="n">
         <v>21847157</v>
@@ -8692,7 +8692,7 @@
         <v>9.59286117553711</v>
       </c>
       <c r="G287" t="n">
-        <v>5.01274728775024</v>
+        <v>5.0127477645874</v>
       </c>
       <c r="H287" t="n">
         <v>14648782</v>
@@ -8721,7 +8721,7 @@
         <v>9.81023597717285</v>
       </c>
       <c r="G288" t="n">
-        <v>5.12633657455444</v>
+        <v>5.1263370513916</v>
       </c>
       <c r="H288" t="n">
         <v>14340532</v>
@@ -8750,7 +8750,7 @@
         <v>10.2166328430176</v>
       </c>
       <c r="G289" t="n">
-        <v>5.33869886398315</v>
+        <v>5.33869934082031</v>
       </c>
       <c r="H289" t="n">
         <v>33645256</v>
@@ -8808,7 +8808,7 @@
         <v>10.1882801055908</v>
       </c>
       <c r="G291" t="n">
-        <v>5.3238844871521</v>
+        <v>5.32388401031494</v>
       </c>
       <c r="H291" t="n">
         <v>12528118</v>
@@ -8837,7 +8837,7 @@
         <v>10.0559644699097</v>
       </c>
       <c r="G292" t="n">
-        <v>5.25474166870117</v>
+        <v>5.25474214553833</v>
       </c>
       <c r="H292" t="n">
         <v>13579641</v>
@@ -8895,7 +8895,7 @@
         <v>10.2166328430176</v>
       </c>
       <c r="G294" t="n">
-        <v>5.33869886398315</v>
+        <v>5.33869934082031</v>
       </c>
       <c r="H294" t="n">
         <v>10806146</v>
@@ -8924,7 +8924,7 @@
         <v>10.1882801055908</v>
       </c>
       <c r="G295" t="n">
-        <v>5.3238844871521</v>
+        <v>5.32388401031494</v>
       </c>
       <c r="H295" t="n">
         <v>11623707</v>
@@ -8953,7 +8953,7 @@
         <v>9.90474700927734</v>
       </c>
       <c r="G296" t="n">
-        <v>5.1757230758667</v>
+        <v>5.17572355270386</v>
       </c>
       <c r="H296" t="n">
         <v>18015198</v>
@@ -8982,7 +8982,7 @@
         <v>9.59286117553711</v>
       </c>
       <c r="G297" t="n">
-        <v>5.01274728775024</v>
+        <v>5.0127477645874</v>
       </c>
       <c r="H297" t="n">
         <v>21475304</v>
@@ -9069,7 +9069,7 @@
         <v>9.92364883422852</v>
       </c>
       <c r="G300" t="n">
-        <v>5.18559980392456</v>
+        <v>5.18560028076172</v>
       </c>
       <c r="H300" t="n">
         <v>16834662</v>
@@ -9098,7 +9098,7 @@
         <v>9.92364883422852</v>
       </c>
       <c r="G301" t="n">
-        <v>5.18559980392456</v>
+        <v>5.18560028076172</v>
       </c>
       <c r="H301" t="n">
         <v>9610216</v>
@@ -9127,7 +9127,7 @@
         <v>9.91419792175293</v>
       </c>
       <c r="G302" t="n">
-        <v>5.18066120147705</v>
+        <v>5.18066215515137</v>
       </c>
       <c r="H302" t="n">
         <v>12321680</v>
@@ -9156,7 +9156,7 @@
         <v>9.81968688964844</v>
       </c>
       <c r="G303" t="n">
-        <v>5.13127565383911</v>
+        <v>5.13127470016479</v>
       </c>
       <c r="H303" t="n">
         <v>12046516</v>
@@ -9185,7 +9185,7 @@
         <v>9.82913780212402</v>
       </c>
       <c r="G304" t="n">
-        <v>5.1362133026123</v>
+        <v>5.13621377944946</v>
       </c>
       <c r="H304" t="n">
         <v>10303430</v>
@@ -9243,7 +9243,7 @@
         <v>9.7535285949707</v>
       </c>
       <c r="G306" t="n">
-        <v>5.09670448303223</v>
+        <v>5.09670400619507</v>
       </c>
       <c r="H306" t="n">
         <v>15358386</v>
@@ -9301,7 +9301,7 @@
         <v>9.83858871459961</v>
       </c>
       <c r="G308" t="n">
-        <v>5.14115285873413</v>
+        <v>5.14115190505981</v>
       </c>
       <c r="H308" t="n">
         <v>13084990</v>
@@ -9330,7 +9330,7 @@
         <v>9.81023597717285</v>
       </c>
       <c r="G309" t="n">
-        <v>5.12633657455444</v>
+        <v>5.1263370513916</v>
       </c>
       <c r="H309" t="n">
         <v>27325083</v>
@@ -9359,7 +9359,7 @@
         <v>9.99925804138184</v>
       </c>
       <c r="G310" t="n">
-        <v>5.22511005401611</v>
+        <v>5.22511053085327</v>
       </c>
       <c r="H310" t="n">
         <v>14960335</v>
@@ -9388,7 +9388,7 @@
         <v>10.1882801055908</v>
       </c>
       <c r="G311" t="n">
-        <v>5.3238844871521</v>
+        <v>5.32388401031494</v>
       </c>
       <c r="H311" t="n">
         <v>16511332</v>
@@ -9446,7 +9446,7 @@
         <v>9.97090530395508</v>
       </c>
       <c r="G313" t="n">
-        <v>5.2102952003479</v>
+        <v>5.21029472351074</v>
       </c>
       <c r="H313" t="n">
         <v>8514700</v>
@@ -9475,7 +9475,7 @@
         <v>9.59286117553711</v>
       </c>
       <c r="G314" t="n">
-        <v>5.01274728775024</v>
+        <v>5.0127477645874</v>
       </c>
       <c r="H314" t="n">
         <v>22107792</v>
@@ -9504,7 +9504,7 @@
         <v>9.53615379333496</v>
       </c>
       <c r="G315" t="n">
-        <v>4.98311471939087</v>
+        <v>4.98311519622803</v>
       </c>
       <c r="H315" t="n">
         <v>27272382</v>
@@ -9591,7 +9591,7 @@
         <v>9.44164276123047</v>
       </c>
       <c r="G318" t="n">
-        <v>4.93372869491577</v>
+        <v>4.93372774124146</v>
       </c>
       <c r="H318" t="n">
         <v>15362502</v>
@@ -9620,7 +9620,7 @@
         <v>9.71572494506836</v>
       </c>
       <c r="G319" t="n">
-        <v>5.07694959640503</v>
+        <v>5.07695007324219</v>
       </c>
       <c r="H319" t="n">
         <v>12278352</v>
@@ -9678,7 +9678,7 @@
         <v>9.70627403259277</v>
       </c>
       <c r="G321" t="n">
-        <v>5.07201194763184</v>
+        <v>5.07201242446899</v>
       </c>
       <c r="H321" t="n">
         <v>8057059</v>
@@ -9765,7 +9765,7 @@
         <v>9.24789619445801</v>
       </c>
       <c r="G324" t="n">
-        <v>4.83248567581177</v>
+        <v>4.83248615264893</v>
       </c>
       <c r="H324" t="n">
         <v>20937458</v>
@@ -9794,7 +9794,7 @@
         <v>9.0777759552002</v>
       </c>
       <c r="G325" t="n">
-        <v>4.74358987808228</v>
+        <v>4.74359083175659</v>
       </c>
       <c r="H325" t="n">
         <v>19454758</v>
@@ -9852,7 +9852,7 @@
         <v>9.05887413024902</v>
       </c>
       <c r="G327" t="n">
-        <v>4.7337121963501</v>
+        <v>4.73371315002441</v>
       </c>
       <c r="H327" t="n">
         <v>14223880</v>
@@ -9881,7 +9881,7 @@
         <v>9.02579498291016</v>
       </c>
       <c r="G328" t="n">
-        <v>4.71642684936523</v>
+        <v>4.71642732620239</v>
       </c>
       <c r="H328" t="n">
         <v>11116251</v>
@@ -9939,7 +9939,7 @@
         <v>8.9832649230957</v>
       </c>
       <c r="G330" t="n">
-        <v>4.69420337677002</v>
+        <v>4.6942024230957</v>
       </c>
       <c r="H330" t="n">
         <v>13777629</v>
@@ -9968,7 +9968,7 @@
         <v>8.64775085449219</v>
       </c>
       <c r="G331" t="n">
-        <v>4.51888036727905</v>
+        <v>4.51888084411621</v>
       </c>
       <c r="H331" t="n">
         <v>22900023</v>
@@ -9997,7 +9997,7 @@
         <v>8.52016162872314</v>
       </c>
       <c r="G332" t="n">
-        <v>4.45220804214478</v>
+        <v>4.45220851898193</v>
       </c>
       <c r="H332" t="n">
         <v>18534807</v>
@@ -10142,7 +10142,7 @@
         <v>9.1628360748291</v>
       </c>
       <c r="G337" t="n">
-        <v>4.78803825378418</v>
+        <v>4.78803777694702</v>
       </c>
       <c r="H337" t="n">
         <v>10917033</v>
@@ -10171,7 +10171,7 @@
         <v>10.018159866333</v>
       </c>
       <c r="G338" t="n">
-        <v>5.23498725891113</v>
+        <v>5.23498678207397</v>
       </c>
       <c r="H338" t="n">
         <v>48963191</v>
@@ -10229,7 +10229,7 @@
         <v>9.81968688964844</v>
       </c>
       <c r="G340" t="n">
-        <v>5.13127565383911</v>
+        <v>5.13127470016479</v>
       </c>
       <c r="H340" t="n">
         <v>12015952</v>
@@ -10258,7 +10258,7 @@
         <v>9.4085636138916</v>
       </c>
       <c r="G341" t="n">
-        <v>4.91644239425659</v>
+        <v>4.91644287109375</v>
       </c>
       <c r="H341" t="n">
         <v>27114233</v>
@@ -10287,7 +10287,7 @@
         <v>9.51725196838379</v>
       </c>
       <c r="G342" t="n">
-        <v>4.97323799133301</v>
+        <v>4.97323846817017</v>
       </c>
       <c r="H342" t="n">
         <v>15505239</v>
@@ -10345,7 +10345,7 @@
         <v>9.71572494506836</v>
       </c>
       <c r="G344" t="n">
-        <v>5.07694959640503</v>
+        <v>5.07695007324219</v>
       </c>
       <c r="H344" t="n">
         <v>12506882</v>
@@ -10374,7 +10374,7 @@
         <v>9.64011573791504</v>
       </c>
       <c r="G345" t="n">
-        <v>5.03744077682495</v>
+        <v>5.03743982315063</v>
       </c>
       <c r="H345" t="n">
         <v>10657369</v>
@@ -10461,7 +10461,7 @@
         <v>9.41329002380371</v>
       </c>
       <c r="G348" t="n">
-        <v>4.91891288757324</v>
+        <v>4.91891241073608</v>
       </c>
       <c r="H348" t="n">
         <v>15385667</v>
@@ -10490,7 +10490,7 @@
         <v>9.46999740600586</v>
       </c>
       <c r="G349" t="n">
-        <v>4.94854497909546</v>
+        <v>4.9485445022583</v>
       </c>
       <c r="H349" t="n">
         <v>12969576</v>
@@ -10577,7 +10577,7 @@
         <v>9.12503242492676</v>
       </c>
       <c r="G352" t="n">
-        <v>4.76828336715698</v>
+        <v>4.76828384399414</v>
       </c>
       <c r="H352" t="n">
         <v>28594627</v>
@@ -10635,7 +10635,7 @@
         <v>9.18646430969238</v>
       </c>
       <c r="G354" t="n">
-        <v>4.80038452148438</v>
+        <v>4.80038499832153</v>
       </c>
       <c r="H354" t="n">
         <v>25071651</v>
@@ -10664,7 +10664,7 @@
         <v>9.03997230529785</v>
       </c>
       <c r="G355" t="n">
-        <v>4.72383546829224</v>
+        <v>4.72383594512939</v>
       </c>
       <c r="H355" t="n">
         <v>13245358</v>
@@ -10722,7 +10722,7 @@
         <v>8.92183303833008</v>
       </c>
       <c r="G357" t="n">
-        <v>4.66210174560547</v>
+        <v>4.66210222244263</v>
       </c>
       <c r="H357" t="n">
         <v>26021303</v>
@@ -10751,7 +10751,7 @@
         <v>8.88402938842773</v>
       </c>
       <c r="G358" t="n">
-        <v>4.64234733581543</v>
+        <v>4.64234781265259</v>
       </c>
       <c r="H358" t="n">
         <v>13153983</v>
@@ -10780,7 +10780,7 @@
         <v>8.94073486328125</v>
       </c>
       <c r="G359" t="n">
-        <v>4.67197942733765</v>
+        <v>4.67197895050049</v>
       </c>
       <c r="H359" t="n">
         <v>11344630</v>
@@ -10838,7 +10838,7 @@
         <v>8.77061557769775</v>
       </c>
       <c r="G361" t="n">
-        <v>4.583083152771</v>
+        <v>4.58308267593384</v>
       </c>
       <c r="H361" t="n">
         <v>15527144</v>
@@ -10867,7 +10867,7 @@
         <v>8.8320484161377</v>
       </c>
       <c r="G362" t="n">
-        <v>4.61518478393555</v>
+        <v>4.61518526077271</v>
       </c>
       <c r="H362" t="n">
         <v>30274610</v>
@@ -10896,7 +10896,7 @@
         <v>9.27624893188477</v>
       </c>
       <c r="G363" t="n">
-        <v>4.8473014831543</v>
+        <v>4.84730195999146</v>
       </c>
       <c r="H363" t="n">
         <v>25316340</v>
@@ -10925,7 +10925,7 @@
         <v>9.2431697845459</v>
       </c>
       <c r="G364" t="n">
-        <v>4.83001708984375</v>
+        <v>4.83001661300659</v>
       </c>
       <c r="H364" t="n">
         <v>17050586</v>
@@ -10954,7 +10954,7 @@
         <v>9.1628360748291</v>
       </c>
       <c r="G365" t="n">
-        <v>4.78803825378418</v>
+        <v>4.78803777694702</v>
       </c>
       <c r="H365" t="n">
         <v>9153930</v>
@@ -10983,7 +10983,7 @@
         <v>9.09667778015137</v>
       </c>
       <c r="G366" t="n">
-        <v>4.75346708297729</v>
+        <v>4.75346660614014</v>
       </c>
       <c r="H366" t="n">
         <v>12587007</v>
@@ -11012,7 +11012,7 @@
         <v>9.19591522216797</v>
       </c>
       <c r="G367" t="n">
-        <v>4.8053240776062</v>
+        <v>4.80532360076904</v>
       </c>
       <c r="H367" t="n">
         <v>19037774</v>
@@ -11070,7 +11070,7 @@
         <v>9.1770133972168</v>
       </c>
       <c r="G369" t="n">
-        <v>4.79544639587402</v>
+        <v>4.79544687271118</v>
       </c>
       <c r="H369" t="n">
         <v>11671909</v>
@@ -11099,7 +11099,7 @@
         <v>9.21954345703125</v>
       </c>
       <c r="G370" t="n">
-        <v>4.8176703453064</v>
+        <v>4.81766986846924</v>
       </c>
       <c r="H370" t="n">
         <v>16534219</v>
@@ -11128,7 +11128,7 @@
         <v>9.44164276123047</v>
       </c>
       <c r="G371" t="n">
-        <v>4.93372869491577</v>
+        <v>4.93372774124146</v>
       </c>
       <c r="H371" t="n">
         <v>17882977</v>
@@ -11157,7 +11157,7 @@
         <v>9.15338516235352</v>
       </c>
       <c r="G372" t="n">
-        <v>4.78309917449951</v>
+        <v>4.78309965133667</v>
       </c>
       <c r="H372" t="n">
         <v>18177957</v>
@@ -11186,7 +11186,7 @@
         <v>9.03524589538574</v>
       </c>
       <c r="G373" t="n">
-        <v>4.72136640548706</v>
+        <v>4.7213659286499</v>
       </c>
       <c r="H373" t="n">
         <v>14262518</v>
@@ -11215,7 +11215,7 @@
         <v>8.96436309814453</v>
       </c>
       <c r="G374" t="n">
-        <v>4.684326171875</v>
+        <v>4.68432664871216</v>
       </c>
       <c r="H374" t="n">
         <v>17381138</v>
@@ -11273,7 +11273,7 @@
         <v>9.02579498291016</v>
       </c>
       <c r="G376" t="n">
-        <v>4.71642684936523</v>
+        <v>4.71642732620239</v>
       </c>
       <c r="H376" t="n">
         <v>11980637</v>
@@ -11302,7 +11302,7 @@
         <v>9.05887413024902</v>
       </c>
       <c r="G377" t="n">
-        <v>4.7337121963501</v>
+        <v>4.73371315002441</v>
       </c>
       <c r="H377" t="n">
         <v>10978967</v>
@@ -11331,7 +11331,7 @@
         <v>9.28569984436035</v>
       </c>
       <c r="G378" t="n">
-        <v>4.85224151611328</v>
+        <v>4.85224008560181</v>
       </c>
       <c r="H378" t="n">
         <v>15716687</v>
@@ -11389,7 +11389,7 @@
         <v>9.14393424987793</v>
       </c>
       <c r="G380" t="n">
-        <v>4.778160572052</v>
+        <v>4.77816104888916</v>
       </c>
       <c r="H380" t="n">
         <v>9809700</v>
@@ -11418,7 +11418,7 @@
         <v>9.03524589538574</v>
       </c>
       <c r="G381" t="n">
-        <v>4.72136640548706</v>
+        <v>4.7213659286499</v>
       </c>
       <c r="H381" t="n">
         <v>11891188</v>
@@ -11447,7 +11447,7 @@
         <v>9.11085510253906</v>
       </c>
       <c r="G382" t="n">
-        <v>4.76087522506714</v>
+        <v>4.7608757019043</v>
       </c>
       <c r="H382" t="n">
         <v>11984142</v>
@@ -11476,7 +11476,7 @@
         <v>8.8320484161377</v>
       </c>
       <c r="G383" t="n">
-        <v>4.61518478393555</v>
+        <v>4.61518526077271</v>
       </c>
       <c r="H383" t="n">
         <v>19945692</v>
@@ -11505,7 +11505,7 @@
         <v>8.72336006164551</v>
       </c>
       <c r="G384" t="n">
-        <v>4.55838918685913</v>
+        <v>4.55838966369629</v>
       </c>
       <c r="H384" t="n">
         <v>11287137</v>
@@ -11534,7 +11534,7 @@
         <v>9.29113101959229</v>
       </c>
       <c r="G385" t="n">
-        <v>4.85507869720459</v>
+        <v>4.85507822036743</v>
       </c>
       <c r="H385" t="n">
         <v>22841806</v>
@@ -11592,7 +11592,7 @@
         <v>9.15826511383057</v>
       </c>
       <c r="G387" t="n">
-        <v>4.78564929962158</v>
+        <v>4.7856502532959</v>
       </c>
       <c r="H387" t="n">
         <v>11192739</v>
@@ -11679,7 +11679,7 @@
         <v>9.3243465423584</v>
       </c>
       <c r="G390" t="n">
-        <v>4.87243509292603</v>
+        <v>4.87243556976318</v>
       </c>
       <c r="H390" t="n">
         <v>8826532</v>
@@ -11708,7 +11708,7 @@
         <v>9.49042987823486</v>
       </c>
       <c r="G391" t="n">
-        <v>4.95922231674194</v>
+        <v>4.95922183990479</v>
       </c>
       <c r="H391" t="n">
         <v>17347305</v>
@@ -11737,7 +11737,7 @@
         <v>9.56635284423828</v>
       </c>
       <c r="G392" t="n">
-        <v>4.99889469146729</v>
+        <v>4.9988956451416</v>
       </c>
       <c r="H392" t="n">
         <v>12609284</v>
@@ -11853,7 +11853,7 @@
         <v>9.77514266967773</v>
       </c>
       <c r="G396" t="n">
-        <v>5.10799884796143</v>
+        <v>5.10799837112427</v>
       </c>
       <c r="H396" t="n">
         <v>7635296</v>
@@ -11882,7 +11882,7 @@
         <v>9.90800857543945</v>
       </c>
       <c r="G397" t="n">
-        <v>5.17742729187012</v>
+        <v>5.17742776870728</v>
       </c>
       <c r="H397" t="n">
         <v>7049651</v>
@@ -11911,7 +11911,7 @@
         <v>9.77514266967773</v>
       </c>
       <c r="G398" t="n">
-        <v>5.10799884796143</v>
+        <v>5.10799837112427</v>
       </c>
       <c r="H398" t="n">
         <v>7661828</v>
@@ -11940,7 +11940,7 @@
         <v>9.51890087127686</v>
       </c>
       <c r="G399" t="n">
-        <v>4.97409915924072</v>
+        <v>4.97409963607788</v>
       </c>
       <c r="H399" t="n">
         <v>13029550</v>
@@ -11969,7 +11969,7 @@
         <v>9.52839183807373</v>
       </c>
       <c r="G400" t="n">
-        <v>4.97905921936035</v>
+        <v>4.97905969619751</v>
       </c>
       <c r="H400" t="n">
         <v>8614315</v>
@@ -11998,7 +11998,7 @@
         <v>9.54737186431885</v>
       </c>
       <c r="G401" t="n">
-        <v>4.98897695541382</v>
+        <v>4.98897647857666</v>
       </c>
       <c r="H401" t="n">
         <v>11150961</v>
@@ -12027,7 +12027,7 @@
         <v>9.64227676391602</v>
       </c>
       <c r="G402" t="n">
-        <v>5.03857040405273</v>
+        <v>5.03856897354126</v>
       </c>
       <c r="H402" t="n">
         <v>7509622</v>
@@ -12085,7 +12085,7 @@
         <v>9.64227676391602</v>
       </c>
       <c r="G404" t="n">
-        <v>5.03857040405273</v>
+        <v>5.03856897354126</v>
       </c>
       <c r="H404" t="n">
         <v>11405236</v>
@@ -12114,7 +12114,7 @@
         <v>9.68023777008057</v>
       </c>
       <c r="G405" t="n">
-        <v>5.05840587615967</v>
+        <v>5.05840635299683</v>
       </c>
       <c r="H405" t="n">
         <v>5302628</v>
@@ -12172,7 +12172,7 @@
         <v>9.54737186431885</v>
       </c>
       <c r="G407" t="n">
-        <v>4.98897695541382</v>
+        <v>4.98897647857666</v>
       </c>
       <c r="H407" t="n">
         <v>11063455</v>
@@ -12230,7 +12230,7 @@
         <v>9.71819972991943</v>
       </c>
       <c r="G409" t="n">
-        <v>5.07824277877808</v>
+        <v>5.07824325561523</v>
       </c>
       <c r="H409" t="n">
         <v>7331584</v>
@@ -12259,7 +12259,7 @@
         <v>9.68972873687744</v>
       </c>
       <c r="G410" t="n">
-        <v>5.06336545944214</v>
+        <v>5.0633659362793</v>
       </c>
       <c r="H410" t="n">
         <v>5148835</v>
@@ -12288,7 +12288,7 @@
         <v>9.68023777008057</v>
       </c>
       <c r="G411" t="n">
-        <v>5.05840587615967</v>
+        <v>5.05840635299683</v>
       </c>
       <c r="H411" t="n">
         <v>5720628</v>
@@ -12317,7 +12317,7 @@
         <v>9.47619438171387</v>
       </c>
       <c r="G412" t="n">
-        <v>4.95178365707397</v>
+        <v>4.95178318023682</v>
       </c>
       <c r="H412" t="n">
         <v>12537171</v>
@@ -12346,7 +12346,7 @@
         <v>9.48093891143799</v>
       </c>
       <c r="G413" t="n">
-        <v>4.95426225662231</v>
+        <v>4.95426273345947</v>
       </c>
       <c r="H413" t="n">
         <v>7676798</v>
@@ -12404,7 +12404,7 @@
         <v>10.0788373947144</v>
       </c>
       <c r="G415" t="n">
-        <v>5.26669406890869</v>
+        <v>5.26669502258301</v>
       </c>
       <c r="H415" t="n">
         <v>28810469</v>
@@ -12462,7 +12462,7 @@
         <v>10.2306833267212</v>
       </c>
       <c r="G417" t="n">
-        <v>5.34604167938232</v>
+        <v>5.34604072570801</v>
       </c>
       <c r="H417" t="n">
         <v>16900204</v>
@@ -12491,7 +12491,7 @@
         <v>10.1547603607178</v>
       </c>
       <c r="G418" t="n">
-        <v>5.30636835098267</v>
+        <v>5.30636739730835</v>
       </c>
       <c r="H418" t="n">
         <v>10053045</v>
@@ -12520,7 +12520,7 @@
         <v>10.8570518493652</v>
       </c>
       <c r="G419" t="n">
-        <v>5.67335081100464</v>
+        <v>5.67334985733032</v>
       </c>
       <c r="H419" t="n">
         <v>44007998</v>
@@ -12549,7 +12549,7 @@
         <v>10.8855228424072</v>
       </c>
       <c r="G420" t="n">
-        <v>5.68822717666626</v>
+        <v>5.68822765350342</v>
       </c>
       <c r="H420" t="n">
         <v>38801858</v>
@@ -12607,7 +12607,7 @@
         <v>11.8535470962524</v>
       </c>
       <c r="G422" t="n">
-        <v>6.19406890869141</v>
+        <v>6.19406795501709</v>
       </c>
       <c r="H422" t="n">
         <v>56385043</v>
@@ -12636,7 +12636,7 @@
         <v>11.7681331634521</v>
       </c>
       <c r="G423" t="n">
-        <v>6.14943504333496</v>
+        <v>6.14943552017212</v>
       </c>
       <c r="H423" t="n">
         <v>20223640</v>
@@ -12665,7 +12665,7 @@
         <v>11.7966041564941</v>
       </c>
       <c r="G424" t="n">
-        <v>6.16431283950806</v>
+        <v>6.16431331634521</v>
       </c>
       <c r="H424" t="n">
         <v>14811732</v>
@@ -12694,7 +12694,7 @@
         <v>11.616286277771</v>
       </c>
       <c r="G425" t="n">
-        <v>6.07008790969849</v>
+        <v>6.07008743286133</v>
       </c>
       <c r="H425" t="n">
         <v>16227272</v>
@@ -12723,7 +12723,7 @@
         <v>11.7491521835327</v>
       </c>
       <c r="G426" t="n">
-        <v>6.13951683044434</v>
+        <v>6.13951730728149</v>
       </c>
       <c r="H426" t="n">
         <v>14260587</v>
@@ -12781,7 +12781,7 @@
         <v>12.6602344512939</v>
       </c>
       <c r="G428" t="n">
-        <v>6.61560344696045</v>
+        <v>6.61560249328613</v>
       </c>
       <c r="H428" t="n">
         <v>42396509</v>
@@ -12926,7 +12926,7 @@
         <v>12.8690233230591</v>
       </c>
       <c r="G433" t="n">
-        <v>6.72470474243164</v>
+        <v>6.72470569610596</v>
       </c>
       <c r="H433" t="n">
         <v>16257813</v>
@@ -12955,7 +12955,7 @@
         <v>12.9544372558594</v>
       </c>
       <c r="G434" t="n">
-        <v>6.76933908462524</v>
+        <v>6.76933813095093</v>
       </c>
       <c r="H434" t="n">
         <v>14217993</v>
@@ -13013,7 +13013,7 @@
         <v>13.0208702087402</v>
       </c>
       <c r="G436" t="n">
-        <v>6.80405378341675</v>
+        <v>6.80405282974243</v>
       </c>
       <c r="H436" t="n">
         <v>8799897</v>
@@ -13042,7 +13042,7 @@
         <v>13.3340539932251</v>
       </c>
       <c r="G437" t="n">
-        <v>6.96770668029785</v>
+        <v>6.96770620346069</v>
       </c>
       <c r="H437" t="n">
         <v>22136931</v>
@@ -13071,7 +13071,7 @@
         <v>13.1727170944214</v>
       </c>
       <c r="G438" t="n">
-        <v>6.88340091705322</v>
+        <v>6.88340044021606</v>
       </c>
       <c r="H438" t="n">
         <v>16431367</v>
@@ -13100,7 +13100,7 @@
         <v>13.3815059661865</v>
       </c>
       <c r="G439" t="n">
-        <v>6.99250268936157</v>
+        <v>6.99250316619873</v>
       </c>
       <c r="H439" t="n">
         <v>11398438</v>
@@ -13158,7 +13158,7 @@
         <v>13.6757097244263</v>
       </c>
       <c r="G441" t="n">
-        <v>7.14623928070068</v>
+        <v>7.14623880386353</v>
       </c>
       <c r="H441" t="n">
         <v>16517396</v>
@@ -13187,7 +13187,7 @@
         <v>13.7421426773071</v>
       </c>
       <c r="G442" t="n">
-        <v>7.18095445632935</v>
+        <v>7.18095254898071</v>
       </c>
       <c r="H442" t="n">
         <v>10134900</v>
@@ -13216,7 +13216,7 @@
         <v>14.2830972671509</v>
       </c>
       <c r="G443" t="n">
-        <v>7.46362829208374</v>
+        <v>7.4636287689209</v>
       </c>
       <c r="H443" t="n">
         <v>30225906</v>
@@ -13245,7 +13245,7 @@
         <v>13.998384475708</v>
       </c>
       <c r="G444" t="n">
-        <v>7.31485271453857</v>
+        <v>7.31485366821289</v>
       </c>
       <c r="H444" t="n">
         <v>23424229</v>
@@ -13274,7 +13274,7 @@
         <v>14.0363464355469</v>
       </c>
       <c r="G445" t="n">
-        <v>7.33468961715698</v>
+        <v>7.33468914031982</v>
       </c>
       <c r="H445" t="n">
         <v>16118823</v>
@@ -13303,7 +13303,7 @@
         <v>14.1312503814697</v>
       </c>
       <c r="G446" t="n">
-        <v>7.38428211212158</v>
+        <v>7.38428258895874</v>
       </c>
       <c r="H446" t="n">
         <v>12929629</v>
@@ -13332,7 +13332,7 @@
         <v>14.0932893753052</v>
       </c>
       <c r="G447" t="n">
-        <v>7.36444520950317</v>
+        <v>7.36444568634033</v>
       </c>
       <c r="H447" t="n">
         <v>8548100</v>
@@ -13361,7 +13361,7 @@
         <v>14.3874921798706</v>
       </c>
       <c r="G448" t="n">
-        <v>7.51818084716797</v>
+        <v>7.51818037033081</v>
       </c>
       <c r="H448" t="n">
         <v>17254730</v>
@@ -13390,7 +13390,7 @@
         <v>14.5108671188354</v>
       </c>
       <c r="G449" t="n">
-        <v>7.58264970779419</v>
+        <v>7.58265066146851</v>
       </c>
       <c r="H449" t="n">
         <v>16230591</v>
@@ -13419,7 +13419,7 @@
         <v>14.4729061126709</v>
       </c>
       <c r="G450" t="n">
-        <v>7.56281328201294</v>
+        <v>7.56281423568726</v>
       </c>
       <c r="H450" t="n">
         <v>9911424</v>
@@ -13448,7 +13448,7 @@
         <v>14.4254541397095</v>
       </c>
       <c r="G451" t="n">
-        <v>7.53801870346069</v>
+        <v>7.53801822662354</v>
       </c>
       <c r="H451" t="n">
         <v>17775976</v>
@@ -13477,7 +13477,7 @@
         <v>14.3400402069092</v>
       </c>
       <c r="G452" t="n">
-        <v>7.49338531494141</v>
+        <v>7.49338483810425</v>
       </c>
       <c r="H452" t="n">
         <v>10844722</v>
@@ -13506,7 +13506,7 @@
         <v>14.1787023544312</v>
       </c>
       <c r="G453" t="n">
-        <v>7.40907764434814</v>
+        <v>7.40907669067383</v>
       </c>
       <c r="H453" t="n">
         <v>10463213</v>
@@ -13564,7 +13564,7 @@
         <v>14.188193321228</v>
       </c>
       <c r="G455" t="n">
-        <v>7.41403722763062</v>
+        <v>7.41403770446777</v>
       </c>
       <c r="H455" t="n">
         <v>10897984</v>
@@ -13593,7 +13593,7 @@
         <v>14.3590211868286</v>
       </c>
       <c r="G456" t="n">
-        <v>7.50330352783203</v>
+        <v>7.50330400466919</v>
       </c>
       <c r="H456" t="n">
         <v>9173855</v>
@@ -13622,7 +13622,7 @@
         <v>14.2071743011475</v>
       </c>
       <c r="G457" t="n">
-        <v>7.42395639419556</v>
+        <v>7.4239559173584</v>
       </c>
       <c r="H457" t="n">
         <v>8454923</v>
@@ -13651,7 +13651,7 @@
         <v>14.2736072540283</v>
       </c>
       <c r="G458" t="n">
-        <v>7.45867156982422</v>
+        <v>7.45866966247559</v>
       </c>
       <c r="H458" t="n">
         <v>7653226</v>
@@ -13680,7 +13680,7 @@
         <v>14.1976833343506</v>
       </c>
       <c r="G459" t="n">
-        <v>7.41899585723877</v>
+        <v>7.41899681091309</v>
       </c>
       <c r="H459" t="n">
         <v>5992592</v>
@@ -13738,7 +13738,7 @@
         <v>14.1217603683472</v>
       </c>
       <c r="G461" t="n">
-        <v>7.37932300567627</v>
+        <v>7.37932348251343</v>
       </c>
       <c r="H461" t="n">
         <v>7266075</v>
@@ -13854,7 +13854,7 @@
         <v>14.1217603683472</v>
       </c>
       <c r="G465" t="n">
-        <v>7.37932300567627</v>
+        <v>7.37932348251343</v>
       </c>
       <c r="H465" t="n">
         <v>24350184</v>
@@ -13883,7 +13883,7 @@
         <v>13.6662187576294</v>
       </c>
       <c r="G466" t="n">
-        <v>7.14128017425537</v>
+        <v>7.14127969741821</v>
       </c>
       <c r="H466" t="n">
         <v>18153330</v>
@@ -13912,7 +13912,7 @@
         <v>14.0648174285889</v>
       </c>
       <c r="G467" t="n">
-        <v>7.34956693649292</v>
+        <v>7.34956789016724</v>
       </c>
       <c r="H467" t="n">
         <v>17861971</v>
@@ -14028,7 +14028,7 @@
         <v>14.3780012130737</v>
       </c>
       <c r="G471" t="n">
-        <v>7.5132212638855</v>
+        <v>7.51322031021118</v>
       </c>
       <c r="H471" t="n">
         <v>14147271</v>
@@ -14057,7 +14057,7 @@
         <v>14.5108671188354</v>
       </c>
       <c r="G472" t="n">
-        <v>7.58264970779419</v>
+        <v>7.58265066146851</v>
       </c>
       <c r="H472" t="n">
         <v>13396869</v>
@@ -14086,7 +14086,7 @@
         <v>14.8620128631592</v>
       </c>
       <c r="G473" t="n">
-        <v>7.76614189147949</v>
+        <v>7.76614141464233</v>
       </c>
       <c r="H473" t="n">
         <v>19743917</v>
@@ -14144,7 +14144,7 @@
         <v>14.6627140045166</v>
       </c>
       <c r="G475" t="n">
-        <v>7.66199922561646</v>
+        <v>7.6619987487793</v>
       </c>
       <c r="H475" t="n">
         <v>8638786</v>
@@ -14173,7 +14173,7 @@
         <v>14.2641162872314</v>
       </c>
       <c r="G476" t="n">
-        <v>7.45371150970459</v>
+        <v>7.45371198654175</v>
       </c>
       <c r="H476" t="n">
         <v>14774462</v>
@@ -14260,7 +14260,7 @@
         <v>14.0363464355469</v>
       </c>
       <c r="G479" t="n">
-        <v>7.33468961715698</v>
+        <v>7.33468914031982</v>
       </c>
       <c r="H479" t="n">
         <v>7466140</v>
@@ -14289,7 +14289,7 @@
         <v>14.1122694015503</v>
       </c>
       <c r="G480" t="n">
-        <v>7.37436246871948</v>
+        <v>7.3743634223938</v>
       </c>
       <c r="H480" t="n">
         <v>8990997</v>
@@ -14318,7 +14318,7 @@
         <v>13.8750085830688</v>
       </c>
       <c r="G481" t="n">
-        <v>7.2503833770752</v>
+        <v>7.25038290023804</v>
       </c>
       <c r="H481" t="n">
         <v>11176699</v>
@@ -14347,7 +14347,7 @@
         <v>14.1217603683472</v>
       </c>
       <c r="G482" t="n">
-        <v>7.37932300567627</v>
+        <v>7.37932348251343</v>
       </c>
       <c r="H482" t="n">
         <v>10722979</v>
@@ -14405,7 +14405,7 @@
         <v>14.2261552810669</v>
       </c>
       <c r="G484" t="n">
-        <v>7.43387508392334</v>
+        <v>7.43387460708618</v>
       </c>
       <c r="H484" t="n">
         <v>8139443</v>
@@ -14434,7 +14434,7 @@
         <v>14.463415145874</v>
       </c>
       <c r="G485" t="n">
-        <v>7.55785465240479</v>
+        <v>7.55785512924194</v>
       </c>
       <c r="H485" t="n">
         <v>9555422</v>
@@ -14463,7 +14463,7 @@
         <v>14.188193321228</v>
       </c>
       <c r="G486" t="n">
-        <v>7.41403722763062</v>
+        <v>7.41403770446777</v>
       </c>
       <c r="H486" t="n">
         <v>8569877</v>
@@ -14492,7 +14492,7 @@
         <v>14.0932893753052</v>
       </c>
       <c r="G487" t="n">
-        <v>7.36444520950317</v>
+        <v>7.36444568634033</v>
       </c>
       <c r="H487" t="n">
         <v>5002470</v>
@@ -14550,7 +14550,7 @@
         <v>13.8560276031494</v>
       </c>
       <c r="G489" t="n">
-        <v>7.24046468734741</v>
+        <v>7.24046421051025</v>
       </c>
       <c r="H489" t="n">
         <v>19858980</v>
@@ -14579,7 +14579,7 @@
         <v>13.7801036834717</v>
       </c>
       <c r="G490" t="n">
-        <v>7.20078992843628</v>
+        <v>7.2007908821106</v>
       </c>
       <c r="H490" t="n">
         <v>8587681</v>
@@ -14608,7 +14608,7 @@
         <v>13.7231616973877</v>
       </c>
       <c r="G491" t="n">
-        <v>7.17103433609009</v>
+        <v>7.17103481292725</v>
       </c>
       <c r="H491" t="n">
         <v>9180585</v>
@@ -14637,7 +14637,7 @@
         <v>13.6851997375488</v>
       </c>
       <c r="G492" t="n">
-        <v>7.15119743347168</v>
+        <v>7.151198387146</v>
       </c>
       <c r="H492" t="n">
         <v>12799230</v>
@@ -14666,7 +14666,7 @@
         <v>13.4099779129028</v>
       </c>
       <c r="G493" t="n">
-        <v>7.00738143920898</v>
+        <v>7.00738096237183</v>
       </c>
       <c r="H493" t="n">
         <v>18901326</v>
@@ -14695,7 +14695,7 @@
         <v>13.8465366363525</v>
       </c>
       <c r="G494" t="n">
-        <v>7.23550462722778</v>
+        <v>7.23550510406494</v>
       </c>
       <c r="H494" t="n">
         <v>12888480</v>
@@ -14724,7 +14724,7 @@
         <v>13.8750085830688</v>
       </c>
       <c r="G495" t="n">
-        <v>7.2503833770752</v>
+        <v>7.25038290023804</v>
       </c>
       <c r="H495" t="n">
         <v>8099387</v>
@@ -14753,7 +14753,7 @@
         <v>13.6757097244263</v>
       </c>
       <c r="G496" t="n">
-        <v>7.14623928070068</v>
+        <v>7.14623880386353</v>
       </c>
       <c r="H496" t="n">
         <v>8595908</v>
@@ -14811,7 +14811,7 @@
         <v>14.1312503814697</v>
       </c>
       <c r="G498" t="n">
-        <v>7.38428211212158</v>
+        <v>7.38428258895874</v>
       </c>
       <c r="H498" t="n">
         <v>10440139</v>
@@ -14898,7 +14898,7 @@
         <v>14.3685111999512</v>
       </c>
       <c r="G501" t="n">
-        <v>7.50826215744019</v>
+        <v>7.50826120376587</v>
       </c>
       <c r="H501" t="n">
         <v>7724096</v>
@@ -14927,7 +14927,7 @@
         <v>14.2356452941895</v>
       </c>
       <c r="G502" t="n">
-        <v>7.43883275985718</v>
+        <v>7.43883371353149</v>
       </c>
       <c r="H502" t="n">
         <v>7136404</v>
@@ -15014,7 +15014,7 @@
         <v>14.6437330245972</v>
       </c>
       <c r="G505" t="n">
-        <v>7.65207958221436</v>
+        <v>7.65207862854004</v>
       </c>
       <c r="H505" t="n">
         <v>7658264</v>
@@ -15043,7 +15043,7 @@
         <v>14.6247529983521</v>
       </c>
       <c r="G506" t="n">
-        <v>7.64216232299805</v>
+        <v>7.64216184616089</v>
       </c>
       <c r="H506" t="n">
         <v>8511432</v>
@@ -15072,7 +15072,7 @@
         <v>14.7196569442749</v>
       </c>
       <c r="G507" t="n">
-        <v>7.69175243377686</v>
+        <v>7.69175291061401</v>
       </c>
       <c r="H507" t="n">
         <v>5529243</v>
@@ -15101,7 +15101,7 @@
         <v>14.6627140045166</v>
       </c>
       <c r="G508" t="n">
-        <v>7.66199922561646</v>
+        <v>7.6619987487793</v>
       </c>
       <c r="H508" t="n">
         <v>4135624</v>
@@ -15130,7 +15130,7 @@
         <v>14.681694984436</v>
       </c>
       <c r="G509" t="n">
-        <v>7.67191648483276</v>
+        <v>7.67191600799561</v>
       </c>
       <c r="H509" t="n">
         <v>4497926</v>
@@ -15188,7 +15188,7 @@
         <v>14.1502313613892</v>
       </c>
       <c r="G511" t="n">
-        <v>7.39420127868652</v>
+        <v>7.39420032501221</v>
       </c>
       <c r="H511" t="n">
         <v>7578279</v>
@@ -15217,7 +15217,7 @@
         <v>14.3874921798706</v>
       </c>
       <c r="G512" t="n">
-        <v>7.51818084716797</v>
+        <v>7.51818037033081</v>
       </c>
       <c r="H512" t="n">
         <v>13920115</v>
@@ -15304,7 +15304,7 @@
         <v>17.0068511962891</v>
       </c>
       <c r="G515" t="n">
-        <v>8.88692569732666</v>
+        <v>8.88692665100098</v>
       </c>
       <c r="H515" t="n">
         <v>31586911</v>
@@ -15333,7 +15333,7 @@
         <v>17.1871681213379</v>
       </c>
       <c r="G516" t="n">
-        <v>8.98115158081055</v>
+        <v>8.98115062713623</v>
       </c>
       <c r="H516" t="n">
         <v>20837824</v>
@@ -15362,7 +15362,7 @@
         <v>17.5288238525391</v>
       </c>
       <c r="G517" t="n">
-        <v>9.15968227386475</v>
+        <v>9.15968418121338</v>
       </c>
       <c r="H517" t="n">
         <v>31797962</v>
@@ -15391,7 +15391,7 @@
         <v>17.6332187652588</v>
       </c>
       <c r="G518" t="n">
-        <v>9.21423530578613</v>
+        <v>9.21423435211182</v>
       </c>
       <c r="H518" t="n">
         <v>17813494</v>
@@ -15420,7 +15420,7 @@
         <v>18.0318164825439</v>
       </c>
       <c r="G519" t="n">
-        <v>9.42252159118652</v>
+        <v>9.42252349853516</v>
       </c>
       <c r="H519" t="n">
         <v>23083991</v>
@@ -15449,7 +15449,7 @@
         <v>18.1551933288574</v>
       </c>
       <c r="G520" t="n">
-        <v>9.48699283599854</v>
+        <v>9.48699378967285</v>
       </c>
       <c r="H520" t="n">
         <v>25512019</v>
@@ -15565,7 +15565,7 @@
         <v>18.1836643218994</v>
       </c>
       <c r="G524" t="n">
-        <v>9.50186920166016</v>
+        <v>9.50187015533447</v>
       </c>
       <c r="H524" t="n">
         <v>18294717</v>
@@ -15652,7 +15652,7 @@
         <v>18.5727710723877</v>
       </c>
       <c r="G527" t="n">
-        <v>9.70519828796387</v>
+        <v>9.70519733428955</v>
       </c>
       <c r="H527" t="n">
         <v>17211089</v>
@@ -15739,7 +15739,7 @@
         <v>18.791051864624</v>
       </c>
       <c r="G530" t="n">
-        <v>9.81925964355469</v>
+        <v>9.81926155090332</v>
       </c>
       <c r="H530" t="n">
         <v>10279617</v>
@@ -15768,7 +15768,7 @@
         <v>18.8328094482422</v>
       </c>
       <c r="G531" t="n">
-        <v>9.8410816192627</v>
+        <v>9.84107971191406</v>
       </c>
       <c r="H531" t="n">
         <v>12778173</v>
@@ -15826,7 +15826,7 @@
         <v>18.4702758789062</v>
       </c>
       <c r="G533" t="n">
-        <v>9.65163803100586</v>
+        <v>9.65163898468018</v>
       </c>
       <c r="H533" t="n">
         <v>14103165</v>
@@ -15855,7 +15855,7 @@
         <v>18.2538928985596</v>
       </c>
       <c r="G534" t="n">
-        <v>9.53856754302979</v>
+        <v>9.5385684967041</v>
       </c>
       <c r="H534" t="n">
         <v>16075846</v>
@@ -15884,7 +15884,7 @@
         <v>17.834415435791</v>
       </c>
       <c r="G535" t="n">
-        <v>9.31936931610107</v>
+        <v>9.31937026977539</v>
       </c>
       <c r="H535" t="n">
         <v>15302703</v>
@@ -15913,7 +15913,7 @@
         <v>17.1871681213379</v>
       </c>
       <c r="G536" t="n">
-        <v>8.98115158081055</v>
+        <v>8.98115062713623</v>
       </c>
       <c r="H536" t="n">
         <v>26215161</v>
@@ -15942,7 +15942,7 @@
         <v>16.7600994110107</v>
       </c>
       <c r="G537" t="n">
-        <v>8.75798606872559</v>
+        <v>8.7579870223999</v>
       </c>
       <c r="H537" t="n">
         <v>28865088</v>
@@ -15971,7 +15971,7 @@
         <v>17.8951549530029</v>
       </c>
       <c r="G538" t="n">
-        <v>9.35110855102539</v>
+        <v>9.35110950469971</v>
       </c>
       <c r="H538" t="n">
         <v>22997887</v>
@@ -16000,7 +16000,7 @@
         <v>17.0315265655518</v>
       </c>
       <c r="G539" t="n">
-        <v>8.89982032775879</v>
+        <v>8.89982223510742</v>
       </c>
       <c r="H539" t="n">
         <v>18906961</v>
@@ -16029,7 +16029,7 @@
         <v>16.5285339355469</v>
       </c>
       <c r="G540" t="n">
-        <v>8.63698291778564</v>
+        <v>8.63698196411133</v>
       </c>
       <c r="H540" t="n">
         <v>20165759</v>
@@ -16058,7 +16058,7 @@
         <v>16.7506084442139</v>
       </c>
       <c r="G541" t="n">
-        <v>8.75302696228027</v>
+        <v>8.75302791595459</v>
       </c>
       <c r="H541" t="n">
         <v>12327961</v>
@@ -16116,7 +16116,7 @@
         <v>16.7980613708496</v>
       </c>
       <c r="G543" t="n">
-        <v>8.77782249450684</v>
+        <v>8.77782440185547</v>
       </c>
       <c r="H543" t="n">
         <v>17359007</v>
@@ -16145,7 +16145,7 @@
         <v>16.8929653167725</v>
       </c>
       <c r="G544" t="n">
-        <v>8.82741451263428</v>
+        <v>8.82741546630859</v>
       </c>
       <c r="H544" t="n">
         <v>15515850</v>
@@ -16290,7 +16290,7 @@
         <v>16.8588008880615</v>
       </c>
       <c r="G549" t="n">
-        <v>8.80956363677979</v>
+        <v>8.80956268310547</v>
       </c>
       <c r="H549" t="n">
         <v>10799807</v>
@@ -16319,7 +16319,7 @@
         <v>16.7221374511719</v>
       </c>
       <c r="G550" t="n">
-        <v>8.73814964294434</v>
+        <v>8.73814868927002</v>
       </c>
       <c r="H550" t="n">
         <v>8960581</v>
@@ -16435,7 +16435,7 @@
         <v>16.2172470092773</v>
       </c>
       <c r="G554" t="n">
-        <v>8.47431755065918</v>
+        <v>8.47431945800781</v>
       </c>
       <c r="H554" t="n">
         <v>17805941</v>
@@ -16522,7 +16522,7 @@
         <v>16.2058582305908</v>
       </c>
       <c r="G557" t="n">
-        <v>8.4683666229248</v>
+        <v>8.46836853027344</v>
       </c>
       <c r="H557" t="n">
         <v>19613827</v>
@@ -16551,7 +16551,7 @@
         <v>16.3747882843018</v>
       </c>
       <c r="G558" t="n">
-        <v>8.55664157867432</v>
+        <v>8.55664253234863</v>
       </c>
       <c r="H558" t="n">
         <v>15356677</v>
@@ -16580,7 +16580,7 @@
         <v>16.3861751556396</v>
       </c>
       <c r="G559" t="n">
-        <v>8.56259155273438</v>
+        <v>8.56259250640869</v>
       </c>
       <c r="H559" t="n">
         <v>9604421</v>
@@ -16638,7 +16638,7 @@
         <v>16.3197422027588</v>
       </c>
       <c r="G561" t="n">
-        <v>8.52787780761719</v>
+        <v>8.52787685394287</v>
       </c>
       <c r="H561" t="n">
         <v>5485265</v>
@@ -16667,7 +16667,7 @@
         <v>16.3254375457764</v>
       </c>
       <c r="G562" t="n">
-        <v>8.53085327148438</v>
+        <v>8.53085231781006</v>
       </c>
       <c r="H562" t="n">
         <v>7438041</v>
@@ -16725,7 +16725,7 @@
         <v>16.327335357666</v>
       </c>
       <c r="G564" t="n">
-        <v>8.53184509277344</v>
+        <v>8.53184604644775</v>
       </c>
       <c r="H564" t="n">
         <v>9408768</v>
@@ -16783,7 +16783,7 @@
         <v>15.9970693588257</v>
       </c>
       <c r="G566" t="n">
-        <v>8.3592643737793</v>
+        <v>8.35926532745361</v>
       </c>
       <c r="H566" t="n">
         <v>8405353</v>
@@ -16812,7 +16812,7 @@
         <v>16.3899726867676</v>
       </c>
       <c r="G567" t="n">
-        <v>8.56457710266113</v>
+        <v>8.56457805633545</v>
       </c>
       <c r="H567" t="n">
         <v>9938343</v>
@@ -16841,7 +16841,7 @@
         <v>16.6822776794434</v>
       </c>
       <c r="G568" t="n">
-        <v>8.71731948852539</v>
+        <v>8.71732044219971</v>
       </c>
       <c r="H568" t="n">
         <v>11088370</v>
@@ -16899,7 +16899,7 @@
         <v>15.7901773452759</v>
       </c>
       <c r="G570" t="n">
-        <v>8.25115489959717</v>
+        <v>8.25115299224854</v>
       </c>
       <c r="H570" t="n">
         <v>11871422</v>
@@ -16928,7 +16928,7 @@
         <v>15.6705980300903</v>
       </c>
       <c r="G571" t="n">
-        <v>8.1886682510376</v>
+        <v>8.18866729736328</v>
       </c>
       <c r="H571" t="n">
         <v>8556944</v>
@@ -17015,7 +17015,7 @@
         <v>15.6611080169678</v>
       </c>
       <c r="G574" t="n">
-        <v>8.18370819091797</v>
+        <v>8.18370723724365</v>
       </c>
       <c r="H574" t="n">
         <v>10252051</v>
@@ -17073,7 +17073,7 @@
         <v>16.7164421081543</v>
       </c>
       <c r="G576" t="n">
-        <v>8.73517417907715</v>
+        <v>8.73517322540283</v>
       </c>
       <c r="H576" t="n">
         <v>19899347</v>
@@ -17102,7 +17102,7 @@
         <v>17.5269260406494</v>
       </c>
       <c r="G577" t="n">
-        <v>9.15869235992432</v>
+        <v>9.15869045257568</v>
       </c>
       <c r="H577" t="n">
         <v>25263368</v>
@@ -17131,7 +17131,7 @@
         <v>17.3655891418457</v>
       </c>
       <c r="G578" t="n">
-        <v>9.07438468933105</v>
+        <v>9.07438373565674</v>
       </c>
       <c r="H578" t="n">
         <v>12479906</v>
@@ -17160,7 +17160,7 @@
         <v>17.5857677459717</v>
       </c>
       <c r="G579" t="n">
-        <v>9.18943786621094</v>
+        <v>9.18943977355957</v>
       </c>
       <c r="H579" t="n">
         <v>9029715</v>
@@ -17218,7 +17218,7 @@
         <v>17.6559963226318</v>
       </c>
       <c r="G581" t="n">
-        <v>9.2261381149292</v>
+        <v>9.22613716125488</v>
       </c>
       <c r="H581" t="n">
         <v>15478215</v>
@@ -17305,7 +17305,7 @@
         <v>17.917932510376</v>
       </c>
       <c r="G584" t="n">
-        <v>9.36301231384277</v>
+        <v>9.36301136016846</v>
       </c>
       <c r="H584" t="n">
         <v>8324996</v>
@@ -17363,7 +17363,7 @@
         <v>18.6923503875732</v>
       </c>
       <c r="G586" t="n">
-        <v>9.76768493652344</v>
+        <v>9.7676830291748</v>
       </c>
       <c r="H586" t="n">
         <v>16750129</v>
@@ -17450,7 +17450,7 @@
         <v>18.6771659851074</v>
       </c>
       <c r="G589" t="n">
-        <v>9.75975036621094</v>
+        <v>9.7597484588623</v>
       </c>
       <c r="H589" t="n">
         <v>9192767</v>
@@ -17479,7 +17479,7 @@
         <v>18.7379055023193</v>
       </c>
       <c r="G590" t="n">
-        <v>9.79148960113525</v>
+        <v>9.7914867401123</v>
       </c>
       <c r="H590" t="n">
         <v>9447483</v>
@@ -17508,7 +17508,7 @@
         <v>18.1684799194336</v>
       </c>
       <c r="G591" t="n">
-        <v>9.49393558502197</v>
+        <v>9.49393463134766</v>
       </c>
       <c r="H591" t="n">
         <v>15355953</v>
@@ -17537,7 +17537,7 @@
         <v>18.5367088317871</v>
       </c>
       <c r="G592" t="n">
-        <v>9.68635272979736</v>
+        <v>9.68635368347168</v>
       </c>
       <c r="H592" t="n">
         <v>24623487</v>
@@ -17566,7 +17566,7 @@
         <v>18.0166320800781</v>
       </c>
       <c r="G593" t="n">
-        <v>9.41458702087402</v>
+        <v>9.41458797454834</v>
       </c>
       <c r="H593" t="n">
         <v>17675403</v>
@@ -17595,7 +17595,7 @@
         <v>17.6237297058105</v>
       </c>
       <c r="G594" t="n">
-        <v>9.20927619934082</v>
+        <v>9.2092752456665</v>
       </c>
       <c r="H594" t="n">
         <v>11102300</v>
@@ -17624,7 +17624,7 @@
         <v>18.0602874755859</v>
       </c>
       <c r="G595" t="n">
-        <v>9.43739891052246</v>
+        <v>9.43739795684814</v>
       </c>
       <c r="H595" t="n">
         <v>14912590</v>
@@ -17653,7 +17653,7 @@
         <v>17.640811920166</v>
       </c>
       <c r="G596" t="n">
-        <v>9.21820259094238</v>
+        <v>9.2182035446167</v>
       </c>
       <c r="H596" t="n">
         <v>12884696</v>
@@ -17682,7 +17682,7 @@
         <v>18.2121353149414</v>
       </c>
       <c r="G597" t="n">
-        <v>9.51674842834473</v>
+        <v>9.51674652099609</v>
       </c>
       <c r="H597" t="n">
         <v>13040119</v>
@@ -17711,7 +17711,7 @@
         <v>18.2481994628906</v>
       </c>
       <c r="G598" t="n">
-        <v>9.53559398651123</v>
+        <v>9.5355920791626</v>
       </c>
       <c r="H598" t="n">
         <v>6300500</v>
@@ -17769,7 +17769,7 @@
         <v>17.7888622283936</v>
       </c>
       <c r="G600" t="n">
-        <v>9.29556751251221</v>
+        <v>9.29556560516357</v>
       </c>
       <c r="H600" t="n">
         <v>9446584</v>
@@ -17798,7 +17798,7 @@
         <v>17.8135375976562</v>
       </c>
       <c r="G601" t="n">
-        <v>9.30846118927002</v>
+        <v>9.3084602355957</v>
       </c>
       <c r="H601" t="n">
         <v>8407392</v>
@@ -17856,7 +17856,7 @@
         <v>18.0223274230957</v>
       </c>
       <c r="G603" t="n">
-        <v>9.41756439208984</v>
+        <v>9.41756534576416</v>
       </c>
       <c r="H603" t="n">
         <v>7532212</v>
@@ -17914,7 +17914,7 @@
         <v>17.8116397857666</v>
       </c>
       <c r="G605" t="n">
-        <v>9.30746936798096</v>
+        <v>9.30746746063232</v>
       </c>
       <c r="H605" t="n">
         <v>9635740</v>
@@ -17943,7 +17943,7 @@
         <v>17.9274215698242</v>
       </c>
       <c r="G606" t="n">
-        <v>9.36797046661377</v>
+        <v>9.36796951293945</v>
       </c>
       <c r="H606" t="n">
         <v>9059025</v>
@@ -17972,7 +17972,7 @@
         <v>17.6047477722168</v>
       </c>
       <c r="G607" t="n">
-        <v>9.1993579864502</v>
+        <v>9.19935607910156</v>
       </c>
       <c r="H607" t="n">
         <v>11340871</v>
@@ -18030,7 +18030,7 @@
         <v>18.3639812469482</v>
       </c>
       <c r="G609" t="n">
-        <v>9.59609508514404</v>
+        <v>9.59609317779541</v>
       </c>
       <c r="H609" t="n">
         <v>12355340</v>
@@ -18088,7 +18088,7 @@
         <v>17.8192310333252</v>
       </c>
       <c r="G611" t="n">
-        <v>9.31143569946289</v>
+        <v>9.31143474578857</v>
       </c>
       <c r="H611" t="n">
         <v>11465942</v>
@@ -18146,7 +18146,7 @@
         <v>17.4301242828369</v>
       </c>
       <c r="G613" t="n">
-        <v>9.1081075668335</v>
+        <v>9.10810852050781</v>
       </c>
       <c r="H613" t="n">
         <v>7368939</v>
@@ -18175,7 +18175,7 @@
         <v>17.346607208252</v>
       </c>
       <c r="G614" t="n">
-        <v>9.06446552276611</v>
+        <v>9.0644645690918</v>
       </c>
       <c r="H614" t="n">
         <v>14175802</v>
@@ -18204,7 +18204,7 @@
         <v>18.0413074493408</v>
       </c>
       <c r="G615" t="n">
-        <v>9.42748069763184</v>
+        <v>9.42748165130615</v>
       </c>
       <c r="H615" t="n">
         <v>15274197</v>
@@ -18320,7 +18320,7 @@
         <v>16.9859714508057</v>
       </c>
       <c r="G619" t="n">
-        <v>8.87601661682129</v>
+        <v>8.87601566314697</v>
       </c>
       <c r="H619" t="n">
         <v>12670293</v>
@@ -18378,7 +18378,7 @@
         <v>17.4908638000488</v>
       </c>
       <c r="G621" t="n">
-        <v>9.1398458480835</v>
+        <v>9.13984775543213</v>
       </c>
       <c r="H621" t="n">
         <v>12455995</v>
@@ -18407,7 +18407,7 @@
         <v>17.0448112487793</v>
       </c>
       <c r="G622" t="n">
-        <v>8.90676307678223</v>
+        <v>8.90676116943359</v>
       </c>
       <c r="H622" t="n">
         <v>10384066</v>
@@ -18465,7 +18465,7 @@
         <v>17.0827732086182</v>
       </c>
       <c r="G624" t="n">
-        <v>8.92659854888916</v>
+        <v>8.92659950256348</v>
       </c>
       <c r="H624" t="n">
         <v>6607557</v>
@@ -18494,7 +18494,7 @@
         <v>16.9366207122803</v>
       </c>
       <c r="G625" t="n">
-        <v>8.85022830963135</v>
+        <v>8.85022926330566</v>
       </c>
       <c r="H625" t="n">
         <v>8463672</v>
@@ -18523,7 +18523,7 @@
         <v>17.3086452484131</v>
       </c>
       <c r="G626" t="n">
-        <v>9.04462909698486</v>
+        <v>9.04463005065918</v>
       </c>
       <c r="H626" t="n">
         <v>12168092</v>
@@ -18581,7 +18581,7 @@
         <v>17.0789775848389</v>
       </c>
       <c r="G628" t="n">
-        <v>8.92461490631104</v>
+        <v>8.92461585998535</v>
       </c>
       <c r="H628" t="n">
         <v>6192351</v>
@@ -18610,7 +18610,7 @@
         <v>16.8341255187988</v>
       </c>
       <c r="G629" t="n">
-        <v>8.79666805267334</v>
+        <v>8.79666900634766</v>
       </c>
       <c r="H629" t="n">
         <v>8173335</v>
@@ -18639,7 +18639,7 @@
         <v>16.7449150085449</v>
       </c>
       <c r="G630" t="n">
-        <v>8.7500524520874</v>
+        <v>8.75005149841309</v>
       </c>
       <c r="H630" t="n">
         <v>7559671</v>
@@ -18697,7 +18697,7 @@
         <v>15.6573114395142</v>
       </c>
       <c r="G632" t="n">
-        <v>8.18172264099121</v>
+        <v>8.18172454833984</v>
       </c>
       <c r="H632" t="n">
         <v>14104317</v>
@@ -18726,7 +18726,7 @@
         <v>15.1751976013184</v>
       </c>
       <c r="G633" t="n">
-        <v>7.92979621887207</v>
+        <v>7.92979717254639</v>
       </c>
       <c r="H633" t="n">
         <v>9489084</v>
@@ -18755,7 +18755,7 @@
         <v>15.6022672653198</v>
       </c>
       <c r="G634" t="n">
-        <v>8.15296173095703</v>
+        <v>8.15296077728271</v>
       </c>
       <c r="H634" t="n">
         <v>11393304</v>
@@ -18813,7 +18813,7 @@
         <v>15.2245483398438</v>
       </c>
       <c r="G636" t="n">
-        <v>7.95558452606201</v>
+        <v>7.95558404922485</v>
       </c>
       <c r="H636" t="n">
         <v>12449207</v>
@@ -18842,7 +18842,7 @@
         <v>15.5016679763794</v>
       </c>
       <c r="G637" t="n">
-        <v>8.10039329528809</v>
+        <v>8.10039234161377</v>
       </c>
       <c r="H637" t="n">
         <v>18010771</v>
@@ -18871,7 +18871,7 @@
         <v>15.505464553833</v>
       </c>
       <c r="G638" t="n">
-        <v>8.10237789154053</v>
+        <v>8.10237693786621</v>
       </c>
       <c r="H638" t="n">
         <v>8031841</v>
@@ -18900,7 +18900,7 @@
         <v>15.5016679763794</v>
       </c>
       <c r="G639" t="n">
-        <v>8.10039329528809</v>
+        <v>8.10039234161377</v>
       </c>
       <c r="H639" t="n">
         <v>6671029</v>
@@ -19074,7 +19074,7 @@
         <v>15.8129549026489</v>
       </c>
       <c r="G645" t="n">
-        <v>8.26305770874023</v>
+        <v>8.26305675506592</v>
       </c>
       <c r="H645" t="n">
         <v>7986360</v>
@@ -19103,7 +19103,7 @@
         <v>15.7180500030518</v>
       </c>
       <c r="G646" t="n">
-        <v>8.21346378326416</v>
+        <v>8.21346473693848</v>
       </c>
       <c r="H646" t="n">
         <v>7926547</v>
@@ -19132,7 +19132,7 @@
         <v>15.7920761108398</v>
       </c>
       <c r="G647" t="n">
-        <v>8.25214576721191</v>
+        <v>8.25214672088623</v>
       </c>
       <c r="H647" t="n">
         <v>4573934</v>
@@ -19161,7 +19161,7 @@
         <v>15.6914768218994</v>
       </c>
       <c r="G648" t="n">
-        <v>8.19957733154297</v>
+        <v>8.1995792388916</v>
       </c>
       <c r="H648" t="n">
         <v>4360779</v>
@@ -19190,7 +19190,7 @@
         <v>15.7863807678223</v>
       </c>
       <c r="G649" t="n">
-        <v>8.24917030334473</v>
+        <v>8.24916934967041</v>
       </c>
       <c r="H649" t="n">
         <v>5261525</v>
@@ -19248,7 +19248,7 @@
         <v>15.9477186203003</v>
       </c>
       <c r="G651" t="n">
-        <v>8.33347702026367</v>
+        <v>8.33347606658936</v>
       </c>
       <c r="H651" t="n">
         <v>6210341</v>
@@ -19335,7 +19335,7 @@
         <v>15.7123556137085</v>
       </c>
       <c r="G654" t="n">
-        <v>8.21048927307129</v>
+        <v>8.21048831939697</v>
       </c>
       <c r="H654" t="n">
         <v>9576435</v>
@@ -19393,7 +19393,7 @@
         <v>13.7421426773071</v>
       </c>
       <c r="G656" t="n">
-        <v>7.18095445632935</v>
+        <v>7.18095254898071</v>
       </c>
       <c r="H656" t="n">
         <v>27942328</v>
@@ -19422,7 +19422,7 @@
         <v>13.7041807174683</v>
       </c>
       <c r="G657" t="n">
-        <v>7.1611156463623</v>
+        <v>7.16111660003662</v>
       </c>
       <c r="H657" t="n">
         <v>14468621</v>
@@ -19480,7 +19480,7 @@
         <v>13.8541297912598</v>
       </c>
       <c r="G659" t="n">
-        <v>7.23947286605835</v>
+        <v>7.23947381973267</v>
       </c>
       <c r="H659" t="n">
         <v>8090449</v>
@@ -19509,7 +19509,7 @@
         <v>13.4877986907959</v>
       </c>
       <c r="G660" t="n">
-        <v>7.04804658889771</v>
+        <v>7.04804706573486</v>
       </c>
       <c r="H660" t="n">
         <v>10692697</v>
@@ -19538,7 +19538,7 @@
         <v>13.4764108657837</v>
       </c>
       <c r="G661" t="n">
-        <v>7.04209470748901</v>
+        <v>7.04209613800049</v>
       </c>
       <c r="H661" t="n">
         <v>18331418</v>
@@ -19567,7 +19567,7 @@
         <v>13.8617219924927</v>
       </c>
       <c r="G662" t="n">
-        <v>7.2434401512146</v>
+        <v>7.24344062805176</v>
       </c>
       <c r="H662" t="n">
         <v>13895019</v>
@@ -19596,7 +19596,7 @@
         <v>13.8427410125732</v>
       </c>
       <c r="G663" t="n">
-        <v>7.23352098464966</v>
+        <v>7.23352146148682</v>
       </c>
       <c r="H663" t="n">
         <v>6180662</v>
@@ -19625,7 +19625,7 @@
         <v>13.7839012145996</v>
       </c>
       <c r="G664" t="n">
-        <v>7.20277404785156</v>
+        <v>7.20277547836304</v>
       </c>
       <c r="H664" t="n">
         <v>7400362</v>
@@ -19654,7 +19654,7 @@
         <v>13.8712120056152</v>
       </c>
       <c r="G665" t="n">
-        <v>7.24839878082275</v>
+        <v>7.24839973449707</v>
       </c>
       <c r="H665" t="n">
         <v>7719008</v>
@@ -19683,7 +19683,7 @@
         <v>13.7307538986206</v>
       </c>
       <c r="G666" t="n">
-        <v>7.1750020980835</v>
+        <v>7.17500257492065</v>
       </c>
       <c r="H666" t="n">
         <v>5663137</v>
@@ -19712,7 +19712,7 @@
         <v>13.4802074432373</v>
       </c>
       <c r="G667" t="n">
-        <v>7.04408025741577</v>
+        <v>7.04407978057861</v>
       </c>
       <c r="H667" t="n">
         <v>7471037</v>
@@ -19741,7 +19741,7 @@
         <v>13.3511371612549</v>
       </c>
       <c r="G668" t="n">
-        <v>6.97663354873657</v>
+        <v>6.97663402557373</v>
       </c>
       <c r="H668" t="n">
         <v>6078170</v>
@@ -19770,7 +19770,7 @@
         <v>13.3340539932251</v>
       </c>
       <c r="G669" t="n">
-        <v>6.96770668029785</v>
+        <v>6.96770620346069</v>
       </c>
       <c r="H669" t="n">
         <v>5380398</v>
@@ -19799,7 +19799,7 @@
         <v>13.0284624099731</v>
       </c>
       <c r="G670" t="n">
-        <v>6.80801963806152</v>
+        <v>6.80802011489868</v>
       </c>
       <c r="H670" t="n">
         <v>8740511</v>
@@ -19828,7 +19828,7 @@
         <v>13.0113792419434</v>
       </c>
       <c r="G671" t="n">
-        <v>6.79909372329712</v>
+        <v>6.79909324645996</v>
       </c>
       <c r="H671" t="n">
         <v>9954709</v>
@@ -19857,7 +19857,7 @@
         <v>13.4289579391479</v>
       </c>
       <c r="G672" t="n">
-        <v>7.01729869842529</v>
+        <v>7.01729965209961</v>
       </c>
       <c r="H672" t="n">
         <v>8669950</v>
@@ -19915,7 +19915,7 @@
         <v>13.4669198989868</v>
       </c>
       <c r="G674" t="n">
-        <v>7.03713655471802</v>
+        <v>7.03713607788086</v>
       </c>
       <c r="H674" t="n">
         <v>13274702</v>
@@ -19973,7 +19973,7 @@
         <v>13.7516326904297</v>
       </c>
       <c r="G676" t="n">
-        <v>7.18591356277466</v>
+        <v>7.18591260910034</v>
       </c>
       <c r="H676" t="n">
         <v>9674767</v>
@@ -20031,7 +20031,7 @@
         <v>14.2128677368164</v>
       </c>
       <c r="G678" t="n">
-        <v>7.42693042755127</v>
+        <v>7.42693090438843</v>
       </c>
       <c r="H678" t="n">
         <v>14461079</v>
@@ -20060,7 +20060,7 @@
         <v>14.1976833343506</v>
       </c>
       <c r="G679" t="n">
-        <v>7.41899585723877</v>
+        <v>7.41899681091309</v>
       </c>
       <c r="H679" t="n">
         <v>10125499</v>
@@ -20089,7 +20089,7 @@
         <v>14.0875940322876</v>
       </c>
       <c r="G680" t="n">
-        <v>7.36146879196167</v>
+        <v>7.36146926879883</v>
       </c>
       <c r="H680" t="n">
         <v>10488138</v>
@@ -20118,7 +20118,7 @@
         <v>13.8180656433105</v>
       </c>
       <c r="G681" t="n">
-        <v>7.22062683105469</v>
+        <v>7.22062730789185</v>
       </c>
       <c r="H681" t="n">
         <v>8184826</v>
@@ -20147,7 +20147,7 @@
         <v>13.9091739654541</v>
       </c>
       <c r="G682" t="n">
-        <v>7.26823568344116</v>
+        <v>7.26823711395264</v>
       </c>
       <c r="H682" t="n">
         <v>5651801</v>
@@ -20176,7 +20176,7 @@
         <v>14.1483325958252</v>
       </c>
       <c r="G683" t="n">
-        <v>7.39320755004883</v>
+        <v>7.39320850372314</v>
       </c>
       <c r="H683" t="n">
         <v>11025862</v>
@@ -20234,7 +20234,7 @@
         <v>13.6662187576294</v>
       </c>
       <c r="G685" t="n">
-        <v>7.14128017425537</v>
+        <v>7.14127969741821</v>
       </c>
       <c r="H685" t="n">
         <v>6688217</v>
@@ -20263,7 +20263,7 @@
         <v>13.6757097244263</v>
       </c>
       <c r="G686" t="n">
-        <v>7.14623928070068</v>
+        <v>7.14623880386353</v>
       </c>
       <c r="H686" t="n">
         <v>5369251</v>
@@ -20292,7 +20292,7 @@
         <v>13.808575630188</v>
       </c>
       <c r="G687" t="n">
-        <v>7.21566772460938</v>
+        <v>7.21566820144653</v>
       </c>
       <c r="H687" t="n">
         <v>8267436</v>
@@ -20321,7 +20321,7 @@
         <v>13.7155685424805</v>
       </c>
       <c r="G688" t="n">
-        <v>7.167067527771</v>
+        <v>7.16706800460815</v>
       </c>
       <c r="H688" t="n">
         <v>6718361</v>
@@ -20350,7 +20350,7 @@
         <v>14.3191614151001</v>
       </c>
       <c r="G689" t="n">
-        <v>7.4824743270874</v>
+        <v>7.48247623443604</v>
       </c>
       <c r="H689" t="n">
         <v>16301224</v>
@@ -20379,7 +20379,7 @@
         <v>14.1730079650879</v>
       </c>
       <c r="G690" t="n">
-        <v>7.40610122680664</v>
+        <v>7.40610265731812</v>
       </c>
       <c r="H690" t="n">
         <v>6873337</v>
@@ -20408,7 +20408,7 @@
         <v>14.2147655487061</v>
       </c>
       <c r="G691" t="n">
-        <v>7.42792320251465</v>
+        <v>7.42792177200317</v>
       </c>
       <c r="H691" t="n">
         <v>6033692</v>
@@ -20437,7 +20437,7 @@
         <v>14.2717094421387</v>
       </c>
       <c r="G692" t="n">
-        <v>7.45767784118652</v>
+        <v>7.45767831802368</v>
       </c>
       <c r="H692" t="n">
         <v>5813803</v>
@@ -20495,7 +20495,7 @@
         <v>14.5810966491699</v>
       </c>
       <c r="G694" t="n">
-        <v>7.61934947967529</v>
+        <v>7.61934900283813</v>
       </c>
       <c r="H694" t="n">
         <v>11327806</v>
@@ -20582,7 +20582,7 @@
         <v>14.6247529983521</v>
       </c>
       <c r="G697" t="n">
-        <v>7.64216232299805</v>
+        <v>7.64216184616089</v>
       </c>
       <c r="H697" t="n">
         <v>5332962</v>
@@ -20611,7 +20611,7 @@
         <v>14.6589183807373</v>
       </c>
       <c r="G698" t="n">
-        <v>7.6600136756897</v>
+        <v>7.66001415252686</v>
       </c>
       <c r="H698" t="n">
         <v>8514044</v>
@@ -20640,7 +20640,7 @@
         <v>14.740535736084</v>
       </c>
       <c r="G699" t="n">
-        <v>7.70266342163086</v>
+        <v>7.7026629447937</v>
       </c>
       <c r="H699" t="n">
         <v>8416113</v>
@@ -20669,7 +20669,7 @@
         <v>14.6741027832031</v>
       </c>
       <c r="G700" t="n">
-        <v>7.66795063018799</v>
+        <v>7.66794872283936</v>
       </c>
       <c r="H700" t="n">
         <v>5280877</v>
@@ -20698,7 +20698,7 @@
         <v>14.3723068237305</v>
       </c>
       <c r="G701" t="n">
-        <v>7.51024484634399</v>
+        <v>7.51024580001831</v>
       </c>
       <c r="H701" t="n">
         <v>8767872</v>
@@ -20727,7 +20727,7 @@
         <v>14.7025737762451</v>
       </c>
       <c r="G702" t="n">
-        <v>7.68282556533813</v>
+        <v>7.68282699584961</v>
       </c>
       <c r="H702" t="n">
         <v>10330063</v>
@@ -20756,7 +20756,7 @@
         <v>14.7234525680542</v>
       </c>
       <c r="G703" t="n">
-        <v>7.69373798370361</v>
+        <v>7.69373750686646</v>
       </c>
       <c r="H703" t="n">
         <v>10764860</v>
@@ -20785,7 +20785,7 @@
         <v>14.6209564208984</v>
       </c>
       <c r="G704" t="n">
-        <v>7.64017772674561</v>
+        <v>7.64017915725708</v>
       </c>
       <c r="H704" t="n">
         <v>5908880</v>
@@ -20814,7 +20814,7 @@
         <v>14.5013771057129</v>
       </c>
       <c r="G705" t="n">
-        <v>7.57769107818604</v>
+        <v>7.57769155502319</v>
       </c>
       <c r="H705" t="n">
         <v>6986701</v>
@@ -20843,7 +20843,7 @@
         <v>14.3912878036499</v>
       </c>
       <c r="G706" t="n">
-        <v>7.52016448974609</v>
+        <v>7.52016401290894</v>
       </c>
       <c r="H706" t="n">
         <v>6378357</v>
@@ -20872,7 +20872,7 @@
         <v>14.0553274154663</v>
       </c>
       <c r="G707" t="n">
-        <v>7.34460926055908</v>
+        <v>7.34460830688477</v>
       </c>
       <c r="H707" t="n">
         <v>8869980</v>
@@ -20930,7 +20930,7 @@
         <v>13.4156723022461</v>
       </c>
       <c r="G709" t="n">
-        <v>7.01035737991333</v>
+        <v>7.01035690307617</v>
       </c>
       <c r="H709" t="n">
         <v>15105489</v>
@@ -20959,7 +20959,7 @@
         <v>13.3245639801025</v>
       </c>
       <c r="G710" t="n">
-        <v>6.96274852752686</v>
+        <v>6.96274757385254</v>
       </c>
       <c r="H710" t="n">
         <v>13805588</v>
@@ -21046,7 +21046,7 @@
         <v>13.7364482879639</v>
       </c>
       <c r="G713" t="n">
-        <v>7.17797756195068</v>
+        <v>7.177978515625</v>
       </c>
       <c r="H713" t="n">
         <v>9194882</v>
@@ -21075,7 +21075,7 @@
         <v>13.1613283157349</v>
       </c>
       <c r="G714" t="n">
-        <v>6.87744951248169</v>
+        <v>6.87744998931885</v>
       </c>
       <c r="H714" t="n">
         <v>11774022</v>
@@ -21133,7 +21133,7 @@
         <v>12.7570362091064</v>
       </c>
       <c r="G716" t="n">
-        <v>6.66618680953979</v>
+        <v>6.66618728637695</v>
       </c>
       <c r="H716" t="n">
         <v>16683638</v>
@@ -21162,7 +21162,7 @@
         <v>13.1366529464722</v>
       </c>
       <c r="G717" t="n">
-        <v>6.86455535888672</v>
+        <v>6.86455583572388</v>
       </c>
       <c r="H717" t="n">
         <v>15045078</v>
@@ -21249,7 +21249,7 @@
         <v>13.4156723022461</v>
       </c>
       <c r="G720" t="n">
-        <v>7.01035737991333</v>
+        <v>7.01035690307617</v>
       </c>
       <c r="H720" t="n">
         <v>11044345</v>
@@ -21307,7 +21307,7 @@
         <v>13.4859008789062</v>
       </c>
       <c r="G722" t="n">
-        <v>7.04705429077148</v>
+        <v>7.0470552444458</v>
       </c>
       <c r="H722" t="n">
         <v>13158928</v>
@@ -21336,7 +21336,7 @@
         <v>13.0512390136719</v>
       </c>
       <c r="G723" t="n">
-        <v>6.81992149353027</v>
+        <v>6.81992197036743</v>
       </c>
       <c r="H723" t="n">
         <v>21047437</v>
@@ -21365,7 +21365,7 @@
         <v>12.7646284103394</v>
       </c>
       <c r="G724" t="n">
-        <v>6.6701545715332</v>
+        <v>6.67015409469604</v>
       </c>
       <c r="H724" t="n">
         <v>29510414</v>
@@ -21394,7 +21394,7 @@
         <v>12.9221687316895</v>
       </c>
       <c r="G725" t="n">
-        <v>6.75247716903687</v>
+        <v>6.75247669219971</v>
       </c>
       <c r="H725" t="n">
         <v>12118944</v>
@@ -21423,7 +21423,7 @@
         <v>13.4517345428467</v>
       </c>
       <c r="G726" t="n">
-        <v>7.02920055389404</v>
+        <v>7.02920150756836</v>
       </c>
       <c r="H726" t="n">
         <v>19284748</v>
@@ -21452,7 +21452,7 @@
         <v>13.6111745834351</v>
       </c>
       <c r="G727" t="n">
-        <v>7.11251497268677</v>
+        <v>7.11251640319824</v>
       </c>
       <c r="H727" t="n">
         <v>11282385</v>
@@ -21481,7 +21481,7 @@
         <v>13.5808048248291</v>
       </c>
       <c r="G728" t="n">
-        <v>7.09664630889893</v>
+        <v>7.09664678573608</v>
       </c>
       <c r="H728" t="n">
         <v>7457464</v>
@@ -21510,7 +21510,7 @@
         <v>13.8958883285522</v>
       </c>
       <c r="G729" t="n">
-        <v>7.2612943649292</v>
+        <v>7.26129341125488</v>
       </c>
       <c r="H729" t="n">
         <v>11061346</v>
@@ -21539,7 +21539,7 @@
         <v>13.9452381134033</v>
       </c>
       <c r="G730" t="n">
-        <v>7.28708171844482</v>
+        <v>7.28708028793335</v>
       </c>
       <c r="H730" t="n">
         <v>8788005</v>
@@ -21568,7 +21568,7 @@
         <v>13.5618238449097</v>
       </c>
       <c r="G731" t="n">
-        <v>7.08672857284546</v>
+        <v>7.08672761917114</v>
       </c>
       <c r="H731" t="n">
         <v>6470916</v>
@@ -21597,7 +21597,7 @@
         <v>13.4289579391479</v>
       </c>
       <c r="G732" t="n">
-        <v>7.01729869842529</v>
+        <v>7.01729965209961</v>
       </c>
       <c r="H732" t="n">
         <v>5500628</v>
@@ -21655,7 +21655,7 @@
         <v>13.83704662323</v>
       </c>
       <c r="G734" t="n">
-        <v>7.23054695129395</v>
+        <v>7.23054599761963</v>
       </c>
       <c r="H734" t="n">
         <v>9171125</v>
@@ -21684,7 +21684,7 @@
         <v>13.6510343551636</v>
       </c>
       <c r="G735" t="n">
-        <v>7.13334512710571</v>
+        <v>7.13334465026855</v>
       </c>
       <c r="H735" t="n">
         <v>6786796</v>
@@ -21771,7 +21771,7 @@
         <v>13.2866020202637</v>
       </c>
       <c r="G738" t="n">
-        <v>6.94291162490845</v>
+        <v>6.94291067123413</v>
       </c>
       <c r="H738" t="n">
         <v>8332316</v>
@@ -21800,7 +21800,7 @@
         <v>13.4194679260254</v>
       </c>
       <c r="G739" t="n">
-        <v>7.01234006881714</v>
+        <v>7.0123405456543</v>
       </c>
       <c r="H739" t="n">
         <v>7431434</v>
@@ -21858,7 +21858,7 @@
         <v>13.3777103424072</v>
       </c>
       <c r="G741" t="n">
-        <v>6.99052000045776</v>
+        <v>6.99051904678345</v>
       </c>
       <c r="H741" t="n">
         <v>4854577</v>
@@ -21916,7 +21916,7 @@
         <v>14.0610208511353</v>
       </c>
       <c r="G743" t="n">
-        <v>7.34758329391479</v>
+        <v>7.34758377075195</v>
       </c>
       <c r="H743" t="n">
         <v>9520996</v>
@@ -21945,7 +21945,7 @@
         <v>13.8541297912598</v>
       </c>
       <c r="G744" t="n">
-        <v>7.23947286605835</v>
+        <v>7.23947381973267</v>
       </c>
       <c r="H744" t="n">
         <v>7203516</v>
@@ -21974,7 +21974,7 @@
         <v>13.9794025421143</v>
       </c>
       <c r="G745" t="n">
-        <v>7.30493450164795</v>
+        <v>7.30493307113647</v>
       </c>
       <c r="H745" t="n">
         <v>6134185</v>
@@ -22032,7 +22032,7 @@
         <v>14.3457336425781</v>
       </c>
       <c r="G747" t="n">
-        <v>7.49636077880859</v>
+        <v>7.49636125564575</v>
       </c>
       <c r="H747" t="n">
         <v>14817897</v>
@@ -22061,7 +22061,7 @@
         <v>14.0629186630249</v>
       </c>
       <c r="G748" t="n">
-        <v>7.34857416152954</v>
+        <v>7.3485746383667</v>
       </c>
       <c r="H748" t="n">
         <v>7175606</v>
@@ -22090,7 +22090,7 @@
         <v>13.8446388244629</v>
       </c>
       <c r="G749" t="n">
-        <v>7.23451328277588</v>
+        <v>7.23451375961304</v>
       </c>
       <c r="H749" t="n">
         <v>6130678</v>
@@ -22119,7 +22119,7 @@
         <v>13.1385507583618</v>
       </c>
       <c r="G750" t="n">
-        <v>6.86554670333862</v>
+        <v>6.86554718017578</v>
       </c>
       <c r="H750" t="n">
         <v>13293607</v>
@@ -22148,7 +22148,7 @@
         <v>13.0607299804688</v>
       </c>
       <c r="G751" t="n">
-        <v>6.82488203048706</v>
+        <v>6.82488107681274</v>
       </c>
       <c r="H751" t="n">
         <v>8837709</v>
@@ -22177,7 +22177,7 @@
         <v>12.6507425308228</v>
       </c>
       <c r="G752" t="n">
-        <v>6.61064291000366</v>
+        <v>6.6106424331665</v>
       </c>
       <c r="H752" t="n">
         <v>10554883</v>
@@ -22206,7 +22206,7 @@
         <v>12.9810104370117</v>
       </c>
       <c r="G753" t="n">
-        <v>6.7832236289978</v>
+        <v>6.78322458267212</v>
       </c>
       <c r="H753" t="n">
         <v>10208458</v>
@@ -22235,7 +22235,7 @@
         <v>13.2353544235229</v>
       </c>
       <c r="G754" t="n">
-        <v>6.91613101959229</v>
+        <v>6.91613149642944</v>
       </c>
       <c r="H754" t="n">
         <v>9267027</v>
@@ -22264,7 +22264,7 @@
         <v>13.2467422485352</v>
       </c>
       <c r="G755" t="n">
-        <v>6.9220814704895</v>
+        <v>6.92208290100098</v>
       </c>
       <c r="H755" t="n">
         <v>8700607</v>
@@ -22322,7 +22322,7 @@
         <v>13.0683221817017</v>
       </c>
       <c r="G757" t="n">
-        <v>6.82884979248047</v>
+        <v>6.82884883880615</v>
       </c>
       <c r="H757" t="n">
         <v>6851792</v>
@@ -22351,7 +22351,7 @@
         <v>13.0569343566895</v>
       </c>
       <c r="G758" t="n">
-        <v>6.82289934158325</v>
+        <v>6.82289743423462</v>
       </c>
       <c r="H758" t="n">
         <v>7445086</v>
@@ -22409,7 +22409,7 @@
         <v>12.8652267456055</v>
       </c>
       <c r="G760" t="n">
-        <v>6.72272205352783</v>
+        <v>6.72272109985352</v>
       </c>
       <c r="H760" t="n">
         <v>10727368</v>
@@ -22438,7 +22438,7 @@
         <v>12.4552402496338</v>
       </c>
       <c r="G761" t="n">
-        <v>6.50848388671875</v>
+        <v>6.50848245620728</v>
       </c>
       <c r="H761" t="n">
         <v>14612321</v>
@@ -22467,7 +22467,7 @@
         <v>11.9750242233276</v>
       </c>
       <c r="G762" t="n">
-        <v>6.25754642486572</v>
+        <v>6.25754594802856</v>
       </c>
       <c r="H762" t="n">
         <v>14168419</v>
@@ -22496,7 +22496,7 @@
         <v>12.0357627868652</v>
       </c>
       <c r="G763" t="n">
-        <v>6.28928565979004</v>
+        <v>6.28928518295288</v>
       </c>
       <c r="H763" t="n">
         <v>8593330</v>
@@ -22554,7 +22554,7 @@
         <v>11.783317565918</v>
       </c>
       <c r="G765" t="n">
-        <v>6.15737009048462</v>
+        <v>6.1573691368103</v>
       </c>
       <c r="H765" t="n">
         <v>8008267</v>
@@ -22612,7 +22612,7 @@
         <v>12.5368576049805</v>
       </c>
       <c r="G767" t="n">
-        <v>6.5511326789856</v>
+        <v>6.55113315582275</v>
       </c>
       <c r="H767" t="n">
         <v>6876849</v>
@@ -22641,7 +22641,7 @@
         <v>12.6849088668823</v>
       </c>
       <c r="G768" t="n">
-        <v>6.6284966468811</v>
+        <v>6.62849712371826</v>
       </c>
       <c r="H768" t="n">
         <v>10069766</v>
@@ -22670,7 +22670,7 @@
         <v>13.0569343566895</v>
       </c>
       <c r="G769" t="n">
-        <v>6.82289934158325</v>
+        <v>6.82289743423462</v>
       </c>
       <c r="H769" t="n">
         <v>9626104</v>
@@ -22728,7 +22728,7 @@
         <v>13.4877986907959</v>
       </c>
       <c r="G771" t="n">
-        <v>7.04804658889771</v>
+        <v>7.04804706573486</v>
       </c>
       <c r="H771" t="n">
         <v>11161105</v>
@@ -22757,7 +22757,7 @@
         <v>13.4175701141357</v>
       </c>
       <c r="G772" t="n">
-        <v>7.01134872436523</v>
+        <v>7.01134824752808</v>
       </c>
       <c r="H772" t="n">
         <v>6522373</v>
@@ -22815,7 +22815,7 @@
         <v>13.8636198043823</v>
       </c>
       <c r="G774" t="n">
-        <v>7.24443244934082</v>
+        <v>7.24443197250366</v>
       </c>
       <c r="H774" t="n">
         <v>8257336</v>
@@ -22873,7 +22873,7 @@
         <v>13.998384475708</v>
       </c>
       <c r="G776" t="n">
-        <v>7.31485271453857</v>
+        <v>7.31485366821289</v>
       </c>
       <c r="H776" t="n">
         <v>7523614</v>
@@ -22902,7 +22902,7 @@
         <v>14.0097732543945</v>
       </c>
       <c r="G777" t="n">
-        <v>7.32080316543579</v>
+        <v>7.32080459594727</v>
       </c>
       <c r="H777" t="n">
         <v>3151251</v>
@@ -22931,7 +22931,7 @@
         <v>13.7801036834717</v>
       </c>
       <c r="G778" t="n">
-        <v>7.20078992843628</v>
+        <v>7.2007908821106</v>
       </c>
       <c r="H778" t="n">
         <v>6594072</v>
@@ -22960,7 +22960,7 @@
         <v>13.5978879928589</v>
       </c>
       <c r="G779" t="n">
-        <v>7.1055736541748</v>
+        <v>7.10557413101196</v>
       </c>
       <c r="H779" t="n">
         <v>6816574</v>
@@ -22989,7 +22989,7 @@
         <v>13.808575630188</v>
       </c>
       <c r="G780" t="n">
-        <v>7.21566772460938</v>
+        <v>7.21566820144653</v>
       </c>
       <c r="H780" t="n">
         <v>8773268</v>
@@ -23018,7 +23018,7 @@
         <v>13.9072761535645</v>
       </c>
       <c r="G781" t="n">
-        <v>7.26724529266357</v>
+        <v>7.26724433898926</v>
       </c>
       <c r="H781" t="n">
         <v>6220740</v>
@@ -23047,7 +23047,7 @@
         <v>13.7535314559937</v>
       </c>
       <c r="G782" t="n">
-        <v>7.18690490722656</v>
+        <v>7.18690538406372</v>
       </c>
       <c r="H782" t="n">
         <v>5944895</v>
@@ -23076,7 +23076,7 @@
         <v>13.7592248916626</v>
       </c>
       <c r="G783" t="n">
-        <v>7.18987894058228</v>
+        <v>7.18987941741943</v>
       </c>
       <c r="H783" t="n">
         <v>6344388</v>
@@ -23105,7 +23105,7 @@
         <v>13.9414415359497</v>
       </c>
       <c r="G784" t="n">
-        <v>7.28509759902954</v>
+        <v>7.28509616851807</v>
       </c>
       <c r="H784" t="n">
         <v>5199734</v>
@@ -23134,7 +23134,7 @@
         <v>14.1578226089478</v>
       </c>
       <c r="G785" t="n">
-        <v>7.3981671333313</v>
+        <v>7.39816808700562</v>
       </c>
       <c r="H785" t="n">
         <v>8865233</v>
@@ -23163,7 +23163,7 @@
         <v>14.3020782470703</v>
       </c>
       <c r="G786" t="n">
-        <v>7.47354745864868</v>
+        <v>7.47354698181152</v>
       </c>
       <c r="H786" t="n">
         <v>10698830</v>
@@ -23192,7 +23192,7 @@
         <v>14.0648174285889</v>
       </c>
       <c r="G787" t="n">
-        <v>7.34956693649292</v>
+        <v>7.34956789016724</v>
       </c>
       <c r="H787" t="n">
         <v>6640516</v>
@@ -23250,7 +23250,7 @@
         <v>14.463415145874</v>
       </c>
       <c r="G789" t="n">
-        <v>7.55785465240479</v>
+        <v>7.55785512924194</v>
       </c>
       <c r="H789" t="n">
         <v>7863580</v>
@@ -23279,7 +23279,7 @@
         <v>12.6981954574585</v>
       </c>
       <c r="G790" t="n">
-        <v>6.63543939590454</v>
+        <v>6.63543891906738</v>
       </c>
       <c r="H790" t="n">
         <v>39180658</v>
@@ -23308,7 +23308,7 @@
         <v>12.329966545105</v>
       </c>
       <c r="G791" t="n">
-        <v>6.44302129745483</v>
+        <v>6.44302177429199</v>
       </c>
       <c r="H791" t="n">
         <v>18166573</v>
@@ -23337,7 +23337,7 @@
         <v>12.2825136184692</v>
       </c>
       <c r="G792" t="n">
-        <v>6.4182243347168</v>
+        <v>6.41822528839111</v>
       </c>
       <c r="H792" t="n">
         <v>14019969</v>
@@ -23482,7 +23482,7 @@
         <v>12.3413553237915</v>
       </c>
       <c r="G797" t="n">
-        <v>6.44897270202637</v>
+        <v>6.44897317886353</v>
       </c>
       <c r="H797" t="n">
         <v>7336696</v>
@@ -23511,7 +23511,7 @@
         <v>12.3470487594604</v>
       </c>
       <c r="G798" t="n">
-        <v>6.45194816589355</v>
+        <v>6.4519476890564</v>
       </c>
       <c r="H798" t="n">
         <v>6190600</v>
@@ -23569,7 +23569,7 @@
         <v>12.4419536590576</v>
       </c>
       <c r="G800" t="n">
-        <v>6.501540184021</v>
+        <v>6.50154113769531</v>
       </c>
       <c r="H800" t="n">
         <v>11998185</v>
@@ -23598,7 +23598,7 @@
         <v>12.4609346389771</v>
       </c>
       <c r="G801" t="n">
-        <v>6.51145792007446</v>
+        <v>6.51145839691162</v>
       </c>
       <c r="H801" t="n">
         <v>8556211</v>
@@ -23627,7 +23627,7 @@
         <v>12.5273675918579</v>
       </c>
       <c r="G802" t="n">
-        <v>6.54617261886597</v>
+        <v>6.54617357254028</v>
       </c>
       <c r="H802" t="n">
         <v>9906002</v>
@@ -23656,7 +23656,7 @@
         <v>12.4419536590576</v>
       </c>
       <c r="G803" t="n">
-        <v>6.501540184021</v>
+        <v>6.50154113769531</v>
       </c>
       <c r="H803" t="n">
         <v>9445802</v>
@@ -23685,7 +23685,7 @@
         <v>12.3546419143677</v>
       </c>
       <c r="G804" t="n">
-        <v>6.4559154510498</v>
+        <v>6.45591497421265</v>
       </c>
       <c r="H804" t="n">
         <v>8359228</v>
@@ -23743,7 +23743,7 @@
         <v>12.271125793457</v>
       </c>
       <c r="G806" t="n">
-        <v>6.41227388381958</v>
+        <v>6.41227340698242</v>
       </c>
       <c r="H806" t="n">
         <v>8618454</v>
@@ -23772,7 +23772,7 @@
         <v>12.1762218475342</v>
       </c>
       <c r="G807" t="n">
-        <v>6.36268186569214</v>
+        <v>6.3626823425293</v>
       </c>
       <c r="H807" t="n">
         <v>9713023</v>
@@ -23801,7 +23801,7 @@
         <v>12.2768201828003</v>
       </c>
       <c r="G808" t="n">
-        <v>6.41525077819824</v>
+        <v>6.41524934768677</v>
       </c>
       <c r="H808" t="n">
         <v>9511991</v>
@@ -23830,7 +23830,7 @@
         <v>12.7247676849365</v>
       </c>
       <c r="G809" t="n">
-        <v>6.64932537078857</v>
+        <v>6.6493239402771</v>
       </c>
       <c r="H809" t="n">
         <v>24281661</v>
@@ -23888,7 +23888,7 @@
         <v>12.1078910827637</v>
       </c>
       <c r="G811" t="n">
-        <v>6.32697582244873</v>
+        <v>6.32697629928589</v>
       </c>
       <c r="H811" t="n">
         <v>16807051</v>
@@ -23917,7 +23917,7 @@
         <v>12.1838140487671</v>
       </c>
       <c r="G812" t="n">
-        <v>6.36664915084839</v>
+        <v>6.36664962768555</v>
       </c>
       <c r="H812" t="n">
         <v>7730804</v>
@@ -23975,7 +23975,7 @@
         <v>12.0642347335815</v>
       </c>
       <c r="G814" t="n">
-        <v>6.30416250228882</v>
+        <v>6.30416345596313</v>
       </c>
       <c r="H814" t="n">
         <v>8829340</v>
@@ -24033,7 +24033,7 @@
         <v>11.9902086257935</v>
       </c>
       <c r="G816" t="n">
-        <v>6.26548004150391</v>
+        <v>6.26548051834106</v>
       </c>
       <c r="H816" t="n">
         <v>10382476</v>
@@ -24062,7 +24062,7 @@
         <v>12.0946035385132</v>
       </c>
       <c r="G817" t="n">
-        <v>6.32003259658813</v>
+        <v>6.32003211975098</v>
       </c>
       <c r="H817" t="n">
         <v>6030222</v>
@@ -24091,7 +24091,7 @@
         <v>12.7000932693481</v>
       </c>
       <c r="G818" t="n">
-        <v>6.63643074035645</v>
+        <v>6.6364312171936</v>
       </c>
       <c r="H818" t="n">
         <v>22601173</v>
@@ -24149,7 +24149,7 @@
         <v>12.4324626922607</v>
       </c>
       <c r="G820" t="n">
-        <v>6.49658155441284</v>
+        <v>6.49658060073853</v>
       </c>
       <c r="H820" t="n">
         <v>10274653</v>
@@ -24178,7 +24178,7 @@
         <v>12.1249732971191</v>
       </c>
       <c r="G821" t="n">
-        <v>6.33590173721313</v>
+        <v>6.33590126037598</v>
       </c>
       <c r="H821" t="n">
         <v>10466970</v>
@@ -24207,7 +24207,7 @@
         <v>12.3698263168335</v>
       </c>
       <c r="G822" t="n">
-        <v>6.46385049819946</v>
+        <v>6.4638500213623</v>
       </c>
       <c r="H822" t="n">
         <v>13630606</v>
@@ -24236,7 +24236,7 @@
         <v>12.4229726791382</v>
       </c>
       <c r="G823" t="n">
-        <v>6.49162101745605</v>
+        <v>6.49162244796753</v>
       </c>
       <c r="H823" t="n">
         <v>7330670</v>
@@ -24265,7 +24265,7 @@
         <v>12.7475461959839</v>
       </c>
       <c r="G824" t="n">
-        <v>6.66122770309448</v>
+        <v>6.66122722625732</v>
       </c>
       <c r="H824" t="n">
         <v>22340562</v>
@@ -24323,7 +24323,7 @@
         <v>12.5956993103027</v>
       </c>
       <c r="G826" t="n">
-        <v>6.58188009262085</v>
+        <v>6.58187961578369</v>
       </c>
       <c r="H826" t="n">
         <v>12110367</v>
@@ -24381,7 +24381,7 @@
         <v>13.0246658325195</v>
       </c>
       <c r="G828" t="n">
-        <v>6.80603694915771</v>
+        <v>6.80603742599487</v>
       </c>
       <c r="H828" t="n">
         <v>23141392</v>
@@ -24410,7 +24410,7 @@
         <v>13.0512390136719</v>
       </c>
       <c r="G829" t="n">
-        <v>6.81992149353027</v>
+        <v>6.81992197036743</v>
       </c>
       <c r="H829" t="n">
         <v>13973303</v>
@@ -24468,7 +24468,7 @@
         <v>13.0322580337524</v>
       </c>
       <c r="G831" t="n">
-        <v>6.81000328063965</v>
+        <v>6.81000375747681</v>
       </c>
       <c r="H831" t="n">
         <v>7823093</v>
@@ -24497,7 +24497,7 @@
         <v>13.2790098190308</v>
       </c>
       <c r="G832" t="n">
-        <v>6.9389443397522</v>
+        <v>6.93894338607788</v>
       </c>
       <c r="H832" t="n">
         <v>11972110</v>
@@ -24526,7 +24526,7 @@
         <v>13.1309585571289</v>
       </c>
       <c r="G833" t="n">
-        <v>6.86157941818237</v>
+        <v>6.86158037185669</v>
       </c>
       <c r="H833" t="n">
         <v>10628349</v>
@@ -24555,7 +24555,7 @@
         <v>13.1879005432129</v>
       </c>
       <c r="G834" t="n">
-        <v>6.89133453369141</v>
+        <v>6.89133405685425</v>
       </c>
       <c r="H834" t="n">
         <v>12846522</v>
@@ -24613,7 +24613,7 @@
         <v>13.4783086776733</v>
       </c>
       <c r="G836" t="n">
-        <v>7.04308795928955</v>
+        <v>7.04308748245239</v>
       </c>
       <c r="H836" t="n">
         <v>14841620</v>
@@ -24642,7 +24642,7 @@
         <v>13.5751113891602</v>
       </c>
       <c r="G837" t="n">
-        <v>7.0936713218689</v>
+        <v>7.09367179870605</v>
       </c>
       <c r="H837" t="n">
         <v>8827788</v>
@@ -24671,7 +24671,7 @@
         <v>13.7136707305908</v>
       </c>
       <c r="G838" t="n">
-        <v>7.16607570648193</v>
+        <v>7.16607522964478</v>
       </c>
       <c r="H838" t="n">
         <v>9323424</v>
@@ -24700,7 +24700,7 @@
         <v>13.9566259384155</v>
       </c>
       <c r="G839" t="n">
-        <v>7.29303312301636</v>
+        <v>7.29303216934204</v>
       </c>
       <c r="H839" t="n">
         <v>22354133</v>
@@ -24729,7 +24729,7 @@
         <v>13.9091739654541</v>
       </c>
       <c r="G840" t="n">
-        <v>7.26823568344116</v>
+        <v>7.26823711395264</v>
       </c>
       <c r="H840" t="n">
         <v>11973943</v>
@@ -24758,7 +24758,7 @@
         <v>13.2884998321533</v>
       </c>
       <c r="G841" t="n">
-        <v>7.28431224822998</v>
+        <v>7.28431177139282</v>
       </c>
       <c r="H841" t="n">
         <v>11265801</v>
@@ -24787,7 +24787,7 @@
         <v>13.1385507583618</v>
       </c>
       <c r="G842" t="n">
-        <v>7.20211458206177</v>
+        <v>7.20211410522461</v>
       </c>
       <c r="H842" t="n">
         <v>7974691</v>
@@ -24874,7 +24874,7 @@
         <v>13.1195697784424</v>
       </c>
       <c r="G845" t="n">
-        <v>7.19170951843262</v>
+        <v>7.19171047210693</v>
       </c>
       <c r="H845" t="n">
         <v>4309815</v>
@@ -24903,7 +24903,7 @@
         <v>13.0341567993164</v>
       </c>
       <c r="G846" t="n">
-        <v>7.14488840103149</v>
+        <v>7.14488935470581</v>
       </c>
       <c r="H846" t="n">
         <v>6218047</v>
@@ -24932,7 +24932,7 @@
         <v>12.8595333099365</v>
       </c>
       <c r="G847" t="n">
-        <v>7.04916715621948</v>
+        <v>7.04916620254517</v>
       </c>
       <c r="H847" t="n">
         <v>12748455</v>
@@ -24961,7 +24961,7 @@
         <v>13.4517345428467</v>
       </c>
       <c r="G848" t="n">
-        <v>7.3737907409668</v>
+        <v>7.37379217147827</v>
       </c>
       <c r="H848" t="n">
         <v>26077111</v>
@@ -25019,7 +25019,7 @@
         <v>12.9753160476685</v>
       </c>
       <c r="G850" t="n">
-        <v>7.11263561248779</v>
+        <v>7.11263513565063</v>
       </c>
       <c r="H850" t="n">
         <v>9037764</v>
@@ -25048,7 +25048,7 @@
         <v>12.9012899398804</v>
       </c>
       <c r="G851" t="n">
-        <v>7.07205629348755</v>
+        <v>7.07205486297607</v>
       </c>
       <c r="H851" t="n">
         <v>7338014</v>
@@ -25077,7 +25077,7 @@
         <v>12.4172792434692</v>
       </c>
       <c r="G852" t="n">
-        <v>6.80673789978027</v>
+        <v>6.80673742294312</v>
       </c>
       <c r="H852" t="n">
         <v>12707250</v>
@@ -25164,7 +25164,7 @@
         <v>12.2464513778687</v>
       </c>
       <c r="G855" t="n">
-        <v>6.71309518814087</v>
+        <v>6.71309471130371</v>
       </c>
       <c r="H855" t="n">
         <v>7854157</v>
@@ -25222,7 +25222,7 @@
         <v>12.5691251754761</v>
       </c>
       <c r="G857" t="n">
-        <v>6.88997411727905</v>
+        <v>6.88997316360474</v>
       </c>
       <c r="H857" t="n">
         <v>8691096</v>
@@ -25280,7 +25280,7 @@
         <v>11.3524522781372</v>
       </c>
       <c r="G859" t="n">
-        <v>6.93350124359131</v>
+        <v>6.93350219726562</v>
       </c>
       <c r="H859" t="n">
         <v>15924075</v>
@@ -25309,7 +25309,7 @@
         <v>11.2708349227905</v>
       </c>
       <c r="G860" t="n">
-        <v>6.88365364074707</v>
+        <v>6.88365411758423</v>
       </c>
       <c r="H860" t="n">
         <v>7714819</v>
@@ -25338,7 +25338,7 @@
         <v>11.177827835083</v>
       </c>
       <c r="G861" t="n">
-        <v>6.82684993743896</v>
+        <v>6.82685041427612</v>
       </c>
       <c r="H861" t="n">
         <v>7598910</v>
@@ -25396,7 +25396,7 @@
         <v>10.8722362518311</v>
       </c>
       <c r="G863" t="n">
-        <v>6.64021015167236</v>
+        <v>6.64021062850952</v>
       </c>
       <c r="H863" t="n">
         <v>6991145</v>
@@ -25454,7 +25454,7 @@
         <v>11.6352672576904</v>
       </c>
       <c r="G865" t="n">
-        <v>7.10623073577881</v>
+        <v>7.10622978210449</v>
       </c>
       <c r="H865" t="n">
         <v>22205120</v>
@@ -25483,7 +25483,7 @@
         <v>11.4929113388062</v>
       </c>
       <c r="G866" t="n">
-        <v>7.01928615570068</v>
+        <v>7.019287109375</v>
       </c>
       <c r="H866" t="n">
         <v>17340802</v>
@@ -25512,7 +25512,7 @@
         <v>11.398006439209</v>
       </c>
       <c r="G867" t="n">
-        <v>6.96132373809814</v>
+        <v>6.96132469177246</v>
       </c>
       <c r="H867" t="n">
         <v>9839102</v>
@@ -25541,7 +25541,7 @@
         <v>10.8551540374756</v>
       </c>
       <c r="G868" t="n">
-        <v>6.62977743148804</v>
+        <v>6.62977695465088</v>
       </c>
       <c r="H868" t="n">
         <v>28158505</v>
@@ -25570,7 +25570,7 @@
         <v>10.794415473938</v>
       </c>
       <c r="G869" t="n">
-        <v>6.59268093109131</v>
+        <v>6.59268045425415</v>
       </c>
       <c r="H869" t="n">
         <v>13751352</v>
@@ -25599,7 +25599,7 @@
         <v>11.2119941711426</v>
       </c>
       <c r="G870" t="n">
-        <v>6.84771680831909</v>
+        <v>6.84771633148193</v>
       </c>
       <c r="H870" t="n">
         <v>16304416</v>
@@ -25628,7 +25628,7 @@
         <v>11.1038026809692</v>
       </c>
       <c r="G871" t="n">
-        <v>6.78163862228394</v>
+        <v>6.78163957595825</v>
       </c>
       <c r="H871" t="n">
         <v>9556509</v>
@@ -25686,7 +25686,7 @@
         <v>11.0753316879272</v>
       </c>
       <c r="G873" t="n">
-        <v>6.76424980163574</v>
+        <v>6.7642502784729</v>
       </c>
       <c r="H873" t="n">
         <v>8606841</v>
@@ -25744,7 +25744,7 @@
         <v>11.3733310699463</v>
       </c>
       <c r="G875" t="n">
-        <v>6.94625282287598</v>
+        <v>6.94625377655029</v>
       </c>
       <c r="H875" t="n">
         <v>12624403</v>
@@ -25773,7 +25773,7 @@
         <v>11.1949110031128</v>
       </c>
       <c r="G876" t="n">
-        <v>6.83728218078613</v>
+        <v>6.83728408813477</v>
       </c>
       <c r="H876" t="n">
         <v>7756257</v>
@@ -25802,7 +25802,7 @@
         <v>11.2898149490356</v>
       </c>
       <c r="G877" t="n">
-        <v>6.89524602890015</v>
+        <v>6.89524555206299</v>
       </c>
       <c r="H877" t="n">
         <v>8169825</v>
@@ -25889,7 +25889,7 @@
         <v>11.4378662109375</v>
       </c>
       <c r="G880" t="n">
-        <v>6.98566770553589</v>
+        <v>6.98566818237305</v>
       </c>
       <c r="H880" t="n">
         <v>10165151</v>
@@ -25947,7 +25947,7 @@
         <v>11.7073936462402</v>
       </c>
       <c r="G882" t="n">
-        <v>7.15028142929077</v>
+        <v>7.15028190612793</v>
       </c>
       <c r="H882" t="n">
         <v>13384556</v>
@@ -25976,7 +25976,7 @@
         <v>11.6827192306519</v>
       </c>
       <c r="G883" t="n">
-        <v>7.13521194458008</v>
+        <v>7.13521146774292</v>
       </c>
       <c r="H883" t="n">
         <v>18176962</v>
@@ -26005,7 +26005,7 @@
         <v>11.6941080093384</v>
       </c>
       <c r="G884" t="n">
-        <v>7.14216804504395</v>
+        <v>7.14216709136963</v>
       </c>
       <c r="H884" t="n">
         <v>5686660</v>
@@ -26034,7 +26034,7 @@
         <v>11.4967069625854</v>
       </c>
       <c r="G885" t="n">
-        <v>7.02160549163818</v>
+        <v>7.02160453796387</v>
       </c>
       <c r="H885" t="n">
         <v>5951436</v>
@@ -26092,7 +26092,7 @@
         <v>11.5935087203979</v>
       </c>
       <c r="G887" t="n">
-        <v>7.08072757720947</v>
+        <v>7.08072710037231</v>
       </c>
       <c r="H887" t="n">
         <v>4740983</v>
@@ -26121,7 +26121,7 @@
         <v>11.6409606933594</v>
       </c>
       <c r="G888" t="n">
-        <v>7.10970735549927</v>
+        <v>7.10970783233643</v>
       </c>
       <c r="H888" t="n">
         <v>6813411</v>
@@ -26150,7 +26150,7 @@
         <v>11.7187833786011</v>
       </c>
       <c r="G889" t="n">
-        <v>7.15723848342896</v>
+        <v>7.1572380065918</v>
       </c>
       <c r="H889" t="n">
         <v>7399451</v>
@@ -26179,7 +26179,7 @@
         <v>11.6751270294189</v>
       </c>
       <c r="G890" t="n">
-        <v>7.13057518005371</v>
+        <v>7.13057470321655</v>
       </c>
       <c r="H890" t="n">
         <v>8437718</v>
@@ -26208,7 +26208,7 @@
         <v>12.0034961700439</v>
       </c>
       <c r="G891" t="n">
-        <v>7.33112668991089</v>
+        <v>7.33112621307373</v>
       </c>
       <c r="H891" t="n">
         <v>12485858</v>
@@ -26237,7 +26237,7 @@
         <v>12.0395593643188</v>
       </c>
       <c r="G892" t="n">
-        <v>7.35315084457397</v>
+        <v>7.35315179824829</v>
       </c>
       <c r="H892" t="n">
         <v>4585342</v>
@@ -26266,7 +26266,7 @@
         <v>11.9940052032471</v>
       </c>
       <c r="G893" t="n">
-        <v>7.32532930374146</v>
+        <v>7.32532978057861</v>
       </c>
       <c r="H893" t="n">
         <v>4682690</v>
@@ -26295,7 +26295,7 @@
         <v>11.9351654052734</v>
       </c>
       <c r="G894" t="n">
-        <v>7.28939294815063</v>
+        <v>7.28939342498779</v>
       </c>
       <c r="H894" t="n">
         <v>5081986</v>
@@ -26324,7 +26324,7 @@
         <v>11.8041973114014</v>
       </c>
       <c r="G895" t="n">
-        <v>7.20940494537354</v>
+        <v>7.20940542221069</v>
       </c>
       <c r="H895" t="n">
         <v>6925731</v>
@@ -26353,7 +26353,7 @@
         <v>11.7966041564941</v>
       </c>
       <c r="G896" t="n">
-        <v>7.20476627349854</v>
+        <v>7.20476770401001</v>
       </c>
       <c r="H896" t="n">
         <v>6462180</v>
@@ -26382,7 +26382,7 @@
         <v>11.7073936462402</v>
       </c>
       <c r="G897" t="n">
-        <v>7.15028142929077</v>
+        <v>7.15028190612793</v>
       </c>
       <c r="H897" t="n">
         <v>7278375</v>
@@ -26440,7 +26440,7 @@
         <v>11.9294700622559</v>
       </c>
       <c r="G899" t="n">
-        <v>7.28591537475586</v>
+        <v>7.2859148979187</v>
       </c>
       <c r="H899" t="n">
         <v>8199234</v>
@@ -26527,7 +26527,7 @@
         <v>11.5840187072754</v>
       </c>
       <c r="G902" t="n">
-        <v>7.07493019104004</v>
+        <v>7.07493114471436</v>
       </c>
       <c r="H902" t="n">
         <v>7964489</v>
@@ -26556,7 +26556,7 @@
         <v>11.3942098617554</v>
       </c>
       <c r="G903" t="n">
-        <v>6.95900535583496</v>
+        <v>6.95900583267212</v>
       </c>
       <c r="H903" t="n">
         <v>7573517</v>
@@ -26585,7 +26585,7 @@
         <v>11.398006439209</v>
       </c>
       <c r="G904" t="n">
-        <v>6.96132373809814</v>
+        <v>6.96132469177246</v>
       </c>
       <c r="H904" t="n">
         <v>6307481</v>
@@ -26672,7 +26672,7 @@
         <v>11.7795219421387</v>
       </c>
       <c r="G907" t="n">
-        <v>7.19433450698853</v>
+        <v>7.19433498382568</v>
       </c>
       <c r="H907" t="n">
         <v>12045507</v>
@@ -26701,7 +26701,7 @@
         <v>11.7187833786011</v>
       </c>
       <c r="G908" t="n">
-        <v>7.15723848342896</v>
+        <v>7.1572380065918</v>
       </c>
       <c r="H908" t="n">
         <v>7115760</v>
@@ -26730,7 +26730,7 @@
         <v>11.6048984527588</v>
       </c>
       <c r="G909" t="n">
-        <v>7.08768177032471</v>
+        <v>7.08768272399902</v>
       </c>
       <c r="H909" t="n">
         <v>5469067</v>
@@ -26759,7 +26759,7 @@
         <v>11.1038026809692</v>
       </c>
       <c r="G910" t="n">
-        <v>6.78163862228394</v>
+        <v>6.78163957595825</v>
       </c>
       <c r="H910" t="n">
         <v>18606256</v>
@@ -26817,7 +26817,7 @@
         <v>11.4587450027466</v>
       </c>
       <c r="G912" t="n">
-        <v>6.99841976165771</v>
+        <v>6.99841928482056</v>
       </c>
       <c r="H912" t="n">
         <v>7746554</v>
@@ -26875,7 +26875,7 @@
         <v>11.0772304534912</v>
       </c>
       <c r="G914" t="n">
-        <v>6.76541137695312</v>
+        <v>6.76540994644165</v>
       </c>
       <c r="H914" t="n">
         <v>8623004</v>
@@ -26904,7 +26904,7 @@
         <v>11.1645421981812</v>
       </c>
       <c r="G915" t="n">
-        <v>6.81873512268066</v>
+        <v>6.81873464584351</v>
       </c>
       <c r="H915" t="n">
         <v>13526423</v>
@@ -26933,7 +26933,7 @@
         <v>11.1038026809692</v>
       </c>
       <c r="G916" t="n">
-        <v>6.78163862228394</v>
+        <v>6.78163957595825</v>
       </c>
       <c r="H916" t="n">
         <v>8534339</v>
@@ -26991,7 +26991,7 @@
         <v>11.0145931243896</v>
       </c>
       <c r="G918" t="n">
-        <v>6.72715520858765</v>
+        <v>6.72715425491333</v>
       </c>
       <c r="H918" t="n">
         <v>7228084</v>
@@ -27078,7 +27078,7 @@
         <v>10.7830257415771</v>
       </c>
       <c r="G921" t="n">
-        <v>6.5857253074646</v>
+        <v>6.58572483062744</v>
       </c>
       <c r="H921" t="n">
         <v>7995093</v>
@@ -27107,7 +27107,7 @@
         <v>10.4907207489014</v>
       </c>
       <c r="G922" t="n">
-        <v>6.40719890594482</v>
+        <v>6.40719985961914</v>
       </c>
       <c r="H922" t="n">
         <v>15734219</v>
@@ -27194,7 +27194,7 @@
         <v>10.9405679702759</v>
       </c>
       <c r="G925" t="n">
-        <v>6.68194341659546</v>
+        <v>6.68194389343262</v>
       </c>
       <c r="H925" t="n">
         <v>12269751</v>
@@ -27223,7 +27223,7 @@
         <v>10.9538536071777</v>
       </c>
       <c r="G926" t="n">
-        <v>6.6900577545166</v>
+        <v>6.69005870819092</v>
       </c>
       <c r="H926" t="n">
         <v>8590883</v>
@@ -27252,7 +27252,7 @@
         <v>10.7165927886963</v>
       </c>
       <c r="G927" t="n">
-        <v>6.5451512336731</v>
+        <v>6.54515171051025</v>
       </c>
       <c r="H927" t="n">
         <v>8356968</v>
@@ -27281,7 +27281,7 @@
         <v>10.8646440505981</v>
       </c>
       <c r="G928" t="n">
-        <v>6.63557291030884</v>
+        <v>6.63557386398315</v>
       </c>
       <c r="H928" t="n">
         <v>5332780</v>
@@ -27339,7 +27339,7 @@
         <v>11.0430641174316</v>
       </c>
       <c r="G930" t="n">
-        <v>6.74454259872437</v>
+        <v>6.74454355239868</v>
       </c>
       <c r="H930" t="n">
         <v>7687713</v>
@@ -27368,7 +27368,7 @@
         <v>11.1417646408081</v>
       </c>
       <c r="G931" t="n">
-        <v>6.80482339859009</v>
+        <v>6.8048243522644</v>
       </c>
       <c r="H931" t="n">
         <v>8405039</v>
@@ -27397,7 +27397,7 @@
         <v>11.2347707748413</v>
       </c>
       <c r="G932" t="n">
-        <v>6.86162710189819</v>
+        <v>6.86162757873535</v>
       </c>
       <c r="H932" t="n">
         <v>7418517</v>
@@ -27513,7 +27513,7 @@
         <v>11.9370632171631</v>
       </c>
       <c r="G936" t="n">
-        <v>7.29055261611938</v>
+        <v>7.29055213928223</v>
       </c>
       <c r="H936" t="n">
         <v>12407160</v>
@@ -27542,7 +27542,7 @@
         <v>11.9617376327515</v>
       </c>
       <c r="G937" t="n">
-        <v>7.30562210083008</v>
+        <v>7.30562162399292</v>
       </c>
       <c r="H937" t="n">
         <v>10596312</v>
@@ -27571,7 +27571,7 @@
         <v>12.0718269348145</v>
       </c>
       <c r="G938" t="n">
-        <v>7.37285852432251</v>
+        <v>7.37285947799683</v>
       </c>
       <c r="H938" t="n">
         <v>9164685</v>
@@ -27600,7 +27600,7 @@
         <v>11.9237756729126</v>
       </c>
       <c r="G939" t="n">
-        <v>7.28243637084961</v>
+        <v>7.28243684768677</v>
       </c>
       <c r="H939" t="n">
         <v>13696213</v>
@@ -27629,7 +27629,7 @@
         <v>11.7795219421387</v>
       </c>
       <c r="G940" t="n">
-        <v>7.19433450698853</v>
+        <v>7.19433498382568</v>
       </c>
       <c r="H940" t="n">
         <v>10017690</v>
@@ -27687,7 +27687,7 @@
         <v>11.9218778610229</v>
       </c>
       <c r="G942" t="n">
-        <v>7.28127813339233</v>
+        <v>7.28127717971802</v>
       </c>
       <c r="H942" t="n">
         <v>5712763</v>
@@ -27716,7 +27716,7 @@
         <v>11.9408588409424</v>
       </c>
       <c r="G943" t="n">
-        <v>7.29287052154541</v>
+        <v>7.29287099838257</v>
       </c>
       <c r="H943" t="n">
         <v>6825742</v>
@@ -27745,7 +27745,7 @@
         <v>11.7586431503296</v>
       </c>
       <c r="G944" t="n">
-        <v>7.18158292770386</v>
+        <v>7.1815824508667</v>
       </c>
       <c r="H944" t="n">
         <v>7605053</v>
@@ -27774,7 +27774,7 @@
         <v>11.7586431503296</v>
       </c>
       <c r="G945" t="n">
-        <v>7.18158292770386</v>
+        <v>7.1815824508667</v>
       </c>
       <c r="H945" t="n">
         <v>7649590</v>
@@ -27803,7 +27803,7 @@
         <v>11.7681331634521</v>
       </c>
       <c r="G946" t="n">
-        <v>7.18737840652466</v>
+        <v>7.18737888336182</v>
       </c>
       <c r="H946" t="n">
         <v>7002623</v>
@@ -27832,7 +27832,7 @@
         <v>11.7073936462402</v>
       </c>
       <c r="G947" t="n">
-        <v>7.15028142929077</v>
+        <v>7.15028190612793</v>
       </c>
       <c r="H947" t="n">
         <v>8019289</v>
@@ -27861,7 +27861,7 @@
         <v>11.5764255523682</v>
       </c>
       <c r="G948" t="n">
-        <v>7.07029342651367</v>
+        <v>7.07029294967651</v>
       </c>
       <c r="H948" t="n">
         <v>8415376</v>
@@ -27919,7 +27919,7 @@
         <v>11.1854209899902</v>
       </c>
       <c r="G950" t="n">
-        <v>6.83148670196533</v>
+        <v>6.83148813247681</v>
       </c>
       <c r="H950" t="n">
         <v>8916775</v>
@@ -27948,7 +27948,7 @@
         <v>11.208197593689</v>
       </c>
       <c r="G951" t="n">
-        <v>6.84539842605591</v>
+        <v>6.84539794921875</v>
       </c>
       <c r="H951" t="n">
         <v>6266730</v>
@@ -27977,7 +27977,7 @@
         <v>11.2613439559937</v>
       </c>
       <c r="G952" t="n">
-        <v>6.87785673141479</v>
+        <v>6.87785768508911</v>
       </c>
       <c r="H952" t="n">
         <v>3876072</v>
@@ -28035,7 +28035,7 @@
         <v>11.1588468551636</v>
       </c>
       <c r="G954" t="n">
-        <v>6.81525659561157</v>
+        <v>6.81525707244873</v>
       </c>
       <c r="H954" t="n">
         <v>6266902</v>
@@ -28064,7 +28064,7 @@
         <v>10.8570518493652</v>
       </c>
       <c r="G955" t="n">
-        <v>6.63093662261963</v>
+        <v>6.63093566894531</v>
       </c>
       <c r="H955" t="n">
         <v>11840992</v>
@@ -28093,7 +28093,7 @@
         <v>10.7090005874634</v>
       </c>
       <c r="G956" t="n">
-        <v>6.54051399230957</v>
+        <v>6.54051446914673</v>
       </c>
       <c r="H956" t="n">
         <v>10188023</v>
@@ -28122,7 +28122,7 @@
         <v>10.6957139968872</v>
       </c>
       <c r="G957" t="n">
-        <v>6.53239917755127</v>
+        <v>6.53239965438843</v>
       </c>
       <c r="H957" t="n">
         <v>9541843</v>
@@ -28151,7 +28151,7 @@
         <v>10.7659435272217</v>
       </c>
       <c r="G958" t="n">
-        <v>6.57529258728027</v>
+        <v>6.5752911567688</v>
       </c>
       <c r="H958" t="n">
         <v>5181589</v>
@@ -28180,7 +28180,7 @@
         <v>10.6577529907227</v>
       </c>
       <c r="G959" t="n">
-        <v>6.50921487808228</v>
+        <v>6.50921440124512</v>
       </c>
       <c r="H959" t="n">
         <v>7014502</v>
@@ -28209,7 +28209,7 @@
         <v>10.7222881317139</v>
       </c>
       <c r="G960" t="n">
-        <v>6.54862880706787</v>
+        <v>6.54862976074219</v>
       </c>
       <c r="H960" t="n">
         <v>8304332</v>
@@ -28238,7 +28238,7 @@
         <v>11.0259809494019</v>
       </c>
       <c r="G961" t="n">
-        <v>6.73410940170288</v>
+        <v>6.73410987854004</v>
       </c>
       <c r="H961" t="n">
         <v>10153227</v>
@@ -28267,7 +28267,7 @@
         <v>11.2575483322144</v>
       </c>
       <c r="G962" t="n">
-        <v>6.87553834915161</v>
+        <v>6.87553882598877</v>
       </c>
       <c r="H962" t="n">
         <v>11291785</v>
@@ -28296,7 +28296,7 @@
         <v>11.3277769088745</v>
       </c>
       <c r="G963" t="n">
-        <v>6.9184308052063</v>
+        <v>6.91843175888062</v>
       </c>
       <c r="H963" t="n">
         <v>7461695</v>
@@ -28325,7 +28325,7 @@
         <v>11.4587450027466</v>
       </c>
       <c r="G964" t="n">
-        <v>6.99841976165771</v>
+        <v>6.99841928482056</v>
       </c>
       <c r="H964" t="n">
         <v>10041863</v>
@@ -28354,7 +28354,7 @@
         <v>11.5783243179321</v>
       </c>
       <c r="G965" t="n">
-        <v>7.07145357131958</v>
+        <v>7.07145309448242</v>
       </c>
       <c r="H965" t="n">
         <v>12448341</v>
@@ -28383,7 +28383,7 @@
         <v>11.5251779556274</v>
       </c>
       <c r="G966" t="n">
-        <v>7.03899383544922</v>
+        <v>7.03899335861206</v>
       </c>
       <c r="H966" t="n">
         <v>9543633</v>
@@ -28441,7 +28441,7 @@
         <v>11.3904142379761</v>
       </c>
       <c r="G968" t="n">
-        <v>6.95668649673462</v>
+        <v>6.95668697357178</v>
       </c>
       <c r="H968" t="n">
         <v>11598281</v>
@@ -28470,7 +28470,7 @@
         <v>11.3125915527344</v>
       </c>
       <c r="G969" t="n">
-        <v>6.90915679931641</v>
+        <v>6.90915727615356</v>
       </c>
       <c r="H969" t="n">
         <v>8141660</v>
@@ -28528,7 +28528,7 @@
         <v>11.2537517547607</v>
       </c>
       <c r="G971" t="n">
-        <v>6.87322044372559</v>
+        <v>6.87321996688843</v>
       </c>
       <c r="H971" t="n">
         <v>7160562</v>
@@ -28586,7 +28586,7 @@
         <v>11.3031015396118</v>
       </c>
       <c r="G973" t="n">
-        <v>6.90336132049561</v>
+        <v>6.90336084365845</v>
       </c>
       <c r="H973" t="n">
         <v>10515673</v>
@@ -28615,7 +28615,7 @@
         <v>11.1512546539307</v>
       </c>
       <c r="G974" t="n">
-        <v>6.81061983108521</v>
+        <v>6.81062126159668</v>
       </c>
       <c r="H974" t="n">
         <v>11762724</v>
@@ -28673,7 +28673,7 @@
         <v>13.2182712554932</v>
       </c>
       <c r="G976" t="n">
-        <v>8.07304954528809</v>
+        <v>8.07304859161377</v>
       </c>
       <c r="H976" t="n">
         <v>73306102</v>
@@ -28702,7 +28702,7 @@
         <v>13.2960920333862</v>
       </c>
       <c r="G977" t="n">
-        <v>8.12057685852051</v>
+        <v>8.12057781219482</v>
       </c>
       <c r="H977" t="n">
         <v>27936738</v>
@@ -28876,7 +28876,7 @@
         <v>13.7706136703491</v>
       </c>
       <c r="G983" t="n">
-        <v>8.41039180755615</v>
+        <v>8.41039276123047</v>
       </c>
       <c r="H983" t="n">
         <v>8348142</v>
@@ -28905,7 +28905,7 @@
         <v>13.9357471466064</v>
       </c>
       <c r="G984" t="n">
-        <v>8.51124572753906</v>
+        <v>8.5112476348877</v>
       </c>
       <c r="H984" t="n">
         <v>10051345</v>
@@ -28934,7 +28934,7 @@
         <v>13.7763080596924</v>
       </c>
       <c r="G985" t="n">
-        <v>8.4138708114624</v>
+        <v>8.41386985778809</v>
       </c>
       <c r="H985" t="n">
         <v>8543442</v>
@@ -28963,7 +28963,7 @@
         <v>13.7668180465698</v>
       </c>
       <c r="G986" t="n">
-        <v>8.40807342529297</v>
+        <v>8.40807437896729</v>
       </c>
       <c r="H986" t="n">
         <v>6878905</v>
@@ -28992,7 +28992,7 @@
         <v>13.7895946502686</v>
       </c>
       <c r="G987" t="n">
-        <v>8.4219856262207</v>
+        <v>8.42198467254639</v>
       </c>
       <c r="H987" t="n">
         <v>7697920</v>
@@ -29079,7 +29079,7 @@
         <v>13.256233215332</v>
       </c>
       <c r="G990" t="n">
-        <v>8.09623336791992</v>
+        <v>8.09623527526855</v>
       </c>
       <c r="H990" t="n">
         <v>8996497</v>
@@ -29108,7 +29108,7 @@
         <v>12.7551383972168</v>
       </c>
       <c r="G991" t="n">
-        <v>7.79019069671631</v>
+        <v>7.79019212722778</v>
       </c>
       <c r="H991" t="n">
         <v>29829158</v>
@@ -29137,7 +29137,7 @@
         <v>12.6830110549927</v>
       </c>
       <c r="G992" t="n">
-        <v>7.74613857269287</v>
+        <v>7.74613952636719</v>
       </c>
       <c r="H992" t="n">
         <v>10755842</v>
@@ -29195,7 +29195,7 @@
         <v>12.8974943161011</v>
       </c>
       <c r="G994" t="n">
-        <v>7.87713479995728</v>
+        <v>7.87713432312012</v>
       </c>
       <c r="H994" t="n">
         <v>8130574</v>
@@ -29224,7 +29224,7 @@
         <v>12.9202709197998</v>
       </c>
       <c r="G995" t="n">
-        <v>7.89104509353638</v>
+        <v>7.89104557037354</v>
       </c>
       <c r="H995" t="n">
         <v>6259587</v>
@@ -29253,7 +29253,7 @@
         <v>12.8044881820679</v>
       </c>
       <c r="G996" t="n">
-        <v>7.82033157348633</v>
+        <v>7.82033205032349</v>
       </c>
       <c r="H996" t="n">
         <v>3736123</v>
@@ -29282,7 +29282,7 @@
         <v>12.7361574172974</v>
       </c>
       <c r="G997" t="n">
-        <v>7.77859783172607</v>
+        <v>7.77859830856323</v>
       </c>
       <c r="H997" t="n">
         <v>4566360</v>
@@ -29311,7 +29311,7 @@
         <v>12.6146793365479</v>
       </c>
       <c r="G998" t="n">
-        <v>7.70440530776978</v>
+        <v>7.70440578460693</v>
       </c>
       <c r="H998" t="n">
         <v>10026295</v>
@@ -29340,7 +29340,7 @@
         <v>12.5292663574219</v>
       </c>
       <c r="G999" t="n">
-        <v>7.65224027633667</v>
+        <v>7.65223932266235</v>
       </c>
       <c r="H999" t="n">
         <v>7457729</v>
@@ -29369,7 +29369,7 @@
         <v>12.686806678772</v>
       </c>
       <c r="G1000" t="n">
-        <v>7.74845838546753</v>
+        <v>7.74845695495605</v>
       </c>
       <c r="H1000" t="n">
         <v>6246944</v>
@@ -29398,7 +29398,7 @@
         <v>12.5786161422729</v>
       </c>
       <c r="G1001" t="n">
-        <v>7.68238067626953</v>
+        <v>7.68238115310669</v>
       </c>
       <c r="H1001" t="n">
         <v>7485137</v>
@@ -29427,7 +29427,7 @@
         <v>12.5862083435059</v>
       </c>
       <c r="G1002" t="n">
-        <v>7.68701648712158</v>
+        <v>7.68701601028442</v>
       </c>
       <c r="H1002" t="n">
         <v>6633338</v>
@@ -29514,7 +29514,7 @@
         <v>12.2198781967163</v>
       </c>
       <c r="G1005" t="n">
-        <v>7.46328115463257</v>
+        <v>7.46328353881836</v>
       </c>
       <c r="H1005" t="n">
         <v>9630979</v>
@@ -29543,7 +29543,7 @@
         <v>12.5216732025146</v>
       </c>
       <c r="G1006" t="n">
-        <v>7.64760303497314</v>
+        <v>7.64760160446167</v>
       </c>
       <c r="H1006" t="n">
         <v>11165502</v>
@@ -29572,7 +29572,7 @@
         <v>12.6469469070435</v>
       </c>
       <c r="G1007" t="n">
-        <v>7.72411441802979</v>
+        <v>7.72411346435547</v>
       </c>
       <c r="H1007" t="n">
         <v>12352255</v>
@@ -29601,7 +29601,7 @@
         <v>12.7836093902588</v>
       </c>
       <c r="G1008" t="n">
-        <v>7.80757999420166</v>
+        <v>7.80758047103882</v>
       </c>
       <c r="H1008" t="n">
         <v>7178859</v>
@@ -29659,7 +29659,7 @@
         <v>12.9107809066772</v>
       </c>
       <c r="G1010" t="n">
-        <v>7.88524866104126</v>
+        <v>7.88525009155273</v>
       </c>
       <c r="H1010" t="n">
         <v>14521662</v>
@@ -29688,7 +29688,7 @@
         <v>12.9088830947876</v>
       </c>
       <c r="G1011" t="n">
-        <v>7.8840913772583</v>
+        <v>7.88409042358398</v>
       </c>
       <c r="H1011" t="n">
         <v>12182873</v>
@@ -29746,7 +29746,7 @@
         <v>12.817774772644</v>
       </c>
       <c r="G1013" t="n">
-        <v>7.82844638824463</v>
+        <v>7.82844591140747</v>
       </c>
       <c r="H1013" t="n">
         <v>6012672</v>
@@ -29775,7 +29775,7 @@
         <v>12.7456474304199</v>
       </c>
       <c r="G1014" t="n">
-        <v>7.78439426422119</v>
+        <v>7.78439474105835</v>
       </c>
       <c r="H1014" t="n">
         <v>6456581</v>
@@ -29804,7 +29804,7 @@
         <v>12.5216732025146</v>
       </c>
       <c r="G1015" t="n">
-        <v>7.64760303497314</v>
+        <v>7.64760160446167</v>
       </c>
       <c r="H1015" t="n">
         <v>6843632</v>
@@ -29833,7 +29833,7 @@
         <v>12.6754179000854</v>
       </c>
       <c r="G1016" t="n">
-        <v>7.74150228500366</v>
+        <v>7.74150085449219</v>
       </c>
       <c r="H1016" t="n">
         <v>6162266</v>
@@ -29862,7 +29862,7 @@
         <v>12.4115839004517</v>
       </c>
       <c r="G1017" t="n">
-        <v>7.5803656578064</v>
+        <v>7.58036518096924</v>
       </c>
       <c r="H1017" t="n">
         <v>11057906</v>
@@ -29891,7 +29891,7 @@
         <v>12.242654800415</v>
       </c>
       <c r="G1018" t="n">
-        <v>7.47719097137451</v>
+        <v>7.47719287872314</v>
       </c>
       <c r="H1018" t="n">
         <v>9452947</v>
@@ -29920,7 +29920,7 @@
         <v>12.299596786499</v>
       </c>
       <c r="G1019" t="n">
-        <v>7.51196956634521</v>
+        <v>7.51196813583374</v>
       </c>
       <c r="H1019" t="n">
         <v>7565735</v>
@@ -29978,7 +29978,7 @@
         <v>12.1781196594238</v>
       </c>
       <c r="G1021" t="n">
-        <v>7.43777704238892</v>
+        <v>7.43777751922607</v>
       </c>
       <c r="H1021" t="n">
         <v>8721406</v>
@@ -30007,7 +30007,7 @@
         <v>12.1762218475342</v>
       </c>
       <c r="G1022" t="n">
-        <v>7.43661689758301</v>
+        <v>7.43661880493164</v>
       </c>
       <c r="H1022" t="n">
         <v>8590564</v>
@@ -30036,7 +30036,7 @@
         <v>12.1002979278564</v>
       </c>
       <c r="G1023" t="n">
-        <v>7.39024782180786</v>
+        <v>7.3902473449707</v>
       </c>
       <c r="H1023" t="n">
         <v>8910297</v>
@@ -30123,7 +30123,7 @@
         <v>11.8193807601929</v>
       </c>
       <c r="G1026" t="n">
-        <v>7.21867752075195</v>
+        <v>7.21867799758911</v>
       </c>
       <c r="H1026" t="n">
         <v>8900948</v>
@@ -30181,7 +30181,7 @@
         <v>11.8231782913208</v>
       </c>
       <c r="G1028" t="n">
-        <v>7.22099637985229</v>
+        <v>7.22099781036377</v>
       </c>
       <c r="H1028" t="n">
         <v>4612748</v>
@@ -30210,7 +30210,7 @@
         <v>11.7017002105713</v>
       </c>
       <c r="G1029" t="n">
-        <v>7.14680433273315</v>
+        <v>7.146803855896</v>
       </c>
       <c r="H1029" t="n">
         <v>7233535</v>
@@ -30268,7 +30268,7 @@
         <v>11.4321718215942</v>
       </c>
       <c r="G1031" t="n">
-        <v>6.98219060897827</v>
+        <v>6.98218965530396</v>
       </c>
       <c r="H1031" t="n">
         <v>9090584</v>
@@ -30355,7 +30355,7 @@
         <v>11.4018020629883</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.96364116668701</v>
+        <v>6.96364164352417</v>
       </c>
       <c r="H1034" t="n">
         <v>8651481</v>
@@ -30413,7 +30413,7 @@
         <v>11.318286895752</v>
       </c>
       <c r="G1036" t="n">
-        <v>6.9126353263855</v>
+        <v>6.91263484954834</v>
       </c>
       <c r="H1036" t="n">
         <v>11133203</v>
@@ -30442,7 +30442,7 @@
         <v>11.1341724395752</v>
       </c>
       <c r="G1037" t="n">
-        <v>6.80018758773804</v>
+        <v>6.80018711090088</v>
       </c>
       <c r="H1037" t="n">
         <v>12092403</v>
@@ -30500,7 +30500,7 @@
         <v>11.398006439209</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.96132373809814</v>
+        <v>6.96132469177246</v>
       </c>
       <c r="H1039" t="n">
         <v>10806337</v>
@@ -30529,7 +30529,7 @@
         <v>11.6827192306519</v>
       </c>
       <c r="G1040" t="n">
-        <v>7.13521194458008</v>
+        <v>7.13521146774292</v>
       </c>
       <c r="H1040" t="n">
         <v>13708744</v>
@@ -30616,7 +30616,7 @@
         <v>11.3733310699463</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.94625282287598</v>
+        <v>6.94625377655029</v>
       </c>
       <c r="H1043" t="n">
         <v>10017356</v>
@@ -30645,7 +30645,7 @@
         <v>11.5137901306152</v>
       </c>
       <c r="G1044" t="n">
-        <v>7.03203773498535</v>
+        <v>7.03203964233398</v>
       </c>
       <c r="H1044" t="n">
         <v>10964207</v>
@@ -30761,7 +30761,7 @@
         <v>11.6922101974487</v>
       </c>
       <c r="G1048" t="n">
-        <v>7.14100885391235</v>
+        <v>7.1410083770752</v>
       </c>
       <c r="H1048" t="n">
         <v>7927723</v>
@@ -30790,7 +30790,7 @@
         <v>11.5840187072754</v>
       </c>
       <c r="G1049" t="n">
-        <v>7.07493019104004</v>
+        <v>7.07493114471436</v>
       </c>
       <c r="H1049" t="n">
         <v>7295141</v>
@@ -30848,7 +30848,7 @@
         <v>11.6504516601562</v>
       </c>
       <c r="G1051" t="n">
-        <v>7.1155047416687</v>
+        <v>7.11550521850586</v>
       </c>
       <c r="H1051" t="n">
         <v>8917979</v>
@@ -30877,7 +30877,7 @@
         <v>11.4644393920898</v>
       </c>
       <c r="G1052" t="n">
-        <v>7.00189781188965</v>
+        <v>7.00189828872681</v>
       </c>
       <c r="H1052" t="n">
         <v>11179493</v>
@@ -30906,7 +30906,7 @@
         <v>10.7621469497681</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.57297277450562</v>
+        <v>6.57297325134277</v>
       </c>
       <c r="H1053" t="n">
         <v>25864410</v>
@@ -30935,7 +30935,7 @@
         <v>10.684326171875</v>
       </c>
       <c r="G1054" t="n">
-        <v>6.52544403076172</v>
+        <v>6.52544355392456</v>
       </c>
       <c r="H1054" t="n">
         <v>16163015</v>
@@ -30993,7 +30993,7 @@
         <v>10.9728345870972</v>
       </c>
       <c r="G1056" t="n">
-        <v>6.70165061950684</v>
+        <v>6.70165157318115</v>
       </c>
       <c r="H1056" t="n">
         <v>18350932</v>
@@ -31022,7 +31022,7 @@
         <v>10.6691408157349</v>
       </c>
       <c r="G1057" t="n">
-        <v>6.51617002487183</v>
+        <v>6.51616954803467</v>
       </c>
       <c r="H1057" t="n">
         <v>22197980</v>
@@ -31051,7 +31051,7 @@
         <v>10.2762365341187</v>
       </c>
       <c r="G1058" t="n">
-        <v>6.27620363235474</v>
+        <v>6.27620410919189</v>
       </c>
       <c r="H1058" t="n">
         <v>21913609</v>
@@ -31080,7 +31080,7 @@
         <v>10.3825302124023</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.34112215042114</v>
+        <v>6.34112310409546</v>
       </c>
       <c r="H1059" t="n">
         <v>13738314</v>
@@ -31109,7 +31109,7 @@
         <v>10.4318809509277</v>
       </c>
       <c r="G1060" t="n">
-        <v>6.37126302719116</v>
+        <v>6.37126350402832</v>
       </c>
       <c r="H1060" t="n">
         <v>11599359</v>
@@ -31196,7 +31196,7 @@
         <v>8.90392112731934</v>
       </c>
       <c r="G1063" t="n">
-        <v>5.43806314468384</v>
+        <v>5.438063621521</v>
       </c>
       <c r="H1063" t="n">
         <v>30088498</v>
@@ -31225,7 +31225,7 @@
         <v>8.8526725769043</v>
       </c>
       <c r="G1064" t="n">
-        <v>5.40676355361938</v>
+        <v>5.40676259994507</v>
       </c>
       <c r="H1064" t="n">
         <v>21534065</v>
@@ -31283,7 +31283,7 @@
         <v>7.4224648475647</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.53326463699341</v>
+        <v>4.53326511383057</v>
       </c>
       <c r="H1066" t="n">
         <v>33515785</v>
@@ -31312,7 +31312,7 @@
         <v>7.95392894744873</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.85785675048828</v>
+        <v>4.85785627365112</v>
       </c>
       <c r="H1067" t="n">
         <v>25562426</v>
@@ -31341,7 +31341,7 @@
         <v>6.80368900299072</v>
       </c>
       <c r="G1068" t="n">
-        <v>4.15534830093384</v>
+        <v>4.15534782409668</v>
       </c>
       <c r="H1068" t="n">
         <v>29062113</v>
@@ -31370,7 +31370,7 @@
         <v>6.5151801109314</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.97914147377014</v>
+        <v>3.97914099693298</v>
       </c>
       <c r="H1069" t="n">
         <v>27201181</v>
@@ -31399,7 +31399,7 @@
         <v>5.8081431388855</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.54731941223145</v>
+        <v>3.54731917381287</v>
       </c>
       <c r="H1070" t="n">
         <v>18643241</v>
@@ -31515,7 +31515,7 @@
         <v>6.30164480209351</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.84872460365295</v>
+        <v>3.84872436523438</v>
       </c>
       <c r="H1074" t="n">
         <v>20477817</v>
@@ -31544,7 +31544,7 @@
         <v>6.48576021194458</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.96117305755615</v>
+        <v>3.96117329597473</v>
       </c>
       <c r="H1075" t="n">
         <v>28998466</v>
@@ -31573,7 +31573,7 @@
         <v>6.53985500335693</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.99421143531799</v>
+        <v>3.99421119689941</v>
       </c>
       <c r="H1076" t="n">
         <v>13580103</v>
@@ -31602,7 +31602,7 @@
         <v>6.14790010452271</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.75482511520386</v>
+        <v>3.75482487678528</v>
       </c>
       <c r="H1077" t="n">
         <v>12042575</v>
@@ -31631,7 +31631,7 @@
         <v>5.98846101760864</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.65744781494141</v>
+        <v>3.65744829177856</v>
       </c>
       <c r="H1078" t="n">
         <v>11504283</v>
@@ -31660,7 +31660,7 @@
         <v>6.23711013793945</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.8093101978302</v>
+        <v>3.80930972099304</v>
       </c>
       <c r="H1079" t="n">
         <v>13657132</v>
@@ -31689,7 +31689,7 @@
         <v>6.00079917907715</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.66498327255249</v>
+        <v>3.66498351097107</v>
       </c>
       <c r="H1080" t="n">
         <v>10059147</v>
@@ -31718,7 +31718,7 @@
         <v>5.96473503112793</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.64295768737793</v>
+        <v>3.64295744895935</v>
       </c>
       <c r="H1081" t="n">
         <v>10832835</v>
@@ -31747,7 +31747,7 @@
         <v>5.88406610488892</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.59368920326233</v>
+        <v>3.59368896484375</v>
       </c>
       <c r="H1082" t="n">
         <v>7043475</v>
@@ -31776,7 +31776,7 @@
         <v>6.27886819839478</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.83481407165527</v>
+        <v>3.83481383323669</v>
       </c>
       <c r="H1083" t="n">
         <v>12359149</v>
@@ -31805,7 +31805,7 @@
         <v>6.68505907058716</v>
       </c>
       <c r="G1084" t="n">
-        <v>4.08289480209351</v>
+        <v>4.08289432525635</v>
       </c>
       <c r="H1084" t="n">
         <v>18328643</v>
@@ -31834,7 +31834,7 @@
         <v>6.7562370300293</v>
       </c>
       <c r="G1085" t="n">
-        <v>4.12636661529541</v>
+        <v>4.12636709213257</v>
       </c>
       <c r="H1085" t="n">
         <v>8123955</v>
@@ -31863,7 +31863,7 @@
         <v>7.09789180755615</v>
       </c>
       <c r="G1086" t="n">
-        <v>4.33503198623657</v>
+        <v>4.33503246307373</v>
       </c>
       <c r="H1086" t="n">
         <v>15935964</v>
@@ -31892,7 +31892,7 @@
         <v>7.07986116409302</v>
       </c>
       <c r="G1087" t="n">
-        <v>4.32401990890503</v>
+        <v>4.32402038574219</v>
       </c>
       <c r="H1087" t="n">
         <v>13540727</v>
@@ -31950,7 +31950,7 @@
         <v>6.74674606323242</v>
       </c>
       <c r="G1089" t="n">
-        <v>4.12057018280029</v>
+        <v>4.12057065963745</v>
       </c>
       <c r="H1089" t="n">
         <v>8283080</v>
@@ -31979,7 +31979,7 @@
         <v>6.94889307022095</v>
       </c>
       <c r="G1090" t="n">
-        <v>4.24403142929077</v>
+        <v>4.24403095245361</v>
       </c>
       <c r="H1090" t="n">
         <v>8733784</v>
@@ -32008,7 +32008,7 @@
         <v>7.05138921737671</v>
       </c>
       <c r="G1091" t="n">
-        <v>4.30663013458252</v>
+        <v>4.30663061141968</v>
       </c>
       <c r="H1091" t="n">
         <v>6915872</v>
@@ -32037,7 +32037,7 @@
         <v>6.73630714416504</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.11419439315796</v>
+        <v>4.11419486999512</v>
       </c>
       <c r="H1092" t="n">
         <v>6799525</v>
@@ -32066,7 +32066,7 @@
         <v>6.88056087493896</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.20229768753052</v>
+        <v>4.20229721069336</v>
       </c>
       <c r="H1093" t="n">
         <v>6105844</v>
@@ -32124,7 +32124,7 @@
         <v>6.97546577453613</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.26026010513306</v>
+        <v>4.26026058197021</v>
       </c>
       <c r="H1095" t="n">
         <v>5839222</v>
@@ -32298,7 +32298,7 @@
         <v>7.28390502929688</v>
       </c>
       <c r="G1101" t="n">
-        <v>4.44863939285278</v>
+        <v>4.44863891601562</v>
       </c>
       <c r="H1101" t="n">
         <v>7811329</v>
@@ -32327,7 +32327,7 @@
         <v>7.23929977416992</v>
       </c>
       <c r="G1102" t="n">
-        <v>4.42139673233032</v>
+        <v>4.42139625549316</v>
       </c>
       <c r="H1102" t="n">
         <v>5352834</v>
@@ -32356,7 +32356,7 @@
         <v>7.21272706985474</v>
       </c>
       <c r="G1103" t="n">
-        <v>4.40516710281372</v>
+        <v>4.40516805648804</v>
       </c>
       <c r="H1103" t="n">
         <v>4378098</v>
@@ -32385,7 +32385,7 @@
         <v>7.37406396865845</v>
       </c>
       <c r="G1104" t="n">
-        <v>4.50370454788208</v>
+        <v>4.50370359420776</v>
       </c>
       <c r="H1104" t="n">
         <v>4807661</v>
@@ -32414,7 +32414,7 @@
         <v>7.2440447807312</v>
       </c>
       <c r="G1105" t="n">
-        <v>4.42429494857788</v>
+        <v>4.42429447174072</v>
       </c>
       <c r="H1105" t="n">
         <v>5941606</v>
@@ -32443,7 +32443,7 @@
         <v>7.20513391494751</v>
       </c>
       <c r="G1106" t="n">
-        <v>4.4005298614502</v>
+        <v>4.40053033828735</v>
       </c>
       <c r="H1106" t="n">
         <v>6205144</v>
@@ -32472,7 +32472,7 @@
         <v>6.999192237854</v>
       </c>
       <c r="G1107" t="n">
-        <v>4.27475118637085</v>
+        <v>4.27475166320801</v>
       </c>
       <c r="H1107" t="n">
         <v>10252854</v>
@@ -32530,7 +32530,7 @@
         <v>6.83595609664917</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.17505550384521</v>
+        <v>4.17505502700806</v>
       </c>
       <c r="H1109" t="n">
         <v>7857836</v>
@@ -32559,7 +32559,7 @@
         <v>7.39589214324951</v>
       </c>
       <c r="G1110" t="n">
-        <v>4.51703596115112</v>
+        <v>4.51703500747681</v>
       </c>
       <c r="H1110" t="n">
         <v>12281582</v>
@@ -32588,7 +32588,7 @@
         <v>7.06088018417358</v>
       </c>
       <c r="G1111" t="n">
-        <v>4.31242704391479</v>
+        <v>4.31242752075195</v>
       </c>
       <c r="H1111" t="n">
         <v>18686809</v>
@@ -32617,7 +32617,7 @@
         <v>6.94889307022095</v>
       </c>
       <c r="G1112" t="n">
-        <v>4.24403142929077</v>
+        <v>4.24403095245361</v>
       </c>
       <c r="H1112" t="n">
         <v>19289986</v>
@@ -32646,7 +32646,7 @@
         <v>6.96502590179443</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.25388431549072</v>
+        <v>4.25388479232788</v>
       </c>
       <c r="H1113" t="n">
         <v>14631558</v>
@@ -32704,7 +32704,7 @@
         <v>7.28390502929688</v>
       </c>
       <c r="G1115" t="n">
-        <v>4.44863939285278</v>
+        <v>4.44863891601562</v>
       </c>
       <c r="H1115" t="n">
         <v>7503292</v>
@@ -32733,7 +32733,7 @@
         <v>7.53065586090088</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.59934234619141</v>
+        <v>4.59934282302856</v>
       </c>
       <c r="H1116" t="n">
         <v>14110902</v>
@@ -32791,7 +32791,7 @@
         <v>7.82960510253906</v>
       </c>
       <c r="G1118" t="n">
-        <v>4.78192567825317</v>
+        <v>4.78192472457886</v>
       </c>
       <c r="H1118" t="n">
         <v>11798728</v>
@@ -32820,7 +32820,7 @@
         <v>7.53729915618896</v>
       </c>
       <c r="G1119" t="n">
-        <v>4.60339975357056</v>
+        <v>4.60340023040771</v>
       </c>
       <c r="H1119" t="n">
         <v>14883017</v>
@@ -32878,7 +32878,7 @@
         <v>7.91311979293823</v>
       </c>
       <c r="G1121" t="n">
-        <v>4.832932472229</v>
+        <v>4.83293151855469</v>
       </c>
       <c r="H1121" t="n">
         <v>11148650</v>
@@ -32994,7 +32994,7 @@
         <v>8.92764663696289</v>
       </c>
       <c r="G1125" t="n">
-        <v>5.45255327224731</v>
+        <v>5.45255279541016</v>
       </c>
       <c r="H1125" t="n">
         <v>17249937</v>
@@ -33023,7 +33023,7 @@
         <v>8.53569316864014</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.21316814422607</v>
+        <v>5.21316766738892</v>
       </c>
       <c r="H1126" t="n">
         <v>18143907</v>
@@ -33081,7 +33081,7 @@
         <v>7.6654200553894</v>
       </c>
       <c r="G1128" t="n">
-        <v>4.68164968490601</v>
+        <v>4.68165016174316</v>
       </c>
       <c r="H1128" t="n">
         <v>24615597</v>
@@ -33110,7 +33110,7 @@
         <v>7.77550888061523</v>
       </c>
       <c r="G1129" t="n">
-        <v>4.74888610839844</v>
+        <v>4.7488865852356</v>
       </c>
       <c r="H1129" t="n">
         <v>15936016</v>
@@ -33139,7 +33139,7 @@
         <v>7.77835607528687</v>
       </c>
       <c r="G1130" t="n">
-        <v>4.7506251335144</v>
+        <v>4.75062561035156</v>
       </c>
       <c r="H1130" t="n">
         <v>10945752</v>
@@ -33197,7 +33197,7 @@
         <v>7.97006320953369</v>
       </c>
       <c r="G1132" t="n">
-        <v>4.86771011352539</v>
+        <v>4.86770963668823</v>
       </c>
       <c r="H1132" t="n">
         <v>13268054</v>
@@ -33226,7 +33226,7 @@
         <v>7.945387840271</v>
       </c>
       <c r="G1133" t="n">
-        <v>4.85263919830322</v>
+        <v>4.85264015197754</v>
       </c>
       <c r="H1133" t="n">
         <v>10951874</v>
@@ -33284,7 +33284,7 @@
         <v>8.1314001083374</v>
       </c>
       <c r="G1135" t="n">
-        <v>4.96624660491943</v>
+        <v>4.96624708175659</v>
       </c>
       <c r="H1135" t="n">
         <v>11120772</v>
@@ -33313,7 +33313,7 @@
         <v>8.602126121521</v>
       </c>
       <c r="G1136" t="n">
-        <v>5.25374174118042</v>
+        <v>5.25374126434326</v>
       </c>
       <c r="H1136" t="n">
         <v>19919897</v>
@@ -33342,7 +33342,7 @@
         <v>8.22345733642578</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.02246999740601</v>
+        <v>5.02247047424316</v>
       </c>
       <c r="H1137" t="n">
         <v>14767769</v>
@@ -33371,7 +33371,7 @@
         <v>8.34303665161133</v>
       </c>
       <c r="G1138" t="n">
-        <v>5.09550285339355</v>
+        <v>5.09550333023071</v>
       </c>
       <c r="H1138" t="n">
         <v>11215982</v>
@@ -33429,7 +33429,7 @@
         <v>8.37815093994141</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.11694955825806</v>
+        <v>5.1169490814209</v>
       </c>
       <c r="H1140" t="n">
         <v>7932243</v>
@@ -33487,7 +33487,7 @@
         <v>8.33829212188721</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.09260559082031</v>
+        <v>5.09260606765747</v>
       </c>
       <c r="H1142" t="n">
         <v>9813243</v>
@@ -33603,7 +33603,7 @@
         <v>8.52525329589844</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.2067928314209</v>
+        <v>5.20679187774658</v>
       </c>
       <c r="H1146" t="n">
         <v>7735786</v>
@@ -33719,7 +33719,7 @@
         <v>8.59453296661377</v>
       </c>
       <c r="G1150" t="n">
-        <v>5.24910497665405</v>
+        <v>5.24910449981689</v>
       </c>
       <c r="H1150" t="n">
         <v>9828412</v>
@@ -33806,7 +33806,7 @@
         <v>8.70557117462158</v>
       </c>
       <c r="G1153" t="n">
-        <v>5.31692123413086</v>
+        <v>5.3169207572937</v>
       </c>
       <c r="H1153" t="n">
         <v>8382162</v>
@@ -33835,7 +33835,7 @@
         <v>8.6951322555542</v>
       </c>
       <c r="G1154" t="n">
-        <v>5.31054544448853</v>
+        <v>5.31054639816284</v>
       </c>
       <c r="H1154" t="n">
         <v>8332593</v>
@@ -33864,7 +33864,7 @@
         <v>8.74637985229492</v>
       </c>
       <c r="G1155" t="n">
-        <v>5.34184455871582</v>
+        <v>5.34184503555298</v>
       </c>
       <c r="H1155" t="n">
         <v>6000919</v>
@@ -33893,7 +33893,7 @@
         <v>8.76630973815918</v>
       </c>
       <c r="G1156" t="n">
-        <v>5.35401725769043</v>
+        <v>5.35401678085327</v>
       </c>
       <c r="H1156" t="n">
         <v>8783510</v>
@@ -33922,7 +33922,7 @@
         <v>8.69133567810059</v>
       </c>
       <c r="G1157" t="n">
-        <v>5.30822610855103</v>
+        <v>5.30822658538818</v>
       </c>
       <c r="H1157" t="n">
         <v>11227734</v>
@@ -33980,7 +33980,7 @@
         <v>8.6135139465332</v>
       </c>
       <c r="G1159" t="n">
-        <v>5.26069736480713</v>
+        <v>5.26069688796997</v>
       </c>
       <c r="H1159" t="n">
         <v>7140068</v>
@@ -34009,7 +34009,7 @@
         <v>8.61066722869873</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.25895833969116</v>
+        <v>5.258957862854</v>
       </c>
       <c r="H1160" t="n">
         <v>7304019</v>
@@ -34154,7 +34154,7 @@
         <v>8.57460308074951</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.23693180084229</v>
+        <v>5.2369327545166</v>
       </c>
       <c r="H1165" t="n">
         <v>12850684</v>
@@ -34212,7 +34212,7 @@
         <v>8.91910552978516</v>
       </c>
       <c r="G1167" t="n">
-        <v>5.44733715057373</v>
+        <v>5.44733667373657</v>
       </c>
       <c r="H1167" t="n">
         <v>9652262</v>
@@ -34241,7 +34241,7 @@
         <v>8.8242015838623</v>
       </c>
       <c r="G1168" t="n">
-        <v>5.38937425613403</v>
+        <v>5.38937473297119</v>
       </c>
       <c r="H1168" t="n">
         <v>11368887</v>
@@ -34299,7 +34299,7 @@
         <v>8.96371078491211</v>
       </c>
       <c r="G1170" t="n">
-        <v>5.47457981109619</v>
+        <v>5.47457885742188</v>
       </c>
       <c r="H1170" t="n">
         <v>5068327</v>
@@ -34415,7 +34415,7 @@
         <v>9.19622611999512</v>
       </c>
       <c r="G1174" t="n">
-        <v>5.61658811569214</v>
+        <v>5.61658763885498</v>
       </c>
       <c r="H1174" t="n">
         <v>5783149</v>
@@ -34618,7 +34618,7 @@
         <v>9.03204154968262</v>
       </c>
       <c r="G1181" t="n">
-        <v>5.51631259918213</v>
+        <v>5.51631307601929</v>
       </c>
       <c r="H1181" t="n">
         <v>6075255</v>
@@ -34647,7 +34647,7 @@
         <v>9.08234119415283</v>
       </c>
       <c r="G1182" t="n">
-        <v>5.54703283309937</v>
+        <v>5.54703378677368</v>
       </c>
       <c r="H1182" t="n">
         <v>5426567</v>
@@ -34676,7 +34676,7 @@
         <v>8.96845626831055</v>
       </c>
       <c r="G1183" t="n">
-        <v>5.47747850418091</v>
+        <v>5.47747802734375</v>
       </c>
       <c r="H1183" t="n">
         <v>6281169</v>
@@ -34705,7 +34705,7 @@
         <v>8.93523979187012</v>
       </c>
       <c r="G1184" t="n">
-        <v>5.457190990448</v>
+        <v>5.45719146728516</v>
       </c>
       <c r="H1184" t="n">
         <v>6926510</v>
@@ -34734,7 +34734,7 @@
         <v>8.76061630249023</v>
       </c>
       <c r="G1185" t="n">
-        <v>5.35053968429565</v>
+        <v>5.3505392074585</v>
       </c>
       <c r="H1185" t="n">
         <v>6811072</v>
@@ -34763,7 +34763,7 @@
         <v>8.65717029571533</v>
       </c>
       <c r="G1186" t="n">
-        <v>5.28735971450806</v>
+        <v>5.28736019134521</v>
       </c>
       <c r="H1186" t="n">
         <v>8371595</v>
@@ -34821,7 +34821,7 @@
         <v>8.80617046356201</v>
       </c>
       <c r="G1188" t="n">
-        <v>5.37836170196533</v>
+        <v>5.37836217880249</v>
       </c>
       <c r="H1188" t="n">
         <v>14198366</v>
@@ -34879,7 +34879,7 @@
         <v>9.14402866363525</v>
       </c>
       <c r="G1190" t="n">
-        <v>5.58470869064331</v>
+        <v>5.58470916748047</v>
       </c>
       <c r="H1190" t="n">
         <v>8524338</v>
@@ -34908,7 +34908,7 @@
         <v>9.12125205993652</v>
       </c>
       <c r="G1191" t="n">
-        <v>5.57079792022705</v>
+        <v>5.57079839706421</v>
       </c>
       <c r="H1191" t="n">
         <v>6203598</v>
@@ -34966,7 +34966,7 @@
         <v>9.38223934173584</v>
       </c>
       <c r="G1193" t="n">
-        <v>5.73019552230835</v>
+        <v>5.73019504547119</v>
       </c>
       <c r="H1193" t="n">
         <v>19751217</v>
@@ -35053,7 +35053,7 @@
         <v>10.327486038208</v>
       </c>
       <c r="G1196" t="n">
-        <v>6.30750417709351</v>
+        <v>6.30750465393066</v>
       </c>
       <c r="H1196" t="n">
         <v>43218612</v>
@@ -35082,7 +35082,7 @@
         <v>10.2610530853271</v>
       </c>
       <c r="G1197" t="n">
-        <v>6.266930103302</v>
+        <v>6.26692962646484</v>
       </c>
       <c r="H1197" t="n">
         <v>15867956</v>
@@ -35111,7 +35111,7 @@
         <v>10.2154989242554</v>
       </c>
       <c r="G1198" t="n">
-        <v>6.23910808563232</v>
+        <v>6.23910856246948</v>
       </c>
       <c r="H1198" t="n">
         <v>8799322</v>
@@ -35140,7 +35140,7 @@
         <v>9.8491678237915</v>
       </c>
       <c r="G1199" t="n">
-        <v>6.01537179946899</v>
+        <v>6.01537227630615</v>
       </c>
       <c r="H1199" t="n">
         <v>13428051</v>
@@ -35198,7 +35198,7 @@
         <v>9.69732093811035</v>
       </c>
       <c r="G1201" t="n">
-        <v>5.92263126373291</v>
+        <v>5.92263174057007</v>
       </c>
       <c r="H1201" t="n">
         <v>11313802</v>
@@ -35314,7 +35314,7 @@
         <v>10.0940208435059</v>
       </c>
       <c r="G1205" t="n">
-        <v>6.16491508483887</v>
+        <v>6.16491460800171</v>
       </c>
       <c r="H1205" t="n">
         <v>14814702</v>
@@ -35343,7 +35343,7 @@
         <v>9.85865879058838</v>
       </c>
       <c r="G1206" t="n">
-        <v>6.02116775512695</v>
+        <v>6.02116823196411</v>
       </c>
       <c r="H1206" t="n">
         <v>8215276</v>
@@ -35401,7 +35401,7 @@
         <v>9.8491678237915</v>
       </c>
       <c r="G1208" t="n">
-        <v>6.01537179946899</v>
+        <v>6.01537227630615</v>
       </c>
       <c r="H1208" t="n">
         <v>10638058</v>
@@ -35430,7 +35430,7 @@
         <v>9.82259464263916</v>
       </c>
       <c r="G1209" t="n">
-        <v>5.99914216995239</v>
+        <v>5.99914264678955</v>
       </c>
       <c r="H1209" t="n">
         <v>5637822</v>
@@ -35459,7 +35459,7 @@
         <v>9.94976711273193</v>
       </c>
       <c r="G1210" t="n">
-        <v>6.07681274414062</v>
+        <v>6.07681322097778</v>
       </c>
       <c r="H1210" t="n">
         <v>6832677</v>
@@ -35488,7 +35488,7 @@
         <v>10.1281871795654</v>
       </c>
       <c r="G1211" t="n">
-        <v>6.18578338623047</v>
+        <v>6.18578243255615</v>
       </c>
       <c r="H1211" t="n">
         <v>12156025</v>
@@ -35517,7 +35517,7 @@
         <v>10.1566581726074</v>
       </c>
       <c r="G1212" t="n">
-        <v>6.20317125320435</v>
+        <v>6.2031717300415</v>
       </c>
       <c r="H1212" t="n">
         <v>10333545</v>
@@ -35546,7 +35546,7 @@
         <v>10.1357793807983</v>
       </c>
       <c r="G1213" t="n">
-        <v>6.19042015075684</v>
+        <v>6.19041967391968</v>
       </c>
       <c r="H1213" t="n">
         <v>8045845</v>
@@ -35604,7 +35604,7 @@
         <v>10.0921230316162</v>
       </c>
       <c r="G1215" t="n">
-        <v>6.16375732421875</v>
+        <v>6.16375637054443</v>
       </c>
       <c r="H1215" t="n">
         <v>7530729</v>
@@ -35662,7 +35662,7 @@
         <v>10.0313844680786</v>
       </c>
       <c r="G1217" t="n">
-        <v>6.12665987014771</v>
+        <v>6.12666082382202</v>
       </c>
       <c r="H1217" t="n">
         <v>6967421</v>
@@ -35836,7 +35836,7 @@
         <v>10.4091033935547</v>
       </c>
       <c r="G1223" t="n">
-        <v>6.3573522567749</v>
+        <v>6.35735177993774</v>
       </c>
       <c r="H1223" t="n">
         <v>10980762</v>
@@ -35894,7 +35894,7 @@
         <v>10.6103010177612</v>
       </c>
       <c r="G1225" t="n">
-        <v>6.48023223876953</v>
+        <v>6.48023319244385</v>
       </c>
       <c r="H1225" t="n">
         <v>23024056</v>
@@ -35923,7 +35923,7 @@
         <v>10.4337787628174</v>
       </c>
       <c r="G1226" t="n">
-        <v>6.37242269515991</v>
+        <v>6.37242221832275</v>
       </c>
       <c r="H1226" t="n">
         <v>11951147</v>
@@ -35952,7 +35952,7 @@
         <v>10.0294857025146</v>
       </c>
       <c r="G1227" t="n">
-        <v>6.12550115585327</v>
+        <v>6.12550067901611</v>
       </c>
       <c r="H1227" t="n">
         <v>18369110</v>
@@ -36010,7 +36010,7 @@
         <v>10.0048112869263</v>
       </c>
       <c r="G1229" t="n">
-        <v>6.1104302406311</v>
+        <v>6.11043071746826</v>
       </c>
       <c r="H1229" t="n">
         <v>8566779</v>
@@ -36039,7 +36039,7 @@
         <v>10.2686452865601</v>
       </c>
       <c r="G1230" t="n">
-        <v>6.27156686782837</v>
+        <v>6.27156734466553</v>
       </c>
       <c r="H1230" t="n">
         <v>10507665</v>
@@ -36068,7 +36068,7 @@
         <v>10.4451665878296</v>
       </c>
       <c r="G1231" t="n">
-        <v>6.3793773651123</v>
+        <v>6.37937688827515</v>
       </c>
       <c r="H1231" t="n">
         <v>12114251</v>
@@ -36097,7 +36097,7 @@
         <v>10.6008100509644</v>
       </c>
       <c r="G1232" t="n">
-        <v>6.47443771362305</v>
+        <v>6.47443675994873</v>
       </c>
       <c r="H1232" t="n">
         <v>13120481</v>
@@ -36155,7 +36155,7 @@
         <v>10.6634473800659</v>
       </c>
       <c r="G1234" t="n">
-        <v>6.51269292831421</v>
+        <v>6.51269245147705</v>
       </c>
       <c r="H1234" t="n">
         <v>14734096</v>
@@ -36184,7 +36184,7 @@
         <v>11.3144912719727</v>
       </c>
       <c r="G1235" t="n">
-        <v>6.91031694412231</v>
+        <v>6.91031742095947</v>
       </c>
       <c r="H1235" t="n">
         <v>26097768</v>
@@ -36242,7 +36242,7 @@
         <v>11.6941080093384</v>
       </c>
       <c r="G1237" t="n">
-        <v>7.14216804504395</v>
+        <v>7.14216709136963</v>
       </c>
       <c r="H1237" t="n">
         <v>12790303</v>
@@ -36271,7 +36271,7 @@
         <v>11.4473571777344</v>
       </c>
       <c r="G1238" t="n">
-        <v>6.99146413803101</v>
+        <v>6.99146556854248</v>
       </c>
       <c r="H1238" t="n">
         <v>12168076</v>
@@ -36329,7 +36329,7 @@
         <v>11.9484510421753</v>
       </c>
       <c r="G1240" t="n">
-        <v>7.29750633239746</v>
+        <v>7.29750728607178</v>
       </c>
       <c r="H1240" t="n">
         <v>15710143</v>
@@ -36387,7 +36387,7 @@
         <v>12.0319671630859</v>
       </c>
       <c r="G1242" t="n">
-        <v>7.34851551055908</v>
+        <v>7.34851408004761</v>
       </c>
       <c r="H1242" t="n">
         <v>11296797</v>
@@ -36416,7 +36416,7 @@
         <v>12.2806158065796</v>
       </c>
       <c r="G1243" t="n">
-        <v>7.50037670135498</v>
+        <v>7.50037717819214</v>
       </c>
       <c r="H1243" t="n">
         <v>14800237</v>
@@ -36445,7 +36445,7 @@
         <v>12.2236738204956</v>
       </c>
       <c r="G1244" t="n">
-        <v>7.46559906005859</v>
+        <v>7.46560001373291</v>
       </c>
       <c r="H1244" t="n">
         <v>9449671</v>
@@ -36503,7 +36503,7 @@
         <v>12.4267692565918</v>
       </c>
       <c r="G1246" t="n">
-        <v>7.58964014053345</v>
+        <v>7.58964061737061</v>
       </c>
       <c r="H1246" t="n">
         <v>11547460</v>
@@ -36532,7 +36532,7 @@
         <v>12.5121831893921</v>
       </c>
       <c r="G1247" t="n">
-        <v>7.64180612564087</v>
+        <v>7.64180660247803</v>
       </c>
       <c r="H1247" t="n">
         <v>12635167</v>
@@ -36561,7 +36561,7 @@
         <v>12.4210748672485</v>
       </c>
       <c r="G1248" t="n">
-        <v>7.5861611366272</v>
+        <v>7.58616256713867</v>
       </c>
       <c r="H1248" t="n">
         <v>5569708</v>
@@ -36619,7 +36619,7 @@
         <v>12.4001960754395</v>
       </c>
       <c r="G1250" t="n">
-        <v>7.57341003417969</v>
+        <v>7.573410987854</v>
       </c>
       <c r="H1250" t="n">
         <v>9534538</v>
@@ -36648,7 +36648,7 @@
         <v>12.5539407730103</v>
       </c>
       <c r="G1251" t="n">
-        <v>7.66730976104736</v>
+        <v>7.66731119155884</v>
       </c>
       <c r="H1251" t="n">
         <v>8910574</v>
@@ -36677,7 +36677,7 @@
         <v>12.5083866119385</v>
       </c>
       <c r="G1252" t="n">
-        <v>7.639488697052</v>
+        <v>7.63948774337769</v>
       </c>
       <c r="H1252" t="n">
         <v>7197930</v>
@@ -36706,7 +36706,7 @@
         <v>12.5558385848999</v>
       </c>
       <c r="G1253" t="n">
-        <v>7.66846990585327</v>
+        <v>7.66846895217896</v>
       </c>
       <c r="H1253" t="n">
         <v>8361176</v>
@@ -36735,7 +36735,7 @@
         <v>12.8595333099365</v>
       </c>
       <c r="G1254" t="n">
-        <v>7.85395097732544</v>
+        <v>7.85394954681396</v>
       </c>
       <c r="H1254" t="n">
         <v>13541806</v>
@@ -36764,7 +36764,7 @@
         <v>12.7760171890259</v>
       </c>
       <c r="G1255" t="n">
-        <v>7.80294322967529</v>
+        <v>7.80294275283813</v>
       </c>
       <c r="H1255" t="n">
         <v>8814988</v>
@@ -36793,7 +36793,7 @@
         <v>12.7228698730469</v>
       </c>
       <c r="G1256" t="n">
-        <v>7.77048397064209</v>
+        <v>7.77048254013062</v>
       </c>
       <c r="H1256" t="n">
         <v>5417455</v>
@@ -36822,7 +36822,7 @@
         <v>13.0740156173706</v>
       </c>
       <c r="G1257" t="n">
-        <v>7.98494482040405</v>
+        <v>7.98494529724121</v>
       </c>
       <c r="H1257" t="n">
         <v>14379979</v>
@@ -36851,7 +36851,7 @@
         <v>13.12526512146</v>
       </c>
       <c r="G1258" t="n">
-        <v>8.01624488830566</v>
+        <v>8.01624584197998</v>
       </c>
       <c r="H1258" t="n">
         <v>16646161</v>
@@ -36880,7 +36880,7 @@
         <v>12.9449462890625</v>
       </c>
       <c r="G1259" t="n">
-        <v>7.90611696243286</v>
+        <v>7.90611600875854</v>
       </c>
       <c r="H1259" t="n">
         <v>8808025</v>
@@ -36967,7 +36967,7 @@
         <v>13.5846014022827</v>
       </c>
       <c r="G1262" t="n">
-        <v>8.29678344726562</v>
+        <v>8.29678440093994</v>
       </c>
       <c r="H1262" t="n">
         <v>13487197</v>
@@ -36996,7 +36996,7 @@
         <v>13.670015335083</v>
       </c>
       <c r="G1263" t="n">
-        <v>8.348952293396</v>
+        <v>8.34895133972168</v>
       </c>
       <c r="H1263" t="n">
         <v>10369090</v>
@@ -37054,7 +37054,7 @@
         <v>13.5238628387451</v>
       </c>
       <c r="G1265" t="n">
-        <v>8.25968837738037</v>
+        <v>8.259690284729</v>
       </c>
       <c r="H1265" t="n">
         <v>19283533</v>
@@ -37112,7 +37112,7 @@
         <v>13.9433403015137</v>
       </c>
       <c r="G1267" t="n">
-        <v>8.5158863067627</v>
+        <v>8.51588439941406</v>
       </c>
       <c r="H1267" t="n">
         <v>8749044</v>
@@ -37141,7 +37141,7 @@
         <v>14.0325498580933</v>
       </c>
       <c r="G1268" t="n">
-        <v>8.57036972045898</v>
+        <v>8.57036876678467</v>
       </c>
       <c r="H1268" t="n">
         <v>7784092</v>
@@ -37170,7 +37170,7 @@
         <v>13.9395437240601</v>
       </c>
       <c r="G1269" t="n">
-        <v>8.51356506347656</v>
+        <v>8.51356601715088</v>
       </c>
       <c r="H1269" t="n">
         <v>10033435</v>
@@ -37199,7 +37199,7 @@
         <v>13.9129695892334</v>
       </c>
       <c r="G1270" t="n">
-        <v>8.49733543395996</v>
+        <v>8.49733638763428</v>
       </c>
       <c r="H1270" t="n">
         <v>6249016</v>
@@ -37228,7 +37228,7 @@
         <v>14.1217603683472</v>
       </c>
       <c r="G1271" t="n">
-        <v>8.62485408782959</v>
+        <v>8.62485504150391</v>
       </c>
       <c r="H1271" t="n">
         <v>19895535</v>
@@ -37315,7 +37315,7 @@
         <v>14.0344476699829</v>
       </c>
       <c r="G1274" t="n">
-        <v>8.57152938842773</v>
+        <v>8.5715274810791</v>
       </c>
       <c r="H1274" t="n">
         <v>12920368</v>
@@ -37402,7 +37402,7 @@
         <v>13.9262571334839</v>
       </c>
       <c r="G1277" t="n">
-        <v>8.50545024871826</v>
+        <v>8.50545120239258</v>
       </c>
       <c r="H1277" t="n">
         <v>12728976</v>
@@ -37431,7 +37431,7 @@
         <v>13.8674163818359</v>
       </c>
       <c r="G1278" t="n">
-        <v>8.46951484680176</v>
+        <v>8.46951389312744</v>
       </c>
       <c r="H1278" t="n">
         <v>15059110</v>
@@ -37460,7 +37460,7 @@
         <v>12.4723234176636</v>
       </c>
       <c r="G1279" t="n">
-        <v>8.78280925750732</v>
+        <v>8.78281021118164</v>
       </c>
       <c r="H1279" t="n">
         <v>22700747</v>
@@ -37489,7 +37489,7 @@
         <v>11.9294700622559</v>
       </c>
       <c r="G1280" t="n">
-        <v>8.40054130554199</v>
+        <v>8.40054225921631</v>
       </c>
       <c r="H1280" t="n">
         <v>45369038</v>
@@ -37518,7 +37518,7 @@
         <v>11.9294700622559</v>
       </c>
       <c r="G1281" t="n">
-        <v>8.40054130554199</v>
+        <v>8.40054225921631</v>
       </c>
       <c r="H1281" t="n">
         <v>0</v>
@@ -37576,7 +37576,7 @@
         <v>13.2372522354126</v>
       </c>
       <c r="G1283" t="n">
-        <v>9.32146167755127</v>
+        <v>9.32146072387695</v>
       </c>
       <c r="H1283" t="n">
         <v>21595725</v>
@@ -37605,7 +37605,7 @@
         <v>12.9506406784058</v>
       </c>
       <c r="G1284" t="n">
-        <v>9.11963367462158</v>
+        <v>9.1196346282959</v>
       </c>
       <c r="H1284" t="n">
         <v>19585832</v>
@@ -37634,7 +37634,7 @@
         <v>12.5653285980225</v>
       </c>
       <c r="G1285" t="n">
-        <v>8.84830284118652</v>
+        <v>8.84830379486084</v>
       </c>
       <c r="H1285" t="n">
         <v>23123548</v>
@@ -37692,7 +37692,7 @@
         <v>12.2160806655884</v>
       </c>
       <c r="G1287" t="n">
-        <v>8.60236930847168</v>
+        <v>8.60236835479736</v>
       </c>
       <c r="H1287" t="n">
         <v>15668469</v>
@@ -37721,7 +37721,7 @@
         <v>11.7947063446045</v>
       </c>
       <c r="G1288" t="n">
-        <v>8.30564403533936</v>
+        <v>8.30564308166504</v>
       </c>
       <c r="H1288" t="n">
         <v>21156645</v>
@@ -37750,7 +37750,7 @@
         <v>12.0699291229248</v>
       </c>
       <c r="G1289" t="n">
-        <v>8.49944972991943</v>
+        <v>8.49945068359375</v>
       </c>
       <c r="H1289" t="n">
         <v>20647766</v>
@@ -37808,7 +37808,7 @@
         <v>11.9636363983154</v>
       </c>
       <c r="G1291" t="n">
-        <v>8.42460155487061</v>
+        <v>8.42460060119629</v>
       </c>
       <c r="H1291" t="n">
         <v>10479299</v>
@@ -37837,7 +37837,7 @@
         <v>12.328067779541</v>
       </c>
       <c r="G1292" t="n">
-        <v>8.68122863769531</v>
+        <v>8.681227684021</v>
       </c>
       <c r="H1292" t="n">
         <v>16271807</v>
@@ -37924,7 +37924,7 @@
         <v>12.6830110549927</v>
       </c>
       <c r="G1295" t="n">
-        <v>8.93117427825928</v>
+        <v>8.93117332458496</v>
       </c>
       <c r="H1295" t="n">
         <v>17565417</v>
@@ -38069,7 +38069,7 @@
         <v>12.5900039672852</v>
       </c>
       <c r="G1300" t="n">
-        <v>8.86567878723145</v>
+        <v>8.86567974090576</v>
       </c>
       <c r="H1300" t="n">
         <v>7794162</v>
@@ -38098,7 +38098,7 @@
         <v>12.7209720611572</v>
       </c>
       <c r="G1301" t="n">
-        <v>8.95790386199951</v>
+        <v>8.95790576934814</v>
       </c>
       <c r="H1301" t="n">
         <v>7278681</v>
@@ -38127,7 +38127,7 @@
         <v>12.8120803833008</v>
       </c>
       <c r="G1302" t="n">
-        <v>9.02206230163574</v>
+        <v>9.02206134796143</v>
       </c>
       <c r="H1302" t="n">
         <v>8396731</v>
@@ -38156,7 +38156,7 @@
         <v>12.5368576049805</v>
       </c>
       <c r="G1303" t="n">
-        <v>8.82825565338135</v>
+        <v>8.82825469970703</v>
       </c>
       <c r="H1303" t="n">
         <v>10867776</v>
@@ -38185,7 +38185,7 @@
         <v>12.6070871353149</v>
       </c>
       <c r="G1304" t="n">
-        <v>8.87770843505859</v>
+        <v>8.87770938873291</v>
       </c>
       <c r="H1304" t="n">
         <v>12787296</v>
@@ -38214,7 +38214,7 @@
         <v>12.6981954574585</v>
       </c>
       <c r="G1305" t="n">
-        <v>8.94186496734619</v>
+        <v>8.94186592102051</v>
       </c>
       <c r="H1305" t="n">
         <v>11976974</v>
@@ -38272,7 +38272,7 @@
         <v>12.5956993103027</v>
       </c>
       <c r="G1307" t="n">
-        <v>8.86969089508057</v>
+        <v>8.86968994140625</v>
       </c>
       <c r="H1307" t="n">
         <v>12231243</v>
@@ -38330,7 +38330,7 @@
         <v>12.8671245574951</v>
       </c>
       <c r="G1309" t="n">
-        <v>9.06082248687744</v>
+        <v>9.06082344055176</v>
       </c>
       <c r="H1309" t="n">
         <v>9826027</v>
@@ -38388,7 +38388,7 @@
         <v>13.2144746780396</v>
       </c>
       <c r="G1311" t="n">
-        <v>9.30542182922363</v>
+        <v>9.30542087554932</v>
       </c>
       <c r="H1311" t="n">
         <v>15170002</v>
@@ -38417,7 +38417,7 @@
         <v>13.1860027313232</v>
       </c>
       <c r="G1312" t="n">
-        <v>9.28537273406982</v>
+        <v>9.28537178039551</v>
       </c>
       <c r="H1312" t="n">
         <v>14812722</v>
@@ -38562,7 +38562,7 @@
         <v>13.996485710144</v>
       </c>
       <c r="G1317" t="n">
-        <v>9.85610008239746</v>
+        <v>9.85610103607178</v>
       </c>
       <c r="H1317" t="n">
         <v>18684880</v>
@@ -38591,7 +38591,7 @@
         <v>14.2830972671509</v>
       </c>
       <c r="G1318" t="n">
-        <v>10.0579290390015</v>
+        <v>10.0579280853271</v>
       </c>
       <c r="H1318" t="n">
         <v>18872699</v>
@@ -38649,7 +38649,7 @@
         <v>14.6494283676147</v>
       </c>
       <c r="G1320" t="n">
-        <v>10.3158922195435</v>
+        <v>10.3158931732178</v>
       </c>
       <c r="H1320" t="n">
         <v>19043847</v>
@@ -38794,7 +38794,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1325" t="n">
-        <v>10.5969982147217</v>
+        <v>10.596999168396</v>
       </c>
       <c r="H1325" t="n">
         <v>28239181</v>
@@ -38852,7 +38852,7 @@
         <v>14.1940002441406</v>
       </c>
       <c r="G1327" t="n">
-        <v>10.1288766860962</v>
+        <v>10.1288757324219</v>
       </c>
       <c r="H1327" t="n">
         <v>15211229</v>
@@ -38968,7 +38968,7 @@
         <v>14.6619997024536</v>
       </c>
       <c r="G1331" t="n">
-        <v>10.4628410339355</v>
+        <v>10.4628419876099</v>
       </c>
       <c r="H1331" t="n">
         <v>8470881</v>
@@ -39055,7 +39055,7 @@
         <v>15.1359996795654</v>
       </c>
       <c r="G1334" t="n">
-        <v>10.8010902404785</v>
+        <v>10.8010892868042</v>
       </c>
       <c r="H1334" t="n">
         <v>8000397</v>
@@ -39084,7 +39084,7 @@
         <v>15.2919998168945</v>
       </c>
       <c r="G1335" t="n">
-        <v>10.912410736084</v>
+        <v>10.9124116897583</v>
       </c>
       <c r="H1335" t="n">
         <v>17012730</v>
@@ -39113,7 +39113,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G1336" t="n">
-        <v>10.9109840393066</v>
+        <v>10.9109830856323</v>
       </c>
       <c r="H1336" t="n">
         <v>10302029</v>
@@ -39200,7 +39200,7 @@
         <v>14.9379997253418</v>
       </c>
       <c r="G1339" t="n">
-        <v>10.6597967147827</v>
+        <v>10.6597957611084</v>
       </c>
       <c r="H1339" t="n">
         <v>7134497</v>
@@ -39229,7 +39229,7 @@
         <v>15.1459999084473</v>
       </c>
       <c r="G1340" t="n">
-        <v>10.8082246780396</v>
+        <v>10.8082256317139</v>
       </c>
       <c r="H1340" t="n">
         <v>10689036</v>
@@ -39258,7 +39258,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1341" t="n">
-        <v>10.7397203445435</v>
+        <v>10.7397193908691</v>
       </c>
       <c r="H1341" t="n">
         <v>9515966</v>
@@ -39316,7 +39316,7 @@
         <v>15.2620000839233</v>
       </c>
       <c r="G1343" t="n">
-        <v>10.8910026550293</v>
+        <v>10.8910036087036</v>
       </c>
       <c r="H1343" t="n">
         <v>14462123</v>
@@ -39345,7 +39345,7 @@
         <v>14.7919998168945</v>
       </c>
       <c r="G1344" t="n">
-        <v>10.7816705703735</v>
+        <v>10.7816715240479</v>
       </c>
       <c r="H1344" t="n">
         <v>12982562</v>
@@ -39403,7 +39403,7 @@
         <v>14.3439998626709</v>
       </c>
       <c r="G1346" t="n">
-        <v>10.4551305770874</v>
+        <v>10.4551296234131</v>
       </c>
       <c r="H1346" t="n">
         <v>10648764</v>
@@ -39490,7 +39490,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1349" t="n">
-        <v>10.4667911529541</v>
+        <v>10.4667930603027</v>
       </c>
       <c r="H1349" t="n">
         <v>6149041</v>
@@ -39548,7 +39548,7 @@
         <v>14.3920001983643</v>
       </c>
       <c r="G1351" t="n">
-        <v>10.4901170730591</v>
+        <v>10.4901161193848</v>
       </c>
       <c r="H1351" t="n">
         <v>5660495</v>
@@ -39635,7 +39635,7 @@
         <v>14.0220003128052</v>
       </c>
       <c r="G1354" t="n">
-        <v>10.2204303741455</v>
+        <v>10.2204294204712</v>
       </c>
       <c r="H1354" t="n">
         <v>7464291</v>
@@ -39693,7 +39693,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1356" t="n">
-        <v>10.8312349319458</v>
+        <v>10.8312358856201</v>
       </c>
       <c r="H1356" t="n">
         <v>19667797</v>
@@ -39722,7 +39722,7 @@
         <v>14.9139995574951</v>
       </c>
       <c r="G1357" t="n">
-        <v>10.8705940246582</v>
+        <v>10.8705949783325</v>
       </c>
       <c r="H1357" t="n">
         <v>14377159</v>
@@ -39780,7 +39780,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1359" t="n">
-        <v>11.0061674118042</v>
+        <v>11.0061683654785</v>
       </c>
       <c r="H1359" t="n">
         <v>11010985</v>
@@ -39896,7 +39896,7 @@
         <v>14.8559999465942</v>
       </c>
       <c r="G1363" t="n">
-        <v>10.8283195495605</v>
+        <v>10.8283205032349</v>
       </c>
       <c r="H1363" t="n">
         <v>8563582</v>
@@ -39925,7 +39925,7 @@
         <v>15.0979995727539</v>
       </c>
       <c r="G1364" t="n">
-        <v>11.0047101974487</v>
+        <v>11.0047092437744</v>
       </c>
       <c r="H1364" t="n">
         <v>12737338</v>
@@ -40099,7 +40099,7 @@
         <v>15.4739999771118</v>
       </c>
       <c r="G1370" t="n">
-        <v>11.2787714004517</v>
+        <v>11.2787704467773</v>
       </c>
       <c r="H1370" t="n">
         <v>10835902</v>
@@ -40186,7 +40186,7 @@
         <v>16.1060009002686</v>
       </c>
       <c r="G1373" t="n">
-        <v>11.739426612854</v>
+        <v>11.7394275665283</v>
       </c>
       <c r="H1373" t="n">
         <v>14181999</v>
@@ -40302,7 +40302,7 @@
         <v>16.6979999542236</v>
       </c>
       <c r="G1377" t="n">
-        <v>12.1709260940552</v>
+        <v>12.1709251403809</v>
       </c>
       <c r="H1377" t="n">
         <v>13263315</v>
@@ -40389,7 +40389,7 @@
         <v>17.4759998321533</v>
       </c>
       <c r="G1380" t="n">
-        <v>12.7379989624023</v>
+        <v>12.737998008728</v>
       </c>
       <c r="H1380" t="n">
         <v>15650056</v>
@@ -40418,7 +40418,7 @@
         <v>17.2320003509521</v>
       </c>
       <c r="G1381" t="n">
-        <v>12.5601511001587</v>
+        <v>12.560152053833</v>
       </c>
       <c r="H1381" t="n">
         <v>10798544</v>
@@ -40505,7 +40505,7 @@
         <v>16.9680004119873</v>
       </c>
       <c r="G1384" t="n">
-        <v>12.3677253723145</v>
+        <v>12.3677263259888</v>
       </c>
       <c r="H1384" t="n">
         <v>9417505</v>
@@ -40534,7 +40534,7 @@
         <v>16.8980007171631</v>
       </c>
       <c r="G1385" t="n">
-        <v>12.3167028427124</v>
+        <v>12.3167037963867</v>
       </c>
       <c r="H1385" t="n">
         <v>7079670</v>
@@ -40563,7 +40563,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1386" t="n">
-        <v>12.3181600570679</v>
+        <v>12.3181610107422</v>
       </c>
       <c r="H1386" t="n">
         <v>12774845</v>
@@ -40592,7 +40592,7 @@
         <v>16.9580001831055</v>
       </c>
       <c r="G1387" t="n">
-        <v>12.3604364395142</v>
+        <v>12.3604373931885</v>
       </c>
       <c r="H1387" t="n">
         <v>10581252</v>
@@ -40621,7 +40621,7 @@
         <v>16.4640007019043</v>
       </c>
       <c r="G1388" t="n">
-        <v>12.0003671646118</v>
+        <v>12.0003681182861</v>
       </c>
       <c r="H1388" t="n">
         <v>20152531</v>
@@ -40679,7 +40679,7 @@
         <v>16.9860000610352</v>
       </c>
       <c r="G1390" t="n">
-        <v>12.3808441162109</v>
+        <v>12.3808450698853</v>
       </c>
       <c r="H1390" t="n">
         <v>7752292</v>
@@ -40766,7 +40766,7 @@
         <v>17.0620002746582</v>
       </c>
       <c r="G1393" t="n">
-        <v>12.4362411499023</v>
+        <v>12.436240196228</v>
       </c>
       <c r="H1393" t="n">
         <v>7418861</v>
@@ -40795,7 +40795,7 @@
         <v>16.8419990539551</v>
       </c>
       <c r="G1394" t="n">
-        <v>12.2758846282959</v>
+        <v>12.2758855819702</v>
       </c>
       <c r="H1394" t="n">
         <v>8997665</v>
@@ -40882,7 +40882,7 @@
         <v>16.7019996643066</v>
       </c>
       <c r="G1397" t="n">
-        <v>12.1738405227661</v>
+        <v>12.1738414764404</v>
       </c>
       <c r="H1397" t="n">
         <v>7156812</v>
@@ -40911,7 +40911,7 @@
         <v>16.6979999542236</v>
       </c>
       <c r="G1398" t="n">
-        <v>12.1709260940552</v>
+        <v>12.1709251403809</v>
       </c>
       <c r="H1398" t="n">
         <v>5839495</v>
@@ -40998,7 +40998,7 @@
         <v>16.5919990539551</v>
       </c>
       <c r="G1401" t="n">
-        <v>12.0936641693115</v>
+        <v>12.0936632156372</v>
       </c>
       <c r="H1401" t="n">
         <v>11656240</v>
@@ -41027,7 +41027,7 @@
         <v>16.0359992980957</v>
       </c>
       <c r="G1402" t="n">
-        <v>11.6884031295776</v>
+        <v>11.688404083252</v>
       </c>
       <c r="H1402" t="n">
         <v>19081376</v>
@@ -41114,7 +41114,7 @@
         <v>16.2479991912842</v>
       </c>
       <c r="G1405" t="n">
-        <v>11.8429279327393</v>
+        <v>11.8429269790649</v>
       </c>
       <c r="H1405" t="n">
         <v>6940441</v>
@@ -41201,7 +41201,7 @@
         <v>15.6859998703003</v>
       </c>
       <c r="G1408" t="n">
-        <v>11.4332933425903</v>
+        <v>11.4332942962646</v>
       </c>
       <c r="H1408" t="n">
         <v>8195845</v>
@@ -41259,7 +41259,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1410" t="n">
-        <v>11.0499000549316</v>
+        <v>11.049901008606</v>
       </c>
       <c r="H1410" t="n">
         <v>9275450</v>
@@ -41288,7 +41288,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1411" t="n">
-        <v>11.4289216995239</v>
+        <v>11.4289207458496</v>
       </c>
       <c r="H1411" t="n">
         <v>9330788</v>
@@ -41346,7 +41346,7 @@
         <v>15.7519998550415</v>
       </c>
       <c r="G1413" t="n">
-        <v>11.4813995361328</v>
+        <v>11.4814004898071</v>
       </c>
       <c r="H1413" t="n">
         <v>6245286</v>
@@ -41462,7 +41462,7 @@
         <v>16.3540000915527</v>
       </c>
       <c r="G1417" t="n">
-        <v>11.9201898574829</v>
+        <v>11.9201889038086</v>
       </c>
       <c r="H1417" t="n">
         <v>9237091</v>
@@ -41549,7 +41549,7 @@
         <v>17.0620002746582</v>
       </c>
       <c r="G1420" t="n">
-        <v>12.4362411499023</v>
+        <v>12.436240196228</v>
       </c>
       <c r="H1420" t="n">
         <v>22351876</v>
@@ -41607,7 +41607,7 @@
         <v>17.4440002441406</v>
       </c>
       <c r="G1422" t="n">
-        <v>12.7146739959717</v>
+        <v>12.714674949646</v>
       </c>
       <c r="H1422" t="n">
         <v>12451584</v>
@@ -41636,7 +41636,7 @@
         <v>17.8740005493164</v>
       </c>
       <c r="G1423" t="n">
-        <v>13.0280961990356</v>
+        <v>13.0280952453613</v>
       </c>
       <c r="H1423" t="n">
         <v>17413106</v>
@@ -41665,7 +41665,7 @@
         <v>17.996000289917</v>
       </c>
       <c r="G1424" t="n">
-        <v>13.1170196533203</v>
+        <v>13.117018699646</v>
       </c>
       <c r="H1424" t="n">
         <v>9916408</v>
@@ -41752,7 +41752,7 @@
         <v>18.4979991912842</v>
       </c>
       <c r="G1427" t="n">
-        <v>13.4829168319702</v>
+        <v>13.4829187393188</v>
       </c>
       <c r="H1427" t="n">
         <v>12643699</v>
@@ -41839,7 +41839,7 @@
         <v>17.8439998626709</v>
       </c>
       <c r="G1430" t="n">
-        <v>13.0062294006348</v>
+        <v>13.0062284469604</v>
       </c>
       <c r="H1430" t="n">
         <v>12382803</v>
@@ -42100,7 +42100,7 @@
         <v>17.0179996490479</v>
       </c>
       <c r="G1439" t="n">
-        <v>12.4041690826416</v>
+        <v>12.4041700363159</v>
       </c>
       <c r="H1439" t="n">
         <v>6510591</v>
@@ -42274,7 +42274,7 @@
         <v>17.0860004425049</v>
       </c>
       <c r="G1445" t="n">
-        <v>12.4537343978882</v>
+        <v>12.4537353515625</v>
       </c>
       <c r="H1445" t="n">
         <v>8809835</v>
@@ -42390,7 +42390,7 @@
         <v>16.8279991149902</v>
       </c>
       <c r="G1449" t="n">
-        <v>12.2656803131104</v>
+        <v>12.2656812667847</v>
       </c>
       <c r="H1449" t="n">
         <v>8587638</v>
@@ -42477,7 +42477,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G1452" t="n">
-        <v>12.6898918151855</v>
+        <v>12.6898927688599</v>
       </c>
       <c r="H1452" t="n">
         <v>16190125</v>
@@ -42506,7 +42506,7 @@
         <v>16.8099994659424</v>
       </c>
       <c r="G1453" t="n">
-        <v>12.2525615692139</v>
+        <v>12.2525596618652</v>
       </c>
       <c r="H1453" t="n">
         <v>84696171</v>
@@ -42564,7 +42564,7 @@
         <v>16.0319995880127</v>
       </c>
       <c r="G1455" t="n">
-        <v>11.6854877471924</v>
+        <v>11.6854887008667</v>
       </c>
       <c r="H1455" t="n">
         <v>15507556</v>
@@ -42680,7 +42680,7 @@
         <v>16.9360008239746</v>
       </c>
       <c r="G1459" t="n">
-        <v>12.3444013595581</v>
+        <v>12.3444004058838</v>
       </c>
       <c r="H1459" t="n">
         <v>9992278</v>
@@ -42854,7 +42854,7 @@
         <v>16.5559997558594</v>
       </c>
       <c r="G1465" t="n">
-        <v>12.0674247741699</v>
+        <v>12.0674238204956</v>
       </c>
       <c r="H1465" t="n">
         <v>9711759</v>
@@ -42883,7 +42883,7 @@
         <v>15.9659996032715</v>
       </c>
       <c r="G1466" t="n">
-        <v>11.6373815536499</v>
+        <v>11.6373825073242</v>
       </c>
       <c r="H1466" t="n">
         <v>17829450</v>
@@ -42912,7 +42912,7 @@
         <v>16.57200050354</v>
       </c>
       <c r="G1467" t="n">
-        <v>12.0790863037109</v>
+        <v>12.0790872573853</v>
       </c>
       <c r="H1467" t="n">
         <v>12451563</v>
@@ -43057,7 +43057,7 @@
         <v>17.0279998779297</v>
       </c>
       <c r="G1472" t="n">
-        <v>12.4114580154419</v>
+        <v>12.4114589691162</v>
       </c>
       <c r="H1472" t="n">
         <v>8292382</v>
@@ -43115,7 +43115,7 @@
         <v>16.8920001983643</v>
       </c>
       <c r="G1474" t="n">
-        <v>12.3123292922974</v>
+        <v>12.3123302459717</v>
       </c>
       <c r="H1474" t="n">
         <v>7551088</v>
@@ -43173,7 +43173,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1476" t="n">
-        <v>12.2598505020142</v>
+        <v>12.2598485946655</v>
       </c>
       <c r="H1476" t="n">
         <v>9565114</v>
@@ -43231,7 +43231,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1478" t="n">
-        <v>12.281717300415</v>
+        <v>12.2817163467407</v>
       </c>
       <c r="H1478" t="n">
         <v>7749950</v>
@@ -43347,7 +43347,7 @@
         <v>17.2859992980957</v>
       </c>
       <c r="G1482" t="n">
-        <v>12.5995101928711</v>
+        <v>12.5995111465454</v>
       </c>
       <c r="H1482" t="n">
         <v>14954555</v>
@@ -43550,7 +43550,7 @@
         <v>17.5359992980957</v>
       </c>
       <c r="G1489" t="n">
-        <v>12.7817325592041</v>
+        <v>12.7817316055298</v>
       </c>
       <c r="H1489" t="n">
         <v>8625008</v>
@@ -43579,7 +43579,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1490" t="n">
-        <v>12.7117605209351</v>
+        <v>12.7117595672607</v>
       </c>
       <c r="H1490" t="n">
         <v>10009713</v>
@@ -43666,7 +43666,7 @@
         <v>17.8759994506836</v>
       </c>
       <c r="G1493" t="n">
-        <v>13.0295534133911</v>
+        <v>13.0295524597168</v>
       </c>
       <c r="H1493" t="n">
         <v>9648515</v>
@@ -43753,7 +43753,7 @@
         <v>17.9559993743896</v>
       </c>
       <c r="G1496" t="n">
-        <v>13.0878648757935</v>
+        <v>13.0878639221191</v>
       </c>
       <c r="H1496" t="n">
         <v>8661810</v>
@@ -43840,7 +43840,7 @@
         <v>17.4580001831055</v>
       </c>
       <c r="G1499" t="n">
-        <v>12.7248802185059</v>
+        <v>12.7248792648315</v>
       </c>
       <c r="H1499" t="n">
         <v>8060360</v>
@@ -43927,7 +43927,7 @@
         <v>16.7080001831055</v>
       </c>
       <c r="G1502" t="n">
-        <v>12.1782159805298</v>
+        <v>12.1782150268555</v>
       </c>
       <c r="H1502" t="n">
         <v>8940028</v>
@@ -43956,7 +43956,7 @@
         <v>15.5659999847412</v>
       </c>
       <c r="G1503" t="n">
-        <v>11.3458271026611</v>
+        <v>11.3458280563354</v>
       </c>
       <c r="H1503" t="n">
         <v>20502015</v>
@@ -43985,7 +43985,7 @@
         <v>15.5679998397827</v>
       </c>
       <c r="G1504" t="n">
-        <v>11.3472862243652</v>
+        <v>11.3472852706909</v>
       </c>
       <c r="H1504" t="n">
         <v>15205979</v>
@@ -44072,7 +44072,7 @@
         <v>15.9280004501343</v>
       </c>
       <c r="G1507" t="n">
-        <v>11.6096849441528</v>
+        <v>11.6096858978271</v>
       </c>
       <c r="H1507" t="n">
         <v>12111703</v>
@@ -44101,7 +44101,7 @@
         <v>15.7440004348755</v>
       </c>
       <c r="G1508" t="n">
-        <v>11.4755697250366</v>
+        <v>11.4755706787109</v>
       </c>
       <c r="H1508" t="n">
         <v>11094009</v>
@@ -44159,7 +44159,7 @@
         <v>16.8719997406006</v>
       </c>
       <c r="G1510" t="n">
-        <v>12.2977514266968</v>
+        <v>12.2977523803711</v>
       </c>
       <c r="H1510" t="n">
         <v>15259763</v>
@@ -44217,7 +44217,7 @@
         <v>16.4479999542236</v>
       </c>
       <c r="G1512" t="n">
-        <v>11.9887046813965</v>
+        <v>11.9887037277222</v>
       </c>
       <c r="H1512" t="n">
         <v>8517545</v>
@@ -44246,7 +44246,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G1513" t="n">
-        <v>12.0193185806274</v>
+        <v>12.0193176269531</v>
       </c>
       <c r="H1513" t="n">
         <v>9130267</v>
@@ -44304,7 +44304,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G1515" t="n">
-        <v>11.8589639663696</v>
+        <v>11.8589630126953</v>
       </c>
       <c r="H1515" t="n">
         <v>7599785</v>
@@ -44420,7 +44420,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1519" t="n">
-        <v>11.5309638977051</v>
+        <v>11.5309648513794</v>
       </c>
       <c r="H1519" t="n">
         <v>12556793</v>
@@ -44478,7 +44478,7 @@
         <v>16.4519996643066</v>
       </c>
       <c r="G1521" t="n">
-        <v>11.9916210174561</v>
+        <v>11.9916200637817</v>
       </c>
       <c r="H1521" t="n">
         <v>6756495</v>
@@ -44594,7 +44594,7 @@
         <v>16.7019996643066</v>
       </c>
       <c r="G1525" t="n">
-        <v>12.1738405227661</v>
+        <v>12.1738414764404</v>
       </c>
       <c r="H1525" t="n">
         <v>4705186</v>
@@ -44652,7 +44652,7 @@
         <v>17.3279991149902</v>
       </c>
       <c r="G1527" t="n">
-        <v>12.6301231384277</v>
+        <v>12.6301240921021</v>
       </c>
       <c r="H1527" t="n">
         <v>13228121</v>
@@ -44826,7 +44826,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1533" t="n">
-        <v>13.1490907669067</v>
+        <v>13.1490898132324</v>
       </c>
       <c r="H1533" t="n">
         <v>6293653</v>
@@ -44913,7 +44913,7 @@
         <v>18.9740009307861</v>
       </c>
       <c r="G1536" t="n">
-        <v>13.829870223999</v>
+        <v>13.8298692703247</v>
       </c>
       <c r="H1536" t="n">
         <v>12639580</v>
@@ -44942,7 +44942,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1537" t="n">
-        <v>13.9508638381958</v>
+        <v>13.9508647918701</v>
       </c>
       <c r="H1537" t="n">
         <v>8814355</v>
@@ -45000,7 +45000,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G1539" t="n">
-        <v>13.84153175354</v>
+        <v>13.8415307998657</v>
       </c>
       <c r="H1539" t="n">
         <v>11809912</v>
@@ -45029,7 +45029,7 @@
         <v>18.7940006256104</v>
       </c>
       <c r="G1540" t="n">
-        <v>13.6986703872681</v>
+        <v>13.6986694335938</v>
       </c>
       <c r="H1540" t="n">
         <v>18772137</v>
@@ -45116,7 +45116,7 @@
         <v>16.6019992828369</v>
       </c>
       <c r="G1543" t="n">
-        <v>12.1009531021118</v>
+        <v>12.1009521484375</v>
       </c>
       <c r="H1543" t="n">
         <v>18049061</v>
@@ -45145,7 +45145,7 @@
         <v>17.4039993286133</v>
       </c>
       <c r="G1544" t="n">
-        <v>12.6855182647705</v>
+        <v>12.6855192184448</v>
       </c>
       <c r="H1544" t="n">
         <v>20085910</v>
@@ -45232,7 +45232,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G1547" t="n">
-        <v>12.3691825866699</v>
+        <v>12.3691835403442</v>
       </c>
       <c r="H1547" t="n">
         <v>13546323</v>
@@ -45290,7 +45290,7 @@
         <v>17.4759998321533</v>
       </c>
       <c r="G1549" t="n">
-        <v>12.7379989624023</v>
+        <v>12.737998008728</v>
       </c>
       <c r="H1549" t="n">
         <v>11088446</v>
@@ -45319,7 +45319,7 @@
         <v>17.3740005493164</v>
       </c>
       <c r="G1550" t="n">
-        <v>12.6636533737183</v>
+        <v>12.6636524200439</v>
       </c>
       <c r="H1550" t="n">
         <v>11443273</v>
@@ -45348,7 +45348,7 @@
         <v>16.4619998931885</v>
       </c>
       <c r="G1551" t="n">
-        <v>11.9989099502563</v>
+        <v>11.998908996582</v>
       </c>
       <c r="H1551" t="n">
         <v>20977707</v>
@@ -45435,7 +45435,7 @@
         <v>17.1060009002686</v>
       </c>
       <c r="G1554" t="n">
-        <v>12.4683122634888</v>
+        <v>12.4683132171631</v>
       </c>
       <c r="H1554" t="n">
         <v>12414926</v>
@@ -45551,7 +45551,7 @@
         <v>17.011999130249</v>
       </c>
       <c r="G1558" t="n">
-        <v>12.3997945785522</v>
+        <v>12.3997955322266</v>
       </c>
       <c r="H1558" t="n">
         <v>12740314</v>
@@ -45609,7 +45609,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1560" t="n">
-        <v>12.281717300415</v>
+        <v>12.2817163467407</v>
       </c>
       <c r="H1560" t="n">
         <v>10002753</v>
@@ -45725,7 +45725,7 @@
         <v>17.0659999847412</v>
       </c>
       <c r="G1564" t="n">
-        <v>12.4391565322876</v>
+        <v>12.4391555786133</v>
       </c>
       <c r="H1564" t="n">
         <v>25063894</v>
@@ -45754,7 +45754,7 @@
         <v>16.0340003967285</v>
       </c>
       <c r="G1565" t="n">
-        <v>11.6869459152222</v>
+        <v>11.6869468688965</v>
       </c>
       <c r="H1565" t="n">
         <v>27661075</v>
@@ -45783,7 +45783,7 @@
         <v>16.8840007781982</v>
       </c>
       <c r="G1566" t="n">
-        <v>12.3064994812012</v>
+        <v>12.3064985275269</v>
       </c>
       <c r="H1566" t="n">
         <v>19995543</v>
@@ -45841,7 +45841,7 @@
         <v>15.2360000610352</v>
       </c>
       <c r="G1568" t="n">
-        <v>11.1052951812744</v>
+        <v>11.1052961349487</v>
       </c>
       <c r="H1568" t="n">
         <v>23131549</v>
@@ -46044,7 +46044,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G1575" t="n">
-        <v>9.81808471679688</v>
+        <v>9.81808567047119</v>
       </c>
       <c r="H1575" t="n">
         <v>19799814</v>
@@ -46247,7 +46247,7 @@
         <v>14.6079998016357</v>
       </c>
       <c r="G1582" t="n">
-        <v>10.6475553512573</v>
+        <v>10.6475563049316</v>
       </c>
       <c r="H1582" t="n">
         <v>10727585</v>
@@ -46363,7 +46363,7 @@
         <v>14.4340000152588</v>
       </c>
       <c r="G1586" t="n">
-        <v>10.5207300186157</v>
+        <v>10.52073097229</v>
       </c>
       <c r="H1586" t="n">
         <v>8201329</v>
@@ -46392,7 +46392,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1587" t="n">
-        <v>10.5323925018311</v>
+        <v>10.5323915481567</v>
       </c>
       <c r="H1587" t="n">
         <v>11175290</v>
@@ -46566,7 +46566,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G1593" t="n">
-        <v>10.4522151947021</v>
+        <v>10.4522142410278</v>
       </c>
       <c r="H1593" t="n">
         <v>15997790</v>
@@ -46653,7 +46653,7 @@
         <v>13.7659997940063</v>
       </c>
       <c r="G1596" t="n">
-        <v>10.0338354110718</v>
+        <v>10.0338344573975</v>
       </c>
       <c r="H1596" t="n">
         <v>11644663</v>
@@ -46711,7 +46711,7 @@
         <v>13.9060001373291</v>
       </c>
       <c r="G1598" t="n">
-        <v>10.1358795166016</v>
+        <v>10.1358785629272</v>
       </c>
       <c r="H1598" t="n">
         <v>10551107</v>
@@ -46769,7 +46769,7 @@
         <v>14.0740003585815</v>
       </c>
       <c r="G1600" t="n">
-        <v>10.2583322525024</v>
+        <v>10.2583312988281</v>
       </c>
       <c r="H1600" t="n">
         <v>16219191</v>
@@ -46798,7 +46798,7 @@
         <v>13.3479995727539</v>
       </c>
       <c r="G1601" t="n">
-        <v>10.5054616928101</v>
+        <v>10.5054626464844</v>
       </c>
       <c r="H1601" t="n">
         <v>15206061</v>
@@ -46856,7 +46856,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1603" t="n">
-        <v>10.6644449234009</v>
+        <v>10.6644458770752</v>
       </c>
       <c r="H1603" t="n">
         <v>11630517</v>
@@ -46885,7 +46885,7 @@
         <v>13.1120004653931</v>
       </c>
       <c r="G1604" t="n">
-        <v>10.3197212219238</v>
+        <v>10.3197202682495</v>
       </c>
       <c r="H1604" t="n">
         <v>12733816</v>
@@ -47059,7 +47059,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G1610" t="n">
-        <v>9.90888404846191</v>
+        <v>9.9088830947876</v>
       </c>
       <c r="H1610" t="n">
         <v>14107680</v>
@@ -47146,7 +47146,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G1613" t="n">
-        <v>10.0190696716309</v>
+        <v>10.0190687179565</v>
       </c>
       <c r="H1613" t="n">
         <v>19205981</v>
@@ -47291,7 +47291,7 @@
         <v>13.253999710083</v>
       </c>
       <c r="G1618" t="n">
-        <v>10.4314794540405</v>
+        <v>10.4314804077148</v>
       </c>
       <c r="H1618" t="n">
         <v>14249318</v>
@@ -47320,7 +47320,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G1619" t="n">
-        <v>10.8375959396362</v>
+        <v>10.8375949859619</v>
       </c>
       <c r="H1619" t="n">
         <v>15173714</v>
@@ -47523,7 +47523,7 @@
         <v>13.1359996795654</v>
       </c>
       <c r="G1626" t="n">
-        <v>10.3386096954346</v>
+        <v>10.3386087417603</v>
       </c>
       <c r="H1626" t="n">
         <v>16671957</v>
@@ -47552,7 +47552,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G1627" t="n">
-        <v>10.5306482315063</v>
+        <v>10.5306491851807</v>
       </c>
       <c r="H1627" t="n">
         <v>12973796</v>
@@ -47668,7 +47668,7 @@
         <v>13.9340000152588</v>
       </c>
       <c r="G1631" t="n">
-        <v>10.9666700363159</v>
+        <v>10.9666709899902</v>
       </c>
       <c r="H1631" t="n">
         <v>37176304</v>
@@ -48045,7 +48045,7 @@
         <v>12.2360000610352</v>
       </c>
       <c r="G1644" t="n">
-        <v>9.63026905059814</v>
+        <v>9.63027000427246</v>
       </c>
       <c r="H1644" t="n">
         <v>18533131</v>
@@ -48161,7 +48161,7 @@
         <v>12.21399974823</v>
       </c>
       <c r="G1648" t="n">
-        <v>9.61295413970947</v>
+        <v>9.61295509338379</v>
       </c>
       <c r="H1648" t="n">
         <v>10255053</v>
@@ -48190,7 +48190,7 @@
         <v>12.4280004501343</v>
       </c>
       <c r="G1649" t="n">
-        <v>9.78138160705566</v>
+        <v>9.78138256072998</v>
       </c>
       <c r="H1649" t="n">
         <v>12342250</v>
@@ -48248,7 +48248,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1651" t="n">
-        <v>9.86953067779541</v>
+        <v>9.86953163146973</v>
       </c>
       <c r="H1651" t="n">
         <v>7639261</v>
@@ -48335,7 +48335,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1654" t="n">
-        <v>9.22415542602539</v>
+        <v>9.22415447235107</v>
       </c>
       <c r="H1654" t="n">
         <v>10328930</v>
@@ -48654,7 +48654,7 @@
         <v>12.253999710083</v>
       </c>
       <c r="G1665" t="n">
-        <v>9.64443588256836</v>
+        <v>9.64443683624268</v>
       </c>
       <c r="H1665" t="n">
         <v>9922342</v>
@@ -48741,7 +48741,7 @@
         <v>12.5679998397827</v>
       </c>
       <c r="G1668" t="n">
-        <v>9.89156913757324</v>
+        <v>9.89156818389893</v>
       </c>
       <c r="H1668" t="n">
         <v>12481446</v>
@@ -48857,7 +48857,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1672" t="n">
-        <v>10.1764783859253</v>
+        <v>10.176477432251</v>
       </c>
       <c r="H1672" t="n">
         <v>10498094</v>
@@ -48915,7 +48915,7 @@
         <v>13.9219999313354</v>
       </c>
       <c r="G1674" t="n">
-        <v>10.9572248458862</v>
+        <v>10.9572257995605</v>
       </c>
       <c r="H1674" t="n">
         <v>13107465</v>
@@ -49118,7 +49118,7 @@
         <v>14.4060001373291</v>
       </c>
       <c r="G1681" t="n">
-        <v>11.33815574646</v>
+        <v>11.3381547927856</v>
       </c>
       <c r="H1681" t="n">
         <v>11966080</v>
@@ -49263,7 +49263,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1686" t="n">
-        <v>11.5223236083984</v>
+        <v>11.5223245620728</v>
       </c>
       <c r="H1686" t="n">
         <v>10556642</v>
@@ -49321,7 +49321,7 @@
         <v>14.4440002441406</v>
       </c>
       <c r="G1688" t="n">
-        <v>11.3680629730225</v>
+        <v>11.3680639266968</v>
       </c>
       <c r="H1688" t="n">
         <v>10311180</v>
@@ -49350,7 +49350,7 @@
         <v>13.8520002365112</v>
       </c>
       <c r="G1689" t="n">
-        <v>10.9021339416504</v>
+        <v>10.9021329879761</v>
       </c>
       <c r="H1689" t="n">
         <v>11980241</v>
@@ -49379,7 +49379,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1690" t="n">
-        <v>11.0500974655151</v>
+        <v>11.0500965118408</v>
       </c>
       <c r="H1690" t="n">
         <v>12286103</v>
@@ -49640,7 +49640,7 @@
         <v>12.8280000686646</v>
       </c>
       <c r="G1699" t="n">
-        <v>10.0961999893188</v>
+        <v>10.0961990356445</v>
       </c>
       <c r="H1699" t="n">
         <v>15987748</v>
@@ -49727,7 +49727,7 @@
         <v>13.1280002593994</v>
       </c>
       <c r="G1702" t="n">
-        <v>10.3323135375977</v>
+        <v>10.3323125839233</v>
       </c>
       <c r="H1702" t="n">
         <v>12143622</v>
@@ -49785,7 +49785,7 @@
         <v>13.7379999160767</v>
       </c>
       <c r="G1704" t="n">
-        <v>10.8124094009399</v>
+        <v>10.8124103546143</v>
       </c>
       <c r="H1704" t="n">
         <v>11457955</v>
@@ -50104,7 +50104,7 @@
         <v>12.8339996337891</v>
       </c>
       <c r="G1715" t="n">
-        <v>10.1009225845337</v>
+        <v>10.1009216308594</v>
       </c>
       <c r="H1715" t="n">
         <v>10252304</v>
@@ -50133,7 +50133,7 @@
         <v>12.826000213623</v>
       </c>
       <c r="G1716" t="n">
-        <v>10.0946254730225</v>
+        <v>10.0946264266968</v>
       </c>
       <c r="H1716" t="n">
         <v>11150967</v>
@@ -50162,7 +50162,7 @@
         <v>12.21399974823</v>
       </c>
       <c r="G1717" t="n">
-        <v>9.61295413970947</v>
+        <v>9.61295509338379</v>
       </c>
       <c r="H1717" t="n">
         <v>16977425</v>
@@ -50191,7 +50191,7 @@
         <v>12.2720003128052</v>
       </c>
       <c r="G1718" t="n">
-        <v>9.65860366821289</v>
+        <v>9.65860462188721</v>
       </c>
       <c r="H1718" t="n">
         <v>10169498</v>
@@ -50249,7 +50249,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1720" t="n">
-        <v>10.1764783859253</v>
+        <v>10.176477432251</v>
       </c>
       <c r="H1720" t="n">
         <v>11699644</v>
@@ -50539,7 +50539,7 @@
         <v>13.0220003128052</v>
       </c>
       <c r="G1730" t="n">
-        <v>10.2488870620728</v>
+        <v>10.2488861083984</v>
       </c>
       <c r="H1730" t="n">
         <v>12297217</v>
@@ -50597,7 +50597,7 @@
         <v>13.173999786377</v>
       </c>
       <c r="G1732" t="n">
-        <v>10.3685169219971</v>
+        <v>10.3685178756714</v>
       </c>
       <c r="H1732" t="n">
         <v>9200454</v>
@@ -50713,7 +50713,7 @@
         <v>13.6520004272461</v>
       </c>
       <c r="G1736" t="n">
-        <v>10.7447233200073</v>
+        <v>10.7447242736816</v>
       </c>
       <c r="H1736" t="n">
         <v>7781915</v>
@@ -50858,7 +50858,7 @@
         <v>13.7340002059937</v>
       </c>
       <c r="G1741" t="n">
-        <v>10.8092613220215</v>
+        <v>10.8092622756958</v>
       </c>
       <c r="H1741" t="n">
         <v>15068075</v>
@@ -50887,7 +50887,7 @@
         <v>13.28600025177</v>
       </c>
       <c r="G1742" t="n">
-        <v>10.4566659927368</v>
+        <v>10.4566669464111</v>
       </c>
       <c r="H1742" t="n">
         <v>15660165</v>
@@ -51061,7 +51061,7 @@
         <v>14.2279996871948</v>
       </c>
       <c r="G1748" t="n">
-        <v>11.1980619430542</v>
+        <v>11.1980609893799</v>
       </c>
       <c r="H1748" t="n">
         <v>10016185</v>
@@ -51090,7 +51090,7 @@
         <v>14.4079999923706</v>
       </c>
       <c r="G1749" t="n">
-        <v>11.3397302627563</v>
+        <v>11.339729309082</v>
       </c>
       <c r="H1749" t="n">
         <v>8631613</v>
@@ -51119,7 +51119,7 @@
         <v>14.5159997940063</v>
       </c>
       <c r="G1750" t="n">
-        <v>11.424729347229</v>
+        <v>11.4247303009033</v>
       </c>
       <c r="H1750" t="n">
         <v>8795173</v>
@@ -51148,7 +51148,7 @@
         <v>14.25</v>
       </c>
       <c r="G1751" t="n">
-        <v>11.2153768539429</v>
+        <v>11.2153759002686</v>
       </c>
       <c r="H1751" t="n">
         <v>10218861</v>
@@ -51206,7 +51206,7 @@
         <v>14.4099998474121</v>
       </c>
       <c r="G1753" t="n">
-        <v>11.3413038253784</v>
+        <v>11.3413028717041</v>
       </c>
       <c r="H1753" t="n">
         <v>9935411</v>
@@ -51235,7 +51235,7 @@
         <v>14.5419998168945</v>
       </c>
       <c r="G1754" t="n">
-        <v>11.4451923370361</v>
+        <v>11.4451932907104</v>
       </c>
       <c r="H1754" t="n">
         <v>6841134</v>
@@ -51264,7 +51264,7 @@
         <v>14.6820001602173</v>
       </c>
       <c r="G1755" t="n">
-        <v>11.5553798675537</v>
+        <v>11.5553789138794</v>
       </c>
       <c r="H1755" t="n">
         <v>8719566</v>
@@ -51322,7 +51322,7 @@
         <v>14.6540002822876</v>
       </c>
       <c r="G1757" t="n">
-        <v>11.5333423614502</v>
+        <v>11.5333433151245</v>
       </c>
       <c r="H1757" t="n">
         <v>4996884</v>
@@ -51351,7 +51351,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1758" t="n">
-        <v>11.5301933288574</v>
+        <v>11.5301942825317</v>
       </c>
       <c r="H1758" t="n">
         <v>4629453</v>
@@ -51438,7 +51438,7 @@
         <v>14.8920001983643</v>
       </c>
       <c r="G1761" t="n">
-        <v>11.7206592559814</v>
+        <v>11.7206583023071</v>
       </c>
       <c r="H1761" t="n">
         <v>15723912</v>
@@ -51525,7 +51525,7 @@
         <v>14.6579999923706</v>
       </c>
       <c r="G1764" t="n">
-        <v>11.5364894866943</v>
+        <v>11.5364904403687</v>
       </c>
       <c r="H1764" t="n">
         <v>7750958</v>
@@ -51554,7 +51554,7 @@
         <v>14.4479999542236</v>
       </c>
       <c r="G1765" t="n">
-        <v>11.3712110519409</v>
+        <v>11.3712120056152</v>
       </c>
       <c r="H1765" t="n">
         <v>7935913</v>
@@ -51583,7 +51583,7 @@
         <v>14.4820003509521</v>
       </c>
       <c r="G1766" t="n">
-        <v>11.397970199585</v>
+        <v>11.3979711532593</v>
       </c>
       <c r="H1766" t="n">
         <v>8112637</v>
@@ -51757,7 +51757,7 @@
         <v>13.5539999008179</v>
       </c>
       <c r="G1772" t="n">
-        <v>10.6675930023193</v>
+        <v>10.6675939559937</v>
       </c>
       <c r="H1772" t="n">
         <v>14317406</v>
@@ -51844,7 +51844,7 @@
         <v>13.253999710083</v>
       </c>
       <c r="G1775" t="n">
-        <v>10.4314794540405</v>
+        <v>10.4314804077148</v>
       </c>
       <c r="H1775" t="n">
         <v>8853439</v>
@@ -51989,7 +51989,7 @@
         <v>13.1180000305176</v>
       </c>
       <c r="G1780" t="n">
-        <v>10.3244428634644</v>
+        <v>10.32444190979</v>
       </c>
       <c r="H1780" t="n">
         <v>6572127</v>
@@ -52018,7 +52018,7 @@
         <v>13.3780002593994</v>
       </c>
       <c r="G1781" t="n">
-        <v>10.52907371521</v>
+        <v>10.5290746688843</v>
       </c>
       <c r="H1781" t="n">
         <v>6912019</v>
@@ -52047,7 +52047,7 @@
         <v>13.2639999389648</v>
       </c>
       <c r="G1782" t="n">
-        <v>10.4393510818481</v>
+        <v>10.4393520355225</v>
       </c>
       <c r="H1782" t="n">
         <v>5485642</v>
@@ -52076,7 +52076,7 @@
         <v>13.6479997634888</v>
       </c>
       <c r="G1783" t="n">
-        <v>10.7415752410889</v>
+        <v>10.7415761947632</v>
       </c>
       <c r="H1783" t="n">
         <v>5995743</v>
@@ -52163,7 +52163,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G1786" t="n">
-        <v>11.2862110137939</v>
+        <v>11.2862100601196</v>
       </c>
       <c r="H1786" t="n">
         <v>8703319</v>
@@ -52250,7 +52250,7 @@
         <v>14.6660003662109</v>
       </c>
       <c r="G1789" t="n">
-        <v>11.5427865982056</v>
+        <v>11.5427875518799</v>
       </c>
       <c r="H1789" t="n">
         <v>10380755</v>
@@ -52308,7 +52308,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G1791" t="n">
-        <v>11.6246395111084</v>
+        <v>11.6246404647827</v>
       </c>
       <c r="H1791" t="n">
         <v>12310217</v>
@@ -52366,7 +52366,7 @@
         <v>14.3159999847412</v>
       </c>
       <c r="G1793" t="n">
-        <v>11.2673215866089</v>
+        <v>11.2673206329346</v>
       </c>
       <c r="H1793" t="n">
         <v>7749051</v>
@@ -52482,7 +52482,7 @@
         <v>14.0240001678467</v>
       </c>
       <c r="G1797" t="n">
-        <v>11.0375032424927</v>
+        <v>11.037504196167</v>
       </c>
       <c r="H1797" t="n">
         <v>11167514</v>
@@ -52540,7 +52540,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G1799" t="n">
-        <v>11.0343561172485</v>
+        <v>11.0343570709229</v>
       </c>
       <c r="H1799" t="n">
         <v>7526207</v>
@@ -52656,7 +52656,7 @@
         <v>14.0240001678467</v>
       </c>
       <c r="G1803" t="n">
-        <v>11.0375032424927</v>
+        <v>11.037504196167</v>
       </c>
       <c r="H1803" t="n">
         <v>10925629</v>
@@ -52801,7 +52801,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G1808" t="n">
-        <v>11.8686227798462</v>
+        <v>11.8686218261719</v>
       </c>
       <c r="H1808" t="n">
         <v>9224277</v>
@@ -52975,7 +52975,7 @@
         <v>15.576000213623</v>
       </c>
       <c r="G1814" t="n">
-        <v>12.258996963501</v>
+        <v>12.2589960098267</v>
       </c>
       <c r="H1814" t="n">
         <v>10154145</v>
@@ -53004,7 +53004,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G1815" t="n">
-        <v>12.4903869628906</v>
+        <v>12.4903879165649</v>
       </c>
       <c r="H1815" t="n">
         <v>11385709</v>
@@ -53062,7 +53062,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1817" t="n">
-        <v>12.5533504486084</v>
+        <v>12.5533514022827</v>
       </c>
       <c r="H1817" t="n">
         <v>14123351</v>
@@ -53091,7 +53091,7 @@
         <v>16.1380004882812</v>
       </c>
       <c r="G1818" t="n">
-        <v>12.7013149261475</v>
+        <v>12.7013158798218</v>
       </c>
       <c r="H1818" t="n">
         <v>10697835</v>
@@ -53120,7 +53120,7 @@
         <v>15.8680000305176</v>
       </c>
       <c r="G1819" t="n">
-        <v>12.4888124465942</v>
+        <v>12.4888134002686</v>
       </c>
       <c r="H1819" t="n">
         <v>11435162</v>
@@ -53236,7 +53236,7 @@
         <v>16.6319999694824</v>
       </c>
       <c r="G1823" t="n">
-        <v>13.0901155471802</v>
+        <v>13.0901145935059</v>
       </c>
       <c r="H1823" t="n">
         <v>12036930</v>
@@ -53352,7 +53352,7 @@
         <v>17.6679992675781</v>
       </c>
       <c r="G1827" t="n">
-        <v>13.9054927825928</v>
+        <v>13.9054918289185</v>
       </c>
       <c r="H1827" t="n">
         <v>15723357</v>
@@ -53932,7 +53932,7 @@
         <v>16.7360000610352</v>
       </c>
       <c r="G1847" t="n">
-        <v>13.171968460083</v>
+        <v>13.1719675064087</v>
       </c>
       <c r="H1847" t="n">
         <v>7644233</v>
@@ -54048,7 +54048,7 @@
         <v>16.2479991912842</v>
       </c>
       <c r="G1851" t="n">
-        <v>12.7878904342651</v>
+        <v>12.7878894805908</v>
       </c>
       <c r="H1851" t="n">
         <v>7050270</v>
@@ -54193,7 +54193,7 @@
         <v>16.9780006408691</v>
       </c>
       <c r="G1856" t="n">
-        <v>13.3624324798584</v>
+        <v>13.3624334335327</v>
       </c>
       <c r="H1856" t="n">
         <v>10577376</v>
@@ -54222,7 +54222,7 @@
         <v>17.0319995880127</v>
       </c>
       <c r="G1857" t="n">
-        <v>13.4049320220947</v>
+        <v>13.404932975769</v>
       </c>
       <c r="H1857" t="n">
         <v>8183518</v>
@@ -54251,7 +54251,7 @@
         <v>16.9680004119873</v>
       </c>
       <c r="G1858" t="n">
-        <v>13.3545618057251</v>
+        <v>13.3545627593994</v>
       </c>
       <c r="H1858" t="n">
         <v>9815276</v>
@@ -80183,6 +80183,35 @@
         <v>134472067</v>
       </c>
       <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>4.26700019836426</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>4.09800004959106</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>4.21999979019165</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>4.21999979019165</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>57662689</v>
+      </c>
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>
